--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\화요일\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5FAB6E6-25DD-40A9-AA0D-24AC98CC0BD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE135377-5D38-4168-A6DE-6D9AB54BCC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8985" yWindow="4530" windowWidth="14385" windowHeight="15885" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="월요일" sheetId="2" r:id="rId1"/>
@@ -23,6 +23,9 @@
     <sheet name="2026-07" sheetId="9" r:id="rId8"/>
     <sheet name="기준표" sheetId="10" r:id="rId9"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId10"/>
+  </externalReferences>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,360 +39,774 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="132">
   <si>
     <t>기준일자</t>
   </si>
   <si>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>길드전 랭킹포인트 — 월요일</t>
+  </si>
+  <si>
+    <t>순위</t>
+  </si>
+  <si>
+    <t>플레이어</t>
+  </si>
+  <si>
+    <t>점수</t>
+  </si>
+  <si>
+    <t>단계</t>
+  </si>
+  <si>
+    <t>단계별 인원</t>
+  </si>
+  <si>
+    <t>인원</t>
+  </si>
+  <si>
+    <t>떪은홍시</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>단계</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">Lv100 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>배회하는 좀비</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>단계</t>
+    </r>
+  </si>
+  <si>
+    <t>뮤지컬보러가서노래따라부르는놈</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>단계</t>
+    </r>
+  </si>
+  <si>
+    <t>독여울</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>단계</t>
+    </r>
+  </si>
+  <si>
+    <t>스무디에얼음빼주세요</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>단계</t>
+    </r>
+  </si>
+  <si>
+    <t>독화살</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>단계</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>프리저</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>-</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>단계</t>
+    </r>
+  </si>
+  <si>
+    <t>왜요뭐</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>단계</t>
+    </r>
+  </si>
+  <si>
+    <t>빨강맛</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>단계</t>
+    </r>
+  </si>
+  <si>
+    <t>별빛여신</t>
+  </si>
+  <si>
+    <t>총 인원</t>
+  </si>
+  <si>
+    <t>떠들어봐안들린다</t>
+  </si>
+  <si>
+    <t>총 점수</t>
+  </si>
+  <si>
+    <t>진짜한입만나못믿니</t>
+  </si>
+  <si>
+    <t>독거노인춘삼</t>
+  </si>
+  <si>
+    <t>아크으</t>
+  </si>
+  <si>
+    <t>독건담</t>
+  </si>
+  <si>
+    <t>아사히</t>
+  </si>
+  <si>
+    <t>영화관에서결말스포한냔</t>
+  </si>
+  <si>
+    <t>미녀와야자수</t>
+  </si>
+  <si>
+    <t>독방구핑</t>
+  </si>
+  <si>
+    <t>뉴스나온그사람</t>
+  </si>
+  <si>
+    <t>니면상시베리아</t>
+  </si>
+  <si>
+    <t>모어쩌라고</t>
+  </si>
+  <si>
+    <t>빡센공주</t>
+  </si>
+  <si>
+    <t>할말있는데나중에말해줌</t>
+  </si>
+  <si>
+    <t>명령하디마라</t>
+  </si>
+  <si>
+    <t>독수리골드</t>
+  </si>
+  <si>
+    <t>습격이다개스키야</t>
+  </si>
+  <si>
+    <t>독과점</t>
+  </si>
+  <si>
+    <t>독잉교</t>
+  </si>
+  <si>
+    <t>해녀도앤댈리는뒈</t>
+  </si>
+  <si>
+    <t>훔쳐뿟노</t>
+  </si>
+  <si>
+    <t>쉰데렐라</t>
+  </si>
+  <si>
+    <t>앞니로조사버리는토끼</t>
+  </si>
+  <si>
+    <t>핑도노·훔치고·생각하는·편</t>
+  </si>
+  <si>
+    <t>독철이</t>
+  </si>
+  <si>
+    <t>베놈이마깐데또까</t>
+  </si>
+  <si>
+    <t>독로이지</t>
+  </si>
+  <si>
+    <t>독독쿠롱</t>
+  </si>
+  <si>
+    <t>이런들어떠하리저런들어떠하리</t>
+  </si>
+  <si>
+    <t>숲속모텔</t>
+  </si>
+  <si>
+    <t>현금만받아</t>
+  </si>
+  <si>
+    <t>독후감상문</t>
+  </si>
+  <si>
+    <t>괴도하미</t>
+  </si>
+  <si>
+    <t>독한다람쥐</t>
+  </si>
+  <si>
+    <t>여썰고</t>
+  </si>
+  <si>
+    <t>라면주면갈께</t>
+  </si>
+  <si>
+    <t>단추가게</t>
+  </si>
+  <si>
+    <t>독골골</t>
+  </si>
+  <si>
+    <t>독눈누눈누</t>
+  </si>
+  <si>
+    <t>엘베닫힘연타범</t>
+  </si>
+  <si>
+    <t>티거Ya드랍더튀어</t>
+  </si>
+  <si>
+    <t>독그릭</t>
+  </si>
+  <si>
+    <t>독한월요일병</t>
+  </si>
+  <si>
+    <t>눈밑에점찍고돌아온아내</t>
+  </si>
+  <si>
+    <t>안톤 쉬거</t>
+  </si>
+  <si>
+    <t>자르반84세</t>
+  </si>
+  <si>
+    <t>독고독</t>
+  </si>
+  <si>
+    <t>주니쯤</t>
+  </si>
+  <si>
+    <t>독팡팡</t>
+  </si>
+  <si>
+    <t>1090</t>
+  </si>
+  <si>
+    <t>독아윤</t>
+  </si>
+  <si>
+    <t>독삼미</t>
+  </si>
+  <si>
+    <t>독터키캔씨Turkey1881</t>
+  </si>
+  <si>
+    <t>독이즈</t>
+  </si>
+  <si>
+    <t>독주</t>
+  </si>
+  <si>
+    <t>린이</t>
+  </si>
+  <si>
+    <t>수색맨</t>
+  </si>
+  <si>
     <t>2026-06-16</t>
   </si>
   <si>
     <t>길드전 랭킹포인트 — 화요일</t>
   </si>
   <si>
-    <t>순위</t>
-  </si>
-  <si>
-    <t>플레이어</t>
-  </si>
-  <si>
-    <t>점수</t>
-  </si>
-  <si>
-    <t>단계</t>
-  </si>
-  <si>
-    <t>단계별 인원</t>
-  </si>
-  <si>
-    <t>인원</t>
-  </si>
-  <si>
-    <t>독화살</t>
-  </si>
-  <si>
-    <t>9단계</t>
-  </si>
-  <si>
-    <t>떪은홍시</t>
-  </si>
-  <si>
-    <t>8단계</t>
-  </si>
-  <si>
-    <t>명령하디마라</t>
-  </si>
-  <si>
-    <t>7단계</t>
-  </si>
-  <si>
-    <t>독한다람쥐</t>
-  </si>
-  <si>
-    <t>6단계</t>
-  </si>
-  <si>
-    <t>습격이다개스키야</t>
-  </si>
-  <si>
-    <t>5단계</t>
-  </si>
-  <si>
-    <t>뮤지컬보러가서노래따라부르는놈</t>
-  </si>
-  <si>
-    <t>4단계</t>
+    <t>Lv100 배회하는 좀비</t>
+  </si>
+  <si>
+    <t>악마인데순둥소예</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>길드전 랭킹포인트 — 수요일</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>길드전 랭킹포인트 — 목요일</t>
+  </si>
+  <si>
+    <t>2026-06-19</t>
+  </si>
+  <si>
+    <t>길드전 랭킹포인트 — 금요일</t>
+  </si>
+  <si>
+    <t>길드전 랭킹포인트 — 토요일</t>
+  </si>
+  <si>
+    <t>독홍시</t>
+  </si>
+  <si>
+    <t>독한련</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>핑도노</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>훔치고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>생각하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>편</t>
+    </r>
+  </si>
+  <si>
+    <t>명령라하지마라</t>
+  </si>
+  <si>
+    <t>독파민</t>
+  </si>
+  <si>
+    <t>독그레핀</t>
+  </si>
+  <si>
+    <t>독아사</t>
+  </si>
+  <si>
+    <t>독살교육</t>
+  </si>
+  <si>
+    <t>독약원샷</t>
+  </si>
+  <si>
+    <t>독계탕</t>
+  </si>
+  <si>
+    <t>독아크</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>티거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>Ya</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>드랍더튀어</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>독터키캔씨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>Turkey1881</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>자르반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>84</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>세</t>
+    </r>
+  </si>
+  <si>
+    <t>독초치이입</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>독레인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>-InfernoRain</t>
+    </r>
+  </si>
+  <si>
+    <t>📦 월별 보관 — 2026-06  (날짜별 길드전 랭킹 누적)</t>
+  </si>
+  <si>
+    <t>날짜</t>
+  </si>
+  <si>
+    <t>📦 월별 보관 — 2026-07  (날짜별 길드전 랭킹 누적)</t>
+  </si>
+  <si>
+    <t>단계 기준표  (점수 → 단계 자동분류 기준)</t>
+  </si>
+  <si>
+    <t>하한점수</t>
+  </si>
+  <si>
+    <t>점수 범위</t>
+  </si>
+  <si>
+    <t>0 ~ 38,000</t>
+  </si>
+  <si>
+    <t>38,001 ~ 145,000</t>
+  </si>
+  <si>
+    <t>145,001 ~ 550,000</t>
+  </si>
+  <si>
+    <t>550,001 ~ 650,000</t>
+  </si>
+  <si>
+    <t>650,001 ~ 1,020,000</t>
+  </si>
+  <si>
+    <t>1,020,001 ~ 2,280,000</t>
+  </si>
+  <si>
+    <t>2,280,001 ~ 2,630,000</t>
+  </si>
+  <si>
+    <t>2,630,001 ~ 7,189,999</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">7,190,000 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>이상</t>
+    </r>
+  </si>
+  <si>
+    <t>※ 단계 셀은 VLOOKUP 근사일치로 자동 계산됩니다. 기준을 바꾸려면 위 '하한점수' 값만 수정하세요.</t>
   </si>
   <si>
     <t>-프리저-</t>
   </si>
   <si>
-    <t>3단계</t>
-  </si>
-  <si>
-    <t>독거노인춘삼</t>
-  </si>
-  <si>
-    <t>2단계</t>
-  </si>
-  <si>
-    <t>독수리골드</t>
-  </si>
-  <si>
-    <t>1단계</t>
-  </si>
-  <si>
-    <t>떠들어봐안들린다</t>
-  </si>
-  <si>
-    <t>총 인원</t>
-  </si>
-  <si>
-    <t>독방구핑</t>
-  </si>
-  <si>
-    <t>총 점수</t>
-  </si>
-  <si>
-    <t>뉴스나온그사람</t>
-  </si>
-  <si>
-    <t>쉰데렐라</t>
-  </si>
-  <si>
-    <t>독로이지</t>
-  </si>
-  <si>
-    <t>Lv100 배회하는 좀비</t>
-  </si>
-  <si>
-    <t>모어쩌라고</t>
-  </si>
-  <si>
-    <t>니면상시베리아</t>
-  </si>
-  <si>
-    <t>진짜한입만나못믿니</t>
-  </si>
-  <si>
-    <t>여썰고</t>
-  </si>
-  <si>
-    <t>아크으</t>
-  </si>
-  <si>
-    <t>핑도노·훔치고·생각하는·편</t>
-  </si>
-  <si>
-    <t>미녀와야자수</t>
-  </si>
-  <si>
-    <t>별빛여신</t>
-  </si>
-  <si>
-    <t>왜요뭐</t>
-  </si>
-  <si>
-    <t>이런들어떠하리저런들어떠하리</t>
-  </si>
-  <si>
-    <t>할말있는데나중에말해줌</t>
-  </si>
-  <si>
-    <t>독건담</t>
-  </si>
-  <si>
-    <t>아사히</t>
-  </si>
-  <si>
-    <t>해녀도앤댈리는뒈</t>
-  </si>
-  <si>
-    <t>빡센공주</t>
-  </si>
-  <si>
-    <t>앞니로조사버리는토끼</t>
-  </si>
-  <si>
-    <t>라면주면갈께</t>
-  </si>
-  <si>
-    <t>훔쳐뿟노</t>
-  </si>
-  <si>
-    <t>숲속모텔</t>
-  </si>
-  <si>
-    <t>독여울</t>
-  </si>
-  <si>
-    <t>베놈이마깐데또까</t>
-  </si>
-  <si>
-    <t>현금만받아</t>
-  </si>
-  <si>
-    <t>독과점</t>
-  </si>
-  <si>
-    <t>독철이</t>
-  </si>
-  <si>
-    <t>스무디에얼음빼주세요</t>
-  </si>
-  <si>
-    <t>독잉교</t>
-  </si>
-  <si>
-    <t>빨강맛</t>
-  </si>
-  <si>
-    <t>영화관에서결말스포한냔</t>
-  </si>
-  <si>
-    <t>독눈누눈누</t>
-  </si>
-  <si>
-    <t>티거Ya드랍더튀어</t>
-  </si>
-  <si>
-    <t>독독쿠롱</t>
-  </si>
-  <si>
-    <t>눈밑에점찍고돌아온아내</t>
-  </si>
-  <si>
-    <t>단추가게</t>
-  </si>
-  <si>
-    <t>괴도하미</t>
-  </si>
-  <si>
-    <t>독골골</t>
-  </si>
-  <si>
-    <t>독그릭</t>
-  </si>
-  <si>
-    <t>독아윤</t>
-  </si>
-  <si>
-    <t>안톤 쉬거</t>
-  </si>
-  <si>
-    <t>독팡팡</t>
-  </si>
-  <si>
-    <t>엘베닫힘연타범</t>
-  </si>
-  <si>
-    <t>독후감상문</t>
-  </si>
-  <si>
-    <t>독한월요일병</t>
-  </si>
-  <si>
-    <t>독고독</t>
-  </si>
-  <si>
-    <t>독터키캔씨Turkey1881</t>
-  </si>
-  <si>
-    <t>독이즈</t>
-  </si>
-  <si>
-    <t>자르반84세</t>
-  </si>
-  <si>
-    <t>악마인데순둥소예</t>
-  </si>
-  <si>
-    <t>독삼미</t>
-  </si>
-  <si>
-    <t>주니쯤</t>
-  </si>
-  <si>
-    <t>1090</t>
-  </si>
-  <si>
-    <t>독주</t>
-  </si>
-  <si>
-    <t>린이</t>
-  </si>
-  <si>
-    <t>수색맨</t>
-  </si>
-  <si>
-    <t>2026-06-15</t>
-  </si>
-  <si>
-    <t>길드전 랭킹포인트 — 월요일</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>길드전 랭킹포인트 — 수요일</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>길드전 랭킹포인트 — 목요일</t>
-  </si>
-  <si>
-    <t>2026-06-19</t>
-  </si>
-  <si>
-    <t>길드전 랭킹포인트 — 금요일</t>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>길드전 랭킹포인트 — 토요일</t>
-  </si>
-  <si>
-    <t>📦 월별 보관 — 2026-06  (날짜별 길드전 랭킹 누적)</t>
-  </si>
-  <si>
-    <t>날짜</t>
-  </si>
-  <si>
-    <t>📦 월별 보관 — 2026-07  (날짜별 길드전 랭킹 누적)</t>
-  </si>
-  <si>
-    <t>단계 기준표  (점수 → 단계 자동분류 기준)</t>
-  </si>
-  <si>
-    <t>하한점수</t>
-  </si>
-  <si>
-    <t>점수 범위</t>
-  </si>
-  <si>
-    <t>0 ~ 38,000</t>
-  </si>
-  <si>
-    <t>38,001 ~ 145,000</t>
-  </si>
-  <si>
-    <t>145,001 ~ 550,000</t>
-  </si>
-  <si>
-    <t>550,001 ~ 650,000</t>
-  </si>
-  <si>
-    <t>650,001 ~ 1,020,000</t>
-  </si>
-  <si>
-    <t>1,020,001 ~ 2,280,000</t>
-  </si>
-  <si>
-    <t>2,280,001 ~ 2,630,000</t>
-  </si>
-  <si>
-    <t>2,630,001 ~ 7,189,999</t>
-  </si>
-  <si>
-    <t>7,190,000 이상</t>
-  </si>
-  <si>
-    <t>※ 단계 셀은 VLOOKUP 근사일치로 자동 계산됩니다. 기준을 바꾸려면 위 '하한점수' 값만 수정하세요.</t>
+    <t>시바스리갈</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -402,6 +819,7 @@
       <sz val="11"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -414,38 +832,6 @@
     <font>
       <b/>
       <sz val="14"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color rgb="FFFFFFFF"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
@@ -466,11 +852,36 @@
       <charset val="129"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <i/>
@@ -567,7 +978,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -618,22 +1029,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -665,54 +1065,61 @@
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -796,6 +1203,114 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="사용안내"/>
+      <sheetName val="월요일"/>
+      <sheetName val="화요일"/>
+      <sheetName val="수요일"/>
+      <sheetName val="목요일"/>
+      <sheetName val="금요일"/>
+      <sheetName val="토요일"/>
+      <sheetName val="2026-06"/>
+      <sheetName val="2026-07"/>
+      <sheetName val="기준표"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9">
+        <row r="4">
+          <cell r="B4">
+            <v>0</v>
+          </cell>
+          <cell r="C4" t="str">
+            <v>1단계</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="B5">
+            <v>38001</v>
+          </cell>
+          <cell r="C5" t="str">
+            <v>2단계</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="B6">
+            <v>145001</v>
+          </cell>
+          <cell r="C6" t="str">
+            <v>3단계</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7">
+            <v>550001</v>
+          </cell>
+          <cell r="C7" t="str">
+            <v>4단계</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8">
+            <v>650001</v>
+          </cell>
+          <cell r="C8" t="str">
+            <v>5단계</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="B9">
+            <v>1020001</v>
+          </cell>
+          <cell r="C9" t="str">
+            <v>6단계</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10">
+            <v>2280001</v>
+          </cell>
+          <cell r="C10" t="str">
+            <v>7단계</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11">
+            <v>2630001</v>
+          </cell>
+          <cell r="C11" t="str">
+            <v>8단계</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="B12">
+            <v>7190000</v>
+          </cell>
+          <cell r="C12" t="str">
+            <v>9단계</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -993,19 +1508,19 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
+      <c r="C1" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
     </row>
     <row r="2" spans="2:8" ht="18" customHeight="1">
       <c r="B2" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
+        <v>2</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
@@ -1032,7 +1547,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" s="5">
         <v>76513151</v>
@@ -1054,7 +1569,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D5" s="5">
         <v>62254586</v>
@@ -1076,7 +1591,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D6" s="5">
         <v>36598969</v>
@@ -1098,7 +1613,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="D7" s="5">
         <v>26859795</v>
@@ -1120,7 +1635,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="D8" s="5">
         <v>22027625</v>
@@ -1142,7 +1657,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D9" s="5">
         <v>19336746</v>
@@ -1186,7 +1701,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D11" s="5">
         <v>16620269</v>
@@ -1208,7 +1723,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="D12" s="5">
         <v>15971399</v>
@@ -1230,7 +1745,7 @@
         <v>10</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D13" s="5">
         <v>15579579</v>
@@ -1252,7 +1767,7 @@
         <v>11</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D14" s="5">
         <v>15166835</v>
@@ -1274,7 +1789,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D15" s="5">
         <v>15136017</v>
@@ -1289,7 +1804,7 @@
         <v>13</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D16" s="5">
         <v>15045625</v>
@@ -1304,7 +1819,7 @@
         <v>14</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D17" s="5">
         <v>11929975</v>
@@ -1319,7 +1834,7 @@
         <v>15</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D18" s="5">
         <v>11703867</v>
@@ -1334,7 +1849,7 @@
         <v>16</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D19" s="5">
         <v>11641804</v>
@@ -1349,7 +1864,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="D20" s="5">
         <v>11224132</v>
@@ -1364,7 +1879,7 @@
         <v>18</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D21" s="5">
         <v>11128193</v>
@@ -1379,7 +1894,7 @@
         <v>19</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D22" s="5">
         <v>10907771</v>
@@ -1394,7 +1909,7 @@
         <v>20</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D23" s="5">
         <v>10606882</v>
@@ -1409,7 +1924,7 @@
         <v>21</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D24" s="5">
         <v>10422796</v>
@@ -1424,7 +1939,7 @@
         <v>22</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D25" s="5">
         <v>10412768</v>
@@ -1439,7 +1954,7 @@
         <v>23</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D26" s="5">
         <v>10128124</v>
@@ -1454,7 +1969,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D27" s="5">
         <v>9706739</v>
@@ -1469,7 +1984,7 @@
         <v>25</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="D28" s="5">
         <v>9164119</v>
@@ -1484,7 +1999,7 @@
         <v>26</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D29" s="5">
         <v>8999382</v>
@@ -1499,7 +2014,7 @@
         <v>27</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D30" s="5">
         <v>8596217</v>
@@ -1514,7 +2029,7 @@
         <v>28</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D31" s="5">
         <v>8456726</v>
@@ -1529,7 +2044,7 @@
         <v>29</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D32" s="5">
         <v>8220352</v>
@@ -1544,7 +2059,7 @@
         <v>30</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D33" s="5">
         <v>8154156</v>
@@ -1559,7 +2074,7 @@
         <v>31</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D34" s="5">
         <v>8127020</v>
@@ -1574,7 +2089,7 @@
         <v>32</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="D35" s="5">
         <v>7952273</v>
@@ -1589,7 +2104,7 @@
         <v>33</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D36" s="5">
         <v>7918857</v>
@@ -1604,7 +2119,7 @@
         <v>34</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="D37" s="5">
         <v>7909501</v>
@@ -1619,7 +2134,7 @@
         <v>35</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D38" s="5">
         <v>7876636</v>
@@ -1649,7 +2164,7 @@
         <v>37</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="D40" s="5">
         <v>7823884</v>
@@ -1664,7 +2179,7 @@
         <v>38</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D41" s="5">
         <v>7679597</v>
@@ -1679,7 +2194,7 @@
         <v>39</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D42" s="5">
         <v>7635056</v>
@@ -1694,7 +2209,7 @@
         <v>40</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D43" s="5">
         <v>7579677</v>
@@ -1709,7 +2224,7 @@
         <v>41</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D44" s="5">
         <v>7552044</v>
@@ -1724,7 +2239,7 @@
         <v>42</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="D45" s="5">
         <v>7462230</v>
@@ -1739,7 +2254,7 @@
         <v>43</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D46" s="5">
         <v>7423633</v>
@@ -1754,7 +2269,7 @@
         <v>44</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="D47" s="5">
         <v>7327050</v>
@@ -1769,7 +2284,7 @@
         <v>45</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="D48" s="5">
         <v>6678842</v>
@@ -1784,7 +2299,7 @@
         <v>46</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D49" s="5">
         <v>6177989</v>
@@ -1799,7 +2314,7 @@
         <v>47</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D50" s="5">
         <v>5901298</v>
@@ -1814,7 +2329,7 @@
         <v>48</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D51" s="5">
         <v>5097585</v>
@@ -1829,7 +2344,7 @@
         <v>49</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D52" s="5">
         <v>5036088</v>
@@ -1844,7 +2359,7 @@
         <v>50</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D53" s="5">
         <v>4821347</v>
@@ -1859,7 +2374,7 @@
         <v>51</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D54" s="5">
         <v>4599953</v>
@@ -1874,7 +2389,7 @@
         <v>52</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D55" s="5">
         <v>4332112</v>
@@ -1889,7 +2404,7 @@
         <v>53</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D56" s="5">
         <v>4235009</v>
@@ -1904,7 +2419,7 @@
         <v>54</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D57" s="5">
         <v>4226803</v>
@@ -1919,7 +2434,7 @@
         <v>55</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D58" s="5">
         <v>3992666</v>
@@ -1934,7 +2449,7 @@
         <v>56</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D59" s="5">
         <v>3935236</v>
@@ -1949,7 +2464,7 @@
         <v>57</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D60" s="5">
         <v>3819189</v>
@@ -1964,7 +2479,7 @@
         <v>58</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D61" s="5">
         <v>2896389</v>
@@ -1979,7 +2494,7 @@
         <v>59</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D62" s="5">
         <v>2645896</v>
@@ -1994,7 +2509,7 @@
         <v>60</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D63" s="5">
         <v>2195612</v>
@@ -2009,7 +2524,7 @@
         <v>61</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D64" s="5">
         <v>1908787</v>
@@ -2024,7 +2539,7 @@
         <v>62</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D65" s="5">
         <v>1890847</v>
@@ -2039,7 +2554,7 @@
         <v>63</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D66" s="5">
         <v>1772463</v>
@@ -2054,7 +2569,7 @@
         <v>64</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D67" s="5">
         <v>1472500</v>
@@ -2069,7 +2584,7 @@
         <v>65</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D68" s="5">
         <v>1425274</v>
@@ -2084,7 +2599,7 @@
         <v>66</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D69" s="5">
         <v>1226829</v>
@@ -2099,7 +2614,7 @@
         <v>67</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D70" s="5">
         <v>460000</v>
@@ -2147,7 +2662,7 @@
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="B2:E2"/>
   </mergeCells>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -2171,19 +2686,19 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
+      <c r="C1" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
     </row>
     <row r="2" spans="2:8" ht="18" customHeight="1">
       <c r="B2" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
+        <v>88</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
@@ -2210,13 +2725,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D4" s="5">
         <v>15915600</v>
       </c>
       <c r="E4" s="6" t="str">
-        <f>IF($D4="","",VLOOKUP($D4,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D4="","",VLOOKUP($D4,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
       <c r="G4" s="7" t="s">
@@ -2224,21 +2739,21 @@
       </c>
       <c r="H4" s="3">
         <f t="shared" ref="H4:H12" si="0">COUNTIF($E$4:$E$73,G4)</f>
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="16.5" customHeight="1">
       <c r="B5" s="3">
         <v>2</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>11</v>
+      <c r="C5" s="11" t="s">
+        <v>9</v>
       </c>
       <c r="D5" s="5">
         <v>12925350</v>
       </c>
       <c r="E5" s="6" t="str">
-        <f>IF($D5="","",VLOOKUP($D5,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D5="","",VLOOKUP($D5,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
       <c r="G5" s="7" t="s">
@@ -2246,7 +2761,7 @@
       </c>
       <c r="H5" s="3">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="16.5" customHeight="1">
@@ -2254,13 +2769,13 @@
         <v>3</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="D6" s="5">
         <v>12016650</v>
       </c>
       <c r="E6" s="6" t="str">
-        <f>IF($D6="","",VLOOKUP($D6,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D6="","",VLOOKUP($D6,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
       <c r="G6" s="7" t="s">
@@ -2268,7 +2783,7 @@
       </c>
       <c r="H6" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="16.5" customHeight="1">
@@ -2276,13 +2791,13 @@
         <v>4</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="D7" s="5">
-        <v>9907350</v>
+        <v>10155600</v>
       </c>
       <c r="E7" s="6" t="str">
-        <f>IF($D7="","",VLOOKUP($D7,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D7="","",VLOOKUP($D7,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
       <c r="G7" s="7" t="s">
@@ -2290,7 +2805,7 @@
       </c>
       <c r="H7" s="3">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="16.5" customHeight="1">
@@ -2298,13 +2813,13 @@
         <v>5</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D8" s="5">
         <v>9868650</v>
       </c>
       <c r="E8" s="6" t="str">
-        <f>IF($D8="","",VLOOKUP($D8,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D8="","",VLOOKUP($D8,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
       <c r="G8" s="7" t="s">
@@ -2320,13 +2835,13 @@
         <v>6</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D9" s="5">
         <v>9143700</v>
       </c>
       <c r="E9" s="6" t="str">
-        <f>IF($D9="","",VLOOKUP($D9,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D9="","",VLOOKUP($D9,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
       <c r="G9" s="7" t="s">
@@ -2342,13 +2857,13 @@
         <v>7</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="D10" s="5">
         <v>9141450</v>
       </c>
       <c r="E10" s="6" t="str">
-        <f>IF($D10="","",VLOOKUP($D10,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D10="","",VLOOKUP($D10,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
       <c r="G10" s="7" t="s">
@@ -2364,13 +2879,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D11" s="5">
         <v>9065250</v>
       </c>
       <c r="E11" s="6" t="str">
-        <f>IF($D11="","",VLOOKUP($D11,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D11="","",VLOOKUP($D11,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
       <c r="G11" s="7" t="s">
@@ -2386,13 +2901,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D12" s="5">
-        <v>9017250</v>
+        <v>9019910</v>
       </c>
       <c r="E12" s="6" t="str">
-        <f>IF($D12="","",VLOOKUP($D12,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D12="","",VLOOKUP($D12,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
       <c r="G12" s="7" t="s">
@@ -2408,13 +2923,13 @@
         <v>10</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D13" s="5">
-        <v>8908800</v>
+        <v>9017250</v>
       </c>
       <c r="E13" s="6" t="str">
-        <f>IF($D13="","",VLOOKUP($D13,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D13="","",VLOOKUP($D13,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
       <c r="G13" s="9" t="s">
@@ -2433,10 +2948,10 @@
         <v>29</v>
       </c>
       <c r="D14" s="5">
-        <v>8266050</v>
+        <v>8908800</v>
       </c>
       <c r="E14" s="6" t="str">
-        <f>IF($D14="","",VLOOKUP($D14,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D14="","",VLOOKUP($D14,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
       <c r="G14" s="9" t="s">
@@ -2444,7 +2959,7 @@
       </c>
       <c r="H14" s="10">
         <f>SUM($D$4:$D$73)</f>
-        <v>385165006</v>
+        <v>392693604</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="16.5" customHeight="1">
@@ -2452,13 +2967,13 @@
         <v>12</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D15" s="5">
-        <v>8226750</v>
+        <v>8560398</v>
       </c>
       <c r="E15" s="6" t="str">
-        <f>IF($D15="","",VLOOKUP($D15,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D15="","",VLOOKUP($D15,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
     </row>
@@ -2467,13 +2982,13 @@
         <v>13</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D16" s="5">
-        <v>8125259</v>
+        <v>8266050</v>
       </c>
       <c r="E16" s="6" t="str">
-        <f>IF($D16="","",VLOOKUP($D16,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D16="","",VLOOKUP($D16,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
     </row>
@@ -2482,13 +2997,13 @@
         <v>14</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D17" s="5">
-        <v>7855412</v>
+        <v>8226750</v>
       </c>
       <c r="E17" s="6" t="str">
-        <f>IF($D17="","",VLOOKUP($D17,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D17="","",VLOOKUP($D17,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
     </row>
@@ -2497,13 +3012,13 @@
         <v>15</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="D18" s="5">
-        <v>7740750</v>
+        <v>8125259</v>
       </c>
       <c r="E18" s="6" t="str">
-        <f>IF($D18="","",VLOOKUP($D18,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D18="","",VLOOKUP($D18,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
     </row>
@@ -2512,13 +3027,13 @@
         <v>16</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="D19" s="5">
-        <v>7716900</v>
+        <v>7740750</v>
       </c>
       <c r="E19" s="6" t="str">
-        <f>IF($D19="","",VLOOKUP($D19,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D19="","",VLOOKUP($D19,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
     </row>
@@ -2527,13 +3042,13 @@
         <v>17</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D20" s="5">
-        <v>7697397</v>
+        <v>7716900</v>
       </c>
       <c r="E20" s="6" t="str">
-        <f>IF($D20="","",VLOOKUP($D20,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D20="","",VLOOKUP($D20,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
     </row>
@@ -2542,13 +3057,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D21" s="5">
-        <v>7694109</v>
+        <v>7697397</v>
       </c>
       <c r="E21" s="6" t="str">
-        <f>IF($D21="","",VLOOKUP($D21,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D21="","",VLOOKUP($D21,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
     </row>
@@ -2557,13 +3072,13 @@
         <v>19</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D22" s="5">
-        <v>7624294</v>
+        <v>7694109</v>
       </c>
       <c r="E22" s="6" t="str">
-        <f>IF($D22="","",VLOOKUP($D22,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D22="","",VLOOKUP($D22,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
     </row>
@@ -2572,13 +3087,13 @@
         <v>20</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="D23" s="5">
-        <v>7548021</v>
+        <v>7624294</v>
       </c>
       <c r="E23" s="6" t="str">
-        <f>IF($D23="","",VLOOKUP($D23,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D23="","",VLOOKUP($D23,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
     </row>
@@ -2587,13 +3102,13 @@
         <v>21</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="D24" s="5">
         <v>7514973</v>
       </c>
       <c r="E24" s="6" t="str">
-        <f>IF($D24="","",VLOOKUP($D24,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D24="","",VLOOKUP($D24,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
     </row>
@@ -2602,13 +3117,13 @@
         <v>22</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D25" s="5">
         <v>7392720</v>
       </c>
       <c r="E25" s="6" t="str">
-        <f>IF($D25="","",VLOOKUP($D25,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D25="","",VLOOKUP($D25,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
     </row>
@@ -2617,13 +3132,13 @@
         <v>23</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D26" s="5">
         <v>7368735</v>
       </c>
       <c r="E26" s="6" t="str">
-        <f>IF($D26="","",VLOOKUP($D26,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D26="","",VLOOKUP($D26,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
     </row>
@@ -2632,13 +3147,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D27" s="5">
-        <v>7299150</v>
+        <v>7321500</v>
       </c>
       <c r="E27" s="6" t="str">
-        <f>IF($D27="","",VLOOKUP($D27,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D27="","",VLOOKUP($D27,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
     </row>
@@ -2647,13 +3162,13 @@
         <v>25</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D28" s="5">
-        <v>7285842</v>
+        <v>7299150</v>
       </c>
       <c r="E28" s="6" t="str">
-        <f>IF($D28="","",VLOOKUP($D28,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D28="","",VLOOKUP($D28,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
     </row>
@@ -2662,13 +3177,13 @@
         <v>26</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D29" s="5">
-        <v>7252456</v>
+        <v>7285842</v>
       </c>
       <c r="E29" s="6" t="str">
-        <f>IF($D29="","",VLOOKUP($D29,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D29="","",VLOOKUP($D29,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
     </row>
@@ -2677,13 +3192,13 @@
         <v>27</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D30" s="5">
-        <v>7210500</v>
+        <v>7252456</v>
       </c>
       <c r="E30" s="6" t="str">
-        <f>IF($D30="","",VLOOKUP($D30,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D30="","",VLOOKUP($D30,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
     </row>
@@ -2692,14 +3207,14 @@
         <v>28</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D31" s="5">
-        <v>7095450</v>
+        <v>7201676</v>
       </c>
       <c r="E31" s="6" t="str">
-        <f>IF($D31="","",VLOOKUP($D31,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <f>IF($D31="","",VLOOKUP($D31,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="32" spans="2:5" ht="16.5" customHeight="1">
@@ -2707,14 +3222,14 @@
         <v>29</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D32" s="5">
-        <v>5739081</v>
+        <v>7195050</v>
       </c>
       <c r="E32" s="6" t="str">
-        <f>IF($D32="","",VLOOKUP($D32,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <f>IF($D32="","",VLOOKUP($D32,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="33" spans="2:5" ht="16.5" customHeight="1">
@@ -2725,10 +3240,10 @@
         <v>49</v>
       </c>
       <c r="D33" s="5">
-        <v>5561285</v>
+        <v>5739081</v>
       </c>
       <c r="E33" s="6" t="str">
-        <f>IF($D33="","",VLOOKUP($D33,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D33="","",VLOOKUP($D33,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -2737,13 +3252,13 @@
         <v>31</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D34" s="5">
-        <v>5434650</v>
+        <v>5563310</v>
       </c>
       <c r="E34" s="6" t="str">
-        <f>IF($D34="","",VLOOKUP($D34,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D34="","",VLOOKUP($D34,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -2752,13 +3267,13 @@
         <v>32</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D35" s="5">
-        <v>5171951</v>
+        <v>5503650</v>
       </c>
       <c r="E35" s="6" t="str">
-        <f>IF($D35="","",VLOOKUP($D35,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D35="","",VLOOKUP($D35,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -2767,13 +3282,13 @@
         <v>33</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D36" s="5">
-        <v>5091005</v>
+        <v>5171951</v>
       </c>
       <c r="E36" s="6" t="str">
-        <f>IF($D36="","",VLOOKUP($D36,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D36="","",VLOOKUP($D36,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -2782,13 +3297,13 @@
         <v>34</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D37" s="5">
-        <v>5016847</v>
+        <v>5118847</v>
       </c>
       <c r="E37" s="6" t="str">
-        <f>IF($D37="","",VLOOKUP($D37,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D37="","",VLOOKUP($D37,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -2797,13 +3312,13 @@
         <v>35</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D38" s="5">
-        <v>4630800</v>
+        <v>5091005</v>
       </c>
       <c r="E38" s="6" t="str">
-        <f>IF($D38="","",VLOOKUP($D38,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D38="","",VLOOKUP($D38,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -2812,13 +3327,13 @@
         <v>36</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="D39" s="5">
-        <v>4537987</v>
+        <v>4630800</v>
       </c>
       <c r="E39" s="6" t="str">
-        <f>IF($D39="","",VLOOKUP($D39,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D39="","",VLOOKUP($D39,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -2827,13 +3342,13 @@
         <v>37</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D40" s="5">
-        <v>4444305</v>
+        <v>4537987</v>
       </c>
       <c r="E40" s="6" t="str">
-        <f>IF($D40="","",VLOOKUP($D40,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D40="","",VLOOKUP($D40,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -2842,13 +3357,13 @@
         <v>38</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D41" s="5">
-        <v>4393558</v>
+        <v>4444305</v>
       </c>
       <c r="E41" s="6" t="str">
-        <f>IF($D41="","",VLOOKUP($D41,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D41="","",VLOOKUP($D41,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -2857,13 +3372,13 @@
         <v>39</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D42" s="5">
-        <v>4361685</v>
+        <v>4393558</v>
       </c>
       <c r="E42" s="6" t="str">
-        <f>IF($D42="","",VLOOKUP($D42,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D42="","",VLOOKUP($D42,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -2872,13 +3387,13 @@
         <v>40</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D43" s="5">
-        <v>4314000</v>
+        <v>4361685</v>
       </c>
       <c r="E43" s="6" t="str">
-        <f>IF($D43="","",VLOOKUP($D43,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D43="","",VLOOKUP($D43,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -2887,13 +3402,13 @@
         <v>41</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="D44" s="5">
-        <v>4305372</v>
+        <v>4314000</v>
       </c>
       <c r="E44" s="6" t="str">
-        <f>IF($D44="","",VLOOKUP($D44,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D44="","",VLOOKUP($D44,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -2902,13 +3417,13 @@
         <v>42</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="D45" s="5">
-        <v>4250088</v>
+        <v>4305372</v>
       </c>
       <c r="E45" s="6" t="str">
-        <f>IF($D45="","",VLOOKUP($D45,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D45="","",VLOOKUP($D45,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -2917,13 +3432,13 @@
         <v>43</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D46" s="5">
-        <v>4174414</v>
+        <v>4250081</v>
       </c>
       <c r="E46" s="6" t="str">
-        <f>IF($D46="","",VLOOKUP($D46,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D46="","",VLOOKUP($D46,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -2932,13 +3447,13 @@
         <v>44</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D47" s="5">
-        <v>4151246</v>
+        <v>4174414</v>
       </c>
       <c r="E47" s="6" t="str">
-        <f>IF($D47="","",VLOOKUP($D47,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D47="","",VLOOKUP($D47,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -2947,13 +3462,13 @@
         <v>45</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D48" s="5">
         <v>4081096</v>
       </c>
       <c r="E48" s="6" t="str">
-        <f>IF($D48="","",VLOOKUP($D48,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D48="","",VLOOKUP($D48,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -2962,13 +3477,13 @@
         <v>46</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="D49" s="5">
-        <v>4033323</v>
+        <v>4075795</v>
       </c>
       <c r="E49" s="6" t="str">
-        <f>IF($D49="","",VLOOKUP($D49,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D49="","",VLOOKUP($D49,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -2977,13 +3492,13 @@
         <v>47</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D50" s="5">
-        <v>4029200</v>
+        <v>4033323</v>
       </c>
       <c r="E50" s="6" t="str">
-        <f>IF($D50="","",VLOOKUP($D50,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D50="","",VLOOKUP($D50,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -2992,13 +3507,13 @@
         <v>48</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D51" s="5">
-        <v>4000500</v>
+        <v>4029200</v>
       </c>
       <c r="E51" s="6" t="str">
-        <f>IF($D51="","",VLOOKUP($D51,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D51="","",VLOOKUP($D51,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -3007,13 +3522,13 @@
         <v>49</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D52" s="5">
-        <v>3893926</v>
+        <v>4008325</v>
       </c>
       <c r="E52" s="6" t="str">
-        <f>IF($D52="","",VLOOKUP($D52,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D52="","",VLOOKUP($D52,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -3022,13 +3537,13 @@
         <v>50</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D53" s="5">
-        <v>3892915</v>
+        <v>4000500</v>
       </c>
       <c r="E53" s="6" t="str">
-        <f>IF($D53="","",VLOOKUP($D53,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D53="","",VLOOKUP($D53,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -3037,13 +3552,13 @@
         <v>51</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D54" s="5">
-        <v>3817624</v>
+        <v>3892915</v>
       </c>
       <c r="E54" s="6" t="str">
-        <f>IF($D54="","",VLOOKUP($D54,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D54="","",VLOOKUP($D54,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -3055,10 +3570,10 @@
         <v>71</v>
       </c>
       <c r="D55" s="5">
-        <v>3776295</v>
+        <v>3817624</v>
       </c>
       <c r="E55" s="6" t="str">
-        <f>IF($D55="","",VLOOKUP($D55,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D55="","",VLOOKUP($D55,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -3067,13 +3582,13 @@
         <v>53</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D56" s="5">
         <v>3636629</v>
       </c>
       <c r="E56" s="6" t="str">
-        <f>IF($D56="","",VLOOKUP($D56,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D56="","",VLOOKUP($D56,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -3082,13 +3597,13 @@
         <v>54</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D57" s="5">
         <v>3620200</v>
       </c>
       <c r="E57" s="6" t="str">
-        <f>IF($D57="","",VLOOKUP($D57,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D57="","",VLOOKUP($D57,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -3097,13 +3612,13 @@
         <v>55</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D58" s="5">
         <v>3414335</v>
       </c>
       <c r="E58" s="6" t="str">
-        <f>IF($D58="","",VLOOKUP($D58,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D58="","",VLOOKUP($D58,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -3112,13 +3627,13 @@
         <v>56</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="D59" s="5">
         <v>3164754</v>
       </c>
       <c r="E59" s="6" t="str">
-        <f>IF($D59="","",VLOOKUP($D59,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D59="","",VLOOKUP($D59,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -3127,13 +3642,13 @@
         <v>57</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D60" s="5">
         <v>3063699</v>
       </c>
       <c r="E60" s="6" t="str">
-        <f>IF($D60="","",VLOOKUP($D60,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D60="","",VLOOKUP($D60,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -3142,13 +3657,13 @@
         <v>58</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D61" s="5">
         <v>2777032</v>
       </c>
       <c r="E61" s="6" t="str">
-        <f>IF($D61="","",VLOOKUP($D61,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D61="","",VLOOKUP($D61,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
     </row>
@@ -3157,13 +3672,13 @@
         <v>59</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D62" s="5">
         <v>2391014</v>
       </c>
       <c r="E62" s="6" t="str">
-        <f>IF($D62="","",VLOOKUP($D62,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D62="","",VLOOKUP($D62,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>7단계</v>
       </c>
     </row>
@@ -3171,14 +3686,14 @@
       <c r="B63" s="3">
         <v>60</v>
       </c>
-      <c r="C63" s="8" t="s">
-        <v>79</v>
+      <c r="C63" s="11" t="s">
+        <v>84</v>
       </c>
       <c r="D63" s="5">
-        <v>2371425</v>
+        <v>2372493</v>
       </c>
       <c r="E63" s="6" t="str">
-        <f>IF($D63="","",VLOOKUP($D63,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D63="","",VLOOKUP($D63,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>7단계</v>
       </c>
     </row>
@@ -3187,14 +3702,14 @@
         <v>61</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D64" s="5">
-        <v>2022500</v>
+        <v>2371425</v>
       </c>
       <c r="E64" s="6" t="str">
-        <f>IF($D64="","",VLOOKUP($D64,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
+        <f>IF($D64="","",VLOOKUP($D64,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>7단계</v>
       </c>
     </row>
     <row r="65" spans="2:5" ht="16.5" customHeight="1">
@@ -3202,13 +3717,13 @@
         <v>62</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D65" s="5">
-        <v>1764375</v>
+        <v>2022500</v>
       </c>
       <c r="E65" s="6" t="str">
-        <f>IF($D65="","",VLOOKUP($D65,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D65="","",VLOOKUP($D65,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>6단계</v>
       </c>
     </row>
@@ -3217,13 +3732,13 @@
         <v>63</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D66" s="5">
-        <v>1739773</v>
+        <v>1764375</v>
       </c>
       <c r="E66" s="6" t="str">
-        <f>IF($D66="","",VLOOKUP($D66,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D66="","",VLOOKUP($D66,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>6단계</v>
       </c>
     </row>
@@ -3232,13 +3747,13 @@
         <v>64</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="D67" s="5">
-        <v>1685105</v>
+        <v>1739773</v>
       </c>
       <c r="E67" s="6" t="str">
-        <f>IF($D67="","",VLOOKUP($D67,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D67="","",VLOOKUP($D67,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>6단계</v>
       </c>
     </row>
@@ -3246,14 +3761,14 @@
       <c r="B68" s="3">
         <v>65</v>
       </c>
-      <c r="C68" s="4">
-        <v>1090</v>
+      <c r="C68" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="D68" s="5">
-        <v>1619227</v>
+        <v>1685105</v>
       </c>
       <c r="E68" s="6" t="str">
-        <f>IF($D68="","",VLOOKUP($D68,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D68="","",VLOOKUP($D68,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>6단계</v>
       </c>
     </row>
@@ -3261,14 +3776,14 @@
       <c r="B69" s="3">
         <v>66</v>
       </c>
-      <c r="C69" s="4" t="s">
-        <v>85</v>
+      <c r="C69" s="4">
+        <v>1090</v>
       </c>
       <c r="D69" s="5">
-        <v>1116967</v>
+        <v>1619227</v>
       </c>
       <c r="E69" s="6" t="str">
-        <f>IF($D69="","",VLOOKUP($D69,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D69="","",VLOOKUP($D69,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>6단계</v>
       </c>
     </row>
@@ -3277,13 +3792,13 @@
         <v>67</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D70" s="5">
         <v>481250</v>
       </c>
       <c r="E70" s="6" t="str">
-        <f>IF($D70="","",VLOOKUP($D70,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D70="","",VLOOKUP($D70,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>3단계</v>
       </c>
     </row>
@@ -3291,14 +3806,14 @@
       <c r="B71" s="3">
         <v>68</v>
       </c>
-      <c r="C71" s="8" t="s">
-        <v>87</v>
+      <c r="C71" s="11" t="s">
+        <v>86</v>
       </c>
       <c r="D71" s="5">
         <v>368750</v>
       </c>
       <c r="E71" s="6" t="str">
-        <f>IF($D71="","",VLOOKUP($D71,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <f>IF($D71="","",VLOOKUP($D71,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>3단계</v>
       </c>
     </row>
@@ -3319,7 +3834,7 @@
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="B2:E2"/>
   </mergeCells>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -3343,19 +3858,19 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
+      <c r="C1" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
     </row>
     <row r="2" spans="2:8" ht="18" customHeight="1">
       <c r="B2" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
+        <v>92</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
@@ -3879,7 +4394,7 @@
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="B2:E2"/>
   </mergeCells>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -3903,19 +4418,19 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
+      <c r="C1" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
     </row>
     <row r="2" spans="2:8" ht="18" customHeight="1">
       <c r="B2" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
+        <v>94</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
@@ -4789,7 +5304,7 @@
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="B2:E2"/>
   </mergeCells>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -4813,19 +5328,19 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
+      <c r="C1" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
     </row>
     <row r="2" spans="2:8" ht="18" customHeight="1">
       <c r="B2" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
+        <v>96</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
@@ -5699,7 +6214,7 @@
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="B2:E2"/>
   </mergeCells>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -5723,19 +6238,19 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
+      <c r="C1" s="27">
+        <v>46193</v>
+      </c>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
     </row>
     <row r="2" spans="2:8" ht="18" customHeight="1">
       <c r="B2" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
@@ -5758,33 +6273,15 @@
       </c>
     </row>
     <row r="4" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B4" s="3">
-        <v>1</v>
-      </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="6" t="str">
-        <f>IF($D4="","",VLOOKUP($D4,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
       <c r="G4" s="7" t="s">
         <v>10</v>
       </c>
       <c r="H4" s="3">
-        <f t="shared" ref="H4:H12" si="0">COUNTIF($E$4:$E$73,G4)</f>
+        <f t="shared" ref="H4:H12" si="0">COUNTIF($E$68:$E$73,G4)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B5" s="3">
-        <v>2</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="6" t="str">
-        <f>IF($D5="","",VLOOKUP($D5,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
       <c r="G5" s="7" t="s">
         <v>12</v>
       </c>
@@ -5794,15 +6291,6 @@
       </c>
     </row>
     <row r="6" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B6" s="3">
-        <v>3</v>
-      </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="6" t="str">
-        <f>IF($D6="","",VLOOKUP($D6,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
       <c r="G6" s="7" t="s">
         <v>14</v>
       </c>
@@ -5812,15 +6300,6 @@
       </c>
     </row>
     <row r="7" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B7" s="3">
-        <v>4</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="6" t="str">
-        <f>IF($D7="","",VLOOKUP($D7,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
       <c r="G7" s="7" t="s">
         <v>16</v>
       </c>
@@ -5830,15 +6309,6 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B8" s="3">
-        <v>5</v>
-      </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="6" t="str">
-        <f>IF($D8="","",VLOOKUP($D8,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
       <c r="G8" s="7" t="s">
         <v>18</v>
       </c>
@@ -5848,15 +6318,6 @@
       </c>
     </row>
     <row r="9" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B9" s="3">
-        <v>6</v>
-      </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="6" t="str">
-        <f>IF($D9="","",VLOOKUP($D9,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
       <c r="G9" s="7" t="s">
         <v>20</v>
       </c>
@@ -5866,15 +6327,6 @@
       </c>
     </row>
     <row r="10" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B10" s="3">
-        <v>7</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="6" t="str">
-        <f>IF($D10="","",VLOOKUP($D10,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
       <c r="G10" s="7" t="s">
         <v>22</v>
       </c>
@@ -5884,15 +6336,6 @@
       </c>
     </row>
     <row r="11" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B11" s="3">
-        <v>8</v>
-      </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="6" t="str">
-        <f>IF($D11="","",VLOOKUP($D11,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
       <c r="G11" s="7" t="s">
         <v>24</v>
       </c>
@@ -5902,15 +6345,6 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B12" s="3">
-        <v>9</v>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="6" t="str">
-        <f>IF($D12="","",VLOOKUP($D12,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
       <c r="G12" s="7" t="s">
         <v>26</v>
       </c>
@@ -5920,628 +6354,78 @@
       </c>
     </row>
     <row r="13" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B13" s="3">
-        <v>10</v>
-      </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="6" t="str">
-        <f>IF($D13="","",VLOOKUP($D13,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
       <c r="G13" s="9" t="s">
         <v>28</v>
       </c>
       <c r="H13" s="6">
-        <f>COUNTA($C$4:$C$73)</f>
+        <f>COUNTA($C$68:$C$73)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B14" s="3">
-        <v>11</v>
-      </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="6" t="str">
-        <f>IF($D14="","",VLOOKUP($D14,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
       <c r="G14" s="9" t="s">
         <v>30</v>
       </c>
       <c r="H14" s="10">
-        <f>SUM($D$4:$D$73)</f>
+        <f>SUM($D$68:$D$73)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B15" s="3">
-        <v>12</v>
-      </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="6" t="str">
-        <f>IF($D15="","",VLOOKUP($D15,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B16" s="3">
-        <v>13</v>
-      </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="6" t="str">
-        <f>IF($D16="","",VLOOKUP($D16,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B17" s="3">
-        <v>14</v>
-      </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="6" t="str">
-        <f>IF($D17="","",VLOOKUP($D17,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B18" s="3">
-        <v>15</v>
-      </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="6" t="str">
-        <f>IF($D18="","",VLOOKUP($D18,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B19" s="3">
-        <v>16</v>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="6" t="str">
-        <f>IF($D19="","",VLOOKUP($D19,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B20" s="3">
-        <v>17</v>
-      </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="6" t="str">
-        <f>IF($D20="","",VLOOKUP($D20,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B21" s="3">
-        <v>18</v>
-      </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="6" t="str">
-        <f>IF($D21="","",VLOOKUP($D21,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B22" s="3">
-        <v>19</v>
-      </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="6" t="str">
-        <f>IF($D22="","",VLOOKUP($D22,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B23" s="3">
-        <v>20</v>
-      </c>
-      <c r="C23" s="8"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="6" t="str">
-        <f>IF($D23="","",VLOOKUP($D23,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B24" s="3">
-        <v>21</v>
-      </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="6" t="str">
-        <f>IF($D24="","",VLOOKUP($D24,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B25" s="3">
-        <v>22</v>
-      </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="6" t="str">
-        <f>IF($D25="","",VLOOKUP($D25,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B26" s="3">
-        <v>23</v>
-      </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="6" t="str">
-        <f>IF($D26="","",VLOOKUP($D26,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B27" s="3">
-        <v>24</v>
-      </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="6" t="str">
-        <f>IF($D27="","",VLOOKUP($D27,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B28" s="3">
-        <v>25</v>
-      </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="6" t="str">
-        <f>IF($D28="","",VLOOKUP($D28,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B29" s="3">
-        <v>26</v>
-      </c>
-      <c r="C29" s="8"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="6" t="str">
-        <f>IF($D29="","",VLOOKUP($D29,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B30" s="3">
-        <v>27</v>
-      </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="6" t="str">
-        <f>IF($D30="","",VLOOKUP($D30,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B31" s="3">
-        <v>28</v>
-      </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="6" t="str">
-        <f>IF($D31="","",VLOOKUP($D31,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B32" s="3">
-        <v>29</v>
-      </c>
-      <c r="C32" s="8"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="6" t="str">
-        <f>IF($D32="","",VLOOKUP($D32,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B33" s="3">
-        <v>30</v>
-      </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="6" t="str">
-        <f>IF($D33="","",VLOOKUP($D33,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B34" s="3">
-        <v>31</v>
-      </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="6" t="str">
-        <f>IF($D34="","",VLOOKUP($D34,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B35" s="3">
-        <v>32</v>
-      </c>
-      <c r="C35" s="8"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="6" t="str">
-        <f>IF($D35="","",VLOOKUP($D35,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B36" s="3">
-        <v>33</v>
-      </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="6" t="str">
-        <f>IF($D36="","",VLOOKUP($D36,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B37" s="3">
-        <v>34</v>
-      </c>
-      <c r="C37" s="8"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="6" t="str">
-        <f>IF($D37="","",VLOOKUP($D37,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B38" s="3">
-        <v>35</v>
-      </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="6" t="str">
-        <f>IF($D38="","",VLOOKUP($D38,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B39" s="3">
-        <v>36</v>
-      </c>
-      <c r="C39" s="8"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="6" t="str">
-        <f>IF($D39="","",VLOOKUP($D39,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B40" s="3">
-        <v>37</v>
-      </c>
-      <c r="C40" s="8"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="6" t="str">
-        <f>IF($D40="","",VLOOKUP($D40,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B41" s="3">
-        <v>38</v>
-      </c>
-      <c r="C41" s="8"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="6" t="str">
-        <f>IF($D41="","",VLOOKUP($D41,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B42" s="3">
-        <v>39</v>
-      </c>
-      <c r="C42" s="8"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="6" t="str">
-        <f>IF($D42="","",VLOOKUP($D42,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B43" s="3">
-        <v>40</v>
-      </c>
-      <c r="C43" s="8"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="6" t="str">
-        <f>IF($D43="","",VLOOKUP($D43,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B44" s="3">
-        <v>41</v>
-      </c>
-      <c r="C44" s="8"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="6" t="str">
-        <f>IF($D44="","",VLOOKUP($D44,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B45" s="3">
-        <v>42</v>
-      </c>
-      <c r="C45" s="8"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="6" t="str">
-        <f>IF($D45="","",VLOOKUP($D45,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B46" s="3">
-        <v>43</v>
-      </c>
-      <c r="C46" s="8"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="6" t="str">
-        <f>IF($D46="","",VLOOKUP($D46,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B47" s="3">
-        <v>44</v>
-      </c>
-      <c r="C47" s="8"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="6" t="str">
-        <f>IF($D47="","",VLOOKUP($D47,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B48" s="3">
-        <v>45</v>
-      </c>
-      <c r="C48" s="8"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="6" t="str">
-        <f>IF($D48="","",VLOOKUP($D48,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B49" s="3">
-        <v>46</v>
-      </c>
-      <c r="C49" s="8"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="6" t="str">
-        <f>IF($D49="","",VLOOKUP($D49,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B50" s="3">
-        <v>47</v>
-      </c>
-      <c r="C50" s="8"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="6" t="str">
-        <f>IF($D50="","",VLOOKUP($D50,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B51" s="3">
-        <v>48</v>
-      </c>
-      <c r="C51" s="8"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="6" t="str">
-        <f>IF($D51="","",VLOOKUP($D51,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B52" s="3">
-        <v>49</v>
-      </c>
-      <c r="C52" s="8"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="6" t="str">
-        <f>IF($D52="","",VLOOKUP($D52,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B53" s="3">
-        <v>50</v>
-      </c>
-      <c r="C53" s="8"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="6" t="str">
-        <f>IF($D53="","",VLOOKUP($D53,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B54" s="3">
-        <v>51</v>
-      </c>
-      <c r="C54" s="8"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="6" t="str">
-        <f>IF($D54="","",VLOOKUP($D54,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B55" s="3">
-        <v>52</v>
-      </c>
-      <c r="C55" s="8"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="6" t="str">
-        <f>IF($D55="","",VLOOKUP($D55,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B56" s="3">
-        <v>53</v>
-      </c>
-      <c r="C56" s="8"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="6" t="str">
-        <f>IF($D56="","",VLOOKUP($D56,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B57" s="3">
-        <v>54</v>
-      </c>
-      <c r="C57" s="8"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="6" t="str">
-        <f>IF($D57="","",VLOOKUP($D57,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B58" s="3">
-        <v>55</v>
-      </c>
-      <c r="C58" s="8"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="6" t="str">
-        <f>IF($D58="","",VLOOKUP($D58,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B59" s="3">
-        <v>56</v>
-      </c>
-      <c r="C59" s="8"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="6" t="str">
-        <f>IF($D59="","",VLOOKUP($D59,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B60" s="3">
-        <v>57</v>
-      </c>
-      <c r="C60" s="8"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="6" t="str">
-        <f>IF($D60="","",VLOOKUP($D60,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B61" s="3">
-        <v>58</v>
-      </c>
-      <c r="C61" s="8"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="6" t="str">
-        <f>IF($D61="","",VLOOKUP($D61,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B62" s="3">
-        <v>59</v>
-      </c>
-      <c r="C62" s="8"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="6" t="str">
-        <f>IF($D62="","",VLOOKUP($D62,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B63" s="3">
-        <v>60</v>
-      </c>
-      <c r="C63" s="8"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="6" t="str">
-        <f>IF($D63="","",VLOOKUP($D63,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B64" s="3">
-        <v>61</v>
-      </c>
-      <c r="C64" s="8"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="6" t="str">
-        <f>IF($D64="","",VLOOKUP($D64,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B65" s="3">
-        <v>62</v>
-      </c>
-      <c r="C65" s="8"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="6" t="str">
-        <f>IF($D65="","",VLOOKUP($D65,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B66" s="3">
-        <v>63</v>
-      </c>
-      <c r="C66" s="8"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="6" t="str">
-        <f>IF($D66="","",VLOOKUP($D66,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B67" s="3">
-        <v>64</v>
-      </c>
-      <c r="C67" s="8"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="6" t="str">
-        <f>IF($D67="","",VLOOKUP($D67,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v/>
-      </c>
-    </row>
+    <row r="15" spans="2:8" ht="16.5" customHeight="1"/>
+    <row r="16" spans="2:8" ht="16.5" customHeight="1"/>
+    <row r="17" ht="16.5" customHeight="1"/>
+    <row r="18" ht="16.5" customHeight="1"/>
+    <row r="19" ht="16.5" customHeight="1"/>
+    <row r="20" ht="16.5" customHeight="1"/>
+    <row r="21" ht="16.5" customHeight="1"/>
+    <row r="22" ht="16.5" customHeight="1"/>
+    <row r="23" ht="16.5" customHeight="1"/>
+    <row r="24" ht="16.5" customHeight="1"/>
+    <row r="25" ht="16.5" customHeight="1"/>
+    <row r="26" ht="16.5" customHeight="1"/>
+    <row r="27" ht="16.5" customHeight="1"/>
+    <row r="28" ht="16.5" customHeight="1"/>
+    <row r="29" ht="16.5" customHeight="1"/>
+    <row r="30" ht="16.5" customHeight="1"/>
+    <row r="31" ht="16.5" customHeight="1"/>
+    <row r="32" ht="16.5" customHeight="1"/>
+    <row r="33" ht="16.5" customHeight="1"/>
+    <row r="34" ht="16.5" customHeight="1"/>
+    <row r="35" ht="16.5" customHeight="1"/>
+    <row r="36" ht="16.5" customHeight="1"/>
+    <row r="37" ht="16.5" customHeight="1"/>
+    <row r="38" ht="16.5" customHeight="1"/>
+    <row r="39" ht="16.5" customHeight="1"/>
+    <row r="40" ht="16.5" customHeight="1"/>
+    <row r="41" ht="16.5" customHeight="1"/>
+    <row r="42" ht="16.5" customHeight="1"/>
+    <row r="43" ht="16.5" customHeight="1"/>
+    <row r="44" ht="16.5" customHeight="1"/>
+    <row r="45" ht="16.5" customHeight="1"/>
+    <row r="46" ht="16.5" customHeight="1"/>
+    <row r="47" ht="16.5" customHeight="1"/>
+    <row r="48" ht="16.5" customHeight="1"/>
+    <row r="49" ht="16.5" customHeight="1"/>
+    <row r="50" ht="16.5" customHeight="1"/>
+    <row r="51" ht="16.5" customHeight="1"/>
+    <row r="52" ht="16.5" customHeight="1"/>
+    <row r="53" ht="16.5" customHeight="1"/>
+    <row r="54" ht="16.5" customHeight="1"/>
+    <row r="55" ht="16.5" customHeight="1"/>
+    <row r="56" ht="16.5" customHeight="1"/>
+    <row r="57" ht="16.5" customHeight="1"/>
+    <row r="58" ht="16.5" customHeight="1"/>
+    <row r="59" ht="16.5" customHeight="1"/>
+    <row r="60" ht="16.5" customHeight="1"/>
+    <row r="61" ht="16.5" customHeight="1"/>
+    <row r="62" ht="16.5" customHeight="1"/>
+    <row r="63" ht="16.5" customHeight="1"/>
+    <row r="64" ht="16.5" customHeight="1"/>
+    <row r="65" spans="2:5" ht="16.5" customHeight="1"/>
+    <row r="66" spans="2:5" ht="16.5" customHeight="1"/>
+    <row r="67" spans="2:5" ht="16.5" customHeight="1"/>
     <row r="68" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B68" s="3">
-        <v>65</v>
-      </c>
+      <c r="B68" s="3"/>
       <c r="C68" s="8"/>
       <c r="D68" s="5"/>
       <c r="E68" s="6" t="str">
@@ -6550,9 +6434,7 @@
       </c>
     </row>
     <row r="69" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B69" s="3">
-        <v>66</v>
-      </c>
+      <c r="B69" s="3"/>
       <c r="C69" s="8"/>
       <c r="D69" s="5"/>
       <c r="E69" s="6" t="str">
@@ -6561,9 +6443,7 @@
       </c>
     </row>
     <row r="70" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B70" s="3">
-        <v>67</v>
-      </c>
+      <c r="B70" s="3"/>
       <c r="C70" s="8"/>
       <c r="D70" s="5"/>
       <c r="E70" s="6" t="str">
@@ -6572,9 +6452,7 @@
       </c>
     </row>
     <row r="71" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B71" s="3">
-        <v>68</v>
-      </c>
+      <c r="B71" s="3"/>
       <c r="C71" s="8"/>
       <c r="D71" s="5"/>
       <c r="E71" s="6" t="str">
@@ -6583,9 +6461,7 @@
       </c>
     </row>
     <row r="72" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B72" s="3">
-        <v>69</v>
-      </c>
+      <c r="B72" s="3"/>
       <c r="C72" s="8"/>
       <c r="D72" s="5"/>
       <c r="E72" s="6" t="str">
@@ -6594,9 +6470,7 @@
       </c>
     </row>
     <row r="73" spans="2:5" ht="16.5" customHeight="1">
-      <c r="B73" s="3">
-        <v>70</v>
-      </c>
+      <c r="B73" s="3"/>
       <c r="C73" s="8"/>
       <c r="D73" s="5"/>
       <c r="E73" s="6" t="str">
@@ -6609,7 +6483,7 @@
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="B2:E2"/>
   </mergeCells>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -6617,7 +6491,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:E136"/>
+  <dimension ref="A1:E200"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -6629,16 +6503,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20.25" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
+        <v>114</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
@@ -6654,17 +6528,17 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>88</v>
+      <c r="A3" s="24">
+        <v>46186</v>
       </c>
       <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>11</v>
+      <c r="C3" s="11" t="s">
+        <v>29</v>
       </c>
       <c r="D3" s="5">
-        <v>76513151</v>
+        <v>20124674</v>
       </c>
       <c r="E3" s="6" t="str">
         <f>IF($D3="","",VLOOKUP($D3,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6672,17 +6546,17 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>88</v>
+      <c r="A4" s="24">
+        <v>46186</v>
       </c>
       <c r="B4" s="3">
         <v>2</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D4" s="5">
-        <v>62254586</v>
+        <v>17878446</v>
       </c>
       <c r="E4" s="6" t="str">
         <f>IF($D4="","",VLOOKUP($D4,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6690,17 +6564,17 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>88</v>
+      <c r="A5" s="24">
+        <v>46186</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="5">
-        <v>36598969</v>
+        <v>17252741</v>
       </c>
       <c r="E5" s="6" t="str">
         <f>IF($D5="","",VLOOKUP($D5,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6708,17 +6582,17 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>88</v>
+      <c r="A6" s="24">
+        <v>46186</v>
       </c>
       <c r="B6" s="3">
         <v>4</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>54</v>
+      <c r="C6" s="11" t="s">
+        <v>34</v>
       </c>
       <c r="D6" s="5">
-        <v>26859795</v>
+        <v>14018518</v>
       </c>
       <c r="E6" s="6" t="str">
         <f>IF($D6="","",VLOOKUP($D6,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6726,17 +6600,17 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>88</v>
+      <c r="A7" s="24">
+        <v>46186</v>
       </c>
       <c r="B7" s="3">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>59</v>
+      <c r="C7" s="11" t="s">
+        <v>73</v>
       </c>
       <c r="D7" s="5">
-        <v>22027625</v>
+        <v>13474398</v>
       </c>
       <c r="E7" s="6" t="str">
         <f>IF($D7="","",VLOOKUP($D7,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6744,17 +6618,17 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>88</v>
+      <c r="A8" s="24">
+        <v>46186</v>
       </c>
       <c r="B8" s="3">
         <v>6</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>9</v>
+      <c r="C8" s="11" t="s">
+        <v>98</v>
       </c>
       <c r="D8" s="5">
-        <v>19336746</v>
+        <v>13425532</v>
       </c>
       <c r="E8" s="6" t="str">
         <f>IF($D8="","",VLOOKUP($D8,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6762,17 +6636,17 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>88</v>
+      <c r="A9" s="24">
+        <v>46186</v>
       </c>
       <c r="B9" s="3">
         <v>7</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>21</v>
+      <c r="C9" s="11" t="s">
+        <v>99</v>
       </c>
       <c r="D9" s="5">
-        <v>17008882</v>
+        <v>11951501</v>
       </c>
       <c r="E9" s="6" t="str">
         <f>IF($D9="","",VLOOKUP($D9,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6780,17 +6654,17 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A10" s="3" t="s">
-        <v>88</v>
+      <c r="A10" s="24">
+        <v>46186</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>43</v>
+      <c r="C10" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="D10" s="5">
-        <v>16620269</v>
+        <v>11050986</v>
       </c>
       <c r="E10" s="6" t="str">
         <f>IF($D10="","",VLOOKUP($D10,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6798,17 +6672,17 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A11" s="3" t="s">
-        <v>88</v>
+      <c r="A11" s="24">
+        <v>46186</v>
       </c>
       <c r="B11" s="3">
         <v>9</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>61</v>
+      <c r="C11" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="D11" s="5">
-        <v>15971399</v>
+        <v>11050649</v>
       </c>
       <c r="E11" s="6" t="str">
         <f>IF($D11="","",VLOOKUP($D11,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6816,17 +6690,17 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A12" s="3" t="s">
-        <v>88</v>
+      <c r="A12" s="24">
+        <v>46186</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>42</v>
+      <c r="C12" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="D12" s="5">
-        <v>15579579</v>
+        <v>10955529</v>
       </c>
       <c r="E12" s="6" t="str">
         <f>IF($D12="","",VLOOKUP($D12,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6834,17 +6708,17 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A13" s="3" t="s">
-        <v>88</v>
+      <c r="A13" s="24">
+        <v>46186</v>
       </c>
       <c r="B13" s="3">
         <v>11</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>27</v>
+      <c r="C13" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="D13" s="5">
-        <v>15166835</v>
+        <v>10698509</v>
       </c>
       <c r="E13" s="6" t="str">
         <f>IF($D13="","",VLOOKUP($D13,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6852,17 +6726,17 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A14" s="3" t="s">
-        <v>88</v>
+      <c r="A14" s="24">
+        <v>46186</v>
       </c>
       <c r="B14" s="3">
         <v>12</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>37</v>
+      <c r="C14" s="11" t="s">
+        <v>100</v>
       </c>
       <c r="D14" s="5">
-        <v>15136017</v>
+        <v>10412961</v>
       </c>
       <c r="E14" s="6" t="str">
         <f>IF($D14="","",VLOOKUP($D14,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6870,17 +6744,17 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A15" s="3" t="s">
-        <v>88</v>
+      <c r="A15" s="24">
+        <v>46186</v>
       </c>
       <c r="B15" s="3">
         <v>13</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="11" t="s">
         <v>23</v>
       </c>
       <c r="D15" s="5">
-        <v>15045625</v>
+        <v>10411072</v>
       </c>
       <c r="E15" s="6" t="str">
         <f>IF($D15="","",VLOOKUP($D15,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6888,17 +6762,17 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A16" s="3" t="s">
-        <v>88</v>
+      <c r="A16" s="24">
+        <v>46186</v>
       </c>
       <c r="B16" s="3">
         <v>14</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>39</v>
+      <c r="C16" s="11" t="s">
+        <v>38</v>
       </c>
       <c r="D16" s="5">
-        <v>11929975</v>
+        <v>9539236</v>
       </c>
       <c r="E16" s="6" t="str">
         <f>IF($D16="","",VLOOKUP($D16,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6906,17 +6780,17 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A17" s="3" t="s">
-        <v>88</v>
+      <c r="A17" s="24">
+        <v>46186</v>
       </c>
       <c r="B17" s="3">
         <v>15</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>46</v>
+      <c r="C17" s="11" t="s">
+        <v>64</v>
       </c>
       <c r="D17" s="5">
-        <v>11703867</v>
+        <v>9099782</v>
       </c>
       <c r="E17" s="6" t="str">
         <f>IF($D17="","",VLOOKUP($D17,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6924,17 +6798,17 @@
       </c>
     </row>
     <row r="18" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A18" s="3" t="s">
-        <v>88</v>
+      <c r="A18" s="24">
+        <v>46186</v>
       </c>
       <c r="B18" s="3">
         <v>16</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>47</v>
+      <c r="C18" s="11" t="s">
+        <v>101</v>
       </c>
       <c r="D18" s="5">
-        <v>11641804</v>
+        <v>8928749</v>
       </c>
       <c r="E18" s="6" t="str">
         <f>IF($D18="","",VLOOKUP($D18,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6942,17 +6816,17 @@
       </c>
     </row>
     <row r="19" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A19" s="3" t="s">
-        <v>88</v>
+      <c r="A19" s="24">
+        <v>46186</v>
       </c>
       <c r="B19" s="3">
         <v>17</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>62</v>
+      <c r="C19" s="11" t="s">
+        <v>41</v>
       </c>
       <c r="D19" s="5">
-        <v>11224132</v>
+        <v>8509653</v>
       </c>
       <c r="E19" s="6" t="str">
         <f>IF($D19="","",VLOOKUP($D19,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6960,17 +6834,17 @@
       </c>
     </row>
     <row r="20" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A20" s="3" t="s">
-        <v>88</v>
+      <c r="A20" s="24">
+        <v>46186</v>
       </c>
       <c r="B20" s="3">
         <v>18</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>41</v>
+      <c r="C20" s="11" t="s">
+        <v>102</v>
       </c>
       <c r="D20" s="5">
-        <v>11128193</v>
+        <v>8453735</v>
       </c>
       <c r="E20" s="6" t="str">
         <f>IF($D20="","",VLOOKUP($D20,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6978,17 +6852,17 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A21" s="3" t="s">
-        <v>88</v>
+      <c r="A21" s="24">
+        <v>46186</v>
       </c>
       <c r="B21" s="3">
         <v>19</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>29</v>
+      <c r="C21" s="11" t="s">
+        <v>103</v>
       </c>
       <c r="D21" s="5">
-        <v>10907771</v>
+        <v>8390684</v>
       </c>
       <c r="E21" s="6" t="str">
         <f>IF($D21="","",VLOOKUP($D21,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6996,17 +6870,17 @@
       </c>
     </row>
     <row r="22" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A22" s="3" t="s">
-        <v>88</v>
+      <c r="A22" s="24">
+        <v>46186</v>
       </c>
       <c r="B22" s="3">
         <v>20</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="11" t="s">
         <v>31</v>
       </c>
       <c r="D22" s="5">
-        <v>10606882</v>
+        <v>8385975</v>
       </c>
       <c r="E22" s="6" t="str">
         <f>IF($D22="","",VLOOKUP($D22,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7014,17 +6888,17 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A23" s="3" t="s">
-        <v>88</v>
+      <c r="A23" s="24">
+        <v>46186</v>
       </c>
       <c r="B23" s="3">
         <v>21</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>36</v>
+      <c r="C23" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="D23" s="5">
-        <v>10422796</v>
+        <v>7931262</v>
       </c>
       <c r="E23" s="6" t="str">
         <f>IF($D23="","",VLOOKUP($D23,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7032,17 +6906,17 @@
       </c>
     </row>
     <row r="24" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A24" s="3" t="s">
-        <v>88</v>
+      <c r="A24" s="24">
+        <v>46186</v>
       </c>
       <c r="B24" s="3">
         <v>22</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>35</v>
+      <c r="C24" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="D24" s="5">
-        <v>10412768</v>
+        <v>7760606</v>
       </c>
       <c r="E24" s="6" t="str">
         <f>IF($D24="","",VLOOKUP($D24,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7050,17 +6924,17 @@
       </c>
     </row>
     <row r="25" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A25" s="3" t="s">
-        <v>88</v>
+      <c r="A25" s="24">
+        <v>46186</v>
       </c>
       <c r="B25" s="3">
         <v>23</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>49</v>
+      <c r="C25" s="11" t="s">
+        <v>62</v>
       </c>
       <c r="D25" s="5">
-        <v>10128124</v>
+        <v>7534842</v>
       </c>
       <c r="E25" s="6" t="str">
         <f>IF($D25="","",VLOOKUP($D25,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7068,17 +6942,17 @@
       </c>
     </row>
     <row r="26" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A26" s="3" t="s">
-        <v>88</v>
+      <c r="A26" s="24">
+        <v>46186</v>
       </c>
       <c r="B26" s="3">
         <v>24</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>45</v>
+      <c r="C26" s="11" t="s">
+        <v>43</v>
       </c>
       <c r="D26" s="5">
-        <v>9706739</v>
+        <v>7400843</v>
       </c>
       <c r="E26" s="6" t="str">
         <f>IF($D26="","",VLOOKUP($D26,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7086,17 +6960,17 @@
       </c>
     </row>
     <row r="27" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A27" s="3" t="s">
-        <v>88</v>
+      <c r="A27" s="24">
+        <v>46186</v>
       </c>
       <c r="B27" s="3">
         <v>25</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>13</v>
+      <c r="C27" s="11" t="s">
+        <v>104</v>
       </c>
       <c r="D27" s="5">
-        <v>9164119</v>
+        <v>7282637</v>
       </c>
       <c r="E27" s="6" t="str">
         <f>IF($D27="","",VLOOKUP($D27,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7104,17 +6978,17 @@
       </c>
     </row>
     <row r="28" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A28" s="3" t="s">
-        <v>88</v>
+      <c r="A28" s="24">
+        <v>46186</v>
       </c>
       <c r="B28" s="3">
         <v>26</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>25</v>
+      <c r="C28" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="D28" s="5">
-        <v>8999382</v>
+        <v>7281876</v>
       </c>
       <c r="E28" s="6" t="str">
         <f>IF($D28="","",VLOOKUP($D28,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7122,17 +6996,17 @@
       </c>
     </row>
     <row r="29" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A29" s="3" t="s">
-        <v>88</v>
+      <c r="A29" s="24">
+        <v>46186</v>
       </c>
       <c r="B29" s="3">
         <v>27</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>17</v>
+      <c r="C29" s="11" t="s">
+        <v>40</v>
       </c>
       <c r="D29" s="5">
-        <v>8596217</v>
+        <v>7280918</v>
       </c>
       <c r="E29" s="6" t="str">
         <f>IF($D29="","",VLOOKUP($D29,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7140,17 +7014,17 @@
       </c>
     </row>
     <row r="30" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A30" s="3" t="s">
-        <v>88</v>
+      <c r="A30" s="24">
+        <v>46186</v>
       </c>
       <c r="B30" s="3">
         <v>28</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>57</v>
+      <c r="C30" s="11" t="s">
+        <v>13</v>
       </c>
       <c r="D30" s="5">
-        <v>8456726</v>
+        <v>7272828</v>
       </c>
       <c r="E30" s="6" t="str">
         <f>IF($D30="","",VLOOKUP($D30,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7158,17 +7032,17 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A31" s="3" t="s">
-        <v>88</v>
+      <c r="A31" s="24">
+        <v>46186</v>
       </c>
       <c r="B31" s="3">
         <v>29</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>60</v>
+      <c r="C31" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="D31" s="5">
-        <v>8220352</v>
+        <v>7236458</v>
       </c>
       <c r="E31" s="6" t="str">
         <f>IF($D31="","",VLOOKUP($D31,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7176,287 +7050,287 @@
       </c>
     </row>
     <row r="32" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A32" s="3" t="s">
-        <v>88</v>
+      <c r="A32" s="24">
+        <v>46186</v>
       </c>
       <c r="B32" s="3">
         <v>30</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>48</v>
+      <c r="C32" s="11" t="s">
+        <v>36</v>
       </c>
       <c r="D32" s="5">
-        <v>8154156</v>
+        <v>6986371</v>
       </c>
       <c r="E32" s="6" t="str">
         <f>IF($D32="","",VLOOKUP($D32,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>8단계</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A33" s="3" t="s">
-        <v>88</v>
+      <c r="A33" s="24">
+        <v>46186</v>
       </c>
       <c r="B33" s="3">
         <v>31</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>52</v>
+      <c r="C33" s="11" t="s">
+        <v>105</v>
       </c>
       <c r="D33" s="5">
-        <v>8127020</v>
+        <v>5884130</v>
       </c>
       <c r="E33" s="6" t="str">
         <f>IF($D33="","",VLOOKUP($D33,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>8단계</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A34" s="3" t="s">
-        <v>88</v>
+      <c r="A34" s="24">
+        <v>46186</v>
       </c>
       <c r="B34" s="3">
         <v>32</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>32</v>
+      <c r="C34" s="11" t="s">
+        <v>50</v>
       </c>
       <c r="D34" s="5">
-        <v>7952273</v>
+        <v>5813157</v>
       </c>
       <c r="E34" s="6" t="str">
         <f>IF($D34="","",VLOOKUP($D34,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>8단계</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A35" s="3" t="s">
-        <v>88</v>
+      <c r="A35" s="24">
+        <v>46186</v>
       </c>
       <c r="B35" s="3">
         <v>33</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>50</v>
+      <c r="C35" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="D35" s="5">
-        <v>7918857</v>
+        <v>5275134</v>
       </c>
       <c r="E35" s="6" t="str">
         <f>IF($D35="","",VLOOKUP($D35,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>8단계</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A36" s="3" t="s">
-        <v>88</v>
+      <c r="A36" s="24">
+        <v>46186</v>
       </c>
       <c r="B36" s="3">
         <v>34</v>
       </c>
-      <c r="C36" s="4" t="s">
-        <v>40</v>
+      <c r="C36" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="D36" s="5">
-        <v>7909501</v>
+        <v>4876688</v>
       </c>
       <c r="E36" s="6" t="str">
         <f>IF($D36="","",VLOOKUP($D36,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>8단계</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A37" s="3" t="s">
-        <v>88</v>
+      <c r="A37" s="24">
+        <v>46186</v>
       </c>
       <c r="B37" s="3">
         <v>35</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>58</v>
+      <c r="C37" s="11" t="s">
+        <v>74</v>
       </c>
       <c r="D37" s="5">
-        <v>7876636</v>
+        <v>4842063</v>
       </c>
       <c r="E37" s="6" t="str">
         <f>IF($D37="","",VLOOKUP($D37,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>8단계</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A38" s="3" t="s">
-        <v>88</v>
+      <c r="A38" s="24">
+        <v>46186</v>
       </c>
       <c r="B38" s="3">
         <v>36</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>55</v>
+      <c r="C38" s="11" t="s">
+        <v>47</v>
       </c>
       <c r="D38" s="5">
-        <v>7824653</v>
+        <v>4668195</v>
       </c>
       <c r="E38" s="6" t="str">
         <f>IF($D38="","",VLOOKUP($D38,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>8단계</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A39" s="3" t="s">
-        <v>88</v>
+      <c r="A39" s="24">
+        <v>46186</v>
       </c>
       <c r="B39" s="3">
         <v>37</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>33</v>
+      <c r="C39" s="11" t="s">
+        <v>60</v>
       </c>
       <c r="D39" s="5">
-        <v>7823884</v>
+        <v>4616477</v>
       </c>
       <c r="E39" s="6" t="str">
         <f>IF($D39="","",VLOOKUP($D39,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>8단계</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A40" s="3" t="s">
-        <v>88</v>
+      <c r="A40" s="24">
+        <v>46186</v>
       </c>
       <c r="B40" s="3">
         <v>38</v>
       </c>
-      <c r="C40" s="4" t="s">
-        <v>65</v>
+      <c r="C40" s="11" t="s">
+        <v>48</v>
       </c>
       <c r="D40" s="5">
-        <v>7679597</v>
+        <v>4498125</v>
       </c>
       <c r="E40" s="6" t="str">
         <f>IF($D40="","",VLOOKUP($D40,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>8단계</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A41" s="3" t="s">
-        <v>88</v>
+      <c r="A41" s="24">
+        <v>46186</v>
       </c>
       <c r="B41" s="3">
         <v>39</v>
       </c>
-      <c r="C41" s="4" t="s">
-        <v>44</v>
+      <c r="C41" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="D41" s="5">
-        <v>7635056</v>
+        <v>3687186</v>
       </c>
       <c r="E41" s="6" t="str">
         <f>IF($D41="","",VLOOKUP($D41,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>8단계</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A42" s="3" t="s">
-        <v>88</v>
+      <c r="A42" s="24">
+        <v>46186</v>
       </c>
       <c r="B42" s="3">
         <v>40</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>53</v>
+      <c r="C42" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="D42" s="5">
-        <v>7579677</v>
+        <v>3611227</v>
       </c>
       <c r="E42" s="6" t="str">
         <f>IF($D42="","",VLOOKUP($D42,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>8단계</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A43" s="3" t="s">
-        <v>88</v>
+      <c r="A43" s="24">
+        <v>46186</v>
       </c>
       <c r="B43" s="3">
         <v>41</v>
       </c>
-      <c r="C43" s="4" t="s">
-        <v>56</v>
+      <c r="C43" s="11" t="s">
+        <v>106</v>
       </c>
       <c r="D43" s="5">
-        <v>7552044</v>
+        <v>3189920</v>
       </c>
       <c r="E43" s="6" t="str">
         <f>IF($D43="","",VLOOKUP($D43,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>8단계</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A44" s="3" t="s">
-        <v>88</v>
+      <c r="A44" s="24">
+        <v>46186</v>
       </c>
       <c r="B44" s="3">
         <v>42</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>75</v>
+      <c r="C44" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="D44" s="5">
-        <v>7462230</v>
+        <v>3120139</v>
       </c>
       <c r="E44" s="6" t="str">
         <f>IF($D44="","",VLOOKUP($D44,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>8단계</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A45" s="3" t="s">
-        <v>88</v>
+      <c r="A45" s="24">
+        <v>46186</v>
       </c>
       <c r="B45" s="3">
         <v>43</v>
       </c>
-      <c r="C45" s="4" t="s">
-        <v>68</v>
+      <c r="C45" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="D45" s="5">
-        <v>7423633</v>
+        <v>3108728</v>
       </c>
       <c r="E45" s="6" t="str">
         <f>IF($D45="","",VLOOKUP($D45,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>8단계</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A46" s="3" t="s">
-        <v>88</v>
+      <c r="A46" s="24">
+        <v>46186</v>
       </c>
       <c r="B46" s="3">
         <v>44</v>
       </c>
-      <c r="C46" s="4" t="s">
-        <v>15</v>
+      <c r="C46" s="11" t="s">
+        <v>77</v>
       </c>
       <c r="D46" s="5">
-        <v>7327050</v>
+        <v>3077202</v>
       </c>
       <c r="E46" s="6" t="str">
         <f>IF($D46="","",VLOOKUP($D46,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>8단계</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A47" s="3" t="s">
-        <v>88</v>
+      <c r="A47" s="24">
+        <v>46186</v>
       </c>
       <c r="B47" s="3">
         <v>45</v>
       </c>
-      <c r="C47" s="4" t="s">
-        <v>38</v>
+      <c r="C47" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="D47" s="5">
-        <v>6678842</v>
+        <v>2968639</v>
       </c>
       <c r="E47" s="6" t="str">
         <f>IF($D47="","",VLOOKUP($D47,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7464,17 +7338,17 @@
       </c>
     </row>
     <row r="48" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A48" s="3" t="s">
-        <v>88</v>
+      <c r="A48" s="24">
+        <v>46186</v>
       </c>
       <c r="B48" s="3">
         <v>46</v>
       </c>
-      <c r="C48" s="4" t="s">
-        <v>51</v>
+      <c r="C48" s="11" t="s">
+        <v>108</v>
       </c>
       <c r="D48" s="5">
-        <v>6177989</v>
+        <v>2968603</v>
       </c>
       <c r="E48" s="6" t="str">
         <f>IF($D48="","",VLOOKUP($D48,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7482,17 +7356,17 @@
       </c>
     </row>
     <row r="49" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A49" s="3" t="s">
-        <v>88</v>
+      <c r="A49" s="24">
+        <v>46186</v>
       </c>
       <c r="B49" s="3">
         <v>47</v>
       </c>
-      <c r="C49" s="4" t="s">
-        <v>67</v>
+      <c r="C49" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="D49" s="5">
-        <v>5901298</v>
+        <v>2953979</v>
       </c>
       <c r="E49" s="6" t="str">
         <f>IF($D49="","",VLOOKUP($D49,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7500,17 +7374,17 @@
       </c>
     </row>
     <row r="50" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A50" s="3" t="s">
-        <v>88</v>
+      <c r="A50" s="24">
+        <v>46186</v>
       </c>
       <c r="B50" s="3">
         <v>48</v>
       </c>
-      <c r="C50" s="4" t="s">
-        <v>69</v>
+      <c r="C50" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="D50" s="5">
-        <v>5097585</v>
+        <v>2772649</v>
       </c>
       <c r="E50" s="6" t="str">
         <f>IF($D50="","",VLOOKUP($D50,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7518,17 +7392,17 @@
       </c>
     </row>
     <row r="51" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A51" s="3" t="s">
-        <v>88</v>
+      <c r="A51" s="24">
+        <v>46186</v>
       </c>
       <c r="B51" s="3">
         <v>49</v>
       </c>
-      <c r="C51" s="4" t="s">
-        <v>63</v>
+      <c r="C51" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="D51" s="5">
-        <v>5036088</v>
+        <v>2738331</v>
       </c>
       <c r="E51" s="6" t="str">
         <f>IF($D51="","",VLOOKUP($D51,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7536,327 +7410,327 @@
       </c>
     </row>
     <row r="52" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A52" s="3" t="s">
-        <v>88</v>
+      <c r="A52" s="24">
+        <v>46186</v>
       </c>
       <c r="B52" s="3">
         <v>50</v>
       </c>
-      <c r="C52" s="4" t="s">
-        <v>74</v>
+      <c r="C52" s="11" t="s">
+        <v>72</v>
       </c>
       <c r="D52" s="5">
-        <v>4821347</v>
+        <v>2460723</v>
       </c>
       <c r="E52" s="6" t="str">
         <f>IF($D52="","",VLOOKUP($D52,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>7단계</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A53" s="3" t="s">
-        <v>88</v>
+      <c r="A53" s="24">
+        <v>46186</v>
       </c>
       <c r="B53" s="3">
         <v>51</v>
       </c>
-      <c r="C53" s="4" t="s">
-        <v>64</v>
+      <c r="C53" s="11" t="s">
+        <v>67</v>
       </c>
       <c r="D53" s="5">
-        <v>4599953</v>
+        <v>2165388</v>
       </c>
       <c r="E53" s="6" t="str">
         <f>IF($D53="","",VLOOKUP($D53,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>6단계</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A54" s="3" t="s">
-        <v>88</v>
+      <c r="A54" s="24">
+        <v>46186</v>
       </c>
       <c r="B54" s="3">
         <v>52</v>
       </c>
-      <c r="C54" s="4" t="s">
-        <v>70</v>
+      <c r="C54" s="11" t="s">
+        <v>90</v>
       </c>
       <c r="D54" s="5">
-        <v>4332112</v>
+        <v>2028076</v>
       </c>
       <c r="E54" s="6" t="str">
         <f>IF($D54="","",VLOOKUP($D54,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>6단계</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A55" s="3" t="s">
-        <v>88</v>
+      <c r="A55" s="24">
+        <v>46186</v>
       </c>
       <c r="B55" s="3">
         <v>53</v>
       </c>
-      <c r="C55" s="4" t="s">
-        <v>76</v>
+      <c r="C55" s="11" t="s">
+        <v>110</v>
       </c>
       <c r="D55" s="5">
-        <v>4235009</v>
+        <v>1829852</v>
       </c>
       <c r="E55" s="6" t="str">
         <f>IF($D55="","",VLOOKUP($D55,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>6단계</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A56" s="3" t="s">
-        <v>88</v>
+      <c r="A56" s="24">
+        <v>46186</v>
       </c>
       <c r="B56" s="3">
         <v>54</v>
       </c>
-      <c r="C56" s="4" t="s">
-        <v>66</v>
+      <c r="C56" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="D56" s="5">
-        <v>4226803</v>
+        <v>1765395</v>
       </c>
       <c r="E56" s="6" t="str">
         <f>IF($D56="","",VLOOKUP($D56,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>6단계</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A57" s="3" t="s">
-        <v>88</v>
+      <c r="A57" s="24">
+        <v>46186</v>
       </c>
       <c r="B57" s="3">
         <v>55</v>
       </c>
-      <c r="C57" s="4" t="s">
-        <v>72</v>
+      <c r="C57" s="11" t="s">
+        <v>81</v>
       </c>
       <c r="D57" s="5">
-        <v>3992666</v>
+        <v>1693947</v>
       </c>
       <c r="E57" s="6" t="str">
         <f>IF($D57="","",VLOOKUP($D57,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>6단계</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A58" s="3" t="s">
-        <v>88</v>
+      <c r="A58" s="24">
+        <v>46186</v>
       </c>
       <c r="B58" s="3">
         <v>56</v>
       </c>
-      <c r="C58" s="4" t="s">
-        <v>80</v>
+      <c r="C58" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="D58" s="5">
-        <v>3935236</v>
+        <v>1288077</v>
       </c>
       <c r="E58" s="6" t="str">
         <f>IF($D58="","",VLOOKUP($D58,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>6단계</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A59" s="3" t="s">
-        <v>88</v>
+      <c r="A59" s="24">
+        <v>46186</v>
       </c>
       <c r="B59" s="3">
         <v>57</v>
       </c>
-      <c r="C59" s="4" t="s">
-        <v>77</v>
+      <c r="C59" s="11" t="s">
+        <v>66</v>
       </c>
       <c r="D59" s="5">
-        <v>3819189</v>
+        <v>1207196</v>
       </c>
       <c r="E59" s="6" t="str">
         <f>IF($D59="","",VLOOKUP($D59,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>6단계</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A60" s="3" t="s">
-        <v>88</v>
+      <c r="A60" s="24">
+        <v>46186</v>
       </c>
       <c r="B60" s="3">
         <v>58</v>
       </c>
-      <c r="C60" s="4" t="s">
-        <v>83</v>
+      <c r="C60" s="11" t="s">
+        <v>84</v>
       </c>
       <c r="D60" s="5">
-        <v>2896389</v>
+        <v>963718</v>
       </c>
       <c r="E60" s="6" t="str">
         <f>IF($D60="","",VLOOKUP($D60,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>5단계</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A61" s="3" t="s">
-        <v>88</v>
+      <c r="A61" s="24">
+        <v>46186</v>
       </c>
       <c r="B61" s="3">
         <v>59</v>
       </c>
-      <c r="C61" s="4" t="s">
-        <v>73</v>
+      <c r="C61" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="D61" s="5">
-        <v>2645896</v>
+        <v>700489</v>
       </c>
       <c r="E61" s="6" t="str">
         <f>IF($D61="","",VLOOKUP($D61,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>5단계</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A62" s="3" t="s">
-        <v>88</v>
+      <c r="A62" s="24">
+        <v>46186</v>
       </c>
       <c r="B62" s="3">
         <v>60</v>
       </c>
-      <c r="C62" s="8" t="s">
-        <v>84</v>
+      <c r="C62" s="11" t="s">
+        <v>76</v>
       </c>
       <c r="D62" s="5">
-        <v>2195612</v>
+        <v>659256</v>
       </c>
       <c r="E62" s="6" t="str">
         <f>IF($D62="","",VLOOKUP($D62,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
+        <v>5단계</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A63" s="3" t="s">
-        <v>88</v>
+      <c r="A63" s="24">
+        <v>46186</v>
       </c>
       <c r="B63" s="3">
         <v>61</v>
       </c>
-      <c r="C63" s="4" t="s">
-        <v>71</v>
+      <c r="C63" s="11" t="s">
+        <v>85</v>
       </c>
       <c r="D63" s="5">
-        <v>1908787</v>
+        <v>384395</v>
       </c>
       <c r="E63" s="6" t="str">
         <f>IF($D63="","",VLOOKUP($D63,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
+        <v>3단계</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A64" s="3" t="s">
-        <v>88</v>
+      <c r="A64" s="24">
+        <v>46186</v>
       </c>
       <c r="B64" s="3">
         <v>62</v>
       </c>
-      <c r="C64" s="4" t="s">
-        <v>82</v>
+      <c r="C64" s="11" t="s">
+        <v>112</v>
       </c>
       <c r="D64" s="5">
-        <v>1890847</v>
+        <v>327964</v>
       </c>
       <c r="E64" s="6" t="str">
         <f>IF($D64="","",VLOOKUP($D64,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
+        <v>3단계</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A65" s="3" t="s">
-        <v>88</v>
+      <c r="A65" s="24">
+        <v>46186</v>
       </c>
       <c r="B65" s="3">
         <v>63</v>
       </c>
-      <c r="C65" s="4" t="s">
-        <v>78</v>
+      <c r="C65" s="11" t="s">
+        <v>86</v>
       </c>
       <c r="D65" s="5">
-        <v>1772463</v>
+        <v>266932</v>
       </c>
       <c r="E65" s="6" t="str">
         <f>IF($D65="","",VLOOKUP($D65,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
+        <v>3단계</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A66" s="3" t="s">
-        <v>88</v>
+      <c r="A66" s="24">
+        <v>46186</v>
       </c>
       <c r="B66" s="3">
         <v>64</v>
       </c>
-      <c r="C66" s="4" t="s">
-        <v>79</v>
+      <c r="C66" s="11" t="s">
+        <v>113</v>
       </c>
       <c r="D66" s="5">
-        <v>1472500</v>
+        <v>89508</v>
       </c>
       <c r="E66" s="6" t="str">
         <f>IF($D66="","",VLOOKUP($D66,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
+        <v>2단계</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="16.5" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="B67" s="3">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="D67" s="5">
-        <v>1425274</v>
+        <v>76513151</v>
       </c>
       <c r="E67" s="6" t="str">
         <f>IF($D67="","",VLOOKUP($D67,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
+        <v>9단계</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="16.5" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="B68" s="3">
-        <v>66</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>86</v>
+        <v>2</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="D68" s="5">
-        <v>1226829</v>
+        <v>62254586</v>
       </c>
       <c r="E68" s="6" t="str">
         <f>IF($D68="","",VLOOKUP($D68,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
+        <v>9단계</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="16.5" customHeight="1">
       <c r="A69" s="3" t="s">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="B69" s="3">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="D69" s="5">
-        <v>460000</v>
+        <v>36598969</v>
       </c>
       <c r="E69" s="6" t="str">
         <f>IF($D69="","",VLOOKUP($D69,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>3단계</v>
+        <v>9단계</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="16.5" customHeight="1">
@@ -7864,13 +7738,13 @@
         <v>1</v>
       </c>
       <c r="B70" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D70" s="5">
-        <v>76513151</v>
+        <v>26859795</v>
       </c>
       <c r="E70" s="6" t="str">
         <f>IF($D70="","",VLOOKUP($D70,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7882,13 +7756,13 @@
         <v>1</v>
       </c>
       <c r="B71" s="3">
-        <v>2</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>34</v>
+        <v>5</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="D71" s="5">
-        <v>62254586</v>
+        <v>22027625</v>
       </c>
       <c r="E71" s="6" t="str">
         <f>IF($D71="","",VLOOKUP($D71,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7900,13 +7774,13 @@
         <v>1</v>
       </c>
       <c r="B72" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D72" s="5">
-        <v>36598969</v>
+        <v>19336746</v>
       </c>
       <c r="E72" s="6" t="str">
         <f>IF($D72="","",VLOOKUP($D72,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7918,13 +7792,13 @@
         <v>1</v>
       </c>
       <c r="B73" s="3">
-        <v>4</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>54</v>
+        <v>7</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="D73" s="5">
-        <v>26859795</v>
+        <v>17008882</v>
       </c>
       <c r="E73" s="6" t="str">
         <f>IF($D73="","",VLOOKUP($D73,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7936,13 +7810,13 @@
         <v>1</v>
       </c>
       <c r="B74" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="D74" s="5">
-        <v>22027625</v>
+        <v>16620269</v>
       </c>
       <c r="E74" s="6" t="str">
         <f>IF($D74="","",VLOOKUP($D74,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7954,13 +7828,13 @@
         <v>1</v>
       </c>
       <c r="B75" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D75" s="5">
-        <v>19336746</v>
+        <v>15971399</v>
       </c>
       <c r="E75" s="6" t="str">
         <f>IF($D75="","",VLOOKUP($D75,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7972,13 +7846,13 @@
         <v>1</v>
       </c>
       <c r="B76" s="3">
-        <v>7</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>21</v>
+        <v>10</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="D76" s="5">
-        <v>17008882</v>
+        <v>15579579</v>
       </c>
       <c r="E76" s="6" t="str">
         <f>IF($D76="","",VLOOKUP($D76,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7990,13 +7864,13 @@
         <v>1</v>
       </c>
       <c r="B77" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="D77" s="5">
-        <v>16620269</v>
+        <v>15166835</v>
       </c>
       <c r="E77" s="6" t="str">
         <f>IF($D77="","",VLOOKUP($D77,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8008,13 +7882,13 @@
         <v>1</v>
       </c>
       <c r="B78" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="D78" s="5">
-        <v>15971399</v>
+        <v>15136017</v>
       </c>
       <c r="E78" s="6" t="str">
         <f>IF($D78="","",VLOOKUP($D78,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8026,13 +7900,13 @@
         <v>1</v>
       </c>
       <c r="B79" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D79" s="5">
-        <v>15579579</v>
+        <v>15045625</v>
       </c>
       <c r="E79" s="6" t="str">
         <f>IF($D79="","",VLOOKUP($D79,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8044,13 +7918,13 @@
         <v>1</v>
       </c>
       <c r="B80" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D80" s="5">
-        <v>15166835</v>
+        <v>11929975</v>
       </c>
       <c r="E80" s="6" t="str">
         <f>IF($D80="","",VLOOKUP($D80,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8062,13 +7936,13 @@
         <v>1</v>
       </c>
       <c r="B81" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D81" s="5">
-        <v>15136017</v>
+        <v>11703867</v>
       </c>
       <c r="E81" s="6" t="str">
         <f>IF($D81="","",VLOOKUP($D81,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8080,13 +7954,13 @@
         <v>1</v>
       </c>
       <c r="B82" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D82" s="5">
-        <v>15045625</v>
+        <v>11641804</v>
       </c>
       <c r="E82" s="6" t="str">
         <f>IF($D82="","",VLOOKUP($D82,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8098,13 +7972,13 @@
         <v>1</v>
       </c>
       <c r="B83" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D83" s="5">
-        <v>11929975</v>
+        <v>11224132</v>
       </c>
       <c r="E83" s="6" t="str">
         <f>IF($D83="","",VLOOKUP($D83,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8116,13 +7990,13 @@
         <v>1</v>
       </c>
       <c r="B84" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D84" s="5">
-        <v>11703867</v>
+        <v>11128193</v>
       </c>
       <c r="E84" s="6" t="str">
         <f>IF($D84="","",VLOOKUP($D84,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8134,13 +8008,13 @@
         <v>1</v>
       </c>
       <c r="B85" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D85" s="5">
-        <v>11641804</v>
+        <v>10907771</v>
       </c>
       <c r="E85" s="6" t="str">
         <f>IF($D85="","",VLOOKUP($D85,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8152,13 +8026,13 @@
         <v>1</v>
       </c>
       <c r="B86" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="D86" s="5">
-        <v>11224132</v>
+        <v>10606882</v>
       </c>
       <c r="E86" s="6" t="str">
         <f>IF($D86="","",VLOOKUP($D86,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8170,13 +8044,13 @@
         <v>1</v>
       </c>
       <c r="B87" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D87" s="5">
-        <v>11128193</v>
+        <v>10422796</v>
       </c>
       <c r="E87" s="6" t="str">
         <f>IF($D87="","",VLOOKUP($D87,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8188,13 +8062,13 @@
         <v>1</v>
       </c>
       <c r="B88" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D88" s="5">
-        <v>10907771</v>
+        <v>10412768</v>
       </c>
       <c r="E88" s="6" t="str">
         <f>IF($D88="","",VLOOKUP($D88,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8206,13 +8080,13 @@
         <v>1</v>
       </c>
       <c r="B89" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="D89" s="5">
-        <v>10606882</v>
+        <v>10128124</v>
       </c>
       <c r="E89" s="6" t="str">
         <f>IF($D89="","",VLOOKUP($D89,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8224,13 +8098,13 @@
         <v>1</v>
       </c>
       <c r="B90" s="3">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D90" s="5">
-        <v>10422796</v>
+        <v>9706739</v>
       </c>
       <c r="E90" s="6" t="str">
         <f>IF($D90="","",VLOOKUP($D90,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8242,13 +8116,13 @@
         <v>1</v>
       </c>
       <c r="B91" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D91" s="5">
-        <v>10412768</v>
+        <v>9164119</v>
       </c>
       <c r="E91" s="6" t="str">
         <f>IF($D91="","",VLOOKUP($D91,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8260,13 +8134,13 @@
         <v>1</v>
       </c>
       <c r="B92" s="3">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D92" s="5">
-        <v>10128124</v>
+        <v>8999382</v>
       </c>
       <c r="E92" s="6" t="str">
         <f>IF($D92="","",VLOOKUP($D92,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8278,13 +8152,13 @@
         <v>1</v>
       </c>
       <c r="B93" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D93" s="5">
-        <v>9706739</v>
+        <v>8596217</v>
       </c>
       <c r="E93" s="6" t="str">
         <f>IF($D93="","",VLOOKUP($D93,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8296,13 +8170,13 @@
         <v>1</v>
       </c>
       <c r="B94" s="3">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D94" s="5">
-        <v>9164119</v>
+        <v>8456726</v>
       </c>
       <c r="E94" s="6" t="str">
         <f>IF($D94="","",VLOOKUP($D94,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8314,13 +8188,13 @@
         <v>1</v>
       </c>
       <c r="B95" s="3">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="D95" s="5">
-        <v>8999382</v>
+        <v>8220352</v>
       </c>
       <c r="E95" s="6" t="str">
         <f>IF($D95="","",VLOOKUP($D95,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8332,13 +8206,13 @@
         <v>1</v>
       </c>
       <c r="B96" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="D96" s="5">
-        <v>8596217</v>
+        <v>8154156</v>
       </c>
       <c r="E96" s="6" t="str">
         <f>IF($D96="","",VLOOKUP($D96,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8350,13 +8224,13 @@
         <v>1</v>
       </c>
       <c r="B97" s="3">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D97" s="5">
-        <v>8456726</v>
+        <v>8127020</v>
       </c>
       <c r="E97" s="6" t="str">
         <f>IF($D97="","",VLOOKUP($D97,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8368,13 +8242,13 @@
         <v>1</v>
       </c>
       <c r="B98" s="3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D98" s="5">
-        <v>8220352</v>
+        <v>7952273</v>
       </c>
       <c r="E98" s="6" t="str">
         <f>IF($D98="","",VLOOKUP($D98,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8386,13 +8260,13 @@
         <v>1</v>
       </c>
       <c r="B99" s="3">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D99" s="5">
-        <v>8154156</v>
+        <v>7918857</v>
       </c>
       <c r="E99" s="6" t="str">
         <f>IF($D99="","",VLOOKUP($D99,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8404,13 +8278,13 @@
         <v>1</v>
       </c>
       <c r="B100" s="3">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D100" s="5">
-        <v>8127020</v>
+        <v>7909501</v>
       </c>
       <c r="E100" s="6" t="str">
         <f>IF($D100="","",VLOOKUP($D100,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8422,13 +8296,13 @@
         <v>1</v>
       </c>
       <c r="B101" s="3">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D101" s="5">
-        <v>7952273</v>
+        <v>7876636</v>
       </c>
       <c r="E101" s="6" t="str">
         <f>IF($D101="","",VLOOKUP($D101,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8440,13 +8314,13 @@
         <v>1</v>
       </c>
       <c r="B102" s="3">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D102" s="5">
-        <v>7918857</v>
+        <v>7824653</v>
       </c>
       <c r="E102" s="6" t="str">
         <f>IF($D102="","",VLOOKUP($D102,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8458,13 +8332,13 @@
         <v>1</v>
       </c>
       <c r="B103" s="3">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D103" s="5">
-        <v>7909501</v>
+        <v>7823884</v>
       </c>
       <c r="E103" s="6" t="str">
         <f>IF($D103="","",VLOOKUP($D103,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8476,13 +8350,13 @@
         <v>1</v>
       </c>
       <c r="B104" s="3">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D104" s="5">
-        <v>7876636</v>
+        <v>7679597</v>
       </c>
       <c r="E104" s="6" t="str">
         <f>IF($D104="","",VLOOKUP($D104,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8494,13 +8368,13 @@
         <v>1</v>
       </c>
       <c r="B105" s="3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D105" s="5">
-        <v>7824653</v>
+        <v>7635056</v>
       </c>
       <c r="E105" s="6" t="str">
         <f>IF($D105="","",VLOOKUP($D105,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8512,13 +8386,13 @@
         <v>1</v>
       </c>
       <c r="B106" s="3">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D106" s="5">
-        <v>7823884</v>
+        <v>7579677</v>
       </c>
       <c r="E106" s="6" t="str">
         <f>IF($D106="","",VLOOKUP($D106,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8530,13 +8404,13 @@
         <v>1</v>
       </c>
       <c r="B107" s="3">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D107" s="5">
-        <v>7679597</v>
+        <v>7552044</v>
       </c>
       <c r="E107" s="6" t="str">
         <f>IF($D107="","",VLOOKUP($D107,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8548,13 +8422,13 @@
         <v>1</v>
       </c>
       <c r="B108" s="3">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="D108" s="5">
-        <v>7635056</v>
+        <v>7462230</v>
       </c>
       <c r="E108" s="6" t="str">
         <f>IF($D108="","",VLOOKUP($D108,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8566,13 +8440,13 @@
         <v>1</v>
       </c>
       <c r="B109" s="3">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D109" s="5">
-        <v>7579677</v>
+        <v>7423633</v>
       </c>
       <c r="E109" s="6" t="str">
         <f>IF($D109="","",VLOOKUP($D109,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8584,13 +8458,13 @@
         <v>1</v>
       </c>
       <c r="B110" s="3">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D110" s="5">
-        <v>7552044</v>
+        <v>7327050</v>
       </c>
       <c r="E110" s="6" t="str">
         <f>IF($D110="","",VLOOKUP($D110,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8602,17 +8476,17 @@
         <v>1</v>
       </c>
       <c r="B111" s="3">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D111" s="5">
-        <v>7462230</v>
+        <v>6678842</v>
       </c>
       <c r="E111" s="6" t="str">
         <f>IF($D111="","",VLOOKUP($D111,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>8단계</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="16.5" customHeight="1">
@@ -8620,17 +8494,17 @@
         <v>1</v>
       </c>
       <c r="B112" s="3">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D112" s="5">
-        <v>7423633</v>
+        <v>6177989</v>
       </c>
       <c r="E112" s="6" t="str">
         <f>IF($D112="","",VLOOKUP($D112,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>8단계</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="16.5" customHeight="1">
@@ -8638,17 +8512,17 @@
         <v>1</v>
       </c>
       <c r="B113" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="D113" s="5">
-        <v>7327050</v>
+        <v>5901298</v>
       </c>
       <c r="E113" s="6" t="str">
         <f>IF($D113="","",VLOOKUP($D113,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>8단계</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="16.5" customHeight="1">
@@ -8656,13 +8530,13 @@
         <v>1</v>
       </c>
       <c r="B114" s="3">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D114" s="5">
-        <v>6678842</v>
+        <v>5097585</v>
       </c>
       <c r="E114" s="6" t="str">
         <f>IF($D114="","",VLOOKUP($D114,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8674,13 +8548,13 @@
         <v>1</v>
       </c>
       <c r="B115" s="3">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="D115" s="5">
-        <v>6177989</v>
+        <v>5036088</v>
       </c>
       <c r="E115" s="6" t="str">
         <f>IF($D115="","",VLOOKUP($D115,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8692,13 +8566,13 @@
         <v>1</v>
       </c>
       <c r="B116" s="3">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D116" s="5">
-        <v>5901298</v>
+        <v>4821347</v>
       </c>
       <c r="E116" s="6" t="str">
         <f>IF($D116="","",VLOOKUP($D116,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8710,13 +8584,13 @@
         <v>1</v>
       </c>
       <c r="B117" s="3">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D117" s="5">
-        <v>5097585</v>
+        <v>4599953</v>
       </c>
       <c r="E117" s="6" t="str">
         <f>IF($D117="","",VLOOKUP($D117,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8728,13 +8602,13 @@
         <v>1</v>
       </c>
       <c r="B118" s="3">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D118" s="5">
-        <v>5036088</v>
+        <v>4332112</v>
       </c>
       <c r="E118" s="6" t="str">
         <f>IF($D118="","",VLOOKUP($D118,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8746,13 +8620,13 @@
         <v>1</v>
       </c>
       <c r="B119" s="3">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D119" s="5">
-        <v>4821347</v>
+        <v>4235009</v>
       </c>
       <c r="E119" s="6" t="str">
         <f>IF($D119="","",VLOOKUP($D119,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8764,13 +8638,13 @@
         <v>1</v>
       </c>
       <c r="B120" s="3">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D120" s="5">
-        <v>4599953</v>
+        <v>4226803</v>
       </c>
       <c r="E120" s="6" t="str">
         <f>IF($D120="","",VLOOKUP($D120,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8782,13 +8656,13 @@
         <v>1</v>
       </c>
       <c r="B121" s="3">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D121" s="5">
-        <v>4332112</v>
+        <v>3992666</v>
       </c>
       <c r="E121" s="6" t="str">
         <f>IF($D121="","",VLOOKUP($D121,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8800,13 +8674,13 @@
         <v>1</v>
       </c>
       <c r="B122" s="3">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D122" s="5">
-        <v>4235009</v>
+        <v>3935236</v>
       </c>
       <c r="E122" s="6" t="str">
         <f>IF($D122="","",VLOOKUP($D122,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8818,13 +8692,13 @@
         <v>1</v>
       </c>
       <c r="B123" s="3">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="D123" s="5">
-        <v>4226803</v>
+        <v>3819189</v>
       </c>
       <c r="E123" s="6" t="str">
         <f>IF($D123="","",VLOOKUP($D123,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8836,13 +8710,13 @@
         <v>1</v>
       </c>
       <c r="B124" s="3">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D124" s="5">
-        <v>3992666</v>
+        <v>2896389</v>
       </c>
       <c r="E124" s="6" t="str">
         <f>IF($D124="","",VLOOKUP($D124,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8854,13 +8728,13 @@
         <v>1</v>
       </c>
       <c r="B125" s="3">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D125" s="5">
-        <v>3935236</v>
+        <v>2645896</v>
       </c>
       <c r="E125" s="6" t="str">
         <f>IF($D125="","",VLOOKUP($D125,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8872,17 +8746,17 @@
         <v>1</v>
       </c>
       <c r="B126" s="3">
-        <v>57</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>77</v>
+        <v>60</v>
+      </c>
+      <c r="C126" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="D126" s="5">
-        <v>3819189</v>
+        <v>2195612</v>
       </c>
       <c r="E126" s="6" t="str">
         <f>IF($D126="","",VLOOKUP($D126,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>6단계</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="16.5" customHeight="1">
@@ -8890,17 +8764,17 @@
         <v>1</v>
       </c>
       <c r="B127" s="3">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D127" s="5">
-        <v>2896389</v>
+        <v>1908787</v>
       </c>
       <c r="E127" s="6" t="str">
         <f>IF($D127="","",VLOOKUP($D127,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>6단계</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="16.5" customHeight="1">
@@ -8908,17 +8782,17 @@
         <v>1</v>
       </c>
       <c r="B128" s="3">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D128" s="5">
-        <v>2645896</v>
+        <v>1890847</v>
       </c>
       <c r="E128" s="6" t="str">
         <f>IF($D128="","",VLOOKUP($D128,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>6단계</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="16.5" customHeight="1">
@@ -8926,13 +8800,13 @@
         <v>1</v>
       </c>
       <c r="B129" s="3">
-        <v>60</v>
-      </c>
-      <c r="C129" s="8" t="s">
-        <v>84</v>
+        <v>63</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="D129" s="5">
-        <v>2195612</v>
+        <v>1772463</v>
       </c>
       <c r="E129" s="6" t="str">
         <f>IF($D129="","",VLOOKUP($D129,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8944,13 +8818,13 @@
         <v>1</v>
       </c>
       <c r="B130" s="3">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D130" s="5">
-        <v>1908787</v>
+        <v>1472500</v>
       </c>
       <c r="E130" s="6" t="str">
         <f>IF($D130="","",VLOOKUP($D130,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8962,13 +8836,13 @@
         <v>1</v>
       </c>
       <c r="B131" s="3">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D131" s="5">
-        <v>1890847</v>
+        <v>1425274</v>
       </c>
       <c r="E131" s="6" t="str">
         <f>IF($D131="","",VLOOKUP($D131,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8980,13 +8854,13 @@
         <v>1</v>
       </c>
       <c r="B132" s="3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D132" s="5">
-        <v>1772463</v>
+        <v>1226829</v>
       </c>
       <c r="E132" s="6" t="str">
         <f>IF($D132="","",VLOOKUP($D132,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8998,70 +8872,1222 @@
         <v>1</v>
       </c>
       <c r="B133" s="3">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D133" s="5">
-        <v>1472500</v>
+        <v>460000</v>
       </c>
       <c r="E133" s="6" t="str">
         <f>IF($D133="","",VLOOKUP($D133,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
+        <v>3단계</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="16.5" customHeight="1">
       <c r="A134" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B134" s="3">
         <v>1</v>
       </c>
-      <c r="B134" s="3">
-        <v>65</v>
-      </c>
       <c r="C134" s="4" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="D134" s="5">
-        <v>1425274</v>
+        <v>76513151</v>
       </c>
       <c r="E134" s="6" t="str">
         <f>IF($D134="","",VLOOKUP($D134,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
+        <v>9단계</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="16.5" customHeight="1">
       <c r="A135" s="3" t="s">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="B135" s="3">
-        <v>66</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>86</v>
+        <v>2</v>
+      </c>
+      <c r="C135" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="D135" s="5">
-        <v>1226829</v>
+        <v>62254586</v>
       </c>
       <c r="E135" s="6" t="str">
         <f>IF($D135="","",VLOOKUP($D135,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
+        <v>9단계</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="16.5" customHeight="1">
       <c r="A136" s="3" t="s">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="B136" s="3">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="D136" s="5">
-        <v>460000</v>
+        <v>36598969</v>
       </c>
       <c r="E136" s="6" t="str">
         <f>IF($D136="","",VLOOKUP($D136,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="16.5">
+      <c r="A137" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B137" s="3">
+        <v>4</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D137" s="5">
+        <v>26859795</v>
+      </c>
+      <c r="E137" s="6" t="str">
+        <f>IF($D137="","",VLOOKUP($D137,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="16.5">
+      <c r="A138" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B138" s="3">
+        <v>5</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D138" s="5">
+        <v>22027625</v>
+      </c>
+      <c r="E138" s="6" t="str">
+        <f>IF($D138="","",VLOOKUP($D138,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="16.5">
+      <c r="A139" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B139" s="3">
+        <v>6</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D139" s="5">
+        <v>19336746</v>
+      </c>
+      <c r="E139" s="6" t="str">
+        <f>IF($D139="","",VLOOKUP($D139,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="16.5">
+      <c r="A140" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B140" s="3">
+        <v>7</v>
+      </c>
+      <c r="C140" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D140" s="5">
+        <v>17008882</v>
+      </c>
+      <c r="E140" s="6" t="str">
+        <f>IF($D140="","",VLOOKUP($D140,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="16.5">
+      <c r="A141" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B141" s="3">
+        <v>8</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D141" s="5">
+        <v>16620269</v>
+      </c>
+      <c r="E141" s="6" t="str">
+        <f>IF($D141="","",VLOOKUP($D141,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="16.5">
+      <c r="A142" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B142" s="3">
+        <v>9</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D142" s="5">
+        <v>15971399</v>
+      </c>
+      <c r="E142" s="6" t="str">
+        <f>IF($D142="","",VLOOKUP($D142,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="16.5">
+      <c r="A143" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B143" s="3">
+        <v>10</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D143" s="5">
+        <v>15579579</v>
+      </c>
+      <c r="E143" s="6" t="str">
+        <f>IF($D143="","",VLOOKUP($D143,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="16.5">
+      <c r="A144" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B144" s="3">
+        <v>11</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D144" s="5">
+        <v>15166835</v>
+      </c>
+      <c r="E144" s="6" t="str">
+        <f>IF($D144="","",VLOOKUP($D144,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" ht="16.5">
+      <c r="A145" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B145" s="3">
+        <v>12</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D145" s="5">
+        <v>15136017</v>
+      </c>
+      <c r="E145" s="6" t="str">
+        <f>IF($D145="","",VLOOKUP($D145,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" ht="16.5">
+      <c r="A146" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B146" s="3">
+        <v>13</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D146" s="5">
+        <v>15045625</v>
+      </c>
+      <c r="E146" s="6" t="str">
+        <f>IF($D146="","",VLOOKUP($D146,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" ht="16.5">
+      <c r="A147" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B147" s="3">
+        <v>14</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D147" s="5">
+        <v>11929975</v>
+      </c>
+      <c r="E147" s="6" t="str">
+        <f>IF($D147="","",VLOOKUP($D147,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="16.5">
+      <c r="A148" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B148" s="3">
+        <v>15</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D148" s="5">
+        <v>11703867</v>
+      </c>
+      <c r="E148" s="6" t="str">
+        <f>IF($D148="","",VLOOKUP($D148,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="16.5">
+      <c r="A149" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B149" s="3">
+        <v>16</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D149" s="5">
+        <v>11641804</v>
+      </c>
+      <c r="E149" s="6" t="str">
+        <f>IF($D149="","",VLOOKUP($D149,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" ht="16.5">
+      <c r="A150" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B150" s="3">
+        <v>17</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D150" s="5">
+        <v>11224132</v>
+      </c>
+      <c r="E150" s="6" t="str">
+        <f>IF($D150="","",VLOOKUP($D150,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="16.5">
+      <c r="A151" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B151" s="3">
+        <v>18</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D151" s="5">
+        <v>11128193</v>
+      </c>
+      <c r="E151" s="6" t="str">
+        <f>IF($D151="","",VLOOKUP($D151,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" ht="16.5">
+      <c r="A152" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B152" s="3">
+        <v>19</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D152" s="5">
+        <v>10907771</v>
+      </c>
+      <c r="E152" s="6" t="str">
+        <f>IF($D152="","",VLOOKUP($D152,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" ht="16.5">
+      <c r="A153" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B153" s="3">
+        <v>20</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D153" s="5">
+        <v>10606882</v>
+      </c>
+      <c r="E153" s="6" t="str">
+        <f>IF($D153="","",VLOOKUP($D153,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" ht="16.5">
+      <c r="A154" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B154" s="3">
+        <v>21</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D154" s="5">
+        <v>10422796</v>
+      </c>
+      <c r="E154" s="6" t="str">
+        <f>IF($D154="","",VLOOKUP($D154,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" ht="16.5">
+      <c r="A155" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B155" s="3">
+        <v>22</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D155" s="5">
+        <v>10412768</v>
+      </c>
+      <c r="E155" s="6" t="str">
+        <f>IF($D155="","",VLOOKUP($D155,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" ht="16.5">
+      <c r="A156" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B156" s="3">
+        <v>23</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D156" s="5">
+        <v>10128124</v>
+      </c>
+      <c r="E156" s="6" t="str">
+        <f>IF($D156="","",VLOOKUP($D156,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" ht="16.5">
+      <c r="A157" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B157" s="3">
+        <v>24</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D157" s="5">
+        <v>9706739</v>
+      </c>
+      <c r="E157" s="6" t="str">
+        <f>IF($D157="","",VLOOKUP($D157,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" ht="16.5">
+      <c r="A158" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B158" s="3">
+        <v>25</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D158" s="5">
+        <v>9164119</v>
+      </c>
+      <c r="E158" s="6" t="str">
+        <f>IF($D158="","",VLOOKUP($D158,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" ht="16.5">
+      <c r="A159" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B159" s="3">
+        <v>26</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D159" s="5">
+        <v>8999382</v>
+      </c>
+      <c r="E159" s="6" t="str">
+        <f>IF($D159="","",VLOOKUP($D159,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" ht="16.5">
+      <c r="A160" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B160" s="3">
+        <v>27</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D160" s="5">
+        <v>8596217</v>
+      </c>
+      <c r="E160" s="6" t="str">
+        <f>IF($D160="","",VLOOKUP($D160,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" ht="16.5">
+      <c r="A161" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B161" s="3">
+        <v>28</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D161" s="5">
+        <v>8456726</v>
+      </c>
+      <c r="E161" s="6" t="str">
+        <f>IF($D161="","",VLOOKUP($D161,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" ht="16.5">
+      <c r="A162" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B162" s="3">
+        <v>29</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D162" s="5">
+        <v>8220352</v>
+      </c>
+      <c r="E162" s="6" t="str">
+        <f>IF($D162="","",VLOOKUP($D162,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" ht="16.5">
+      <c r="A163" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B163" s="3">
+        <v>30</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D163" s="5">
+        <v>8154156</v>
+      </c>
+      <c r="E163" s="6" t="str">
+        <f>IF($D163="","",VLOOKUP($D163,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" ht="16.5">
+      <c r="A164" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B164" s="3">
+        <v>31</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D164" s="5">
+        <v>8127020</v>
+      </c>
+      <c r="E164" s="6" t="str">
+        <f>IF($D164="","",VLOOKUP($D164,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="16.5">
+      <c r="A165" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B165" s="3">
+        <v>32</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D165" s="5">
+        <v>7952273</v>
+      </c>
+      <c r="E165" s="6" t="str">
+        <f>IF($D165="","",VLOOKUP($D165,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" ht="16.5">
+      <c r="A166" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B166" s="3">
+        <v>33</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D166" s="5">
+        <v>7918857</v>
+      </c>
+      <c r="E166" s="6" t="str">
+        <f>IF($D166="","",VLOOKUP($D166,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" ht="16.5">
+      <c r="A167" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B167" s="3">
+        <v>34</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D167" s="5">
+        <v>7909501</v>
+      </c>
+      <c r="E167" s="6" t="str">
+        <f>IF($D167="","",VLOOKUP($D167,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" ht="16.5">
+      <c r="A168" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B168" s="3">
+        <v>35</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D168" s="5">
+        <v>7876636</v>
+      </c>
+      <c r="E168" s="6" t="str">
+        <f>IF($D168="","",VLOOKUP($D168,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="16.5">
+      <c r="A169" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B169" s="3">
+        <v>36</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D169" s="5">
+        <v>7824653</v>
+      </c>
+      <c r="E169" s="6" t="str">
+        <f>IF($D169="","",VLOOKUP($D169,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" ht="16.5">
+      <c r="A170" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B170" s="3">
+        <v>37</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D170" s="5">
+        <v>7823884</v>
+      </c>
+      <c r="E170" s="6" t="str">
+        <f>IF($D170="","",VLOOKUP($D170,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" ht="16.5">
+      <c r="A171" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B171" s="3">
+        <v>38</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D171" s="5">
+        <v>7679597</v>
+      </c>
+      <c r="E171" s="6" t="str">
+        <f>IF($D171="","",VLOOKUP($D171,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" ht="16.5">
+      <c r="A172" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B172" s="3">
+        <v>39</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D172" s="5">
+        <v>7635056</v>
+      </c>
+      <c r="E172" s="6" t="str">
+        <f>IF($D172="","",VLOOKUP($D172,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="16.5">
+      <c r="A173" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B173" s="3">
+        <v>40</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D173" s="5">
+        <v>7579677</v>
+      </c>
+      <c r="E173" s="6" t="str">
+        <f>IF($D173="","",VLOOKUP($D173,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" ht="16.5">
+      <c r="A174" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B174" s="3">
+        <v>41</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D174" s="5">
+        <v>7552044</v>
+      </c>
+      <c r="E174" s="6" t="str">
+        <f>IF($D174="","",VLOOKUP($D174,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" ht="16.5">
+      <c r="A175" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B175" s="3">
+        <v>42</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D175" s="5">
+        <v>7462230</v>
+      </c>
+      <c r="E175" s="6" t="str">
+        <f>IF($D175="","",VLOOKUP($D175,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" ht="16.5">
+      <c r="A176" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B176" s="3">
+        <v>43</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D176" s="5">
+        <v>7423633</v>
+      </c>
+      <c r="E176" s="6" t="str">
+        <f>IF($D176="","",VLOOKUP($D176,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" ht="16.5">
+      <c r="A177" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B177" s="3">
+        <v>44</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D177" s="5">
+        <v>7327050</v>
+      </c>
+      <c r="E177" s="6" t="str">
+        <f>IF($D177="","",VLOOKUP($D177,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" ht="16.5">
+      <c r="A178" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B178" s="3">
+        <v>45</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D178" s="5">
+        <v>6678842</v>
+      </c>
+      <c r="E178" s="6" t="str">
+        <f>IF($D178="","",VLOOKUP($D178,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" ht="16.5">
+      <c r="A179" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B179" s="3">
+        <v>46</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D179" s="5">
+        <v>6177989</v>
+      </c>
+      <c r="E179" s="6" t="str">
+        <f>IF($D179="","",VLOOKUP($D179,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" ht="16.5">
+      <c r="A180" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B180" s="3">
+        <v>47</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D180" s="5">
+        <v>5901298</v>
+      </c>
+      <c r="E180" s="6" t="str">
+        <f>IF($D180="","",VLOOKUP($D180,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" ht="16.5">
+      <c r="A181" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B181" s="3">
+        <v>48</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D181" s="5">
+        <v>5097585</v>
+      </c>
+      <c r="E181" s="6" t="str">
+        <f>IF($D181="","",VLOOKUP($D181,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" ht="16.5">
+      <c r="A182" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B182" s="3">
+        <v>49</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D182" s="5">
+        <v>5036088</v>
+      </c>
+      <c r="E182" s="6" t="str">
+        <f>IF($D182="","",VLOOKUP($D182,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" ht="16.5">
+      <c r="A183" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B183" s="3">
+        <v>50</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D183" s="5">
+        <v>4821347</v>
+      </c>
+      <c r="E183" s="6" t="str">
+        <f>IF($D183="","",VLOOKUP($D183,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" ht="16.5">
+      <c r="A184" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B184" s="3">
+        <v>51</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D184" s="5">
+        <v>4599953</v>
+      </c>
+      <c r="E184" s="6" t="str">
+        <f>IF($D184="","",VLOOKUP($D184,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" ht="16.5">
+      <c r="A185" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B185" s="3">
+        <v>52</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D185" s="5">
+        <v>4332112</v>
+      </c>
+      <c r="E185" s="6" t="str">
+        <f>IF($D185="","",VLOOKUP($D185,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" ht="16.5">
+      <c r="A186" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B186" s="3">
+        <v>53</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D186" s="5">
+        <v>4235009</v>
+      </c>
+      <c r="E186" s="6" t="str">
+        <f>IF($D186="","",VLOOKUP($D186,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" ht="16.5">
+      <c r="A187" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B187" s="3">
+        <v>54</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D187" s="5">
+        <v>4226803</v>
+      </c>
+      <c r="E187" s="6" t="str">
+        <f>IF($D187="","",VLOOKUP($D187,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" ht="16.5">
+      <c r="A188" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B188" s="3">
+        <v>55</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D188" s="5">
+        <v>3992666</v>
+      </c>
+      <c r="E188" s="6" t="str">
+        <f>IF($D188="","",VLOOKUP($D188,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" ht="16.5">
+      <c r="A189" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B189" s="3">
+        <v>56</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D189" s="5">
+        <v>3935236</v>
+      </c>
+      <c r="E189" s="6" t="str">
+        <f>IF($D189="","",VLOOKUP($D189,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" ht="16.5">
+      <c r="A190" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B190" s="3">
+        <v>57</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D190" s="5">
+        <v>3819189</v>
+      </c>
+      <c r="E190" s="6" t="str">
+        <f>IF($D190="","",VLOOKUP($D190,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" ht="16.5">
+      <c r="A191" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B191" s="3">
+        <v>58</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D191" s="5">
+        <v>2896389</v>
+      </c>
+      <c r="E191" s="6" t="str">
+        <f>IF($D191="","",VLOOKUP($D191,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" ht="16.5">
+      <c r="A192" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B192" s="3">
+        <v>59</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D192" s="5">
+        <v>2645896</v>
+      </c>
+      <c r="E192" s="6" t="str">
+        <f>IF($D192="","",VLOOKUP($D192,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" ht="16.5">
+      <c r="A193" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B193" s="3">
+        <v>60</v>
+      </c>
+      <c r="C193" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D193" s="5">
+        <v>2195612</v>
+      </c>
+      <c r="E193" s="6" t="str">
+        <f>IF($D193="","",VLOOKUP($D193,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" ht="16.5">
+      <c r="A194" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B194" s="3">
+        <v>61</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D194" s="5">
+        <v>1908787</v>
+      </c>
+      <c r="E194" s="6" t="str">
+        <f>IF($D194="","",VLOOKUP($D194,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" ht="16.5">
+      <c r="A195" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B195" s="3">
+        <v>62</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D195" s="5">
+        <v>1890847</v>
+      </c>
+      <c r="E195" s="6" t="str">
+        <f>IF($D195="","",VLOOKUP($D195,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" ht="16.5">
+      <c r="A196" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B196" s="3">
+        <v>63</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D196" s="5">
+        <v>1772463</v>
+      </c>
+      <c r="E196" s="6" t="str">
+        <f>IF($D196="","",VLOOKUP($D196,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" ht="16.5">
+      <c r="A197" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B197" s="3">
+        <v>64</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D197" s="5">
+        <v>1472500</v>
+      </c>
+      <c r="E197" s="6" t="str">
+        <f>IF($D197="","",VLOOKUP($D197,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" ht="16.5">
+      <c r="A198" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B198" s="3">
+        <v>65</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D198" s="5">
+        <v>1425274</v>
+      </c>
+      <c r="E198" s="6" t="str">
+        <f>IF($D198="","",VLOOKUP($D198,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" ht="16.5">
+      <c r="A199" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B199" s="3">
+        <v>66</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D199" s="5">
+        <v>1226829</v>
+      </c>
+      <c r="E199" s="6" t="str">
+        <f>IF($D199="","",VLOOKUP($D199,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" ht="16.5">
+      <c r="A200" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B200" s="3">
+        <v>67</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D200" s="5">
+        <v>460000</v>
+      </c>
+      <c r="E200" s="6" t="str">
+        <f>IF($D200="","",VLOOKUP($D200,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>3단계</v>
       </c>
     </row>
@@ -9069,7 +10095,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -9089,16 +10115,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20.25" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
+        <v>116</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
@@ -9117,7 +10143,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -9134,135 +10160,135 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="19.5" customHeight="1">
-      <c r="B2" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
+      <c r="B2" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
     </row>
     <row r="3" spans="2:4">
-      <c r="B3" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="11" t="s">
-        <v>103</v>
+      <c r="D3" s="12" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="16.5" customHeight="1">
-      <c r="B4" s="12">
+      <c r="B4" s="13">
         <v>0</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="14" t="s">
-        <v>104</v>
+      <c r="D4" s="15" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="16.5" customHeight="1">
-      <c r="B5" s="12">
+      <c r="B5" s="13">
         <v>38001</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="14" t="s">
-        <v>105</v>
+      <c r="D5" s="15" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="16.5" customHeight="1">
-      <c r="B6" s="12">
+      <c r="B6" s="13">
         <v>145001</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="14" t="s">
-        <v>106</v>
+      <c r="D6" s="15" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="16.5" customHeight="1">
-      <c r="B7" s="12">
+      <c r="B7" s="13">
         <v>550001</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="14" t="s">
-        <v>107</v>
+      <c r="D7" s="15" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="16.5" customHeight="1">
-      <c r="B8" s="12">
+      <c r="B8" s="13">
         <v>650001</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="14" t="s">
-        <v>108</v>
+      <c r="D8" s="15" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="16.5" customHeight="1">
-      <c r="B9" s="12">
+      <c r="B9" s="13">
         <v>1020001</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="14" t="s">
-        <v>109</v>
+      <c r="D9" s="15" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="16.5" customHeight="1">
-      <c r="B10" s="12">
+      <c r="B10" s="13">
         <v>2280001</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="14" t="s">
-        <v>110</v>
+      <c r="D10" s="15" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="16.5" customHeight="1">
-      <c r="B11" s="12">
+      <c r="B11" s="13">
         <v>2630001</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="14" t="s">
-        <v>111</v>
+      <c r="D11" s="15" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="16.5" customHeight="1">
-      <c r="B12" s="12">
+      <c r="B12" s="13">
         <v>7190000</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="14" t="s">
-        <v>112</v>
+      <c r="D12" s="15" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="2:4">
-      <c r="B14" s="28" t="s">
-        <v>113</v>
-      </c>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
+      <c r="B14" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B14:D14"/>
   </mergeCells>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -7,12 +7,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용안내" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월요일" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화요일" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="수요일" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="목요일" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="금요일" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="토요일" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월요일" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화요일" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="수요일" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="목요일" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="금요일" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="토요일" sheetId="7" state="hidden" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-06" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기준표" sheetId="10" state="visible" r:id="rId10"/>
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -158,6 +158,13 @@
       <charset val="129"/>
       <family val="3"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="14">
@@ -315,7 +322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -414,6 +421,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -674,13 +683,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B21"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" s="34" t="inlineStr">
+        <is>
+          <t>📋 데이터 입력 안내 (업데이트됨)</t>
+        </is>
+      </c>
+    </row>
     <row r="2" ht="26.25" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -688,14 +704,38 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="35" t="inlineStr">
+        <is>
+          <t>✅ 데이터 입력 방법</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="17.25" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>월별 보관 시트(예: 2026-06)에 날짜, 순위, 플레이어, 점수, 단계 순으로 입력하세요.</t>
+        </is>
+      </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>1. 매주 데이터 입력 (요일 시트)</t>
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>새 달이 시작되면 새 시트(예: 2026-07)를 만들고 같은 형식으로 입력하세요.</t>
+        </is>
+      </c>
+    </row>
     <row r="6" ht="16.5" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>요일 시트(월~토)는 더 이상 사용하지 않습니다.</t>
+        </is>
+      </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
           <t>• [월요일]~[토요일] 시트의 C1 '기준일자'에 그 날짜(예: 2026-06-16)를 먼저 입력하세요.</t>
@@ -1011,8 +1051,8 @@
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="D1" s="34" t="n"/>
-      <c r="E1" s="34" t="n"/>
+      <c r="D1" s="36" t="n"/>
+      <c r="E1" s="36" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="B2" s="30" t="inlineStr">
@@ -2363,8 +2403,8 @@
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="D1" s="34" t="n"/>
-      <c r="E1" s="34" t="n"/>
+      <c r="D1" s="36" t="n"/>
+      <c r="E1" s="36" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="B2" s="30" t="inlineStr">
@@ -3709,8 +3749,8 @@
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="D1" s="34" t="n"/>
-      <c r="E1" s="34" t="n"/>
+      <c r="D1" s="36" t="n"/>
+      <c r="E1" s="36" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="B2" s="30" t="inlineStr">
@@ -4309,8 +4349,8 @@
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="D1" s="34" t="n"/>
-      <c r="E1" s="34" t="n"/>
+      <c r="D1" s="36" t="n"/>
+      <c r="E1" s="36" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="B2" s="30" t="inlineStr">
@@ -5259,8 +5299,8 @@
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="D1" s="34" t="n"/>
-      <c r="E1" s="34" t="n"/>
+      <c r="D1" s="36" t="n"/>
+      <c r="E1" s="36" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="B2" s="30" t="inlineStr">
@@ -6205,10 +6245,10 @@
         </is>
       </c>
       <c r="C1" s="31" t="n">
-        <v>46188</v>
-      </c>
-      <c r="D1" s="34" t="n"/>
-      <c r="E1" s="34" t="n"/>
+        <v>46193</v>
+      </c>
+      <c r="D1" s="36" t="n"/>
+      <c r="E1" s="36" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="B2" s="30" t="inlineStr">

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD9B4BE-0F21-44FB-9977-CD2D612624FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{814CF8B3-59E7-49E3-9A7E-41B471C26A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22590" yWindow="705" windowWidth="14385" windowHeight="15885" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="기준표" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,14 +39,302 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="111">
+  <si>
+    <t>📦 월별 보관 — 2026-06  (날짜별 길드전 랭킹 누적)</t>
+  </si>
+  <si>
+    <t>날짜</t>
+  </si>
+  <si>
+    <t>순위</t>
+  </si>
+  <si>
+    <t>플레이어</t>
+  </si>
+  <si>
+    <t>점수</t>
+  </si>
+  <si>
+    <t>단계</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>떠들어봐안들린다</t>
+  </si>
+  <si>
+    <t>9단계</t>
+  </si>
+  <si>
+    <t>-프리저-</t>
+  </si>
+  <si>
+    <t>독화살</t>
+  </si>
+  <si>
+    <t>독건담</t>
+  </si>
+  <si>
+    <t>눈밑에점찍고돌아온아내</t>
+  </si>
+  <si>
+    <t>독홍시</t>
+  </si>
+  <si>
+    <t>독한련</t>
+  </si>
+  <si>
+    <t>습격이다개스키야</t>
+  </si>
+  <si>
+    <t>독여울</t>
+  </si>
+  <si>
+    <t>독한다람쥐</t>
+  </si>
+  <si>
+    <t>Lv100 배회하는 좀비</t>
+  </si>
+  <si>
+    <t>핑도노·훔치고·생각하는·편</t>
+  </si>
+  <si>
+    <t>왜요뭐</t>
+  </si>
+  <si>
+    <t>독방구핑</t>
+  </si>
+  <si>
+    <t>여썰고</t>
+  </si>
+  <si>
+    <t>명령라하지마라</t>
+  </si>
+  <si>
+    <t>모어쩌라고</t>
+  </si>
+  <si>
+    <t>독파민</t>
+  </si>
+  <si>
+    <t>독그레핀</t>
+  </si>
+  <si>
+    <t>진짜한입만나못믿니</t>
+  </si>
+  <si>
+    <t>뉴스나온그사람</t>
+  </si>
+  <si>
+    <t>독아윤</t>
+  </si>
+  <si>
+    <t>괴도하미</t>
+  </si>
+  <si>
+    <t>할말있는데나중에말해줌</t>
+  </si>
+  <si>
+    <t>독아사</t>
+  </si>
+  <si>
+    <t>엘베닫힘연타범</t>
+  </si>
+  <si>
+    <t>니면상시베리아</t>
+  </si>
+  <si>
+    <t>뮤지컬보러가서노래따라부르는놈</t>
+  </si>
+  <si>
+    <t>독수리골드</t>
+  </si>
+  <si>
+    <t>영화관에서결말스포한냔</t>
+  </si>
+  <si>
+    <t>8단계</t>
+  </si>
+  <si>
+    <t>독살교육</t>
+  </si>
+  <si>
+    <t>훔쳐뿟노</t>
+  </si>
+  <si>
+    <t>독거노인춘삼</t>
+  </si>
+  <si>
+    <t>독독쿠롱</t>
+  </si>
+  <si>
+    <t>안톤 쉬거</t>
+  </si>
+  <si>
+    <t>독과점</t>
+  </si>
+  <si>
+    <t>현금만받아</t>
+  </si>
+  <si>
+    <t>독잉교</t>
+  </si>
+  <si>
+    <t>독로이지</t>
+  </si>
+  <si>
+    <t>독눈누눈누</t>
+  </si>
+  <si>
+    <t>독약원샷</t>
+  </si>
+  <si>
+    <t>독철이</t>
+  </si>
+  <si>
+    <t>독계탕</t>
+  </si>
+  <si>
+    <t>주니쯤</t>
+  </si>
+  <si>
+    <t>독후감상문</t>
+  </si>
+  <si>
+    <t>독아크</t>
+  </si>
+  <si>
+    <t>티거Ya드랍더튀어</t>
+  </si>
+  <si>
+    <t>1090</t>
+  </si>
+  <si>
+    <t>별빛여신</t>
+  </si>
+  <si>
+    <t>독한월요일병</t>
+  </si>
+  <si>
+    <t>7단계</t>
+  </si>
+  <si>
+    <t>독골골</t>
+  </si>
+  <si>
+    <t>6단계</t>
+  </si>
+  <si>
+    <t>악마인데순둥소예</t>
+  </si>
+  <si>
+    <t>독터키캔씨Turkey1881</t>
+  </si>
+  <si>
+    <t>독그릭</t>
+  </si>
+  <si>
+    <t>독삼미</t>
+  </si>
+  <si>
+    <t>자르반84세</t>
+  </si>
+  <si>
+    <t>단추가게</t>
+  </si>
+  <si>
+    <t>독주</t>
+  </si>
+  <si>
+    <t>5단계</t>
+  </si>
+  <si>
+    <t>독이즈</t>
+  </si>
+  <si>
+    <t>독고독</t>
+  </si>
+  <si>
+    <t>린이</t>
+  </si>
+  <si>
+    <t>3단계</t>
+  </si>
+  <si>
+    <t>독초치이입</t>
+  </si>
+  <si>
+    <t>수색맨</t>
+  </si>
+  <si>
+    <t>독레인-InfernoRain</t>
+  </si>
+  <si>
+    <t>2단계</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>떪은홍시</t>
+  </si>
+  <si>
+    <t>스무디에얼음빼주세요</t>
+  </si>
+  <si>
+    <t>빨강맛</t>
+  </si>
+  <si>
+    <t>아크으</t>
+  </si>
+  <si>
+    <t>아사히</t>
+  </si>
+  <si>
+    <t>미녀와야자수</t>
+  </si>
+  <si>
+    <t>빡센공주</t>
+  </si>
+  <si>
+    <t>명령하디마라</t>
+  </si>
+  <si>
+    <t>해녀도앤댈리는뒈</t>
+  </si>
+  <si>
+    <t>쉰데렐라</t>
+  </si>
+  <si>
+    <t>앞니로조사버리는토끼</t>
+  </si>
+  <si>
+    <t>베놈이마깐데또까</t>
+  </si>
+  <si>
+    <t>이런들어떠하리저런들어떠하리</t>
+  </si>
+  <si>
+    <t>숲속모텔</t>
+  </si>
+  <si>
+    <t>라면주면갈께</t>
+  </si>
+  <si>
+    <t>독팡팡</t>
+  </si>
+  <si>
+    <t>2026-06-16</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
   <si>
     <t>하한점수</t>
   </si>
   <si>
-    <t>단계</t>
-  </si>
-  <si>
     <t>점수 범위</t>
   </si>
   <si>
@@ -55,15 +344,9 @@
     <t>0 ~ 38,000</t>
   </si>
   <si>
-    <t>2단계</t>
-  </si>
-  <si>
     <t>38,001 ~ 145,000</t>
   </si>
   <si>
-    <t>3단계</t>
-  </si>
-  <si>
     <t>145,001 ~ 550,000</t>
   </si>
   <si>
@@ -73,298 +356,19 @@
     <t>550,001 ~ 650,000</t>
   </si>
   <si>
-    <t>5단계</t>
-  </si>
-  <si>
     <t>650,001 ~ 1,020,000</t>
   </si>
   <si>
-    <t>6단계</t>
-  </si>
-  <si>
     <t>1,020,001 ~ 2,280,000</t>
   </si>
   <si>
-    <t>7단계</t>
-  </si>
-  <si>
     <t>2,280,001 ~ 2,630,000</t>
   </si>
   <si>
-    <t>8단계</t>
-  </si>
-  <si>
     <t>2,630,001 ~ 7,189,999</t>
   </si>
   <si>
-    <t>9단계</t>
-  </si>
-  <si>
     <t>7,190,000 이상</t>
-  </si>
-  <si>
-    <t>📦 월별 보관 — 2026-06  (날짜별 길드전 랭킹 누적)</t>
-  </si>
-  <si>
-    <t>날짜</t>
-  </si>
-  <si>
-    <t>순위</t>
-  </si>
-  <si>
-    <t>플레이어</t>
-  </si>
-  <si>
-    <t>점수</t>
-  </si>
-  <si>
-    <t>2026-06-13</t>
-  </si>
-  <si>
-    <t>떠들어봐안들린다</t>
-  </si>
-  <si>
-    <t>-프리저-</t>
-  </si>
-  <si>
-    <t>독화살</t>
-  </si>
-  <si>
-    <t>독건담</t>
-  </si>
-  <si>
-    <t>눈밑에점찍고돌아온아내</t>
-  </si>
-  <si>
-    <t>독홍시</t>
-  </si>
-  <si>
-    <t>독한련</t>
-  </si>
-  <si>
-    <t>습격이다개스키야</t>
-  </si>
-  <si>
-    <t>독여울</t>
-  </si>
-  <si>
-    <t>독한다람쥐</t>
-  </si>
-  <si>
-    <t>Lv100 배회하는 좀비</t>
-  </si>
-  <si>
-    <t>핑도노·훔치고·생각하는·편</t>
-  </si>
-  <si>
-    <t>왜요뭐</t>
-  </si>
-  <si>
-    <t>독방구핑</t>
-  </si>
-  <si>
-    <t>여썰고</t>
-  </si>
-  <si>
-    <t>명령라하지마라</t>
-  </si>
-  <si>
-    <t>모어쩌라고</t>
-  </si>
-  <si>
-    <t>독파민</t>
-  </si>
-  <si>
-    <t>독그레핀</t>
-  </si>
-  <si>
-    <t>진짜한입만나못믿니</t>
-  </si>
-  <si>
-    <t>뉴스나온그사람</t>
-  </si>
-  <si>
-    <t>독아윤</t>
-  </si>
-  <si>
-    <t>괴도하미</t>
-  </si>
-  <si>
-    <t>할말있는데나중에말해줌</t>
-  </si>
-  <si>
-    <t>독아사</t>
-  </si>
-  <si>
-    <t>엘베닫힘연타범</t>
-  </si>
-  <si>
-    <t>니면상시베리아</t>
-  </si>
-  <si>
-    <t>뮤지컬보러가서노래따라부르는놈</t>
-  </si>
-  <si>
-    <t>독수리골드</t>
-  </si>
-  <si>
-    <t>영화관에서결말스포한냔</t>
-  </si>
-  <si>
-    <t>독살교육</t>
-  </si>
-  <si>
-    <t>훔쳐뿟노</t>
-  </si>
-  <si>
-    <t>독거노인춘삼</t>
-  </si>
-  <si>
-    <t>독독쿠롱</t>
-  </si>
-  <si>
-    <t>안톤 쉬거</t>
-  </si>
-  <si>
-    <t>독과점</t>
-  </si>
-  <si>
-    <t>현금만받아</t>
-  </si>
-  <si>
-    <t>독잉교</t>
-  </si>
-  <si>
-    <t>독로이지</t>
-  </si>
-  <si>
-    <t>독눈누눈누</t>
-  </si>
-  <si>
-    <t>독약원샷</t>
-  </si>
-  <si>
-    <t>독철이</t>
-  </si>
-  <si>
-    <t>독계탕</t>
-  </si>
-  <si>
-    <t>주니쯤</t>
-  </si>
-  <si>
-    <t>독후감상문</t>
-  </si>
-  <si>
-    <t>독아크</t>
-  </si>
-  <si>
-    <t>티거Ya드랍더튀어</t>
-  </si>
-  <si>
-    <t>1090</t>
-  </si>
-  <si>
-    <t>별빛여신</t>
-  </si>
-  <si>
-    <t>독한월요일병</t>
-  </si>
-  <si>
-    <t>독골골</t>
-  </si>
-  <si>
-    <t>악마인데순둥소예</t>
-  </si>
-  <si>
-    <t>독터키캔씨Turkey1881</t>
-  </si>
-  <si>
-    <t>독그릭</t>
-  </si>
-  <si>
-    <t>독삼미</t>
-  </si>
-  <si>
-    <t>자르반84세</t>
-  </si>
-  <si>
-    <t>단추가게</t>
-  </si>
-  <si>
-    <t>독주</t>
-  </si>
-  <si>
-    <t>독이즈</t>
-  </si>
-  <si>
-    <t>독고독</t>
-  </si>
-  <si>
-    <t>린이</t>
-  </si>
-  <si>
-    <t>독초치이입</t>
-  </si>
-  <si>
-    <t>수색맨</t>
-  </si>
-  <si>
-    <t>독레인-InfernoRain</t>
-  </si>
-  <si>
-    <t>2026-06-15</t>
-  </si>
-  <si>
-    <t>떪은홍시</t>
-  </si>
-  <si>
-    <t>스무디에얼음빼주세요</t>
-  </si>
-  <si>
-    <t>빨강맛</t>
-  </si>
-  <si>
-    <t>아크으</t>
-  </si>
-  <si>
-    <t>아사히</t>
-  </si>
-  <si>
-    <t>미녀와야자수</t>
-  </si>
-  <si>
-    <t>빡센공주</t>
-  </si>
-  <si>
-    <t>명령하디마라</t>
-  </si>
-  <si>
-    <t>해녀도앤댈리는뒈</t>
-  </si>
-  <si>
-    <t>쉰데렐라</t>
-  </si>
-  <si>
-    <t>앞니로조사버리는토끼</t>
-  </si>
-  <si>
-    <t>베놈이마깐데또까</t>
-  </si>
-  <si>
-    <t>이런들어떠하리저런들어떠하리</t>
-  </si>
-  <si>
-    <t>숲속모텔</t>
-  </si>
-  <si>
-    <t>라면주면갈께</t>
-  </si>
-  <si>
-    <t>독팡팡</t>
-  </si>
-  <si>
-    <t>2026-06-16</t>
   </si>
   <si>
     <t>📦 월별 보관 — 2026-07  (날짜별 길드전 랭킹 누적)</t>
@@ -480,10 +484,6 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="월요일"/>
       <sheetName val="화요일"/>
@@ -873,13 +873,13 @@
   <sheetData>
     <row r="3" spans="2:4">
       <c r="B3" t="s">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>2</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="2:4">
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:4">
@@ -898,10 +898,10 @@
         <v>38001</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="2:4">
@@ -909,10 +909,10 @@
         <v>145001</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="2:4">
@@ -920,10 +920,10 @@
         <v>550001</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>103</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="2:4">
@@ -931,10 +931,10 @@
         <v>650001</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="2:4">
@@ -942,10 +942,10 @@
         <v>1020001</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="2:4">
@@ -953,10 +953,10 @@
         <v>2280001</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="2:4">
@@ -964,10 +964,10 @@
         <v>2630001</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="2:4">
@@ -975,10 +975,10 @@
         <v>7190000</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -989,7 +989,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E201"/>
+  <dimension ref="A1:E260"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="49.75" bestFit="1" customWidth="1"/>
@@ -1001,3474 +1001,4477 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D3">
-        <v>20124674</v>
+        <v>17446200</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D4">
-        <v>17878446</v>
+        <v>14003031</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B5">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D5">
-        <v>17252741</v>
+        <v>13095050</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B6">
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>14018518</v>
+        <v>13026900</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B7">
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D7">
-        <v>13474398</v>
+        <v>12386494</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B8">
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D8">
-        <v>13425532</v>
+        <v>12178410</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B9">
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D9">
-        <v>11951501</v>
+        <v>11676697</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B10">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D10">
-        <v>11050986</v>
+        <v>11190330</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B11">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="D11">
-        <v>11050649</v>
+        <v>10362894</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B12">
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="D12">
-        <v>10955529</v>
+        <v>9791580</v>
       </c>
       <c r="E12" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B13">
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D13">
-        <v>10698509</v>
+        <v>9726006</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B14">
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D14">
-        <v>10412961</v>
+        <v>9298860</v>
       </c>
       <c r="E14" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B15">
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D15">
-        <v>10411072</v>
+        <v>8487782</v>
       </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B16">
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D16">
-        <v>9539236</v>
+        <v>8428931</v>
       </c>
       <c r="E16" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B17">
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D17">
-        <v>9099782</v>
+        <v>8351700</v>
       </c>
       <c r="E17" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B18">
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D18">
-        <v>8928749</v>
+        <v>8099944</v>
       </c>
       <c r="E18" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B19">
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="D19">
-        <v>8509653</v>
+        <v>7972413</v>
       </c>
       <c r="E19" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B20">
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="D20">
-        <v>8453735</v>
+        <v>7829890</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B21">
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D21">
-        <v>8390684</v>
+        <v>7747410</v>
       </c>
       <c r="E21" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B22">
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D22">
-        <v>8385975</v>
+        <v>7734457</v>
       </c>
       <c r="E22" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B23">
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D23">
-        <v>7931262</v>
+        <v>7656699</v>
       </c>
       <c r="E23" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B24">
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D24">
-        <v>7760606</v>
+        <v>7629930</v>
       </c>
       <c r="E24" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B25">
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D25">
-        <v>7534842</v>
+        <v>7629170</v>
       </c>
       <c r="E25" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B26">
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="D26">
-        <v>7400843</v>
+        <v>7530750</v>
       </c>
       <c r="E26" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B27">
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="D27">
-        <v>7282637</v>
+        <v>7494390</v>
       </c>
       <c r="E27" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B28">
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="D28">
-        <v>7281876</v>
+        <v>7425030</v>
       </c>
       <c r="E28" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B29">
         <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="D29">
-        <v>7280918</v>
+        <v>7233630</v>
       </c>
       <c r="E29" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B30">
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="D30">
-        <v>7272828</v>
+        <v>7218568</v>
       </c>
       <c r="E30" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B31">
         <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="D31">
-        <v>7236458</v>
+        <v>7215859</v>
       </c>
       <c r="E31" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B32">
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="D32">
-        <v>6986371</v>
+        <v>7202018</v>
       </c>
       <c r="E32" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B33">
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D33">
-        <v>5884130</v>
+        <v>5747056</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B34">
         <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D34">
-        <v>5813157</v>
+        <v>5659102</v>
       </c>
       <c r="E34" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B35">
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D35">
-        <v>5275134</v>
+        <v>5575024</v>
       </c>
       <c r="E35" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B36">
         <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D36">
-        <v>4876688</v>
+        <v>5545974</v>
       </c>
       <c r="E36" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B37">
         <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="D37">
-        <v>4842063</v>
+        <v>5391755</v>
       </c>
       <c r="E37" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B38">
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D38">
-        <v>4668195</v>
+        <v>5181490</v>
       </c>
       <c r="E38" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B39">
         <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D39">
-        <v>4616477</v>
+        <v>5131950</v>
       </c>
       <c r="E39" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B40">
         <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D40">
-        <v>4498125</v>
+        <v>4904007</v>
       </c>
       <c r="E40" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B41">
         <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D41">
-        <v>3687186</v>
+        <v>4573837</v>
       </c>
       <c r="E41" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B42">
         <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="D42">
-        <v>3611227</v>
+        <v>4490575</v>
       </c>
       <c r="E42" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B43">
         <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D43">
-        <v>3189920</v>
+        <v>4397353</v>
       </c>
       <c r="E43" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B44">
         <v>42</v>
       </c>
       <c r="C44" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D44">
-        <v>3120139</v>
+        <v>4297031</v>
       </c>
       <c r="E44" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B45">
         <v>43</v>
       </c>
       <c r="C45" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="D45">
-        <v>3108728</v>
+        <v>4182965</v>
       </c>
       <c r="E45" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B46">
         <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="D46">
-        <v>3077202</v>
+        <v>4030862</v>
       </c>
       <c r="E46" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B47">
         <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="D47">
-        <v>2968639</v>
+        <v>3998435</v>
       </c>
       <c r="E47" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B48">
         <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="D48">
-        <v>2968603</v>
+        <v>3927862</v>
       </c>
       <c r="E48" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B49">
         <v>47</v>
       </c>
       <c r="C49" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="D49">
-        <v>2953979</v>
+        <v>3788029</v>
       </c>
       <c r="E49" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B50">
         <v>48</v>
       </c>
       <c r="C50" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="D50">
-        <v>2772649</v>
+        <v>3775539</v>
       </c>
       <c r="E50" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B51">
         <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D51">
-        <v>2738331</v>
+        <v>3644353</v>
       </c>
       <c r="E51" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B52">
         <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="D52">
-        <v>2460723</v>
+        <v>3436366</v>
       </c>
       <c r="E52" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B53">
         <v>51</v>
       </c>
       <c r="C53" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="D53">
-        <v>2165388</v>
+        <v>3375232</v>
       </c>
       <c r="E53" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B54">
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D54">
-        <v>2028076</v>
+        <v>3219637</v>
       </c>
       <c r="E54" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B55">
         <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D55">
-        <v>1829852</v>
+        <v>3100693</v>
       </c>
       <c r="E55" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B56">
         <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="D56">
-        <v>1765395</v>
+        <v>3087580</v>
       </c>
       <c r="E56" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B57">
         <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="D57">
-        <v>1693947</v>
+        <v>2720000</v>
       </c>
       <c r="E57" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B58">
         <v>56</v>
       </c>
       <c r="C58" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="D58">
-        <v>1288077</v>
+        <v>2670936</v>
       </c>
       <c r="E58" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B59">
         <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="D59">
-        <v>1207196</v>
+        <v>2294961</v>
       </c>
       <c r="E59" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B60">
         <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="D60">
-        <v>963718</v>
+        <v>2202597</v>
       </c>
       <c r="E60" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B61">
         <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="D61">
-        <v>700489</v>
+        <v>2155923</v>
       </c>
       <c r="E61" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B62">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>86</v>
+        <v>7</v>
       </c>
       <c r="D62">
-        <v>659256</v>
+        <v>20124674</v>
       </c>
       <c r="E62" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B63">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="D63">
-        <v>384395</v>
+        <v>17878446</v>
       </c>
       <c r="E63" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B64">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="C64" t="s">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="D64">
-        <v>327964</v>
+        <v>17252741</v>
       </c>
       <c r="E64" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B65">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="C65" t="s">
-        <v>89</v>
+        <v>11</v>
       </c>
       <c r="D65">
-        <v>266932</v>
+        <v>14018518</v>
       </c>
       <c r="E65" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B66">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="C66" t="s">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="D66">
-        <v>89508</v>
+        <v>13474398</v>
       </c>
       <c r="E66" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C67" t="s">
-        <v>92</v>
+        <v>13</v>
       </c>
       <c r="D67">
-        <v>76513151</v>
+        <v>13425532</v>
       </c>
       <c r="E67" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C68" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D68">
-        <v>62254586</v>
+        <v>11951501</v>
       </c>
       <c r="E68" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="D69">
-        <v>36598969</v>
+        <v>11050986</v>
       </c>
       <c r="E69" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B70">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C70" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="D70">
-        <v>26859795</v>
+        <v>11050649</v>
       </c>
       <c r="E70" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B71">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C71" t="s">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="D71">
-        <v>22027625</v>
+        <v>10955529</v>
       </c>
       <c r="E71" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B72">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C72" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D72">
-        <v>19336746</v>
+        <v>10698509</v>
       </c>
       <c r="E72" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B73">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D73">
-        <v>17008882</v>
+        <v>10412961</v>
       </c>
       <c r="E73" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B74">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D74">
-        <v>16620269</v>
+        <v>10411072</v>
       </c>
       <c r="E74" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B75">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C75" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="D75">
-        <v>15971399</v>
+        <v>9539236</v>
       </c>
       <c r="E75" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B76">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C76" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="D76">
-        <v>15579579</v>
+        <v>9099782</v>
       </c>
       <c r="E76" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B77">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C77" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D77">
-        <v>15166835</v>
+        <v>8928749</v>
       </c>
       <c r="E77" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B78">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C78" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="D78">
-        <v>15136017</v>
+        <v>8509653</v>
       </c>
       <c r="E78" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B79">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C79" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="D79">
-        <v>15045625</v>
+        <v>8453735</v>
       </c>
       <c r="E79" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B80">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C80" t="s">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="D80">
-        <v>11929975</v>
+        <v>8390684</v>
       </c>
       <c r="E80" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B81">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C81" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D81">
-        <v>11703867</v>
+        <v>8385975</v>
       </c>
       <c r="E81" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B82">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C82" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="D82">
-        <v>11641804</v>
+        <v>7931262</v>
       </c>
       <c r="E82" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B83">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C83" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="D83">
-        <v>11224132</v>
+        <v>7760606</v>
       </c>
       <c r="E83" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B84">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C84" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="D84">
-        <v>11128193</v>
+        <v>7534842</v>
       </c>
       <c r="E84" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B85">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C85" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D85">
-        <v>10907771</v>
+        <v>7400843</v>
       </c>
       <c r="E85" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B86">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C86" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D86">
-        <v>10606882</v>
+        <v>7282637</v>
       </c>
       <c r="E86" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B87">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C87" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D87">
-        <v>10422796</v>
+        <v>7281876</v>
       </c>
       <c r="E87" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B88">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C88" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D88">
-        <v>10412768</v>
+        <v>7280918</v>
       </c>
       <c r="E88" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B89">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C89" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="D89">
-        <v>10128124</v>
+        <v>7272828</v>
       </c>
       <c r="E89" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B90">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C90" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D90">
-        <v>9706739</v>
+        <v>7236458</v>
       </c>
       <c r="E90" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B91">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C91" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="D91">
-        <v>9164119</v>
+        <v>6986371</v>
       </c>
       <c r="E91" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B92">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C92" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="D92">
-        <v>8999382</v>
+        <v>5884130</v>
       </c>
       <c r="E92" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B93">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C93" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D93">
-        <v>8596217</v>
+        <v>5813157</v>
       </c>
       <c r="E93" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B94">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C94" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="D94">
-        <v>8456726</v>
+        <v>5275134</v>
       </c>
       <c r="E94" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B95">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C95" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="D95">
-        <v>8220352</v>
+        <v>4876688</v>
       </c>
       <c r="E95" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B96">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C96" t="s">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="D96">
-        <v>8154156</v>
+        <v>4842063</v>
       </c>
       <c r="E96" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B97">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C97" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="D97">
-        <v>8127020</v>
+        <v>4668195</v>
       </c>
       <c r="E97" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B98">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C98" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="D98">
-        <v>7952273</v>
+        <v>4616477</v>
       </c>
       <c r="E98" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B99">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C99" t="s">
-        <v>102</v>
+        <v>46</v>
       </c>
       <c r="D99">
-        <v>7918857</v>
+        <v>4498125</v>
       </c>
       <c r="E99" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B100">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C100" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D100">
-        <v>7909501</v>
+        <v>3687186</v>
       </c>
       <c r="E100" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B101">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C101" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="D101">
-        <v>7876636</v>
+        <v>3611227</v>
       </c>
       <c r="E101" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B102">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C102" t="s">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="D102">
-        <v>7824653</v>
+        <v>3189920</v>
       </c>
       <c r="E102" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B103">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C103" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D103">
-        <v>7823884</v>
+        <v>3120139</v>
       </c>
       <c r="E103" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B104">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C104" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D104">
-        <v>7679597</v>
+        <v>3108728</v>
       </c>
       <c r="E104" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B105">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C105" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="D105">
-        <v>7635056</v>
+        <v>3077202</v>
       </c>
       <c r="E105" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B106">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C106" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="D106">
-        <v>7579677</v>
+        <v>2968639</v>
       </c>
       <c r="E106" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B107">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C107" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D107">
-        <v>7552044</v>
+        <v>2968603</v>
       </c>
       <c r="E107" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B108">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C108" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="D108">
-        <v>7462230</v>
+        <v>2953979</v>
       </c>
       <c r="E108" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B109">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C109" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D109">
-        <v>7423633</v>
+        <v>2772649</v>
       </c>
       <c r="E109" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B110">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C110" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D110">
-        <v>7327050</v>
+        <v>2738331</v>
       </c>
       <c r="E110" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B111">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C111" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="D111">
-        <v>6678842</v>
+        <v>2460723</v>
       </c>
       <c r="E111" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B112">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C112" t="s">
-        <v>106</v>
+        <v>60</v>
       </c>
       <c r="D112">
-        <v>6177989</v>
+        <v>2165388</v>
       </c>
       <c r="E112" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B113">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C113" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="D113">
-        <v>5901298</v>
+        <v>2028076</v>
       </c>
       <c r="E113" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B114">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C114" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="D114">
-        <v>5097585</v>
+        <v>1829852</v>
       </c>
       <c r="E114" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B115">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C115" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D115">
-        <v>5036088</v>
+        <v>1765395</v>
       </c>
       <c r="E115" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B116">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C116" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D116">
-        <v>4821347</v>
+        <v>1693947</v>
       </c>
       <c r="E116" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B117">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C117" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D117">
-        <v>4599953</v>
+        <v>1288077</v>
       </c>
       <c r="E117" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B118">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C118" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D118">
-        <v>4332112</v>
+        <v>1207196</v>
       </c>
       <c r="E118" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B119">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C119" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D119">
-        <v>4235009</v>
+        <v>963718</v>
       </c>
       <c r="E119" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B120">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C120" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="D120">
-        <v>4226803</v>
+        <v>700489</v>
       </c>
       <c r="E120" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B121">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C121" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="D121">
-        <v>3992666</v>
+        <v>659256</v>
       </c>
       <c r="E121" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B122">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C122" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D122">
-        <v>3935236</v>
+        <v>384395</v>
       </c>
       <c r="E122" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B123">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C123" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="D123">
-        <v>3819189</v>
+        <v>327964</v>
       </c>
       <c r="E123" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B124">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C124" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D124">
-        <v>2896389</v>
+        <v>266932</v>
       </c>
       <c r="E124" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B125">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C125" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="D125">
-        <v>2645896</v>
+        <v>89508</v>
       </c>
       <c r="E125" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="B126">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="C126" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D126">
-        <v>2195612</v>
+        <v>76513151</v>
       </c>
       <c r="E126" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="B127">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C127" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D127">
-        <v>1908787</v>
+        <v>62254586</v>
       </c>
       <c r="E127" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="B128">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="C128" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="D128">
-        <v>1890847</v>
+        <v>36598969</v>
       </c>
       <c r="E128" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="B129">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="C129" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="D129">
-        <v>1772463</v>
+        <v>26859795</v>
       </c>
       <c r="E129" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="B130">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="C130" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D130">
-        <v>1472500</v>
+        <v>22027625</v>
       </c>
       <c r="E130" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="B131">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="C131" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="D131">
-        <v>1425274</v>
+        <v>19336746</v>
       </c>
       <c r="E131" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="B132">
-        <v>66</v>
+        <v>7</v>
       </c>
       <c r="C132" t="s">
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="D132">
-        <v>1226829</v>
+        <v>17008882</v>
       </c>
       <c r="E132" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="B133">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="C133" t="s">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="D133">
-        <v>460000</v>
+        <v>16620269</v>
       </c>
       <c r="E133" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>108</v>
-      </c>
-      <c r="B134" s="1">
-        <v>1</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D134" s="3">
-        <v>15915600</v>
-      </c>
-      <c r="E134" s="4" t="str">
-        <f>IF($D134="","",VLOOKUP($D134,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B134">
+        <v>9</v>
+      </c>
+      <c r="C134" t="s">
+        <v>81</v>
+      </c>
+      <c r="D134">
+        <v>15971399</v>
+      </c>
+      <c r="E134" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" t="s">
-        <v>108</v>
-      </c>
-      <c r="B135" s="1">
-        <v>2</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D135" s="3">
-        <v>12925350</v>
-      </c>
-      <c r="E135" s="4" t="str">
-        <f>IF($D135="","",VLOOKUP($D135,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B135">
+        <v>10</v>
+      </c>
+      <c r="C135" t="s">
+        <v>57</v>
+      </c>
+      <c r="D135">
+        <v>15579579</v>
+      </c>
+      <c r="E135" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>108</v>
-      </c>
-      <c r="B136" s="1">
-        <v>3</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D136" s="3">
-        <v>12016650</v>
-      </c>
-      <c r="E136" s="4" t="str">
-        <f>IF($D136="","",VLOOKUP($D136,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B136">
+        <v>11</v>
+      </c>
+      <c r="C136" t="s">
+        <v>7</v>
+      </c>
+      <c r="D136">
+        <v>15166835</v>
+      </c>
+      <c r="E136" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>108</v>
-      </c>
-      <c r="B137" s="1">
-        <v>4</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D137" s="3">
-        <v>9907350</v>
-      </c>
-      <c r="E137" s="4" t="str">
-        <f>IF($D137="","",VLOOKUP($D137,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B137">
+        <v>12</v>
+      </c>
+      <c r="C137" t="s">
+        <v>27</v>
+      </c>
+      <c r="D137">
+        <v>15136017</v>
+      </c>
+      <c r="E137" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" t="s">
-        <v>108</v>
-      </c>
-      <c r="B138" s="1">
-        <v>5</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D138" s="3">
-        <v>9868650</v>
-      </c>
-      <c r="E138" s="4" t="str">
-        <f>IF($D138="","",VLOOKUP($D138,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B138">
+        <v>13</v>
+      </c>
+      <c r="C138" t="s">
+        <v>41</v>
+      </c>
+      <c r="D138">
+        <v>15045625</v>
+      </c>
+      <c r="E138" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>108</v>
-      </c>
-      <c r="B139" s="1">
-        <v>6</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D139" s="3">
-        <v>9143700</v>
-      </c>
-      <c r="E139" s="4" t="str">
-        <f>IF($D139="","",VLOOKUP($D139,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B139">
+        <v>14</v>
+      </c>
+      <c r="C139" t="s">
+        <v>82</v>
+      </c>
+      <c r="D139">
+        <v>11929975</v>
+      </c>
+      <c r="E139" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" t="s">
-        <v>108</v>
-      </c>
-      <c r="B140" s="1">
-        <v>7</v>
-      </c>
-      <c r="C140" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D140" s="3">
-        <v>9141450</v>
-      </c>
-      <c r="E140" s="4" t="str">
-        <f>IF($D140="","",VLOOKUP($D140,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B140">
+        <v>15</v>
+      </c>
+      <c r="C140" t="s">
+        <v>11</v>
+      </c>
+      <c r="D140">
+        <v>11703867</v>
+      </c>
+      <c r="E140" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" t="s">
-        <v>108</v>
-      </c>
-      <c r="B141" s="1">
-        <v>8</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D141" s="3">
-        <v>9065250</v>
-      </c>
-      <c r="E141" s="4" t="str">
-        <f>IF($D141="","",VLOOKUP($D141,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B141">
+        <v>16</v>
+      </c>
+      <c r="C141" t="s">
+        <v>83</v>
+      </c>
+      <c r="D141">
+        <v>11641804</v>
+      </c>
+      <c r="E141" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" t="s">
-        <v>108</v>
-      </c>
-      <c r="B142" s="1">
-        <v>9</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D142" s="3">
-        <v>9017250</v>
-      </c>
-      <c r="E142" s="4" t="str">
-        <f>IF($D142="","",VLOOKUP($D142,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B142">
+        <v>17</v>
+      </c>
+      <c r="C142" t="s">
+        <v>37</v>
+      </c>
+      <c r="D142">
+        <v>11224132</v>
+      </c>
+      <c r="E142" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" t="s">
-        <v>108</v>
-      </c>
-      <c r="B143" s="1">
-        <v>10</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D143" s="3">
-        <v>8908800</v>
-      </c>
-      <c r="E143" s="4" t="str">
-        <f>IF($D143="","",VLOOKUP($D143,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B143">
+        <v>18</v>
+      </c>
+      <c r="C143" t="s">
+        <v>84</v>
+      </c>
+      <c r="D143">
+        <v>11128193</v>
+      </c>
+      <c r="E143" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" t="s">
-        <v>108</v>
-      </c>
-      <c r="B144" s="1">
-        <v>11</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D144" s="3">
-        <v>8266050</v>
-      </c>
-      <c r="E144" s="4" t="str">
-        <f>IF($D144="","",VLOOKUP($D144,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B144">
+        <v>19</v>
+      </c>
+      <c r="C144" t="s">
+        <v>21</v>
+      </c>
+      <c r="D144">
+        <v>10907771</v>
+      </c>
+      <c r="E144" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" t="s">
-        <v>108</v>
-      </c>
-      <c r="B145" s="1">
-        <v>12</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D145" s="3">
-        <v>8226750</v>
-      </c>
-      <c r="E145" s="4" t="str">
-        <f>IF($D145="","",VLOOKUP($D145,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B145">
+        <v>20</v>
+      </c>
+      <c r="C145" t="s">
+        <v>28</v>
+      </c>
+      <c r="D145">
+        <v>10606882</v>
+      </c>
+      <c r="E145" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" t="s">
-        <v>108</v>
-      </c>
-      <c r="B146" s="1">
-        <v>13</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D146" s="3">
-        <v>8125259</v>
-      </c>
-      <c r="E146" s="4" t="str">
-        <f>IF($D146="","",VLOOKUP($D146,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B146">
+        <v>21</v>
+      </c>
+      <c r="C146" t="s">
+        <v>34</v>
+      </c>
+      <c r="D146">
+        <v>10422796</v>
+      </c>
+      <c r="E146" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" t="s">
-        <v>108</v>
-      </c>
-      <c r="B147" s="1">
-        <v>14</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D147" s="3">
-        <v>7855412</v>
-      </c>
-      <c r="E147" s="4" t="str">
-        <f>IF($D147="","",VLOOKUP($D147,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B147">
+        <v>22</v>
+      </c>
+      <c r="C147" t="s">
+        <v>24</v>
+      </c>
+      <c r="D147">
+        <v>10412768</v>
+      </c>
+      <c r="E147" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" t="s">
-        <v>108</v>
-      </c>
-      <c r="B148" s="1">
-        <v>15</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D148" s="3">
-        <v>7740750</v>
-      </c>
-      <c r="E148" s="4" t="str">
-        <f>IF($D148="","",VLOOKUP($D148,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B148">
+        <v>23</v>
+      </c>
+      <c r="C148" t="s">
+        <v>85</v>
+      </c>
+      <c r="D148">
+        <v>10128124</v>
+      </c>
+      <c r="E148" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" t="s">
-        <v>108</v>
-      </c>
-      <c r="B149" s="1">
-        <v>16</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D149" s="3">
-        <v>7716900</v>
-      </c>
-      <c r="E149" s="4" t="str">
-        <f>IF($D149="","",VLOOKUP($D149,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B149">
+        <v>24</v>
+      </c>
+      <c r="C149" t="s">
+        <v>31</v>
+      </c>
+      <c r="D149">
+        <v>9706739</v>
+      </c>
+      <c r="E149" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" t="s">
-        <v>108</v>
-      </c>
-      <c r="B150" s="1">
-        <v>17</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D150" s="3">
-        <v>7697397</v>
-      </c>
-      <c r="E150" s="4" t="str">
-        <f>IF($D150="","",VLOOKUP($D150,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B150">
+        <v>25</v>
+      </c>
+      <c r="C150" t="s">
+        <v>86</v>
+      </c>
+      <c r="D150">
+        <v>9164119</v>
+      </c>
+      <c r="E150" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" t="s">
-        <v>108</v>
-      </c>
-      <c r="B151" s="1">
-        <v>18</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D151" s="3">
-        <v>7694109</v>
-      </c>
-      <c r="E151" s="4" t="str">
-        <f>IF($D151="","",VLOOKUP($D151,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B151">
+        <v>26</v>
+      </c>
+      <c r="C151" t="s">
+        <v>36</v>
+      </c>
+      <c r="D151">
+        <v>8999382</v>
+      </c>
+      <c r="E151" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" t="s">
-        <v>108</v>
-      </c>
-      <c r="B152" s="1">
-        <v>19</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D152" s="3">
-        <v>7624294</v>
-      </c>
-      <c r="E152" s="4" t="str">
-        <f>IF($D152="","",VLOOKUP($D152,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B152">
+        <v>27</v>
+      </c>
+      <c r="C152" t="s">
+        <v>15</v>
+      </c>
+      <c r="D152">
+        <v>8596217</v>
+      </c>
+      <c r="E152" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" t="s">
-        <v>108</v>
-      </c>
-      <c r="B153" s="1">
-        <v>20</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D153" s="3">
-        <v>7548021</v>
-      </c>
-      <c r="E153" s="4" t="str">
-        <f>IF($D153="","",VLOOKUP($D153,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B153">
+        <v>28</v>
+      </c>
+      <c r="C153" t="s">
+        <v>44</v>
+      </c>
+      <c r="D153">
+        <v>8456726</v>
+      </c>
+      <c r="E153" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" t="s">
-        <v>108</v>
-      </c>
-      <c r="B154" s="1">
-        <v>21</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D154" s="3">
-        <v>7514973</v>
-      </c>
-      <c r="E154" s="4" t="str">
-        <f>IF($D154="","",VLOOKUP($D154,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B154">
+        <v>29</v>
+      </c>
+      <c r="C154" t="s">
+        <v>46</v>
+      </c>
+      <c r="D154">
+        <v>8220352</v>
+      </c>
+      <c r="E154" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>108</v>
-      </c>
-      <c r="B155" s="1">
-        <v>22</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D155" s="3">
-        <v>7392720</v>
-      </c>
-      <c r="E155" s="4" t="str">
-        <f>IF($D155="","",VLOOKUP($D155,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B155">
+        <v>30</v>
+      </c>
+      <c r="C155" t="s">
+        <v>87</v>
+      </c>
+      <c r="D155">
+        <v>8154156</v>
+      </c>
+      <c r="E155" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>108</v>
-      </c>
-      <c r="B156" s="1">
-        <v>23</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D156" s="3">
-        <v>7368735</v>
-      </c>
-      <c r="E156" s="4" t="str">
-        <f>IF($D156="","",VLOOKUP($D156,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B156">
+        <v>31</v>
+      </c>
+      <c r="C156" t="s">
+        <v>40</v>
+      </c>
+      <c r="D156">
+        <v>8127020</v>
+      </c>
+      <c r="E156" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" t="s">
-        <v>108</v>
-      </c>
-      <c r="B157" s="1">
-        <v>24</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D157" s="3">
-        <v>7299150</v>
-      </c>
-      <c r="E157" s="4" t="str">
-        <f>IF($D157="","",VLOOKUP($D157,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B157">
+        <v>32</v>
+      </c>
+      <c r="C157" t="s">
+        <v>88</v>
+      </c>
+      <c r="D157">
+        <v>7952273</v>
+      </c>
+      <c r="E157" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" t="s">
-        <v>108</v>
-      </c>
-      <c r="B158" s="1">
-        <v>25</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D158" s="3">
-        <v>7285842</v>
-      </c>
-      <c r="E158" s="4" t="str">
-        <f>IF($D158="","",VLOOKUP($D158,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B158">
+        <v>33</v>
+      </c>
+      <c r="C158" t="s">
+        <v>89</v>
+      </c>
+      <c r="D158">
+        <v>7918857</v>
+      </c>
+      <c r="E158" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" t="s">
-        <v>108</v>
-      </c>
-      <c r="B159" s="1">
-        <v>26</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D159" s="3">
-        <v>7252456</v>
-      </c>
-      <c r="E159" s="4" t="str">
-        <f>IF($D159="","",VLOOKUP($D159,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B159">
+        <v>34</v>
+      </c>
+      <c r="C159" t="s">
+        <v>19</v>
+      </c>
+      <c r="D159">
+        <v>7909501</v>
+      </c>
+      <c r="E159" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>108</v>
-      </c>
-      <c r="B160" s="1">
-        <v>27</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D160" s="3">
-        <v>7210500</v>
-      </c>
-      <c r="E160" s="4" t="str">
-        <f>IF($D160="","",VLOOKUP($D160,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>78</v>
+      </c>
+      <c r="B160">
+        <v>35</v>
+      </c>
+      <c r="C160" t="s">
+        <v>50</v>
+      </c>
+      <c r="D160">
+        <v>7876636</v>
+      </c>
+      <c r="E160" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" t="s">
-        <v>108</v>
-      </c>
-      <c r="B161" s="1">
-        <v>28</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D161" s="3">
-        <v>7095450</v>
-      </c>
-      <c r="E161" s="4" t="str">
-        <f>IF($D161="","",VLOOKUP($D161,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B161">
+        <v>36</v>
+      </c>
+      <c r="C161" t="s">
+        <v>90</v>
+      </c>
+      <c r="D161">
+        <v>7824653</v>
+      </c>
+      <c r="E161" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" t="s">
-        <v>108</v>
-      </c>
-      <c r="B162" s="1">
-        <v>29</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D162" s="3">
-        <v>5739081</v>
-      </c>
-      <c r="E162" s="4" t="str">
-        <f>IF($D162="","",VLOOKUP($D162,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B162">
+        <v>37</v>
+      </c>
+      <c r="C162" t="s">
+        <v>47</v>
+      </c>
+      <c r="D162">
+        <v>7823884</v>
+      </c>
+      <c r="E162" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" t="s">
-        <v>108</v>
-      </c>
-      <c r="B163" s="1">
-        <v>30</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D163" s="3">
-        <v>5561285</v>
-      </c>
-      <c r="E163" s="4" t="str">
-        <f>IF($D163="","",VLOOKUP($D163,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B163">
+        <v>38</v>
+      </c>
+      <c r="C163" t="s">
+        <v>42</v>
+      </c>
+      <c r="D163">
+        <v>7679597</v>
+      </c>
+      <c r="E163" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" t="s">
-        <v>108</v>
-      </c>
-      <c r="B164" s="1">
-        <v>31</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D164" s="3">
-        <v>5434650</v>
-      </c>
-      <c r="E164" s="4" t="str">
-        <f>IF($D164="","",VLOOKUP($D164,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B164">
+        <v>39</v>
+      </c>
+      <c r="C164" t="s">
+        <v>91</v>
+      </c>
+      <c r="D164">
+        <v>7635056</v>
+      </c>
+      <c r="E164" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>108</v>
-      </c>
-      <c r="B165" s="1">
-        <v>32</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D165" s="3">
-        <v>5171951</v>
-      </c>
-      <c r="E165" s="4" t="str">
-        <f>IF($D165="","",VLOOKUP($D165,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B165">
+        <v>40</v>
+      </c>
+      <c r="C165" t="s">
+        <v>92</v>
+      </c>
+      <c r="D165">
+        <v>7579677</v>
+      </c>
+      <c r="E165" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" t="s">
-        <v>108</v>
-      </c>
-      <c r="B166" s="1">
-        <v>33</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D166" s="3">
-        <v>5091005</v>
-      </c>
-      <c r="E166" s="4" t="str">
-        <f>IF($D166="","",VLOOKUP($D166,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B166">
+        <v>41</v>
+      </c>
+      <c r="C166" t="s">
+        <v>45</v>
+      </c>
+      <c r="D166">
+        <v>7552044</v>
+      </c>
+      <c r="E166" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>108</v>
-      </c>
-      <c r="B167" s="1">
-        <v>34</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D167" s="3">
-        <v>5016847</v>
-      </c>
-      <c r="E167" s="4" t="str">
-        <f>IF($D167="","",VLOOKUP($D167,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B167">
+        <v>42</v>
+      </c>
+      <c r="C167" t="s">
+        <v>53</v>
+      </c>
+      <c r="D167">
+        <v>7462230</v>
+      </c>
+      <c r="E167" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" t="s">
-        <v>108</v>
-      </c>
-      <c r="B168" s="1">
-        <v>35</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D168" s="3">
-        <v>4630800</v>
-      </c>
-      <c r="E168" s="4" t="str">
-        <f>IF($D168="","",VLOOKUP($D168,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B168">
+        <v>43</v>
+      </c>
+      <c r="C168" t="s">
+        <v>30</v>
+      </c>
+      <c r="D168">
+        <v>7423633</v>
+      </c>
+      <c r="E168" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" t="s">
-        <v>108</v>
-      </c>
-      <c r="B169" s="1">
-        <v>36</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D169" s="3">
-        <v>4537987</v>
-      </c>
-      <c r="E169" s="4" t="str">
-        <f>IF($D169="","",VLOOKUP($D169,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B169">
+        <v>44</v>
+      </c>
+      <c r="C169" t="s">
+        <v>17</v>
+      </c>
+      <c r="D169">
+        <v>7327050</v>
+      </c>
+      <c r="E169" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" t="s">
-        <v>108</v>
-      </c>
-      <c r="B170" s="1">
-        <v>37</v>
-      </c>
-      <c r="C170" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D170" s="3">
-        <v>4444305</v>
-      </c>
-      <c r="E170" s="4" t="str">
-        <f>IF($D170="","",VLOOKUP($D170,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B170">
+        <v>45</v>
+      </c>
+      <c r="C170" t="s">
+        <v>22</v>
+      </c>
+      <c r="D170">
+        <v>6678842</v>
+      </c>
+      <c r="E170" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" t="s">
-        <v>108</v>
-      </c>
-      <c r="B171" s="1">
-        <v>38</v>
-      </c>
-      <c r="C171" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D171" s="3">
-        <v>4393558</v>
-      </c>
-      <c r="E171" s="4" t="str">
-        <f>IF($D171="","",VLOOKUP($D171,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B171">
+        <v>46</v>
+      </c>
+      <c r="C171" t="s">
+        <v>93</v>
+      </c>
+      <c r="D171">
+        <v>6177989</v>
+      </c>
+      <c r="E171" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" t="s">
-        <v>108</v>
-      </c>
-      <c r="B172" s="1">
-        <v>39</v>
-      </c>
-      <c r="C172" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D172" s="3">
-        <v>4361685</v>
-      </c>
-      <c r="E172" s="4" t="str">
-        <f>IF($D172="","",VLOOKUP($D172,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B172">
+        <v>47</v>
+      </c>
+      <c r="C172" t="s">
+        <v>67</v>
+      </c>
+      <c r="D172">
+        <v>5901298</v>
+      </c>
+      <c r="E172" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" t="s">
-        <v>108</v>
-      </c>
-      <c r="B173" s="1">
-        <v>40</v>
-      </c>
-      <c r="C173" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D173" s="3">
-        <v>4314000</v>
-      </c>
-      <c r="E173" s="4" t="str">
-        <f>IF($D173="","",VLOOKUP($D173,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B173">
+        <v>48</v>
+      </c>
+      <c r="C173" t="s">
+        <v>60</v>
+      </c>
+      <c r="D173">
+        <v>5097585</v>
+      </c>
+      <c r="E173" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" t="s">
-        <v>108</v>
-      </c>
-      <c r="B174" s="1">
-        <v>41</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D174" s="3">
-        <v>4305372</v>
-      </c>
-      <c r="E174" s="4" t="str">
-        <f>IF($D174="","",VLOOKUP($D174,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B174">
+        <v>49</v>
+      </c>
+      <c r="C174" t="s">
+        <v>48</v>
+      </c>
+      <c r="D174">
+        <v>5036088</v>
+      </c>
+      <c r="E174" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" t="s">
-        <v>108</v>
-      </c>
-      <c r="B175" s="1">
-        <v>42</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D175" s="3">
-        <v>4250088</v>
-      </c>
-      <c r="E175" s="4" t="str">
-        <f>IF($D175="","",VLOOKUP($D175,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B175">
+        <v>50</v>
+      </c>
+      <c r="C175" t="s">
+        <v>33</v>
+      </c>
+      <c r="D175">
+        <v>4821347</v>
+      </c>
+      <c r="E175" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" t="s">
-        <v>108</v>
-      </c>
-      <c r="B176" s="1">
-        <v>43</v>
-      </c>
-      <c r="C176" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D176" s="3">
-        <v>4174414</v>
-      </c>
-      <c r="E176" s="4" t="str">
-        <f>IF($D176="","",VLOOKUP($D176,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B176">
+        <v>51</v>
+      </c>
+      <c r="C176" t="s">
+        <v>55</v>
+      </c>
+      <c r="D176">
+        <v>4599953</v>
+      </c>
+      <c r="E176" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" t="s">
-        <v>108</v>
-      </c>
-      <c r="B177" s="1">
-        <v>44</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D177" s="3">
-        <v>4151246</v>
-      </c>
-      <c r="E177" s="4" t="str">
-        <f>IF($D177="","",VLOOKUP($D177,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B177">
+        <v>52</v>
+      </c>
+      <c r="C177" t="s">
+        <v>64</v>
+      </c>
+      <c r="D177">
+        <v>4332112</v>
+      </c>
+      <c r="E177" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" t="s">
-        <v>108</v>
-      </c>
-      <c r="B178" s="1">
-        <v>45</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D178" s="3">
-        <v>4081096</v>
-      </c>
-      <c r="E178" s="4" t="str">
-        <f>IF($D178="","",VLOOKUP($D178,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B178">
+        <v>53</v>
+      </c>
+      <c r="C178" t="s">
+        <v>58</v>
+      </c>
+      <c r="D178">
+        <v>4235009</v>
+      </c>
+      <c r="E178" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" t="s">
-        <v>108</v>
-      </c>
-      <c r="B179" s="1">
-        <v>46</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D179" s="3">
-        <v>4033323</v>
-      </c>
-      <c r="E179" s="4" t="str">
-        <f>IF($D179="","",VLOOKUP($D179,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B179">
+        <v>54</v>
+      </c>
+      <c r="C179" t="s">
+        <v>12</v>
+      </c>
+      <c r="D179">
+        <v>4226803</v>
+      </c>
+      <c r="E179" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" t="s">
-        <v>108</v>
-      </c>
-      <c r="B180" s="1">
-        <v>47</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D180" s="3">
-        <v>4029200</v>
-      </c>
-      <c r="E180" s="4" t="str">
-        <f>IF($D180="","",VLOOKUP($D180,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B180">
+        <v>55</v>
+      </c>
+      <c r="C180" t="s">
+        <v>43</v>
+      </c>
+      <c r="D180">
+        <v>3992666</v>
+      </c>
+      <c r="E180" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" t="s">
-        <v>108</v>
-      </c>
-      <c r="B181" s="1">
-        <v>48</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D181" s="3">
-        <v>4000500</v>
-      </c>
-      <c r="E181" s="4" t="str">
-        <f>IF($D181="","",VLOOKUP($D181,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B181">
+        <v>56</v>
+      </c>
+      <c r="C181" t="s">
+        <v>66</v>
+      </c>
+      <c r="D181">
+        <v>3935236</v>
+      </c>
+      <c r="E181" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" t="s">
-        <v>108</v>
-      </c>
-      <c r="B182" s="1">
-        <v>49</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D182" s="3">
-        <v>3893926</v>
-      </c>
-      <c r="E182" s="4" t="str">
-        <f>IF($D182="","",VLOOKUP($D182,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B182">
+        <v>57</v>
+      </c>
+      <c r="C182" t="s">
+        <v>71</v>
+      </c>
+      <c r="D182">
+        <v>3819189</v>
+      </c>
+      <c r="E182" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="A183" t="s">
-        <v>108</v>
-      </c>
-      <c r="B183" s="1">
-        <v>50</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D183" s="3">
-        <v>3892915</v>
-      </c>
-      <c r="E183" s="4" t="str">
-        <f>IF($D183="","",VLOOKUP($D183,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B183">
+        <v>58</v>
+      </c>
+      <c r="C183" t="s">
+        <v>52</v>
+      </c>
+      <c r="D183">
+        <v>2896389</v>
+      </c>
+      <c r="E183" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" t="s">
-        <v>108</v>
-      </c>
-      <c r="B184" s="1">
-        <v>51</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D184" s="3">
-        <v>3817624</v>
-      </c>
-      <c r="E184" s="4" t="str">
-        <f>IF($D184="","",VLOOKUP($D184,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B184">
+        <v>59</v>
+      </c>
+      <c r="C184" t="s">
+        <v>94</v>
+      </c>
+      <c r="D184">
+        <v>2645896</v>
+      </c>
+      <c r="E184" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" t="s">
-        <v>108</v>
-      </c>
-      <c r="B185" s="1">
-        <v>52</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D185" s="3">
-        <v>3776295</v>
-      </c>
-      <c r="E185" s="4" t="str">
-        <f>IF($D185="","",VLOOKUP($D185,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B185">
+        <v>60</v>
+      </c>
+      <c r="C185" t="s">
+        <v>56</v>
+      </c>
+      <c r="D185">
+        <v>2195612</v>
+      </c>
+      <c r="E185" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" t="s">
-        <v>108</v>
-      </c>
-      <c r="B186" s="1">
-        <v>53</v>
-      </c>
-      <c r="C186" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B186">
         <v>61</v>
       </c>
-      <c r="D186" s="3">
-        <v>3636629</v>
-      </c>
-      <c r="E186" s="4" t="str">
-        <f>IF($D186="","",VLOOKUP($D186,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+      <c r="C186" t="s">
+        <v>29</v>
+      </c>
+      <c r="D186">
+        <v>1908787</v>
+      </c>
+      <c r="E186" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" t="s">
-        <v>108</v>
-      </c>
-      <c r="B187" s="1">
-        <v>54</v>
-      </c>
-      <c r="C187" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D187" s="3">
-        <v>3620200</v>
-      </c>
-      <c r="E187" s="4" t="str">
-        <f>IF($D187="","",VLOOKUP($D187,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B187">
+        <v>62</v>
+      </c>
+      <c r="C187" t="s">
+        <v>65</v>
+      </c>
+      <c r="D187">
+        <v>1890847</v>
+      </c>
+      <c r="E187" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" t="s">
-        <v>108</v>
-      </c>
-      <c r="B188" s="1">
-        <v>55</v>
-      </c>
-      <c r="C188" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D188" s="3">
-        <v>3414335</v>
-      </c>
-      <c r="E188" s="4" t="str">
-        <f>IF($D188="","",VLOOKUP($D188,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B188">
+        <v>63</v>
+      </c>
+      <c r="C188" t="s">
+        <v>63</v>
+      </c>
+      <c r="D188">
+        <v>1772463</v>
+      </c>
+      <c r="E188" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="189" spans="1:5">
       <c r="A189" t="s">
-        <v>108</v>
-      </c>
-      <c r="B189" s="1">
-        <v>56</v>
-      </c>
-      <c r="C189" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D189" s="3">
-        <v>3164754</v>
-      </c>
-      <c r="E189" s="4" t="str">
-        <f>IF($D189="","",VLOOKUP($D189,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B189">
+        <v>64</v>
+      </c>
+      <c r="C189" t="s">
+        <v>70</v>
+      </c>
+      <c r="D189">
+        <v>1472500</v>
+      </c>
+      <c r="E189" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="190" spans="1:5">
       <c r="A190" t="s">
-        <v>108</v>
-      </c>
-      <c r="B190" s="1">
-        <v>57</v>
-      </c>
-      <c r="C190" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D190" s="3">
-        <v>3063699</v>
-      </c>
-      <c r="E190" s="4" t="str">
-        <f>IF($D190="","",VLOOKUP($D190,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B190">
+        <v>65</v>
+      </c>
+      <c r="C190" t="s">
+        <v>68</v>
+      </c>
+      <c r="D190">
+        <v>1425274</v>
+      </c>
+      <c r="E190" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" t="s">
-        <v>108</v>
-      </c>
-      <c r="B191" s="1">
-        <v>58</v>
-      </c>
-      <c r="C191" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D191" s="3">
-        <v>2777032</v>
-      </c>
-      <c r="E191" s="4" t="str">
-        <f>IF($D191="","",VLOOKUP($D191,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>78</v>
+      </c>
+      <c r="B191">
+        <v>66</v>
+      </c>
+      <c r="C191" t="s">
+        <v>72</v>
+      </c>
+      <c r="D191">
+        <v>1226829</v>
+      </c>
+      <c r="E191" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" t="s">
-        <v>108</v>
-      </c>
-      <c r="B192" s="1">
-        <v>59</v>
-      </c>
-      <c r="C192" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D192" s="3">
-        <v>2391014</v>
-      </c>
-      <c r="E192" s="4" t="str">
-        <f>IF($D192="","",VLOOKUP($D192,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>7단계</v>
+        <v>78</v>
+      </c>
+      <c r="B192">
+        <v>67</v>
+      </c>
+      <c r="C192" t="s">
+        <v>75</v>
+      </c>
+      <c r="D192">
+        <v>460000</v>
+      </c>
+      <c r="E192" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B193" s="1">
-        <v>60</v>
-      </c>
-      <c r="C193" s="5" t="s">
-        <v>85</v>
+        <v>1</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="D193" s="3">
-        <v>2371425</v>
+        <v>15915600</v>
       </c>
       <c r="E193" s="4" t="str">
         <f>IF($D193="","",VLOOKUP($D193,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>7단계</v>
+        <v>9단계</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B194" s="1">
-        <v>61</v>
-      </c>
-      <c r="C194" s="2" t="s">
-        <v>82</v>
+        <v>2</v>
+      </c>
+      <c r="C194" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="D194" s="3">
-        <v>2022500</v>
+        <v>12925350</v>
       </c>
       <c r="E194" s="4" t="str">
         <f>IF($D194="","",VLOOKUP($D194,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
+        <v>9단계</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B195" s="1">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D195" s="3">
-        <v>1764375</v>
+        <v>12016650</v>
       </c>
       <c r="E195" s="4" t="str">
         <f>IF($D195="","",VLOOKUP($D195,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
+        <v>9단계</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B196" s="1">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="D196" s="3">
-        <v>1739773</v>
+        <v>9907350</v>
       </c>
       <c r="E196" s="4" t="str">
         <f>IF($D196="","",VLOOKUP($D196,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
+        <v>9단계</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B197" s="1">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="D197" s="3">
-        <v>1685105</v>
+        <v>9868650</v>
       </c>
       <c r="E197" s="4" t="str">
         <f>IF($D197="","",VLOOKUP($D197,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
+        <v>9단계</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B198" s="1">
-        <v>65</v>
-      </c>
-      <c r="C198" s="2">
-        <v>1090</v>
+        <v>6</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="D198" s="3">
-        <v>1619227</v>
+        <v>9143700</v>
       </c>
       <c r="E198" s="4" t="str">
         <f>IF($D198="","",VLOOKUP($D198,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
+        <v>9단계</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B199" s="1">
-        <v>66</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>84</v>
+        <v>7</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="D199" s="3">
-        <v>1116967</v>
+        <v>9141450</v>
       </c>
       <c r="E199" s="4" t="str">
         <f>IF($D199="","",VLOOKUP($D199,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
+        <v>9단계</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B200" s="1">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="D200" s="3">
-        <v>481250</v>
+        <v>9065250</v>
       </c>
       <c r="E200" s="4" t="str">
         <f>IF($D200="","",VLOOKUP($D200,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>3단계</v>
+        <v>9단계</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B201" s="1">
-        <v>68</v>
-      </c>
-      <c r="C201" s="5" t="s">
-        <v>89</v>
+        <v>9</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="D201" s="3">
-        <v>368750</v>
+        <v>9017250</v>
       </c>
       <c r="E201" s="4" t="str">
         <f>IF($D201="","",VLOOKUP($D201,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" t="s">
+        <v>95</v>
+      </c>
+      <c r="B202" s="1">
+        <v>10</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D202" s="3">
+        <v>8908800</v>
+      </c>
+      <c r="E202" s="4" t="str">
+        <f>IF($D202="","",VLOOKUP($D202,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" t="s">
+        <v>95</v>
+      </c>
+      <c r="B203" s="1">
+        <v>11</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D203" s="3">
+        <v>8266050</v>
+      </c>
+      <c r="E203" s="4" t="str">
+        <f>IF($D203="","",VLOOKUP($D203,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" t="s">
+        <v>95</v>
+      </c>
+      <c r="B204" s="1">
+        <v>12</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D204" s="3">
+        <v>8226750</v>
+      </c>
+      <c r="E204" s="4" t="str">
+        <f>IF($D204="","",VLOOKUP($D204,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" t="s">
+        <v>95</v>
+      </c>
+      <c r="B205" s="1">
+        <v>13</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D205" s="3">
+        <v>8125259</v>
+      </c>
+      <c r="E205" s="4" t="str">
+        <f>IF($D205="","",VLOOKUP($D205,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" t="s">
+        <v>95</v>
+      </c>
+      <c r="B206" s="1">
+        <v>14</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D206" s="3">
+        <v>7855412</v>
+      </c>
+      <c r="E206" s="4" t="str">
+        <f>IF($D206="","",VLOOKUP($D206,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" t="s">
+        <v>95</v>
+      </c>
+      <c r="B207" s="1">
+        <v>15</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D207" s="3">
+        <v>7740750</v>
+      </c>
+      <c r="E207" s="4" t="str">
+        <f>IF($D207="","",VLOOKUP($D207,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" t="s">
+        <v>95</v>
+      </c>
+      <c r="B208" s="1">
+        <v>16</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D208" s="3">
+        <v>7716900</v>
+      </c>
+      <c r="E208" s="4" t="str">
+        <f>IF($D208="","",VLOOKUP($D208,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" t="s">
+        <v>95</v>
+      </c>
+      <c r="B209" s="1">
+        <v>17</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D209" s="3">
+        <v>7697397</v>
+      </c>
+      <c r="E209" s="4" t="str">
+        <f>IF($D209="","",VLOOKUP($D209,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" t="s">
+        <v>95</v>
+      </c>
+      <c r="B210" s="1">
+        <v>18</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D210" s="3">
+        <v>7694109</v>
+      </c>
+      <c r="E210" s="4" t="str">
+        <f>IF($D210="","",VLOOKUP($D210,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" t="s">
+        <v>95</v>
+      </c>
+      <c r="B211" s="1">
+        <v>19</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D211" s="3">
+        <v>7624294</v>
+      </c>
+      <c r="E211" s="4" t="str">
+        <f>IF($D211="","",VLOOKUP($D211,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" t="s">
+        <v>95</v>
+      </c>
+      <c r="B212" s="1">
+        <v>20</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D212" s="3">
+        <v>7548021</v>
+      </c>
+      <c r="E212" s="4" t="str">
+        <f>IF($D212="","",VLOOKUP($D212,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" t="s">
+        <v>95</v>
+      </c>
+      <c r="B213" s="1">
+        <v>21</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D213" s="3">
+        <v>7514973</v>
+      </c>
+      <c r="E213" s="4" t="str">
+        <f>IF($D213="","",VLOOKUP($D213,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" t="s">
+        <v>95</v>
+      </c>
+      <c r="B214" s="1">
+        <v>22</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D214" s="3">
+        <v>7392720</v>
+      </c>
+      <c r="E214" s="4" t="str">
+        <f>IF($D214="","",VLOOKUP($D214,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" t="s">
+        <v>95</v>
+      </c>
+      <c r="B215" s="1">
+        <v>23</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D215" s="3">
+        <v>7368735</v>
+      </c>
+      <c r="E215" s="4" t="str">
+        <f>IF($D215="","",VLOOKUP($D215,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" t="s">
+        <v>95</v>
+      </c>
+      <c r="B216" s="1">
+        <v>24</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D216" s="3">
+        <v>7299150</v>
+      </c>
+      <c r="E216" s="4" t="str">
+        <f>IF($D216="","",VLOOKUP($D216,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" t="s">
+        <v>95</v>
+      </c>
+      <c r="B217" s="1">
+        <v>25</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D217" s="3">
+        <v>7285842</v>
+      </c>
+      <c r="E217" s="4" t="str">
+        <f>IF($D217="","",VLOOKUP($D217,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" t="s">
+        <v>95</v>
+      </c>
+      <c r="B218" s="1">
+        <v>26</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D218" s="3">
+        <v>7252456</v>
+      </c>
+      <c r="E218" s="4" t="str">
+        <f>IF($D218="","",VLOOKUP($D218,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" t="s">
+        <v>95</v>
+      </c>
+      <c r="B219" s="1">
+        <v>27</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D219" s="3">
+        <v>7210500</v>
+      </c>
+      <c r="E219" s="4" t="str">
+        <f>IF($D219="","",VLOOKUP($D219,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" t="s">
+        <v>95</v>
+      </c>
+      <c r="B220" s="1">
+        <v>28</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D220" s="3">
+        <v>7095450</v>
+      </c>
+      <c r="E220" s="4" t="str">
+        <f>IF($D220="","",VLOOKUP($D220,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" t="s">
+        <v>95</v>
+      </c>
+      <c r="B221" s="1">
+        <v>29</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D221" s="3">
+        <v>5739081</v>
+      </c>
+      <c r="E221" s="4" t="str">
+        <f>IF($D221="","",VLOOKUP($D221,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" t="s">
+        <v>95</v>
+      </c>
+      <c r="B222" s="1">
+        <v>30</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D222" s="3">
+        <v>5561285</v>
+      </c>
+      <c r="E222" s="4" t="str">
+        <f>IF($D222="","",VLOOKUP($D222,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" t="s">
+        <v>95</v>
+      </c>
+      <c r="B223" s="1">
+        <v>31</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D223" s="3">
+        <v>5434650</v>
+      </c>
+      <c r="E223" s="4" t="str">
+        <f>IF($D223="","",VLOOKUP($D223,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" t="s">
+        <v>95</v>
+      </c>
+      <c r="B224" s="1">
+        <v>32</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D224" s="3">
+        <v>5171951</v>
+      </c>
+      <c r="E224" s="4" t="str">
+        <f>IF($D224="","",VLOOKUP($D224,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" t="s">
+        <v>95</v>
+      </c>
+      <c r="B225" s="1">
+        <v>33</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D225" s="3">
+        <v>5091005</v>
+      </c>
+      <c r="E225" s="4" t="str">
+        <f>IF($D225="","",VLOOKUP($D225,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" t="s">
+        <v>95</v>
+      </c>
+      <c r="B226" s="1">
+        <v>34</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D226" s="3">
+        <v>5016847</v>
+      </c>
+      <c r="E226" s="4" t="str">
+        <f>IF($D226="","",VLOOKUP($D226,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" t="s">
+        <v>95</v>
+      </c>
+      <c r="B227" s="1">
+        <v>35</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D227" s="3">
+        <v>4630800</v>
+      </c>
+      <c r="E227" s="4" t="str">
+        <f>IF($D227="","",VLOOKUP($D227,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" t="s">
+        <v>95</v>
+      </c>
+      <c r="B228" s="1">
+        <v>36</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D228" s="3">
+        <v>4537987</v>
+      </c>
+      <c r="E228" s="4" t="str">
+        <f>IF($D228="","",VLOOKUP($D228,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" t="s">
+        <v>95</v>
+      </c>
+      <c r="B229" s="1">
+        <v>37</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D229" s="3">
+        <v>4444305</v>
+      </c>
+      <c r="E229" s="4" t="str">
+        <f>IF($D229="","",VLOOKUP($D229,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" t="s">
+        <v>95</v>
+      </c>
+      <c r="B230" s="1">
+        <v>38</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D230" s="3">
+        <v>4393558</v>
+      </c>
+      <c r="E230" s="4" t="str">
+        <f>IF($D230="","",VLOOKUP($D230,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" t="s">
+        <v>95</v>
+      </c>
+      <c r="B231" s="1">
+        <v>39</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D231" s="3">
+        <v>4361685</v>
+      </c>
+      <c r="E231" s="4" t="str">
+        <f>IF($D231="","",VLOOKUP($D231,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" t="s">
+        <v>95</v>
+      </c>
+      <c r="B232" s="1">
+        <v>40</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D232" s="3">
+        <v>4314000</v>
+      </c>
+      <c r="E232" s="4" t="str">
+        <f>IF($D232="","",VLOOKUP($D232,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" t="s">
+        <v>95</v>
+      </c>
+      <c r="B233" s="1">
+        <v>41</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D233" s="3">
+        <v>4305372</v>
+      </c>
+      <c r="E233" s="4" t="str">
+        <f>IF($D233="","",VLOOKUP($D233,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" t="s">
+        <v>95</v>
+      </c>
+      <c r="B234" s="1">
+        <v>42</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D234" s="3">
+        <v>4250088</v>
+      </c>
+      <c r="E234" s="4" t="str">
+        <f>IF($D234="","",VLOOKUP($D234,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" t="s">
+        <v>95</v>
+      </c>
+      <c r="B235" s="1">
+        <v>43</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D235" s="3">
+        <v>4174414</v>
+      </c>
+      <c r="E235" s="4" t="str">
+        <f>IF($D235="","",VLOOKUP($D235,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" t="s">
+        <v>95</v>
+      </c>
+      <c r="B236" s="1">
+        <v>44</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D236" s="3">
+        <v>4151246</v>
+      </c>
+      <c r="E236" s="4" t="str">
+        <f>IF($D236="","",VLOOKUP($D236,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" t="s">
+        <v>95</v>
+      </c>
+      <c r="B237" s="1">
+        <v>45</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D237" s="3">
+        <v>4081096</v>
+      </c>
+      <c r="E237" s="4" t="str">
+        <f>IF($D237="","",VLOOKUP($D237,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" t="s">
+        <v>95</v>
+      </c>
+      <c r="B238" s="1">
+        <v>46</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D238" s="3">
+        <v>4033323</v>
+      </c>
+      <c r="E238" s="4" t="str">
+        <f>IF($D238="","",VLOOKUP($D238,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" t="s">
+        <v>95</v>
+      </c>
+      <c r="B239" s="1">
+        <v>47</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D239" s="3">
+        <v>4029200</v>
+      </c>
+      <c r="E239" s="4" t="str">
+        <f>IF($D239="","",VLOOKUP($D239,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" t="s">
+        <v>95</v>
+      </c>
+      <c r="B240" s="1">
+        <v>48</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D240" s="3">
+        <v>4000500</v>
+      </c>
+      <c r="E240" s="4" t="str">
+        <f>IF($D240="","",VLOOKUP($D240,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" t="s">
+        <v>95</v>
+      </c>
+      <c r="B241" s="1">
+        <v>49</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D241" s="3">
+        <v>3893926</v>
+      </c>
+      <c r="E241" s="4" t="str">
+        <f>IF($D241="","",VLOOKUP($D241,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" t="s">
+        <v>95</v>
+      </c>
+      <c r="B242" s="1">
+        <v>50</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D242" s="3">
+        <v>3892915</v>
+      </c>
+      <c r="E242" s="4" t="str">
+        <f>IF($D242="","",VLOOKUP($D242,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" t="s">
+        <v>95</v>
+      </c>
+      <c r="B243" s="1">
+        <v>51</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D243" s="3">
+        <v>3817624</v>
+      </c>
+      <c r="E243" s="4" t="str">
+        <f>IF($D243="","",VLOOKUP($D243,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" t="s">
+        <v>95</v>
+      </c>
+      <c r="B244" s="1">
+        <v>52</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D244" s="3">
+        <v>3776295</v>
+      </c>
+      <c r="E244" s="4" t="str">
+        <f>IF($D244="","",VLOOKUP($D244,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" t="s">
+        <v>95</v>
+      </c>
+      <c r="B245" s="1">
+        <v>53</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D245" s="3">
+        <v>3636629</v>
+      </c>
+      <c r="E245" s="4" t="str">
+        <f>IF($D245="","",VLOOKUP($D245,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" t="s">
+        <v>95</v>
+      </c>
+      <c r="B246" s="1">
+        <v>54</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D246" s="3">
+        <v>3620200</v>
+      </c>
+      <c r="E246" s="4" t="str">
+        <f>IF($D246="","",VLOOKUP($D246,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" t="s">
+        <v>95</v>
+      </c>
+      <c r="B247" s="1">
+        <v>55</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D247" s="3">
+        <v>3414335</v>
+      </c>
+      <c r="E247" s="4" t="str">
+        <f>IF($D247="","",VLOOKUP($D247,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" t="s">
+        <v>95</v>
+      </c>
+      <c r="B248" s="1">
+        <v>56</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D248" s="3">
+        <v>3164754</v>
+      </c>
+      <c r="E248" s="4" t="str">
+        <f>IF($D248="","",VLOOKUP($D248,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" t="s">
+        <v>95</v>
+      </c>
+      <c r="B249" s="1">
+        <v>57</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D249" s="3">
+        <v>3063699</v>
+      </c>
+      <c r="E249" s="4" t="str">
+        <f>IF($D249="","",VLOOKUP($D249,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" t="s">
+        <v>95</v>
+      </c>
+      <c r="B250" s="1">
+        <v>58</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D250" s="3">
+        <v>2777032</v>
+      </c>
+      <c r="E250" s="4" t="str">
+        <f>IF($D250="","",VLOOKUP($D250,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" t="s">
+        <v>95</v>
+      </c>
+      <c r="B251" s="1">
+        <v>59</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D251" s="3">
+        <v>2391014</v>
+      </c>
+      <c r="E251" s="4" t="str">
+        <f>IF($D251="","",VLOOKUP($D251,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>7단계</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" t="s">
+        <v>95</v>
+      </c>
+      <c r="B252" s="1">
+        <v>60</v>
+      </c>
+      <c r="C252" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D252" s="3">
+        <v>2371425</v>
+      </c>
+      <c r="E252" s="4" t="str">
+        <f>IF($D252="","",VLOOKUP($D252,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>7단계</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" t="s">
+        <v>95</v>
+      </c>
+      <c r="B253" s="1">
+        <v>61</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D253" s="3">
+        <v>2022500</v>
+      </c>
+      <c r="E253" s="4" t="str">
+        <f>IF($D253="","",VLOOKUP($D253,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" t="s">
+        <v>95</v>
+      </c>
+      <c r="B254" s="1">
+        <v>62</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D254" s="3">
+        <v>1764375</v>
+      </c>
+      <c r="E254" s="4" t="str">
+        <f>IF($D254="","",VLOOKUP($D254,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" t="s">
+        <v>95</v>
+      </c>
+      <c r="B255" s="1">
+        <v>63</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D255" s="3">
+        <v>1739773</v>
+      </c>
+      <c r="E255" s="4" t="str">
+        <f>IF($D255="","",VLOOKUP($D255,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" t="s">
+        <v>95</v>
+      </c>
+      <c r="B256" s="1">
+        <v>64</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D256" s="3">
+        <v>1685105</v>
+      </c>
+      <c r="E256" s="4" t="str">
+        <f>IF($D256="","",VLOOKUP($D256,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" t="s">
+        <v>95</v>
+      </c>
+      <c r="B257" s="1">
+        <v>65</v>
+      </c>
+      <c r="C257" s="2">
+        <v>1090</v>
+      </c>
+      <c r="D257" s="3">
+        <v>1619227</v>
+      </c>
+      <c r="E257" s="4" t="str">
+        <f>IF($D257="","",VLOOKUP($D257,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" t="s">
+        <v>95</v>
+      </c>
+      <c r="B258" s="1">
+        <v>66</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D258" s="3">
+        <v>1116967</v>
+      </c>
+      <c r="E258" s="4" t="str">
+        <f>IF($D258="","",VLOOKUP($D258,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" t="s">
+        <v>95</v>
+      </c>
+      <c r="B259" s="1">
+        <v>67</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D259" s="3">
+        <v>481250</v>
+      </c>
+      <c r="E259" s="4" t="str">
+        <f>IF($D259="","",VLOOKUP($D259,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>3단계</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" t="s">
+        <v>95</v>
+      </c>
+      <c r="B260" s="1">
+        <v>68</v>
+      </c>
+      <c r="C260" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D260" s="3">
+        <v>368750</v>
+      </c>
+      <c r="E260" s="4" t="str">
+        <f>IF($D260="","",VLOOKUP($D260,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>3단계</v>
       </c>
     </row>
@@ -4485,24 +5488,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{814CF8B3-59E7-49E3-9A7E-41B471C26A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F35D080-EF37-4203-9228-2022DFA27B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,6 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="112">
   <si>
     <t>📦 월별 보관 — 2026-06  (날짜별 길드전 랭킹 누적)</t>
   </si>
@@ -372,6 +371,9 @@
   </si>
   <si>
     <t>📦 월별 보관 — 2026-07  (날짜별 길드전 랭킹 누적)</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
   </si>
 </sst>
 </file>
@@ -496,15 +498,15 @@
       <sheetName val="기준표"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8">
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1">
         <row r="4">
           <cell r="B4">
             <v>0</v>
@@ -989,13 +991,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E260"/>
+  <dimension ref="A1:E261"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="49.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5473,6 +5475,24 @@
       <c r="E260" s="4" t="str">
         <f>IF($D260="","",VLOOKUP($D260,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>3단계</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" t="s">
+        <v>111</v>
+      </c>
+      <c r="B261" s="1">
+        <v>68</v>
+      </c>
+      <c r="C261" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D261" s="3">
+        <v>311111168750</v>
+      </c>
+      <c r="E261" s="4" t="str">
+        <f>IF($D261="","",VLOOKUP($D261,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
   </sheetData>

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F35D080-EF37-4203-9228-2022DFA27B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A134F4E4-3B96-48D6-830F-879110ACB88C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -422,7 +422,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -445,11 +445,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -465,6 +476,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5481,14 +5498,14 @@
       <c r="A261" t="s">
         <v>111</v>
       </c>
-      <c r="B261" s="1">
-        <v>68</v>
+      <c r="B261" s="6">
+        <v>1</v>
       </c>
       <c r="C261" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D261" s="3">
-        <v>311111168750</v>
+      <c r="D261" s="7">
+        <v>2000012321</v>
       </c>
       <c r="E261" s="4" t="str">
         <f>IF($D261="","",VLOOKUP($D261,[1]기준표!$B$4:$C$12,2,TRUE()))</f>

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A134F4E4-3B96-48D6-830F-879110ACB88C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12D5AF4-DA2A-4C9D-8333-F2520FB6E0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="111">
   <si>
     <t>📦 월별 보관 — 2026-06  (날짜별 길드전 랭킹 누적)</t>
   </si>
@@ -371,9 +371,6 @@
   </si>
   <si>
     <t>📦 월별 보관 — 2026-07  (날짜별 길드전 랭킹 누적)</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
   </si>
 </sst>
 </file>
@@ -422,7 +419,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -445,22 +442,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -476,12 +462,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1008,7 +988,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E261"/>
+  <dimension ref="A1:E260"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="49.75" bestFit="1" customWidth="1"/>
@@ -5492,24 +5472,6 @@
       <c r="E260" s="4" t="str">
         <f>IF($D260="","",VLOOKUP($D260,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>3단계</v>
-      </c>
-    </row>
-    <row r="261" spans="1:5">
-      <c r="A261" t="s">
-        <v>111</v>
-      </c>
-      <c r="B261" s="6">
-        <v>1</v>
-      </c>
-      <c r="C261" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D261" s="7">
-        <v>2000012321</v>
-      </c>
-      <c r="E261" s="4" t="str">
-        <f>IF($D261="","",VLOOKUP($D261,[1]기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
       </c>
     </row>
   </sheetData>

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12D5AF4-DA2A-4C9D-8333-F2520FB6E0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D4867B-3B8E-429A-87BC-C1D7019BD957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27068DC4-F330-4A99-BCF5-8A3BF90F7E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21429AD9-1B55-47E2-BD52-2E8D36635C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21600" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="기준표" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="150">
   <si>
     <t>📦 월별 보관 — 2026-06  (날짜별 길드전 랭킹 누적)</t>
   </si>
@@ -304,9 +304,6 @@
     <t>명령하디마라</t>
   </si>
   <si>
-    <t>해녀도앤댈리는뒈</t>
-  </si>
-  <si>
     <t>쉰데렐라</t>
   </si>
   <si>
@@ -355,33 +352,12 @@
     <t>임당터는단소빌런</t>
   </si>
   <si>
-    <t>쇠속모텔</t>
-  </si>
-  <si>
-    <t>왜요워</t>
-  </si>
-  <si>
-    <t>댓은홍시</t>
-  </si>
-  <si>
-    <t>베늉이마깐데또까</t>
-  </si>
-  <si>
-    <t>독킨답</t>
-  </si>
-  <si>
     <t>핑도노-품치고-생각하는-편</t>
   </si>
   <si>
-    <t>독거너인춘삼</t>
-  </si>
-  <si>
     <t>뉴스나은그사람</t>
   </si>
   <si>
-    <t>진짜한잉만나못민니</t>
-  </si>
-  <si>
     <t>슴격이다개스키야</t>
   </si>
   <si>
@@ -391,51 +367,15 @@
     <t>티거Ya드람더튀어</t>
   </si>
   <si>
-    <t>스무디에원음빠주세요</t>
-  </si>
-  <si>
     <t>미너와야자수</t>
   </si>
   <si>
-    <t>품처뻥노</t>
-  </si>
-  <si>
-    <t>신데렐라</t>
-  </si>
-  <si>
-    <t>앙니로조사버리는토끼</t>
-  </si>
-  <si>
-    <t>해네도앤댈리는뎨</t>
-  </si>
-  <si>
     <t>엘베단힘연타법</t>
   </si>
   <si>
-    <t>이란들어머하리지런들이떠하리</t>
-  </si>
-  <si>
-    <t>빠센궁주</t>
-  </si>
-  <si>
-    <t>눈밀에정역고톨아온아네</t>
-  </si>
-  <si>
-    <t>빠강맛</t>
-  </si>
-  <si>
-    <t>독한원요일병</t>
-  </si>
-  <si>
-    <t>악마인데슨등소에</t>
-  </si>
-  <si>
     <t>주니품</t>
   </si>
   <si>
-    <t>시바스리칼</t>
-  </si>
-  <si>
     <t>하한점수</t>
   </si>
   <si>
@@ -476,13 +416,105 @@
   </si>
   <si>
     <t>📦 월별 보관 — 2026-07  (날짜별 길드전 랭킹 누적)</t>
+  </si>
+  <si>
+    <t>숲속모텔</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>왜요뭐</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>떫은홍시</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>베놈이마깐데또까</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>독건담</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>독거노인춘삼</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>진짜한입만나못믿니</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>스무디에얼음빼주세요</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>쉰데렐라</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>훔쳐뿟노</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>앞니로조사버리는토끼</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>햬녜도얜덀리는뒈</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>이런들어떠하리저런들어떠하리</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>순살소거기육전</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>빡센공주</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>눈밑에점찍고돌아온아내</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>빨강맛</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>독한월요일병</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>독독쿠롱</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>악마인데순둥소예</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>독이즈</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>시바스리갈</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>독터키캔씨Turkey1881</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -526,6 +558,13 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -562,7 +601,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -588,6 +627,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -858,13 +901,13 @@
   <sheetData>
     <row r="3" spans="2:4" ht="16.5" customHeight="1">
       <c r="B3" s="1" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="16.5" customHeight="1">
@@ -872,10 +915,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="16.5" customHeight="1">
@@ -886,7 +929,7 @@
         <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="16.5" customHeight="1">
@@ -897,7 +940,7 @@
         <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="16.5" customHeight="1">
@@ -905,10 +948,10 @@
         <v>550001</v>
       </c>
       <c r="C7" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="16.5" customHeight="1">
@@ -919,7 +962,7 @@
         <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="16.5" customHeight="1">
@@ -930,7 +973,7 @@
         <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="16.5" customHeight="1">
@@ -941,7 +984,7 @@
         <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="16.5" customHeight="1">
@@ -952,7 +995,7 @@
         <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="16.5" customHeight="1">
@@ -963,7 +1006,7 @@
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -3598,8 +3641,8 @@
       <c r="B155">
         <v>30</v>
       </c>
-      <c r="C155" s="1" t="s">
-        <v>89</v>
+      <c r="C155" s="10" t="s">
+        <v>138</v>
       </c>
       <c r="D155">
         <v>8154156</v>
@@ -3633,7 +3676,7 @@
         <v>32</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D157">
         <v>7952273</v>
@@ -3650,7 +3693,7 @@
         <v>33</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D158">
         <v>7918857</v>
@@ -3701,7 +3744,7 @@
         <v>36</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D161">
         <v>7824653</v>
@@ -3752,7 +3795,7 @@
         <v>39</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D164">
         <v>7635056</v>
@@ -3769,7 +3812,7 @@
         <v>40</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D165">
         <v>7579677</v>
@@ -3871,7 +3914,7 @@
         <v>46</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D171">
         <v>6177989</v>
@@ -4239,7 +4282,7 @@
     </row>
     <row r="193" spans="1:5" ht="16.5" customHeight="1">
       <c r="A193" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B193" s="2">
         <v>1</v>
@@ -4257,7 +4300,7 @@
     </row>
     <row r="194" spans="1:5" ht="16.5" customHeight="1">
       <c r="A194" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B194" s="2">
         <v>2</v>
@@ -4275,7 +4318,7 @@
     </row>
     <row r="195" spans="1:5" ht="16.5" customHeight="1">
       <c r="A195" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B195" s="2">
         <v>3</v>
@@ -4293,7 +4336,7 @@
     </row>
     <row r="196" spans="1:5" ht="16.5" customHeight="1">
       <c r="A196" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B196" s="2">
         <v>4</v>
@@ -4311,7 +4354,7 @@
     </row>
     <row r="197" spans="1:5" ht="16.5" customHeight="1">
       <c r="A197" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B197" s="2">
         <v>5</v>
@@ -4329,7 +4372,7 @@
     </row>
     <row r="198" spans="1:5" ht="16.5" customHeight="1">
       <c r="A198" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B198" s="2">
         <v>6</v>
@@ -4347,7 +4390,7 @@
     </row>
     <row r="199" spans="1:5" ht="16.5" customHeight="1">
       <c r="A199" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B199" s="2">
         <v>7</v>
@@ -4365,7 +4408,7 @@
     </row>
     <row r="200" spans="1:5" ht="16.5" customHeight="1">
       <c r="A200" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B200" s="2">
         <v>8</v>
@@ -4383,7 +4426,7 @@
     </row>
     <row r="201" spans="1:5" ht="16.5" customHeight="1">
       <c r="A201" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B201" s="2">
         <v>9</v>
@@ -4401,7 +4444,7 @@
     </row>
     <row r="202" spans="1:5" ht="16.5" customHeight="1">
       <c r="A202" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B202" s="2">
         <v>10</v>
@@ -4419,7 +4462,7 @@
     </row>
     <row r="203" spans="1:5" ht="16.5" customHeight="1">
       <c r="A203" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B203" s="2">
         <v>11</v>
@@ -4437,7 +4480,7 @@
     </row>
     <row r="204" spans="1:5" ht="16.5" customHeight="1">
       <c r="A204" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B204" s="2">
         <v>12</v>
@@ -4455,13 +4498,13 @@
     </row>
     <row r="205" spans="1:5" ht="16.5" customHeight="1">
       <c r="A205" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B205" s="2">
         <v>13</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D205" s="4">
         <v>8125259</v>
@@ -4473,7 +4516,7 @@
     </row>
     <row r="206" spans="1:5" ht="16.5" customHeight="1">
       <c r="A206" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B206" s="2">
         <v>14</v>
@@ -4491,7 +4534,7 @@
     </row>
     <row r="207" spans="1:5" ht="16.5" customHeight="1">
       <c r="A207" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B207" s="2">
         <v>15</v>
@@ -4509,7 +4552,7 @@
     </row>
     <row r="208" spans="1:5" ht="16.5" customHeight="1">
       <c r="A208" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B208" s="2">
         <v>16</v>
@@ -4527,7 +4570,7 @@
     </row>
     <row r="209" spans="1:5" ht="16.5" customHeight="1">
       <c r="A209" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B209" s="2">
         <v>17</v>
@@ -4545,7 +4588,7 @@
     </row>
     <row r="210" spans="1:5" ht="16.5" customHeight="1">
       <c r="A210" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B210" s="2">
         <v>18</v>
@@ -4563,7 +4606,7 @@
     </row>
     <row r="211" spans="1:5" ht="16.5" customHeight="1">
       <c r="A211" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B211" s="2">
         <v>19</v>
@@ -4581,7 +4624,7 @@
     </row>
     <row r="212" spans="1:5" ht="16.5" customHeight="1">
       <c r="A212" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B212" s="2">
         <v>20</v>
@@ -4599,7 +4642,7 @@
     </row>
     <row r="213" spans="1:5" ht="16.5" customHeight="1">
       <c r="A213" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B213" s="2">
         <v>21</v>
@@ -4617,7 +4660,7 @@
     </row>
     <row r="214" spans="1:5" ht="16.5" customHeight="1">
       <c r="A214" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B214" s="2">
         <v>22</v>
@@ -4635,7 +4678,7 @@
     </row>
     <row r="215" spans="1:5" ht="16.5" customHeight="1">
       <c r="A215" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B215" s="2">
         <v>23</v>
@@ -4653,7 +4696,7 @@
     </row>
     <row r="216" spans="1:5" ht="16.5" customHeight="1">
       <c r="A216" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B216" s="2">
         <v>24</v>
@@ -4671,13 +4714,13 @@
     </row>
     <row r="217" spans="1:5" ht="16.5" customHeight="1">
       <c r="A217" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B217" s="2">
         <v>25</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D217" s="4">
         <v>7285842</v>
@@ -4689,7 +4732,7 @@
     </row>
     <row r="218" spans="1:5" ht="16.5" customHeight="1">
       <c r="A218" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B218" s="2">
         <v>26</v>
@@ -4707,7 +4750,7 @@
     </row>
     <row r="219" spans="1:5" ht="16.5" customHeight="1">
       <c r="A219" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B219" s="2">
         <v>27</v>
@@ -4725,7 +4768,7 @@
     </row>
     <row r="220" spans="1:5" ht="16.5" customHeight="1">
       <c r="A220" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B220" s="2">
         <v>28</v>
@@ -4743,13 +4786,13 @@
     </row>
     <row r="221" spans="1:5" ht="16.5" customHeight="1">
       <c r="A221" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B221" s="2">
         <v>29</v>
       </c>
-      <c r="C221" s="3" t="s">
-        <v>89</v>
+      <c r="C221" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="D221" s="4">
         <v>5739081</v>
@@ -4761,7 +4804,7 @@
     </row>
     <row r="222" spans="1:5" ht="16.5" customHeight="1">
       <c r="A222" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B222" s="2">
         <v>30</v>
@@ -4779,13 +4822,13 @@
     </row>
     <row r="223" spans="1:5" ht="16.5" customHeight="1">
       <c r="A223" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B223" s="2">
         <v>31</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D223" s="4">
         <v>5434650</v>
@@ -4797,13 +4840,13 @@
     </row>
     <row r="224" spans="1:5" ht="16.5" customHeight="1">
       <c r="A224" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B224" s="2">
         <v>32</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D224" s="4">
         <v>5171951</v>
@@ -4815,7 +4858,7 @@
     </row>
     <row r="225" spans="1:5" ht="16.5" customHeight="1">
       <c r="A225" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B225" s="2">
         <v>33</v>
@@ -4833,13 +4876,13 @@
     </row>
     <row r="226" spans="1:5" ht="16.5" customHeight="1">
       <c r="A226" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B226" s="2">
         <v>34</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D226" s="4">
         <v>5016847</v>
@@ -4851,7 +4894,7 @@
     </row>
     <row r="227" spans="1:5" ht="16.5" customHeight="1">
       <c r="A227" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B227" s="2">
         <v>35</v>
@@ -4869,13 +4912,13 @@
     </row>
     <row r="228" spans="1:5" ht="16.5" customHeight="1">
       <c r="A228" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B228" s="2">
         <v>36</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D228" s="4">
         <v>4537987</v>
@@ -4887,7 +4930,7 @@
     </row>
     <row r="229" spans="1:5" ht="16.5" customHeight="1">
       <c r="A229" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B229" s="2">
         <v>37</v>
@@ -4905,7 +4948,7 @@
     </row>
     <row r="230" spans="1:5" ht="16.5" customHeight="1">
       <c r="A230" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B230" s="2">
         <v>38</v>
@@ -4923,7 +4966,7 @@
     </row>
     <row r="231" spans="1:5" ht="16.5" customHeight="1">
       <c r="A231" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B231" s="2">
         <v>39</v>
@@ -4941,7 +4984,7 @@
     </row>
     <row r="232" spans="1:5" ht="16.5" customHeight="1">
       <c r="A232" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B232" s="2">
         <v>40</v>
@@ -4959,7 +5002,7 @@
     </row>
     <row r="233" spans="1:5" ht="16.5" customHeight="1">
       <c r="A233" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B233" s="2">
         <v>41</v>
@@ -4977,7 +5020,7 @@
     </row>
     <row r="234" spans="1:5" ht="16.5" customHeight="1">
       <c r="A234" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B234" s="2">
         <v>42</v>
@@ -4995,7 +5038,7 @@
     </row>
     <row r="235" spans="1:5" ht="16.5" customHeight="1">
       <c r="A235" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B235" s="2">
         <v>43</v>
@@ -5013,7 +5056,7 @@
     </row>
     <row r="236" spans="1:5" ht="16.5" customHeight="1">
       <c r="A236" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B236" s="2">
         <v>44</v>
@@ -5031,7 +5074,7 @@
     </row>
     <row r="237" spans="1:5" ht="16.5" customHeight="1">
       <c r="A237" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B237" s="2">
         <v>45</v>
@@ -5049,7 +5092,7 @@
     </row>
     <row r="238" spans="1:5" ht="16.5" customHeight="1">
       <c r="A238" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B238" s="2">
         <v>46</v>
@@ -5067,7 +5110,7 @@
     </row>
     <row r="239" spans="1:5" ht="16.5" customHeight="1">
       <c r="A239" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B239" s="2">
         <v>47</v>
@@ -5085,7 +5128,7 @@
     </row>
     <row r="240" spans="1:5" ht="16.5" customHeight="1">
       <c r="A240" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B240" s="2">
         <v>48</v>
@@ -5103,7 +5146,7 @@
     </row>
     <row r="241" spans="1:5" ht="16.5" customHeight="1">
       <c r="A241" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B241" s="2">
         <v>49</v>
@@ -5121,7 +5164,7 @@
     </row>
     <row r="242" spans="1:5" ht="16.5" customHeight="1">
       <c r="A242" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B242" s="2">
         <v>50</v>
@@ -5139,7 +5182,7 @@
     </row>
     <row r="243" spans="1:5" ht="16.5" customHeight="1">
       <c r="A243" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B243" s="2">
         <v>51</v>
@@ -5157,7 +5200,7 @@
     </row>
     <row r="244" spans="1:5" ht="16.5" customHeight="1">
       <c r="A244" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B244" s="2">
         <v>52</v>
@@ -5175,7 +5218,7 @@
     </row>
     <row r="245" spans="1:5" ht="16.5" customHeight="1">
       <c r="A245" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B245" s="2">
         <v>53</v>
@@ -5193,7 +5236,7 @@
     </row>
     <row r="246" spans="1:5" ht="16.5" customHeight="1">
       <c r="A246" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B246" s="2">
         <v>54</v>
@@ -5211,7 +5254,7 @@
     </row>
     <row r="247" spans="1:5" ht="16.5" customHeight="1">
       <c r="A247" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B247" s="2">
         <v>55</v>
@@ -5229,7 +5272,7 @@
     </row>
     <row r="248" spans="1:5" ht="16.5" customHeight="1">
       <c r="A248" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B248" s="2">
         <v>56</v>
@@ -5247,7 +5290,7 @@
     </row>
     <row r="249" spans="1:5" ht="16.5" customHeight="1">
       <c r="A249" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B249" s="2">
         <v>57</v>
@@ -5265,7 +5308,7 @@
     </row>
     <row r="250" spans="1:5" ht="16.5" customHeight="1">
       <c r="A250" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B250" s="2">
         <v>58</v>
@@ -5283,7 +5326,7 @@
     </row>
     <row r="251" spans="1:5" ht="16.5" customHeight="1">
       <c r="A251" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B251" s="2">
         <v>59</v>
@@ -5301,7 +5344,7 @@
     </row>
     <row r="252" spans="1:5" ht="16.5" customHeight="1">
       <c r="A252" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B252" s="2">
         <v>60</v>
@@ -5319,7 +5362,7 @@
     </row>
     <row r="253" spans="1:5" ht="16.5" customHeight="1">
       <c r="A253" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B253" s="2">
         <v>61</v>
@@ -5337,7 +5380,7 @@
     </row>
     <row r="254" spans="1:5" ht="16.5" customHeight="1">
       <c r="A254" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B254" s="2">
         <v>62</v>
@@ -5355,7 +5398,7 @@
     </row>
     <row r="255" spans="1:5" ht="16.5" customHeight="1">
       <c r="A255" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B255" s="2">
         <v>63</v>
@@ -5373,7 +5416,7 @@
     </row>
     <row r="256" spans="1:5" ht="16.5" customHeight="1">
       <c r="A256" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B256" s="2">
         <v>64</v>
@@ -5391,7 +5434,7 @@
     </row>
     <row r="257" spans="1:5" ht="16.5" customHeight="1">
       <c r="A257" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B257" s="2">
         <v>65</v>
@@ -5409,7 +5452,7 @@
     </row>
     <row r="258" spans="1:5" ht="16.5" customHeight="1">
       <c r="A258" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B258" s="2">
         <v>66</v>
@@ -5427,7 +5470,7 @@
     </row>
     <row r="259" spans="1:5" ht="16.5" customHeight="1">
       <c r="A259" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B259" s="2">
         <v>67</v>
@@ -5445,7 +5488,7 @@
     </row>
     <row r="260" spans="1:5" ht="16.5" customHeight="1">
       <c r="A260" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B260" s="2">
         <v>68</v>
@@ -5463,7 +5506,7 @@
     </row>
     <row r="261" spans="1:5" ht="16.5" customHeight="1">
       <c r="A261" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B261" s="2">
         <v>1</v>
@@ -5481,7 +5524,7 @@
     </row>
     <row r="262" spans="1:5" ht="16.5" customHeight="1">
       <c r="A262" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B262" s="2">
         <v>2</v>
@@ -5499,7 +5542,7 @@
     </row>
     <row r="263" spans="1:5" ht="16.5" customHeight="1">
       <c r="A263" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B263" s="2">
         <v>3</v>
@@ -5517,7 +5560,7 @@
     </row>
     <row r="264" spans="1:5" ht="16.5" customHeight="1">
       <c r="A264" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B264" s="2">
         <v>4</v>
@@ -5535,7 +5578,7 @@
     </row>
     <row r="265" spans="1:5" ht="16.5" customHeight="1">
       <c r="A265" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B265" s="2">
         <v>5</v>
@@ -5553,7 +5596,7 @@
     </row>
     <row r="266" spans="1:5" ht="16.5" customHeight="1">
       <c r="A266" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B266" s="2">
         <v>6</v>
@@ -5571,7 +5614,7 @@
     </row>
     <row r="267" spans="1:5" ht="16.5" customHeight="1">
       <c r="A267" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B267" s="2">
         <v>7</v>
@@ -5589,7 +5632,7 @@
     </row>
     <row r="268" spans="1:5" ht="16.5" customHeight="1">
       <c r="A268" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B268" s="2">
         <v>8</v>
@@ -5607,7 +5650,7 @@
     </row>
     <row r="269" spans="1:5" ht="16.5" customHeight="1">
       <c r="A269" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B269" s="2">
         <v>9</v>
@@ -5625,7 +5668,7 @@
     </row>
     <row r="270" spans="1:5" ht="16.5" customHeight="1">
       <c r="A270" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B270" s="2">
         <v>10</v>
@@ -5643,7 +5686,7 @@
     </row>
     <row r="271" spans="1:5" ht="16.5" customHeight="1">
       <c r="A271" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B271" s="2">
         <v>11</v>
@@ -5661,7 +5704,7 @@
     </row>
     <row r="272" spans="1:5" ht="16.5" customHeight="1">
       <c r="A272" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B272" s="2">
         <v>12</v>
@@ -5679,13 +5722,13 @@
     </row>
     <row r="273" spans="1:5" ht="16.5" customHeight="1">
       <c r="A273" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B273" s="2">
         <v>13</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D273" s="4">
         <v>8798439</v>
@@ -5697,7 +5740,7 @@
     </row>
     <row r="274" spans="1:5" ht="16.5" customHeight="1">
       <c r="A274" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B274" s="2">
         <v>14</v>
@@ -5715,7 +5758,7 @@
     </row>
     <row r="275" spans="1:5" ht="16.5" customHeight="1">
       <c r="A275" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B275" s="2">
         <v>15</v>
@@ -5733,7 +5776,7 @@
     </row>
     <row r="276" spans="1:5" ht="16.5" customHeight="1">
       <c r="A276" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B276" s="2">
         <v>16</v>
@@ -5751,7 +5794,7 @@
     </row>
     <row r="277" spans="1:5" ht="16.5" customHeight="1">
       <c r="A277" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B277" s="2">
         <v>17</v>
@@ -5769,7 +5812,7 @@
     </row>
     <row r="278" spans="1:5" ht="16.5" customHeight="1">
       <c r="A278" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B278" s="2">
         <v>18</v>
@@ -5787,7 +5830,7 @@
     </row>
     <row r="279" spans="1:5" ht="16.5" customHeight="1">
       <c r="A279" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B279" s="2">
         <v>19</v>
@@ -5805,7 +5848,7 @@
     </row>
     <row r="280" spans="1:5" ht="16.5" customHeight="1">
       <c r="A280" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B280" s="2">
         <v>20</v>
@@ -5823,7 +5866,7 @@
     </row>
     <row r="281" spans="1:5" ht="16.5" customHeight="1">
       <c r="A281" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B281" s="2">
         <v>21</v>
@@ -5841,13 +5884,13 @@
     </row>
     <row r="282" spans="1:5" ht="16.5" customHeight="1">
       <c r="A282" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B282" s="2">
         <v>22</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D282" s="4">
         <v>8051401</v>
@@ -5859,7 +5902,7 @@
     </row>
     <row r="283" spans="1:5" ht="16.5" customHeight="1">
       <c r="A283" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B283" s="2">
         <v>23</v>
@@ -5877,7 +5920,7 @@
     </row>
     <row r="284" spans="1:5" ht="16.5" customHeight="1">
       <c r="A284" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B284" s="2">
         <v>24</v>
@@ -5895,7 +5938,7 @@
     </row>
     <row r="285" spans="1:5" ht="16.5" customHeight="1">
       <c r="A285" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B285" s="2">
         <v>25</v>
@@ -5913,7 +5956,7 @@
     </row>
     <row r="286" spans="1:5" ht="16.5" customHeight="1">
       <c r="A286" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B286" s="2">
         <v>26</v>
@@ -5931,7 +5974,7 @@
     </row>
     <row r="287" spans="1:5" ht="16.5" customHeight="1">
       <c r="A287" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B287" s="2">
         <v>27</v>
@@ -5949,7 +5992,7 @@
     </row>
     <row r="288" spans="1:5" ht="16.5" customHeight="1">
       <c r="A288" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B288" s="2">
         <v>28</v>
@@ -5967,13 +6010,13 @@
     </row>
     <row r="289" spans="1:5" ht="16.5" customHeight="1">
       <c r="A289" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B289" s="2">
         <v>29</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D289" s="4">
         <v>7511676</v>
@@ -5985,7 +6028,7 @@
     </row>
     <row r="290" spans="1:5" ht="16.5" customHeight="1">
       <c r="A290" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B290" s="2">
         <v>30</v>
@@ -6003,13 +6046,13 @@
     </row>
     <row r="291" spans="1:5" ht="16.5" customHeight="1">
       <c r="A291" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B291" s="2">
         <v>31</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D291" s="4">
         <v>7435700</v>
@@ -6021,7 +6064,7 @@
     </row>
     <row r="292" spans="1:5" ht="16.5" customHeight="1">
       <c r="A292" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B292" s="2">
         <v>32</v>
@@ -6039,7 +6082,7 @@
     </row>
     <row r="293" spans="1:5" ht="16.5" customHeight="1">
       <c r="A293" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B293" s="2">
         <v>33</v>
@@ -6057,7 +6100,7 @@
     </row>
     <row r="294" spans="1:5" ht="16.5" customHeight="1">
       <c r="A294" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B294" s="2">
         <v>34</v>
@@ -6075,7 +6118,7 @@
     </row>
     <row r="295" spans="1:5" ht="16.5" customHeight="1">
       <c r="A295" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B295" s="2">
         <v>35</v>
@@ -6093,13 +6136,13 @@
     </row>
     <row r="296" spans="1:5" ht="16.5" customHeight="1">
       <c r="A296" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B296" s="2">
         <v>36</v>
       </c>
       <c r="C296" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D296" s="4">
         <v>7216687</v>
@@ -6111,7 +6154,7 @@
     </row>
     <row r="297" spans="1:5" ht="16.5" customHeight="1">
       <c r="A297" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B297" s="2">
         <v>37</v>
@@ -6129,7 +6172,7 @@
     </row>
     <row r="298" spans="1:5" ht="16.5" customHeight="1">
       <c r="A298" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B298" s="2">
         <v>38</v>
@@ -6147,13 +6190,13 @@
     </row>
     <row r="299" spans="1:5" ht="16.5" customHeight="1">
       <c r="A299" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B299" s="2">
         <v>39</v>
       </c>
-      <c r="C299" s="6" t="s">
-        <v>89</v>
+      <c r="C299" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="D299" s="4">
         <v>5960246</v>
@@ -6165,7 +6208,7 @@
     </row>
     <row r="300" spans="1:5" ht="16.5" customHeight="1">
       <c r="A300" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B300" s="2">
         <v>40</v>
@@ -6183,7 +6226,7 @@
     </row>
     <row r="301" spans="1:5" ht="16.5" customHeight="1">
       <c r="A301" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B301" s="2">
         <v>41</v>
@@ -6201,7 +6244,7 @@
     </row>
     <row r="302" spans="1:5" ht="16.5" customHeight="1">
       <c r="A302" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B302" s="2">
         <v>42</v>
@@ -6219,7 +6262,7 @@
     </row>
     <row r="303" spans="1:5" ht="16.5" customHeight="1">
       <c r="A303" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B303" s="2">
         <v>43</v>
@@ -6237,13 +6280,13 @@
     </row>
     <row r="304" spans="1:5" ht="16.5" customHeight="1">
       <c r="A304" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B304" s="2">
         <v>44</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D304" s="4">
         <v>4816595</v>
@@ -6255,7 +6298,7 @@
     </row>
     <row r="305" spans="1:5" ht="16.5" customHeight="1">
       <c r="A305" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B305" s="2">
         <v>45</v>
@@ -6273,7 +6316,7 @@
     </row>
     <row r="306" spans="1:5" ht="16.5" customHeight="1">
       <c r="A306" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B306" s="2">
         <v>46</v>
@@ -6291,7 +6334,7 @@
     </row>
     <row r="307" spans="1:5" ht="16.5" customHeight="1">
       <c r="A307" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B307" s="2">
         <v>47</v>
@@ -6309,7 +6352,7 @@
     </row>
     <row r="308" spans="1:5" ht="16.5" customHeight="1">
       <c r="A308" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B308" s="2">
         <v>48</v>
@@ -6327,7 +6370,7 @@
     </row>
     <row r="309" spans="1:5" ht="16.5" customHeight="1">
       <c r="A309" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B309" s="2">
         <v>49</v>
@@ -6345,7 +6388,7 @@
     </row>
     <row r="310" spans="1:5" ht="16.5" customHeight="1">
       <c r="A310" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B310" s="2">
         <v>50</v>
@@ -6363,7 +6406,7 @@
     </row>
     <row r="311" spans="1:5" ht="16.5" customHeight="1">
       <c r="A311" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B311" s="2">
         <v>51</v>
@@ -6381,7 +6424,7 @@
     </row>
     <row r="312" spans="1:5" ht="16.5" customHeight="1">
       <c r="A312" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B312" s="2">
         <v>52</v>
@@ -6399,7 +6442,7 @@
     </row>
     <row r="313" spans="1:5" ht="16.5" customHeight="1">
       <c r="A313" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B313" s="2">
         <v>53</v>
@@ -6417,7 +6460,7 @@
     </row>
     <row r="314" spans="1:5" ht="16.5" customHeight="1">
       <c r="A314" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B314" s="2">
         <v>54</v>
@@ -6435,7 +6478,7 @@
     </row>
     <row r="315" spans="1:5" ht="16.5" customHeight="1">
       <c r="A315" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B315" s="2">
         <v>55</v>
@@ -6453,7 +6496,7 @@
     </row>
     <row r="316" spans="1:5" ht="16.5" customHeight="1">
       <c r="A316" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B316" s="2">
         <v>56</v>
@@ -6471,7 +6514,7 @@
     </row>
     <row r="317" spans="1:5" ht="16.5" customHeight="1">
       <c r="A317" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B317" s="2">
         <v>57</v>
@@ -6489,7 +6532,7 @@
     </row>
     <row r="318" spans="1:5" ht="16.5" customHeight="1">
       <c r="A318" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B318" s="2">
         <v>58</v>
@@ -6507,7 +6550,7 @@
     </row>
     <row r="319" spans="1:5" ht="16.5" customHeight="1">
       <c r="A319" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B319" s="2">
         <v>59</v>
@@ -6525,7 +6568,7 @@
     </row>
     <row r="320" spans="1:5" ht="16.5" customHeight="1">
       <c r="A320" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B320" s="2">
         <v>60</v>
@@ -6543,7 +6586,7 @@
     </row>
     <row r="321" spans="1:5" ht="16.5" customHeight="1">
       <c r="A321" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B321" s="2">
         <v>61</v>
@@ -6561,13 +6604,13 @@
     </row>
     <row r="322" spans="1:5" ht="16.5" customHeight="1">
       <c r="A322" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B322" s="2">
         <v>62</v>
       </c>
       <c r="C322" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D322" s="4">
         <v>2161578</v>
@@ -6579,13 +6622,13 @@
     </row>
     <row r="323" spans="1:5" ht="16.5" customHeight="1">
       <c r="A323" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B323" s="2">
         <v>63</v>
       </c>
       <c r="C323" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D323" s="4">
         <v>2130311</v>
@@ -6597,7 +6640,7 @@
     </row>
     <row r="324" spans="1:5" ht="16.5" customHeight="1">
       <c r="A324" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B324" s="2">
         <v>64</v>
@@ -6615,7 +6658,7 @@
     </row>
     <row r="325" spans="1:5" ht="16.5" customHeight="1">
       <c r="A325" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B325" s="2">
         <v>65</v>
@@ -6633,7 +6676,7 @@
     </row>
     <row r="326" spans="1:5" ht="16.5" customHeight="1">
       <c r="A326" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B326" s="2">
         <v>66</v>
@@ -6651,7 +6694,7 @@
     </row>
     <row r="327" spans="1:5" ht="16.5" customHeight="1">
       <c r="A327" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B327" s="2">
         <v>67</v>
@@ -6669,7 +6712,7 @@
     </row>
     <row r="328" spans="1:5">
       <c r="A328" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B328" s="9">
         <v>1</v>
@@ -6687,13 +6730,13 @@
     </row>
     <row r="329" spans="1:5">
       <c r="A329" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B329" s="9">
         <v>2</v>
       </c>
       <c r="C329" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D329" s="9">
         <v>45927381</v>
@@ -6705,7 +6748,7 @@
     </row>
     <row r="330" spans="1:5">
       <c r="A330" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B330" s="9">
         <v>3</v>
@@ -6723,7 +6766,7 @@
     </row>
     <row r="331" spans="1:5">
       <c r="A331" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B331" s="9">
         <v>4</v>
@@ -6741,7 +6784,7 @@
     </row>
     <row r="332" spans="1:5">
       <c r="A332" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B332" s="9">
         <v>5</v>
@@ -6759,7 +6802,7 @@
     </row>
     <row r="333" spans="1:5">
       <c r="A333" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B333" s="9">
         <v>6</v>
@@ -6777,13 +6820,13 @@
     </row>
     <row r="334" spans="1:5">
       <c r="A334" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B334" s="9">
         <v>7</v>
       </c>
       <c r="C334" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D334" s="9">
         <v>29064577</v>
@@ -6795,13 +6838,13 @@
     </row>
     <row r="335" spans="1:5">
       <c r="A335" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B335" s="9">
         <v>8</v>
       </c>
       <c r="C335" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D335" s="9">
         <v>28830256</v>
@@ -6813,13 +6856,13 @@
     </row>
     <row r="336" spans="1:5">
       <c r="A336" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B336" s="9">
         <v>9</v>
       </c>
       <c r="C336" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D336" s="9">
         <v>27963110</v>
@@ -6831,13 +6874,13 @@
     </row>
     <row r="337" spans="1:5">
       <c r="A337" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B337" s="9">
         <v>10</v>
       </c>
       <c r="C337" s="8" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="D337" s="9">
         <v>27716398</v>
@@ -6849,7 +6892,7 @@
     </row>
     <row r="338" spans="1:5">
       <c r="A338" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B338" s="9">
         <v>11</v>
@@ -6867,7 +6910,7 @@
     </row>
     <row r="339" spans="1:5">
       <c r="A339" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B339" s="9">
         <v>12</v>
@@ -6885,13 +6928,13 @@
     </row>
     <row r="340" spans="1:5">
       <c r="A340" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B340" s="9">
         <v>13</v>
       </c>
       <c r="C340" s="8" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="D340" s="9">
         <v>25598926</v>
@@ -6903,13 +6946,13 @@
     </row>
     <row r="341" spans="1:5">
       <c r="A341" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B341" s="9">
         <v>14</v>
       </c>
       <c r="C341" s="8" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="D341" s="9">
         <v>25275492</v>
@@ -6921,13 +6964,13 @@
     </row>
     <row r="342" spans="1:5">
       <c r="A342" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B342" s="9">
         <v>15</v>
       </c>
       <c r="C342" s="8" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="D342" s="9">
         <v>24620930</v>
@@ -6939,13 +6982,13 @@
     </row>
     <row r="343" spans="1:5">
       <c r="A343" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B343" s="9">
         <v>16</v>
       </c>
       <c r="C343" s="8" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="D343" s="9">
         <v>24434321</v>
@@ -6957,13 +7000,13 @@
     </row>
     <row r="344" spans="1:5">
       <c r="A344" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B344" s="9">
         <v>17</v>
       </c>
       <c r="C344" s="8" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D344" s="9">
         <v>21605033</v>
@@ -6975,7 +7018,7 @@
     </row>
     <row r="345" spans="1:5">
       <c r="A345" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B345" s="9">
         <v>18</v>
@@ -6993,13 +7036,13 @@
     </row>
     <row r="346" spans="1:5">
       <c r="A346" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B346" s="9">
         <v>19</v>
       </c>
       <c r="C346" s="8" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="D346" s="9">
         <v>21123578</v>
@@ -7011,13 +7054,13 @@
     </row>
     <row r="347" spans="1:5">
       <c r="A347" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B347" s="9">
         <v>20</v>
       </c>
       <c r="C347" s="8" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D347" s="9">
         <v>19328458</v>
@@ -7029,13 +7072,13 @@
     </row>
     <row r="348" spans="1:5">
       <c r="A348" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B348" s="9">
         <v>21</v>
       </c>
       <c r="C348" s="8" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D348" s="9">
         <v>18986692</v>
@@ -7047,13 +7090,13 @@
     </row>
     <row r="349" spans="1:5">
       <c r="A349" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B349" s="9">
         <v>22</v>
       </c>
       <c r="C349" s="8" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D349" s="9">
         <v>18188828</v>
@@ -7065,7 +7108,7 @@
     </row>
     <row r="350" spans="1:5">
       <c r="A350" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B350" s="9">
         <v>23</v>
@@ -7083,13 +7126,13 @@
     </row>
     <row r="351" spans="1:5">
       <c r="A351" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B351" s="9">
         <v>24</v>
       </c>
       <c r="C351" s="8" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D351" s="9">
         <v>17451192</v>
@@ -7101,13 +7144,13 @@
     </row>
     <row r="352" spans="1:5">
       <c r="A352" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B352" s="9">
         <v>25</v>
       </c>
       <c r="C352" s="8" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D352" s="9">
         <v>17095537</v>
@@ -7119,13 +7162,13 @@
     </row>
     <row r="353" spans="1:5">
       <c r="A353" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B353" s="9">
         <v>26</v>
       </c>
       <c r="C353" s="8" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="D353" s="9">
         <v>16940645</v>
@@ -7137,7 +7180,7 @@
     </row>
     <row r="354" spans="1:5">
       <c r="A354" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B354" s="9">
         <v>27</v>
@@ -7155,7 +7198,7 @@
     </row>
     <row r="355" spans="1:5">
       <c r="A355" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B355" s="9">
         <v>28</v>
@@ -7173,13 +7216,13 @@
     </row>
     <row r="356" spans="1:5">
       <c r="A356" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B356" s="9">
         <v>29</v>
       </c>
       <c r="C356" s="8" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D356" s="9">
         <v>16370099</v>
@@ -7191,7 +7234,7 @@
     </row>
     <row r="357" spans="1:5">
       <c r="A357" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B357" s="9">
         <v>30</v>
@@ -7209,7 +7252,7 @@
     </row>
     <row r="358" spans="1:5">
       <c r="A358" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B358" s="9">
         <v>31</v>
@@ -7227,13 +7270,13 @@
     </row>
     <row r="359" spans="1:5">
       <c r="A359" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B359" s="9">
         <v>32</v>
       </c>
       <c r="C359" s="8" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="D359" s="9">
         <v>14253593</v>
@@ -7245,13 +7288,13 @@
     </row>
     <row r="360" spans="1:5">
       <c r="A360" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B360" s="9">
         <v>33</v>
       </c>
       <c r="C360" s="8" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="D360" s="9">
         <v>13958262</v>
@@ -7263,13 +7306,13 @@
     </row>
     <row r="361" spans="1:5">
       <c r="A361" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B361" s="9">
         <v>34</v>
       </c>
       <c r="C361" s="8" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="D361" s="9">
         <v>13903501</v>
@@ -7281,13 +7324,13 @@
     </row>
     <row r="362" spans="1:5">
       <c r="A362" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B362" s="9">
         <v>35</v>
       </c>
       <c r="C362" s="8" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="D362" s="9">
         <v>13791347</v>
@@ -7299,7 +7342,7 @@
     </row>
     <row r="363" spans="1:5">
       <c r="A363" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B363" s="9">
         <v>36</v>
@@ -7317,13 +7360,13 @@
     </row>
     <row r="364" spans="1:5">
       <c r="A364" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B364" s="9">
         <v>37</v>
       </c>
       <c r="C364" s="8" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="D364" s="9">
         <v>12684262</v>
@@ -7335,13 +7378,13 @@
     </row>
     <row r="365" spans="1:5">
       <c r="A365" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B365" s="9">
         <v>38</v>
       </c>
       <c r="C365" s="8" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D365" s="9">
         <v>12215462</v>
@@ -7353,13 +7396,13 @@
     </row>
     <row r="366" spans="1:5">
       <c r="A366" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B366" s="9">
         <v>39</v>
       </c>
       <c r="C366" s="8" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="D366" s="9">
         <v>11325863</v>
@@ -7371,7 +7414,7 @@
     </row>
     <row r="367" spans="1:5">
       <c r="A367" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B367" s="9">
         <v>40</v>
@@ -7389,7 +7432,7 @@
     </row>
     <row r="368" spans="1:5">
       <c r="A368" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B368" s="9">
         <v>41</v>
@@ -7407,7 +7450,7 @@
     </row>
     <row r="369" spans="1:5">
       <c r="A369" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B369" s="9">
         <v>42</v>
@@ -7425,7 +7468,7 @@
     </row>
     <row r="370" spans="1:5">
       <c r="A370" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B370" s="9">
         <v>43</v>
@@ -7443,7 +7486,7 @@
     </row>
     <row r="371" spans="1:5">
       <c r="A371" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B371" s="9">
         <v>44</v>
@@ -7461,13 +7504,13 @@
     </row>
     <row r="372" spans="1:5">
       <c r="A372" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B372" s="9">
         <v>45</v>
       </c>
       <c r="C372" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D372" s="9">
         <v>9257137</v>
@@ -7479,7 +7522,7 @@
     </row>
     <row r="373" spans="1:5">
       <c r="A373" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B373" s="9">
         <v>46</v>
@@ -7497,7 +7540,7 @@
     </row>
     <row r="374" spans="1:5">
       <c r="A374" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B374" s="9">
         <v>47</v>
@@ -7515,7 +7558,7 @@
     </row>
     <row r="375" spans="1:5">
       <c r="A375" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B375" s="9">
         <v>48</v>
@@ -7533,13 +7576,13 @@
     </row>
     <row r="376" spans="1:5">
       <c r="A376" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B376" s="9">
         <v>49</v>
       </c>
       <c r="C376" s="8" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="D376" s="9">
         <v>8449715</v>
@@ -7551,7 +7594,7 @@
     </row>
     <row r="377" spans="1:5">
       <c r="A377" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B377" s="9">
         <v>50</v>
@@ -7569,7 +7612,7 @@
     </row>
     <row r="378" spans="1:5">
       <c r="A378" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B378" s="9">
         <v>51</v>
@@ -7587,13 +7630,13 @@
     </row>
     <row r="379" spans="1:5">
       <c r="A379" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B379" s="9">
         <v>52</v>
       </c>
       <c r="C379" s="8" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="D379" s="9">
         <v>6388100</v>
@@ -7605,7 +7648,7 @@
     </row>
     <row r="380" spans="1:5">
       <c r="A380" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B380" s="9">
         <v>53</v>
@@ -7623,13 +7666,13 @@
     </row>
     <row r="381" spans="1:5">
       <c r="A381" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B381" s="9">
         <v>54</v>
       </c>
       <c r="C381" s="8" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="D381" s="9">
         <v>5593709</v>
@@ -7641,13 +7684,13 @@
     </row>
     <row r="382" spans="1:5">
       <c r="A382" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B382" s="9">
         <v>55</v>
       </c>
       <c r="C382" s="8" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="D382" s="9">
         <v>4942793</v>
@@ -7659,13 +7702,13 @@
     </row>
     <row r="383" spans="1:5">
       <c r="A383" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B383" s="9">
         <v>56</v>
       </c>
-      <c r="C383" s="8" t="s">
-        <v>72</v>
+      <c r="C383" s="11">
+        <v>1090</v>
       </c>
       <c r="D383" s="9">
         <v>4587543</v>
@@ -7677,7 +7720,7 @@
     </row>
     <row r="384" spans="1:5">
       <c r="A384" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B384" s="9">
         <v>57</v>
@@ -7695,13 +7738,13 @@
     </row>
     <row r="385" spans="1:5">
       <c r="A385" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B385" s="9">
         <v>58</v>
       </c>
       <c r="C385" s="8" t="s">
-        <v>65</v>
+        <v>145</v>
       </c>
       <c r="D385" s="9">
         <v>3613479</v>
@@ -7713,13 +7756,13 @@
     </row>
     <row r="386" spans="1:5">
       <c r="A386" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B386" s="9">
         <v>59</v>
       </c>
       <c r="C386" s="8" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="D386" s="9">
         <v>2363818</v>
@@ -7731,13 +7774,13 @@
     </row>
     <row r="387" spans="1:5">
       <c r="A387" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B387" s="9">
         <v>60</v>
       </c>
       <c r="C387" s="8" t="s">
-        <v>60</v>
+        <v>147</v>
       </c>
       <c r="D387" s="9">
         <v>2307050</v>
@@ -7749,13 +7792,13 @@
     </row>
     <row r="388" spans="1:5">
       <c r="A388" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B388" s="9">
         <v>61</v>
       </c>
       <c r="C388" s="8" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="D388" s="9">
         <v>2215136</v>
@@ -7767,7 +7810,7 @@
     </row>
     <row r="389" spans="1:5">
       <c r="A389" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B389" s="9">
         <v>62</v>
@@ -7785,13 +7828,13 @@
     </row>
     <row r="390" spans="1:5">
       <c r="A390" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B390" s="9">
         <v>63</v>
       </c>
       <c r="C390" s="8" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="D390" s="9">
         <v>1109775</v>
@@ -7803,13 +7846,13 @@
     </row>
     <row r="391" spans="1:5">
       <c r="A391" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B391" s="9">
         <v>64</v>
       </c>
       <c r="C391" s="8" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="D391" s="9">
         <v>999218</v>
@@ -7821,7 +7864,7 @@
     </row>
     <row r="392" spans="1:5">
       <c r="A392" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B392" s="9">
         <v>65</v>
@@ -7839,7 +7882,7 @@
     </row>
     <row r="393" spans="1:5">
       <c r="A393" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B393" s="9">
         <v>66</v>
@@ -7869,7 +7912,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{033D44F0-FAD3-4404-B6E2-435C5DFDD8D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A66B3FC1-1F68-45EF-9776-AADA8BB5C0D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21600" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="기준표" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="120">
   <si>
     <t>📦 월별 보관 — 2026-06  (날짜별 길드전 랭킹 누적)</t>
   </si>
@@ -103,12 +103,12 @@
     <t>별빛여신</t>
   </si>
   <si>
+    <t>뉴스에나온그사람</t>
+  </si>
+  <si>
     <t>독로이지</t>
   </si>
   <si>
-    <t>슴격이다개스키야</t>
-  </si>
-  <si>
     <t>핑도노-품치고-생각하는-편</t>
   </si>
   <si>
@@ -127,21 +127,12 @@
     <t>독그레핀</t>
   </si>
   <si>
-    <t>떠들어와안들린다</t>
-  </si>
-  <si>
     <t>명령라하지마라</t>
   </si>
   <si>
-    <t>뮤지컬로라거셰노메따리부른느</t>
-  </si>
-  <si>
     <t>독한다람쥐</t>
   </si>
   <si>
-    <t>영화관에서걸말스포한날</t>
-  </si>
-  <si>
     <t>독파민</t>
   </si>
   <si>
@@ -154,9 +145,6 @@
     <t>8단계</t>
   </si>
   <si>
-    <t>티거Ya드람더튀어</t>
-  </si>
-  <si>
     <t>독눈누눈누</t>
   </si>
   <si>
@@ -292,9 +280,6 @@
     <t>아사히</t>
   </si>
   <si>
-    <t>미너와야자수</t>
-  </si>
-  <si>
     <t>빡센공주</t>
   </si>
   <si>
@@ -385,7 +370,30 @@
     <t>📦 월별 보관 — 2026-07  (날짜별 길드전 랭킹 누적)</t>
   </si>
   <si>
-    <t>뮤지컬보러가서노래따라부르는놈</t>
+    <t>뺙센공주</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>엘베닫힘연타법</t>
+  </si>
+  <si>
+    <t>엘베닫힘연타법</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>미녀와야자수</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>티거Ya드랍더튀어</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>습격이다개스키야</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>떠들어봐안들린다</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -393,59 +401,7 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>진짜한입만나못믿니</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>습격이다개스키야</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>티거Ya드랍더튀어</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>미녀와야자수</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>엘베닫힘연타범</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>이런들어떠하리저런들어떠하리</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>뺙센공주</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>자르반84세</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>독아윤</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>주니쯤</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>독팡팡</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>시바스리갈</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>뉴스에나온그사람</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>뉴스에나온그사람</t>
+    <t>뮤지컬보러가서노래따라부르는놈</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -453,7 +409,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -504,6 +460,13 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -540,7 +503,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -568,6 +531,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -837,13 +801,13 @@
   <sheetData>
     <row r="3" spans="2:4" ht="16.5" customHeight="1">
       <c r="B3" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="16.5" customHeight="1">
@@ -851,10 +815,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="16.5" customHeight="1">
@@ -862,10 +826,10 @@
         <v>38001</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="16.5" customHeight="1">
@@ -873,10 +837,10 @@
         <v>145001</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="16.5" customHeight="1">
@@ -884,10 +848,10 @@
         <v>550001</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="16.5" customHeight="1">
@@ -895,10 +859,10 @@
         <v>650001</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="16.5" customHeight="1">
@@ -906,10 +870,10 @@
         <v>1020001</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="16.5" customHeight="1">
@@ -917,10 +881,10 @@
         <v>2280001</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="16.5" customHeight="1">
@@ -928,10 +892,10 @@
         <v>2630001</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="16.5" customHeight="1">
@@ -942,7 +906,7 @@
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -954,7 +918,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E393"/>
+  <dimension ref="A1:E394"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="49.75" customWidth="1"/>
@@ -1232,7 +1196,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>131</v>
+        <v>22</v>
       </c>
       <c r="D17">
         <v>8351700</v>
@@ -1249,7 +1213,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D18">
         <v>8099944</v>
@@ -1265,8 +1229,8 @@
       <c r="B19">
         <v>17</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>23</v>
+      <c r="C19" s="10" t="s">
+        <v>116</v>
       </c>
       <c r="D19">
         <v>7972413</v>
@@ -1384,8 +1348,8 @@
       <c r="B26">
         <v>24</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>30</v>
+      <c r="C26" s="10" t="s">
+        <v>117</v>
       </c>
       <c r="D26">
         <v>7530750</v>
@@ -1402,7 +1366,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D27">
         <v>7494390</v>
@@ -1418,8 +1382,8 @@
       <c r="B28">
         <v>26</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>32</v>
+      <c r="C28" s="10" t="s">
+        <v>119</v>
       </c>
       <c r="D28">
         <v>7425030</v>
@@ -1436,7 +1400,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D29">
         <v>7233630</v>
@@ -1452,8 +1416,8 @@
       <c r="B30">
         <v>28</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>34</v>
+      <c r="C30" s="10" t="s">
+        <v>118</v>
       </c>
       <c r="D30">
         <v>7218568</v>
@@ -1470,7 +1434,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D31">
         <v>7215859</v>
@@ -1487,7 +1451,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D32">
         <v>7202018</v>
@@ -1504,13 +1468,13 @@
         <v>31</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D33">
         <v>5747056</v>
       </c>
       <c r="E33" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="16.5" customHeight="1">
@@ -1520,14 +1484,14 @@
       <c r="B34">
         <v>32</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>39</v>
+      <c r="C34" s="10" t="s">
+        <v>115</v>
       </c>
       <c r="D34">
         <v>5659102</v>
       </c>
       <c r="E34" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="16.5" customHeight="1">
@@ -1538,13 +1502,13 @@
         <v>33</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D35">
         <v>5575024</v>
       </c>
       <c r="E35" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="16.5" customHeight="1">
@@ -1555,13 +1519,13 @@
         <v>34</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D36">
         <v>5545974</v>
       </c>
       <c r="E36" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="16.5" customHeight="1">
@@ -1572,13 +1536,13 @@
         <v>35</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D37">
         <v>5391755</v>
       </c>
       <c r="E37" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="16.5" customHeight="1">
@@ -1589,13 +1553,13 @@
         <v>36</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D38">
         <v>5181490</v>
       </c>
       <c r="E38" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="16.5" customHeight="1">
@@ -1606,13 +1570,13 @@
         <v>37</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D39">
         <v>5131950</v>
       </c>
       <c r="E39" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="16.5" customHeight="1">
@@ -1623,13 +1587,13 @@
         <v>38</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D40">
         <v>4904007</v>
       </c>
       <c r="E40" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="16.5" customHeight="1">
@@ -1640,13 +1604,13 @@
         <v>39</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D41">
         <v>4573837</v>
       </c>
       <c r="E41" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="16.5" customHeight="1">
@@ -1657,13 +1621,13 @@
         <v>40</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D42">
         <v>4490575</v>
       </c>
       <c r="E42" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="16.5" customHeight="1">
@@ -1674,13 +1638,13 @@
         <v>41</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D43">
         <v>4397353</v>
       </c>
       <c r="E43" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="16.5" customHeight="1">
@@ -1691,13 +1655,13 @@
         <v>42</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D44">
         <v>4297031</v>
       </c>
       <c r="E44" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="16.5" customHeight="1">
@@ -1707,14 +1671,14 @@
       <c r="B45">
         <v>43</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>50</v>
+      <c r="C45" s="10" t="s">
+        <v>113</v>
       </c>
       <c r="D45">
         <v>4182965</v>
       </c>
       <c r="E45" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="16.5" customHeight="1">
@@ -1725,13 +1689,13 @@
         <v>44</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D46">
         <v>4030862</v>
       </c>
       <c r="E46" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="16.5" customHeight="1">
@@ -1742,13 +1706,13 @@
         <v>45</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D47">
         <v>3998435</v>
       </c>
       <c r="E47" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="16.5" customHeight="1">
@@ -1759,13 +1723,13 @@
         <v>46</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D48">
         <v>3927862</v>
       </c>
       <c r="E48" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="16.5" customHeight="1">
@@ -1776,13 +1740,13 @@
         <v>47</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D49">
         <v>3788029</v>
       </c>
       <c r="E49" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="16.5" customHeight="1">
@@ -1793,13 +1757,13 @@
         <v>48</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D50">
         <v>3775539</v>
       </c>
       <c r="E50" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="16.5" customHeight="1">
@@ -1810,13 +1774,13 @@
         <v>49</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D51">
         <v>3644353</v>
       </c>
       <c r="E51" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="16.5" customHeight="1">
@@ -1827,13 +1791,13 @@
         <v>50</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D52">
         <v>3436366</v>
       </c>
       <c r="E52" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="16.5" customHeight="1">
@@ -1844,13 +1808,13 @@
         <v>51</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D53">
         <v>3375232</v>
       </c>
       <c r="E53" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="16.5" customHeight="1">
@@ -1861,13 +1825,13 @@
         <v>52</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D54">
         <v>3219637</v>
       </c>
       <c r="E54" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="16.5" customHeight="1">
@@ -1878,13 +1842,13 @@
         <v>53</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D55">
         <v>3100693</v>
       </c>
       <c r="E55" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="16.5" customHeight="1">
@@ -1895,13 +1859,13 @@
         <v>54</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D56">
         <v>3087580</v>
       </c>
       <c r="E56" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="16.5" customHeight="1">
@@ -1912,13 +1876,13 @@
         <v>55</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D57">
         <v>2720000</v>
       </c>
       <c r="E57" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="16.5" customHeight="1">
@@ -1929,13 +1893,13 @@
         <v>56</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D58">
         <v>2670936</v>
       </c>
       <c r="E58" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="16.5" customHeight="1">
@@ -1946,13 +1910,13 @@
         <v>57</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D59">
         <v>2294961</v>
       </c>
       <c r="E59" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="16.5" customHeight="1">
@@ -1963,13 +1927,13 @@
         <v>58</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D60">
         <v>2202597</v>
       </c>
       <c r="E60" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="16.5" customHeight="1">
@@ -1980,24 +1944,24 @@
         <v>59</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D61">
         <v>2155923</v>
       </c>
       <c r="E61" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="16.5" customHeight="1">
       <c r="A62" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B62">
         <v>1</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>30</v>
+      <c r="C62" s="10" t="s">
+        <v>117</v>
       </c>
       <c r="D62">
         <v>20124674</v>
@@ -2008,7 +1972,7 @@
     </row>
     <row r="63" spans="1:5" ht="16.5" customHeight="1">
       <c r="A63" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B63">
         <v>2</v>
@@ -2025,7 +1989,7 @@
     </row>
     <row r="64" spans="1:5" ht="16.5" customHeight="1">
       <c r="A64" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B64">
         <v>3</v>
@@ -2042,7 +2006,7 @@
     </row>
     <row r="65" spans="1:5" ht="16.5" customHeight="1">
       <c r="A65" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B65">
         <v>4</v>
@@ -2059,7 +2023,7 @@
     </row>
     <row r="66" spans="1:5" ht="16.5" customHeight="1">
       <c r="A66" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B66">
         <v>5</v>
@@ -2076,7 +2040,7 @@
     </row>
     <row r="67" spans="1:5" ht="16.5" customHeight="1">
       <c r="A67" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B67">
         <v>6</v>
@@ -2093,7 +2057,7 @@
     </row>
     <row r="68" spans="1:5" ht="16.5" customHeight="1">
       <c r="A68" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B68">
         <v>7</v>
@@ -2110,13 +2074,13 @@
     </row>
     <row r="69" spans="1:5" ht="16.5" customHeight="1">
       <c r="A69" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B69">
         <v>8</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>23</v>
+      <c r="C69" s="10" t="s">
+        <v>116</v>
       </c>
       <c r="D69">
         <v>11050986</v>
@@ -2127,7 +2091,7 @@
     </row>
     <row r="70" spans="1:5" ht="16.5" customHeight="1">
       <c r="A70" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B70">
         <v>9</v>
@@ -2144,13 +2108,13 @@
     </row>
     <row r="71" spans="1:5" ht="16.5" customHeight="1">
       <c r="A71" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B71">
         <v>10</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D71">
         <v>10955529</v>
@@ -2161,7 +2125,7 @@
     </row>
     <row r="72" spans="1:5" ht="16.5" customHeight="1">
       <c r="A72" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B72">
         <v>11</v>
@@ -2178,7 +2142,7 @@
     </row>
     <row r="73" spans="1:5" ht="16.5" customHeight="1">
       <c r="A73" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B73">
         <v>12</v>
@@ -2195,7 +2159,7 @@
     </row>
     <row r="74" spans="1:5" ht="16.5" customHeight="1">
       <c r="A74" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B74">
         <v>13</v>
@@ -2212,7 +2176,7 @@
     </row>
     <row r="75" spans="1:5" ht="16.5" customHeight="1">
       <c r="A75" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B75">
         <v>14</v>
@@ -2229,13 +2193,13 @@
     </row>
     <row r="76" spans="1:5" ht="16.5" customHeight="1">
       <c r="A76" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B76">
         <v>15</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D76">
         <v>9099782</v>
@@ -2246,13 +2210,13 @@
     </row>
     <row r="77" spans="1:5" ht="16.5" customHeight="1">
       <c r="A77" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B77">
         <v>16</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D77">
         <v>8928749</v>
@@ -2263,7 +2227,7 @@
     </row>
     <row r="78" spans="1:5" ht="16.5" customHeight="1">
       <c r="A78" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B78">
         <v>17</v>
@@ -2280,13 +2244,13 @@
     </row>
     <row r="79" spans="1:5" ht="16.5" customHeight="1">
       <c r="A79" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B79">
         <v>18</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D79">
         <v>8453735</v>
@@ -2297,7 +2261,7 @@
     </row>
     <row r="80" spans="1:5" ht="16.5" customHeight="1">
       <c r="A80" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B80">
         <v>19</v>
@@ -2314,13 +2278,13 @@
     </row>
     <row r="81" spans="1:5" ht="16.5" customHeight="1">
       <c r="A81" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B81">
         <v>20</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D81">
         <v>8385975</v>
@@ -2331,13 +2295,13 @@
     </row>
     <row r="82" spans="1:5" ht="16.5" customHeight="1">
       <c r="A82" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B82">
         <v>21</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>131</v>
+        <v>22</v>
       </c>
       <c r="D82">
         <v>7931262</v>
@@ -2348,13 +2312,13 @@
     </row>
     <row r="83" spans="1:5" ht="16.5" customHeight="1">
       <c r="A83" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B83">
         <v>22</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D83">
         <v>7760606</v>
@@ -2365,13 +2329,13 @@
     </row>
     <row r="84" spans="1:5" ht="16.5" customHeight="1">
       <c r="A84" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B84">
         <v>23</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D84">
         <v>7534842</v>
@@ -2382,7 +2346,7 @@
     </row>
     <row r="85" spans="1:5" ht="16.5" customHeight="1">
       <c r="A85" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B85">
         <v>24</v>
@@ -2399,7 +2363,7 @@
     </row>
     <row r="86" spans="1:5" ht="16.5" customHeight="1">
       <c r="A86" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B86">
         <v>25</v>
@@ -2416,13 +2380,13 @@
     </row>
     <row r="87" spans="1:5" ht="16.5" customHeight="1">
       <c r="A87" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B87">
         <v>26</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D87">
         <v>7281876</v>
@@ -2433,7 +2397,7 @@
     </row>
     <row r="88" spans="1:5" ht="16.5" customHeight="1">
       <c r="A88" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B88">
         <v>27</v>
@@ -2450,13 +2414,13 @@
     </row>
     <row r="89" spans="1:5" ht="16.5" customHeight="1">
       <c r="A89" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B89">
         <v>28</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>32</v>
+      <c r="C89" s="10" t="s">
+        <v>119</v>
       </c>
       <c r="D89">
         <v>7272828</v>
@@ -2467,13 +2431,13 @@
     </row>
     <row r="90" spans="1:5" ht="16.5" customHeight="1">
       <c r="A90" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B90">
         <v>29</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D90">
         <v>7236458</v>
@@ -2484,24 +2448,24 @@
     </row>
     <row r="91" spans="1:5" ht="16.5" customHeight="1">
       <c r="A91" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B91">
         <v>30</v>
       </c>
-      <c r="C91" s="1" t="s">
-        <v>34</v>
+      <c r="C91" s="10" t="s">
+        <v>118</v>
       </c>
       <c r="D91">
         <v>6986371</v>
       </c>
       <c r="E91" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="16.5" customHeight="1">
       <c r="A92" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B92">
         <v>31</v>
@@ -2513,29 +2477,29 @@
         <v>5884130</v>
       </c>
       <c r="E92" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="16.5" customHeight="1">
       <c r="A93" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B93">
         <v>32</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D93">
         <v>5813157</v>
       </c>
       <c r="E93" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="16.5" customHeight="1">
       <c r="A94" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B94">
         <v>33</v>
@@ -2547,29 +2511,29 @@
         <v>5275134</v>
       </c>
       <c r="E94" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="16.5" customHeight="1">
       <c r="A95" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B95">
         <v>34</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D95">
         <v>4876688</v>
       </c>
       <c r="E95" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="16.5" customHeight="1">
       <c r="A96" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B96">
         <v>35</v>
@@ -2581,233 +2545,233 @@
         <v>4842063</v>
       </c>
       <c r="E96" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="16.5" customHeight="1">
       <c r="A97" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B97">
         <v>36</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D97">
         <v>4668195</v>
       </c>
       <c r="E97" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="16.5" customHeight="1">
       <c r="A98" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B98">
         <v>37</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D98">
         <v>4616477</v>
       </c>
       <c r="E98" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="16.5" customHeight="1">
       <c r="A99" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B99">
         <v>38</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D99">
         <v>4498125</v>
       </c>
       <c r="E99" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="16.5" customHeight="1">
       <c r="A100" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B100">
         <v>39</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D100">
         <v>3687186</v>
       </c>
       <c r="E100" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="16.5" customHeight="1">
       <c r="A101" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B101">
         <v>40</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D101">
         <v>3611227</v>
       </c>
       <c r="E101" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="16.5" customHeight="1">
       <c r="A102" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B102">
         <v>41</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D102">
         <v>3189920</v>
       </c>
       <c r="E102" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="16.5" customHeight="1">
       <c r="A103" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B103">
         <v>42</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D103">
         <v>3120139</v>
       </c>
       <c r="E103" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="16.5" customHeight="1">
       <c r="A104" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B104">
         <v>43</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D104">
         <v>3108728</v>
       </c>
       <c r="E104" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="16.5" customHeight="1">
       <c r="A105" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B105">
         <v>44</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D105">
         <v>3077202</v>
       </c>
       <c r="E105" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="16.5" customHeight="1">
       <c r="A106" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B106">
         <v>45</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D106">
         <v>2968639</v>
       </c>
       <c r="E106" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="16.5" customHeight="1">
       <c r="A107" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B107">
         <v>46</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D107">
         <v>2968603</v>
       </c>
       <c r="E107" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="16.5" customHeight="1">
       <c r="A108" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B108">
         <v>47</v>
       </c>
-      <c r="C108" s="1" t="s">
-        <v>39</v>
+      <c r="C108" s="10" t="s">
+        <v>115</v>
       </c>
       <c r="D108">
         <v>2953979</v>
       </c>
       <c r="E108" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="16.5" customHeight="1">
       <c r="A109" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B109">
         <v>48</v>
       </c>
       <c r="C109" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D109">
         <v>2772649</v>
       </c>
       <c r="E109" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="16.5" customHeight="1">
       <c r="A110" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B110">
         <v>49</v>
@@ -2819,273 +2783,273 @@
         <v>2738331</v>
       </c>
       <c r="E110" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="16.5" customHeight="1">
       <c r="A111" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B111">
         <v>50</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D111">
         <v>2460723</v>
       </c>
       <c r="E111" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="16.5" customHeight="1">
       <c r="A112" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B112">
         <v>51</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D112">
         <v>2165388</v>
       </c>
       <c r="E112" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="16.5" customHeight="1">
       <c r="A113" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B113">
         <v>52</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D113">
         <v>2028076</v>
       </c>
       <c r="E113" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="16.5" customHeight="1">
       <c r="A114" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B114">
         <v>53</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D114">
         <v>1829852</v>
       </c>
       <c r="E114" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="16.5" customHeight="1">
       <c r="A115" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B115">
         <v>54</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D115">
         <v>1765395</v>
       </c>
       <c r="E115" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="16.5" customHeight="1">
       <c r="A116" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B116">
         <v>55</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D116">
         <v>1693947</v>
       </c>
       <c r="E116" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="16.5" customHeight="1">
       <c r="A117" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B117">
         <v>56</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D117">
         <v>1288077</v>
       </c>
       <c r="E117" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="16.5" customHeight="1">
       <c r="A118" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B118">
         <v>57</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D118">
         <v>1207196</v>
       </c>
       <c r="E118" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="16.5" customHeight="1">
       <c r="A119" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B119">
         <v>58</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D119">
         <v>963718</v>
       </c>
       <c r="E119" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="16.5" customHeight="1">
       <c r="A120" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B120">
         <v>59</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D120">
         <v>700489</v>
       </c>
       <c r="E120" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="16.5" customHeight="1">
       <c r="A121" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B121">
         <v>60</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D121">
         <v>659256</v>
       </c>
       <c r="E121" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="16.5" customHeight="1">
       <c r="A122" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B122">
         <v>61</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D122">
         <v>384395</v>
       </c>
       <c r="E122" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="16.5" customHeight="1">
       <c r="A123" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B123">
         <v>62</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D123">
         <v>327964</v>
       </c>
       <c r="E123" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="16.5" customHeight="1">
       <c r="A124" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B124">
         <v>63</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D124">
         <v>266932</v>
       </c>
       <c r="E124" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="16.5" customHeight="1">
       <c r="A125" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B125">
         <v>64</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D125">
         <v>89508</v>
       </c>
       <c r="E125" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="16.5" customHeight="1">
       <c r="A126" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D126">
         <v>76513151</v>
@@ -3096,7 +3060,7 @@
     </row>
     <row r="127" spans="1:5" ht="16.5" customHeight="1">
       <c r="A127" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B127">
         <v>2</v>
@@ -3113,13 +3077,13 @@
     </row>
     <row r="128" spans="1:5" ht="16.5" customHeight="1">
       <c r="A128" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B128">
         <v>3</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>32</v>
+      <c r="C128" s="10" t="s">
+        <v>119</v>
       </c>
       <c r="D128">
         <v>36598969</v>
@@ -3130,7 +3094,7 @@
     </row>
     <row r="129" spans="1:5" ht="16.5" customHeight="1">
       <c r="A129" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B129">
         <v>4</v>
@@ -3147,13 +3111,13 @@
     </row>
     <row r="130" spans="1:5" ht="16.5" customHeight="1">
       <c r="A130" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B130">
         <v>5</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D130">
         <v>22027625</v>
@@ -3164,7 +3128,7 @@
     </row>
     <row r="131" spans="1:5" ht="16.5" customHeight="1">
       <c r="A131" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B131">
         <v>6</v>
@@ -3181,7 +3145,7 @@
     </row>
     <row r="132" spans="1:5" ht="16.5" customHeight="1">
       <c r="A132" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B132">
         <v>7</v>
@@ -3198,7 +3162,7 @@
     </row>
     <row r="133" spans="1:5" ht="16.5" customHeight="1">
       <c r="A133" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B133">
         <v>8</v>
@@ -3215,13 +3179,13 @@
     </row>
     <row r="134" spans="1:5" ht="16.5" customHeight="1">
       <c r="A134" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B134">
         <v>9</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D134">
         <v>15971399</v>
@@ -3232,7 +3196,7 @@
     </row>
     <row r="135" spans="1:5" ht="16.5" customHeight="1">
       <c r="A135" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B135">
         <v>10</v>
@@ -3249,13 +3213,13 @@
     </row>
     <row r="136" spans="1:5" ht="16.5" customHeight="1">
       <c r="A136" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B136">
         <v>11</v>
       </c>
-      <c r="C136" s="1" t="s">
-        <v>30</v>
+      <c r="C136" s="10" t="s">
+        <v>117</v>
       </c>
       <c r="D136">
         <v>15166835</v>
@@ -3266,13 +3230,13 @@
     </row>
     <row r="137" spans="1:5" ht="16.5" customHeight="1">
       <c r="A137" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B137">
         <v>12</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D137">
         <v>15136017</v>
@@ -3283,7 +3247,7 @@
     </row>
     <row r="138" spans="1:5" ht="16.5" customHeight="1">
       <c r="A138" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B138">
         <v>13</v>
@@ -3300,13 +3264,13 @@
     </row>
     <row r="139" spans="1:5" ht="16.5" customHeight="1">
       <c r="A139" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B139">
         <v>14</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D139">
         <v>11929975</v>
@@ -3317,7 +3281,7 @@
     </row>
     <row r="140" spans="1:5" ht="16.5" customHeight="1">
       <c r="A140" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B140">
         <v>15</v>
@@ -3334,13 +3298,13 @@
     </row>
     <row r="141" spans="1:5" ht="16.5" customHeight="1">
       <c r="A141" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B141">
         <v>16</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D141">
         <v>11641804</v>
@@ -3351,13 +3315,13 @@
     </row>
     <row r="142" spans="1:5" ht="16.5" customHeight="1">
       <c r="A142" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B142">
         <v>17</v>
       </c>
-      <c r="C142" s="1" t="s">
-        <v>34</v>
+      <c r="C142" s="10" t="s">
+        <v>118</v>
       </c>
       <c r="D142">
         <v>11224132</v>
@@ -3368,13 +3332,13 @@
     </row>
     <row r="143" spans="1:5" ht="16.5" customHeight="1">
       <c r="A143" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B143">
         <v>18</v>
       </c>
-      <c r="C143" s="1" t="s">
-        <v>85</v>
+      <c r="C143" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="D143">
         <v>11128193</v>
@@ -3385,7 +3349,7 @@
     </row>
     <row r="144" spans="1:5" ht="16.5" customHeight="1">
       <c r="A144" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B144">
         <v>19</v>
@@ -3402,13 +3366,13 @@
     </row>
     <row r="145" spans="1:5" ht="16.5" customHeight="1">
       <c r="A145" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B145">
         <v>20</v>
       </c>
       <c r="C145" s="10" t="s">
-        <v>131</v>
+        <v>22</v>
       </c>
       <c r="D145">
         <v>10606882</v>
@@ -3419,7 +3383,7 @@
     </row>
     <row r="146" spans="1:5" ht="16.5" customHeight="1">
       <c r="A146" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B146">
         <v>21</v>
@@ -3436,7 +3400,7 @@
     </row>
     <row r="147" spans="1:5" ht="16.5" customHeight="1">
       <c r="A147" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B147">
         <v>22</v>
@@ -3453,13 +3417,13 @@
     </row>
     <row r="148" spans="1:5" ht="16.5" customHeight="1">
       <c r="A148" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B148">
         <v>23</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D148">
         <v>10128124</v>
@@ -3470,7 +3434,7 @@
     </row>
     <row r="149" spans="1:5" ht="16.5" customHeight="1">
       <c r="A149" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B149">
         <v>24</v>
@@ -3487,13 +3451,13 @@
     </row>
     <row r="150" spans="1:5" ht="16.5" customHeight="1">
       <c r="A150" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B150">
         <v>25</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D150">
         <v>9164119</v>
@@ -3504,13 +3468,13 @@
     </row>
     <row r="151" spans="1:5" ht="16.5" customHeight="1">
       <c r="A151" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B151">
         <v>26</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D151">
         <v>8999382</v>
@@ -3521,13 +3485,13 @@
     </row>
     <row r="152" spans="1:5" ht="16.5" customHeight="1">
       <c r="A152" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B152">
         <v>27</v>
       </c>
-      <c r="C152" s="1" t="s">
-        <v>23</v>
+      <c r="C152" s="10" t="s">
+        <v>116</v>
       </c>
       <c r="D152">
         <v>8596217</v>
@@ -3538,13 +3502,13 @@
     </row>
     <row r="153" spans="1:5" ht="16.5" customHeight="1">
       <c r="A153" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B153">
         <v>28</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D153">
         <v>8456726</v>
@@ -3555,13 +3519,13 @@
     </row>
     <row r="154" spans="1:5" ht="16.5" customHeight="1">
       <c r="A154" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B154">
         <v>29</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D154">
         <v>8220352</v>
@@ -3572,13 +3536,13 @@
     </row>
     <row r="155" spans="1:5" ht="16.5" customHeight="1">
       <c r="A155" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B155">
         <v>30</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D155">
         <v>8154156</v>
@@ -3589,13 +3553,13 @@
     </row>
     <row r="156" spans="1:5" ht="16.5" customHeight="1">
       <c r="A156" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B156">
         <v>31</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D156">
         <v>8127020</v>
@@ -3606,13 +3570,13 @@
     </row>
     <row r="157" spans="1:5" ht="16.5" customHeight="1">
       <c r="A157" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B157">
         <v>32</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D157">
         <v>7952273</v>
@@ -3623,13 +3587,13 @@
     </row>
     <row r="158" spans="1:5" ht="16.5" customHeight="1">
       <c r="A158" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B158">
         <v>33</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D158">
         <v>7918857</v>
@@ -3640,7 +3604,7 @@
     </row>
     <row r="159" spans="1:5" ht="16.5" customHeight="1">
       <c r="A159" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B159">
         <v>34</v>
@@ -3657,13 +3621,13 @@
     </row>
     <row r="160" spans="1:5" ht="16.5" customHeight="1">
       <c r="A160" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B160">
         <v>35</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D160">
         <v>7876636</v>
@@ -3674,13 +3638,13 @@
     </row>
     <row r="161" spans="1:5" ht="16.5" customHeight="1">
       <c r="A161" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B161">
         <v>36</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D161">
         <v>7824653</v>
@@ -3691,13 +3655,13 @@
     </row>
     <row r="162" spans="1:5" ht="16.5" customHeight="1">
       <c r="A162" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B162">
         <v>37</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D162">
         <v>7823884</v>
@@ -3708,13 +3672,13 @@
     </row>
     <row r="163" spans="1:5" ht="16.5" customHeight="1">
       <c r="A163" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B163">
         <v>38</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D163">
         <v>7679597</v>
@@ -3725,13 +3689,13 @@
     </row>
     <row r="164" spans="1:5" ht="16.5" customHeight="1">
       <c r="A164" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B164">
         <v>39</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D164">
         <v>7635056</v>
@@ -3742,13 +3706,13 @@
     </row>
     <row r="165" spans="1:5" ht="16.5" customHeight="1">
       <c r="A165" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B165">
         <v>40</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D165">
         <v>7579677</v>
@@ -3759,13 +3723,13 @@
     </row>
     <row r="166" spans="1:5" ht="16.5" customHeight="1">
       <c r="A166" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B166">
         <v>41</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D166">
         <v>7552044</v>
@@ -3776,13 +3740,13 @@
     </row>
     <row r="167" spans="1:5" ht="16.5" customHeight="1">
       <c r="A167" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B167">
         <v>42</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D167">
         <v>7462230</v>
@@ -3793,13 +3757,13 @@
     </row>
     <row r="168" spans="1:5" ht="16.5" customHeight="1">
       <c r="A168" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B168">
         <v>43</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D168">
         <v>7423633</v>
@@ -3810,13 +3774,13 @@
     </row>
     <row r="169" spans="1:5" ht="16.5" customHeight="1">
       <c r="A169" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B169">
         <v>44</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D169">
         <v>7327050</v>
@@ -3827,160 +3791,160 @@
     </row>
     <row r="170" spans="1:5" ht="16.5" customHeight="1">
       <c r="A170" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B170">
         <v>45</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D170">
         <v>6678842</v>
       </c>
       <c r="E170" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="16.5" customHeight="1">
       <c r="A171" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B171">
         <v>46</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D171">
         <v>6177989</v>
       </c>
       <c r="E171" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="16.5" customHeight="1">
       <c r="A172" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B172">
         <v>47</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D172">
         <v>5901298</v>
       </c>
       <c r="E172" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="16.5" customHeight="1">
       <c r="A173" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B173">
         <v>48</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D173">
         <v>5097585</v>
       </c>
       <c r="E173" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="16.5" customHeight="1">
       <c r="A174" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B174">
         <v>49</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D174">
         <v>5036088</v>
       </c>
       <c r="E174" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="16.5" customHeight="1">
       <c r="A175" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B175">
         <v>50</v>
       </c>
-      <c r="C175" s="1" t="s">
-        <v>50</v>
+      <c r="C175" s="11" t="s">
+        <v>112</v>
       </c>
       <c r="D175">
         <v>4821347</v>
       </c>
       <c r="E175" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="16.5" customHeight="1">
       <c r="A176" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B176">
         <v>51</v>
       </c>
-      <c r="C176" s="1" t="s">
-        <v>39</v>
+      <c r="C176" s="10" t="s">
+        <v>115</v>
       </c>
       <c r="D176">
         <v>4599953</v>
       </c>
       <c r="E176" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="16.5" customHeight="1">
       <c r="A177" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B177">
         <v>52</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D177">
         <v>4332112</v>
       </c>
       <c r="E177" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="16.5" customHeight="1">
       <c r="A178" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B178">
         <v>53</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D178">
         <v>4235009</v>
       </c>
       <c r="E178" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="16.5" customHeight="1">
       <c r="A179" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B179">
         <v>54</v>
@@ -3992,12 +3956,12 @@
         <v>4226803</v>
       </c>
       <c r="E179" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="16.5" customHeight="1">
       <c r="A180" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B180">
         <v>55</v>
@@ -4009,216 +3973,216 @@
         <v>3992666</v>
       </c>
       <c r="E180" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="16.5" customHeight="1">
       <c r="A181" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B181">
         <v>56</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D181">
         <v>3935236</v>
       </c>
       <c r="E181" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="16.5" customHeight="1">
       <c r="A182" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B182">
         <v>57</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D182">
         <v>3819189</v>
       </c>
       <c r="E182" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="16.5" customHeight="1">
       <c r="A183" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B183">
         <v>58</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D183">
         <v>2896389</v>
       </c>
       <c r="E183" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="184" spans="1:5" ht="16.5" customHeight="1">
       <c r="A184" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B184">
         <v>59</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D184">
         <v>2645896</v>
       </c>
       <c r="E184" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="185" spans="1:5" ht="16.5" customHeight="1">
       <c r="A185" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B185">
         <v>60</v>
       </c>
       <c r="C185" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D185">
         <v>2195612</v>
       </c>
       <c r="E185" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="16.5" customHeight="1">
       <c r="A186" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B186">
         <v>61</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D186">
         <v>1908787</v>
       </c>
       <c r="E186" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="16.5" customHeight="1">
       <c r="A187" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B187">
         <v>62</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D187">
         <v>1890847</v>
       </c>
       <c r="E187" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="16.5" customHeight="1">
       <c r="A188" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B188">
         <v>63</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D188">
         <v>1772463</v>
       </c>
       <c r="E188" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="189" spans="1:5" ht="16.5" customHeight="1">
       <c r="A189" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B189">
         <v>64</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D189">
         <v>1472500</v>
       </c>
       <c r="E189" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="16.5" customHeight="1">
       <c r="A190" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B190">
         <v>65</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D190">
         <v>1425274</v>
       </c>
       <c r="E190" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="191" spans="1:5" ht="16.5" customHeight="1">
       <c r="A191" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B191">
         <v>66</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D191">
         <v>1226829</v>
       </c>
       <c r="E191" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="16.5" customHeight="1">
       <c r="A192" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B192">
         <v>67</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D192">
         <v>460000</v>
       </c>
       <c r="E192" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="193" spans="1:5" ht="16.5" customHeight="1">
       <c r="A193" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B193" s="2">
         <v>1</v>
@@ -4236,13 +4200,13 @@
     </row>
     <row r="194" spans="1:5" ht="16.5" customHeight="1">
       <c r="A194" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B194" s="2">
         <v>2</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D194" s="4">
         <v>12925350</v>
@@ -4254,13 +4218,13 @@
     </row>
     <row r="195" spans="1:5" ht="16.5" customHeight="1">
       <c r="A195" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B195" s="2">
         <v>3</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D195" s="4">
         <v>12016650</v>
@@ -4272,13 +4236,13 @@
     </row>
     <row r="196" spans="1:5" ht="16.5" customHeight="1">
       <c r="A196" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B196" s="2">
         <v>4</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D196" s="4">
         <v>9907350</v>
@@ -4290,13 +4254,13 @@
     </row>
     <row r="197" spans="1:5" ht="16.5" customHeight="1">
       <c r="A197" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B197" s="2">
         <v>5</v>
       </c>
-      <c r="C197" s="3" t="s">
-        <v>23</v>
+      <c r="C197" s="7" t="s">
+        <v>116</v>
       </c>
       <c r="D197" s="4">
         <v>9868650</v>
@@ -4308,13 +4272,13 @@
     </row>
     <row r="198" spans="1:5" ht="16.5" customHeight="1">
       <c r="A198" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B198" s="2">
         <v>6</v>
       </c>
-      <c r="C198" s="3" t="s">
-        <v>32</v>
+      <c r="C198" s="7" t="s">
+        <v>119</v>
       </c>
       <c r="D198" s="4">
         <v>9143700</v>
@@ -4326,7 +4290,7 @@
     </row>
     <row r="199" spans="1:5" ht="16.5" customHeight="1">
       <c r="A199" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B199" s="2">
         <v>7</v>
@@ -4344,7 +4308,7 @@
     </row>
     <row r="200" spans="1:5" ht="16.5" customHeight="1">
       <c r="A200" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B200" s="2">
         <v>8</v>
@@ -4362,13 +4326,13 @@
     </row>
     <row r="201" spans="1:5" ht="16.5" customHeight="1">
       <c r="A201" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B201" s="2">
         <v>9</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D201" s="4">
         <v>9017250</v>
@@ -4380,13 +4344,13 @@
     </row>
     <row r="202" spans="1:5" ht="16.5" customHeight="1">
       <c r="A202" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B202" s="2">
         <v>10</v>
       </c>
-      <c r="C202" s="3" t="s">
-        <v>30</v>
+      <c r="C202" s="7" t="s">
+        <v>117</v>
       </c>
       <c r="D202" s="4">
         <v>8908800</v>
@@ -4398,7 +4362,7 @@
     </row>
     <row r="203" spans="1:5" ht="16.5" customHeight="1">
       <c r="A203" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B203" s="2">
         <v>11</v>
@@ -4416,13 +4380,13 @@
     </row>
     <row r="204" spans="1:5" ht="16.5" customHeight="1">
       <c r="A204" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B204" s="2">
         <v>12</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>131</v>
+        <v>22</v>
       </c>
       <c r="D204" s="4">
         <v>8226750</v>
@@ -4434,13 +4398,13 @@
     </row>
     <row r="205" spans="1:5" ht="16.5" customHeight="1">
       <c r="A205" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B205" s="2">
         <v>13</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D205" s="4">
         <v>8125259</v>
@@ -4452,13 +4416,13 @@
     </row>
     <row r="206" spans="1:5" ht="16.5" customHeight="1">
       <c r="A206" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B206" s="2">
         <v>14</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D206" s="4">
         <v>7855412</v>
@@ -4470,7 +4434,7 @@
     </row>
     <row r="207" spans="1:5" ht="16.5" customHeight="1">
       <c r="A207" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B207" s="2">
         <v>15</v>
@@ -4488,7 +4452,7 @@
     </row>
     <row r="208" spans="1:5" ht="16.5" customHeight="1">
       <c r="A208" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B208" s="2">
         <v>16</v>
@@ -4506,7 +4470,7 @@
     </row>
     <row r="209" spans="1:5" ht="16.5" customHeight="1">
       <c r="A209" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B209" s="2">
         <v>17</v>
@@ -4524,13 +4488,13 @@
     </row>
     <row r="210" spans="1:5" ht="16.5" customHeight="1">
       <c r="A210" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B210" s="2">
         <v>18</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D210" s="4">
         <v>7694109</v>
@@ -4542,13 +4506,13 @@
     </row>
     <row r="211" spans="1:5" ht="16.5" customHeight="1">
       <c r="A211" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B211" s="2">
         <v>19</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D211" s="4">
         <v>7624294</v>
@@ -4560,13 +4524,13 @@
     </row>
     <row r="212" spans="1:5" ht="16.5" customHeight="1">
       <c r="A212" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B212" s="2">
         <v>20</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D212" s="4">
         <v>7548021</v>
@@ -4578,7 +4542,7 @@
     </row>
     <row r="213" spans="1:5" ht="16.5" customHeight="1">
       <c r="A213" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B213" s="2">
         <v>21</v>
@@ -4596,13 +4560,13 @@
     </row>
     <row r="214" spans="1:5" ht="16.5" customHeight="1">
       <c r="A214" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B214" s="2">
         <v>22</v>
       </c>
-      <c r="C214" s="3" t="s">
-        <v>85</v>
+      <c r="C214" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="D214" s="4">
         <v>7392720</v>
@@ -4614,7 +4578,7 @@
     </row>
     <row r="215" spans="1:5" ht="16.5" customHeight="1">
       <c r="A215" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B215" s="2">
         <v>23</v>
@@ -4632,7 +4596,7 @@
     </row>
     <row r="216" spans="1:5" ht="16.5" customHeight="1">
       <c r="A216" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B216" s="2">
         <v>24</v>
@@ -4650,13 +4614,13 @@
     </row>
     <row r="217" spans="1:5" ht="16.5" customHeight="1">
       <c r="A217" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B217" s="2">
         <v>25</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D217" s="4">
         <v>7285842</v>
@@ -4668,7 +4632,7 @@
     </row>
     <row r="218" spans="1:5" ht="16.5" customHeight="1">
       <c r="A218" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B218" s="2">
         <v>26</v>
@@ -4686,7 +4650,7 @@
     </row>
     <row r="219" spans="1:5" ht="16.5" customHeight="1">
       <c r="A219" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B219" s="2">
         <v>27</v>
@@ -4704,13 +4668,13 @@
     </row>
     <row r="220" spans="1:5" ht="16.5" customHeight="1">
       <c r="A220" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B220" s="2">
         <v>28</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D220" s="4">
         <v>7095450</v>
@@ -4722,13 +4686,13 @@
     </row>
     <row r="221" spans="1:5" ht="16.5" customHeight="1">
       <c r="A221" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B221" s="2">
         <v>29</v>
       </c>
       <c r="C221" s="7" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D221" s="4">
         <v>5739081</v>
@@ -4740,13 +4704,13 @@
     </row>
     <row r="222" spans="1:5" ht="16.5" customHeight="1">
       <c r="A222" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B222" s="2">
         <v>30</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D222" s="4">
         <v>5561285</v>
@@ -4758,13 +4722,13 @@
     </row>
     <row r="223" spans="1:5" ht="16.5" customHeight="1">
       <c r="A223" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B223" s="2">
         <v>31</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D223" s="4">
         <v>5434650</v>
@@ -4776,13 +4740,13 @@
     </row>
     <row r="224" spans="1:5" ht="16.5" customHeight="1">
       <c r="A224" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B224" s="2">
         <v>32</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D224" s="4">
         <v>5171951</v>
@@ -4794,13 +4758,13 @@
     </row>
     <row r="225" spans="1:5" ht="16.5" customHeight="1">
       <c r="A225" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B225" s="2">
         <v>33</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D225" s="4">
         <v>5091005</v>
@@ -4812,13 +4776,13 @@
     </row>
     <row r="226" spans="1:5" ht="16.5" customHeight="1">
       <c r="A226" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B226" s="2">
         <v>34</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D226" s="4">
         <v>5016847</v>
@@ -4830,7 +4794,7 @@
     </row>
     <row r="227" spans="1:5" ht="16.5" customHeight="1">
       <c r="A227" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B227" s="2">
         <v>35</v>
@@ -4848,13 +4812,13 @@
     </row>
     <row r="228" spans="1:5" ht="16.5" customHeight="1">
       <c r="A228" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B228" s="2">
         <v>36</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D228" s="4">
         <v>4537987</v>
@@ -4866,13 +4830,13 @@
     </row>
     <row r="229" spans="1:5" ht="16.5" customHeight="1">
       <c r="A229" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B229" s="2">
         <v>37</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D229" s="4">
         <v>4444305</v>
@@ -4884,13 +4848,13 @@
     </row>
     <row r="230" spans="1:5" ht="16.5" customHeight="1">
       <c r="A230" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B230" s="2">
         <v>38</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D230" s="4">
         <v>4393558</v>
@@ -4902,13 +4866,13 @@
     </row>
     <row r="231" spans="1:5" ht="16.5" customHeight="1">
       <c r="A231" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B231" s="2">
         <v>39</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D231" s="4">
         <v>4361685</v>
@@ -4920,13 +4884,13 @@
     </row>
     <row r="232" spans="1:5" ht="16.5" customHeight="1">
       <c r="A232" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B232" s="2">
         <v>40</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D232" s="4">
         <v>4314000</v>
@@ -4938,13 +4902,13 @@
     </row>
     <row r="233" spans="1:5" ht="16.5" customHeight="1">
       <c r="A233" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B233" s="2">
         <v>41</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D233" s="4">
         <v>4305372</v>
@@ -4956,13 +4920,13 @@
     </row>
     <row r="234" spans="1:5" ht="16.5" customHeight="1">
       <c r="A234" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B234" s="2">
         <v>42</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D234" s="4">
         <v>4250088</v>
@@ -4974,13 +4938,13 @@
     </row>
     <row r="235" spans="1:5" ht="16.5" customHeight="1">
       <c r="A235" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B235" s="2">
         <v>43</v>
       </c>
-      <c r="C235" s="3" t="s">
-        <v>34</v>
+      <c r="C235" s="7" t="s">
+        <v>118</v>
       </c>
       <c r="D235" s="4">
         <v>4174414</v>
@@ -4992,13 +4956,13 @@
     </row>
     <row r="236" spans="1:5" ht="16.5" customHeight="1">
       <c r="A236" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B236" s="2">
         <v>44</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D236" s="4">
         <v>4151246</v>
@@ -5010,13 +4974,13 @@
     </row>
     <row r="237" spans="1:5" ht="16.5" customHeight="1">
       <c r="A237" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B237" s="2">
         <v>45</v>
       </c>
-      <c r="C237" s="3" t="s">
-        <v>39</v>
+      <c r="C237" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="D237" s="4">
         <v>4081096</v>
@@ -5028,13 +4992,13 @@
     </row>
     <row r="238" spans="1:5" ht="16.5" customHeight="1">
       <c r="A238" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B238" s="2">
         <v>46</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D238" s="4">
         <v>4033323</v>
@@ -5046,7 +5010,7 @@
     </row>
     <row r="239" spans="1:5" ht="16.5" customHeight="1">
       <c r="A239" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B239" s="2">
         <v>47</v>
@@ -5064,13 +5028,13 @@
     </row>
     <row r="240" spans="1:5" ht="16.5" customHeight="1">
       <c r="A240" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B240" s="2">
         <v>48</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D240" s="4">
         <v>4000500</v>
@@ -5082,13 +5046,13 @@
     </row>
     <row r="241" spans="1:5" ht="16.5" customHeight="1">
       <c r="A241" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B241" s="2">
         <v>49</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D241" s="4">
         <v>3893926</v>
@@ -5100,13 +5064,13 @@
     </row>
     <row r="242" spans="1:5" ht="16.5" customHeight="1">
       <c r="A242" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B242" s="2">
         <v>50</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D242" s="4">
         <v>3892915</v>
@@ -5118,13 +5082,13 @@
     </row>
     <row r="243" spans="1:5" ht="16.5" customHeight="1">
       <c r="A243" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B243" s="2">
         <v>51</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D243" s="4">
         <v>3817624</v>
@@ -5136,13 +5100,13 @@
     </row>
     <row r="244" spans="1:5" ht="16.5" customHeight="1">
       <c r="A244" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B244" s="2">
         <v>52</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D244" s="4">
         <v>3776295</v>
@@ -5154,7 +5118,7 @@
     </row>
     <row r="245" spans="1:5" ht="16.5" customHeight="1">
       <c r="A245" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B245" s="2">
         <v>53</v>
@@ -5172,13 +5136,13 @@
     </row>
     <row r="246" spans="1:5" ht="16.5" customHeight="1">
       <c r="A246" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B246" s="2">
         <v>54</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D246" s="4">
         <v>3620200</v>
@@ -5190,13 +5154,13 @@
     </row>
     <row r="247" spans="1:5" ht="16.5" customHeight="1">
       <c r="A247" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B247" s="2">
         <v>55</v>
       </c>
-      <c r="C247" s="3" t="s">
-        <v>50</v>
+      <c r="C247" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="D247" s="4">
         <v>3414335</v>
@@ -5208,13 +5172,13 @@
     </row>
     <row r="248" spans="1:5" ht="16.5" customHeight="1">
       <c r="A248" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B248" s="2">
         <v>56</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D248" s="4">
         <v>3164754</v>
@@ -5226,13 +5190,13 @@
     </row>
     <row r="249" spans="1:5" ht="16.5" customHeight="1">
       <c r="A249" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B249" s="2">
         <v>57</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D249" s="4">
         <v>3063699</v>
@@ -5244,13 +5208,13 @@
     </row>
     <row r="250" spans="1:5" ht="16.5" customHeight="1">
       <c r="A250" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B250" s="2">
         <v>58</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D250" s="4">
         <v>2777032</v>
@@ -5262,13 +5226,13 @@
     </row>
     <row r="251" spans="1:5" ht="16.5" customHeight="1">
       <c r="A251" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B251" s="2">
         <v>59</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D251" s="4">
         <v>2391014</v>
@@ -5280,13 +5244,13 @@
     </row>
     <row r="252" spans="1:5" ht="16.5" customHeight="1">
       <c r="A252" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B252" s="2">
         <v>60</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D252" s="4">
         <v>2371425</v>
@@ -5298,13 +5262,13 @@
     </row>
     <row r="253" spans="1:5" ht="16.5" customHeight="1">
       <c r="A253" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B253" s="2">
         <v>61</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D253" s="4">
         <v>2022500</v>
@@ -5316,13 +5280,13 @@
     </row>
     <row r="254" spans="1:5" ht="16.5" customHeight="1">
       <c r="A254" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B254" s="2">
         <v>62</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D254" s="4">
         <v>1764375</v>
@@ -5334,13 +5298,13 @@
     </row>
     <row r="255" spans="1:5" ht="16.5" customHeight="1">
       <c r="A255" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B255" s="2">
         <v>63</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D255" s="4">
         <v>1739773</v>
@@ -5352,13 +5316,13 @@
     </row>
     <row r="256" spans="1:5" ht="16.5" customHeight="1">
       <c r="A256" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B256" s="2">
         <v>64</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D256" s="4">
         <v>1685105</v>
@@ -5370,7 +5334,7 @@
     </row>
     <row r="257" spans="1:5" ht="16.5" customHeight="1">
       <c r="A257" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B257" s="2">
         <v>65</v>
@@ -5388,13 +5352,13 @@
     </row>
     <row r="258" spans="1:5" ht="16.5" customHeight="1">
       <c r="A258" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B258" s="2">
         <v>66</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D258" s="4">
         <v>1116967</v>
@@ -5406,13 +5370,13 @@
     </row>
     <row r="259" spans="1:5" ht="16.5" customHeight="1">
       <c r="A259" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B259" s="2">
         <v>67</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D259" s="4">
         <v>481250</v>
@@ -5424,13 +5388,13 @@
     </row>
     <row r="260" spans="1:5" ht="16.5" customHeight="1">
       <c r="A260" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B260" s="2">
         <v>68</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D260" s="4">
         <v>368750</v>
@@ -5442,13 +5406,13 @@
     </row>
     <row r="261" spans="1:5" ht="16.5" customHeight="1">
       <c r="A261" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B261" s="2">
         <v>1</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D261" s="4">
         <v>32997950</v>
@@ -5460,13 +5424,13 @@
     </row>
     <row r="262" spans="1:5" ht="16.5" customHeight="1">
       <c r="A262" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B262" s="2">
         <v>2</v>
       </c>
-      <c r="C262" s="6" t="s">
-        <v>32</v>
+      <c r="C262" s="7" t="s">
+        <v>119</v>
       </c>
       <c r="D262" s="4">
         <v>15520250</v>
@@ -5478,7 +5442,7 @@
     </row>
     <row r="263" spans="1:5" ht="16.5" customHeight="1">
       <c r="A263" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B263" s="2">
         <v>3</v>
@@ -5496,7 +5460,7 @@
     </row>
     <row r="264" spans="1:5" ht="16.5" customHeight="1">
       <c r="A264" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B264" s="2">
         <v>4</v>
@@ -5514,13 +5478,13 @@
     </row>
     <row r="265" spans="1:5" ht="16.5" customHeight="1">
       <c r="A265" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B265" s="2">
         <v>5</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D265" s="4">
         <v>11730150</v>
@@ -5532,7 +5496,7 @@
     </row>
     <row r="266" spans="1:5" ht="16.5" customHeight="1">
       <c r="A266" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B266" s="2">
         <v>6</v>
@@ -5550,13 +5514,13 @@
     </row>
     <row r="267" spans="1:5" ht="16.5" customHeight="1">
       <c r="A267" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B267" s="2">
         <v>7</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D267" s="4">
         <v>10310343</v>
@@ -5568,7 +5532,7 @@
     </row>
     <row r="268" spans="1:5" ht="16.5" customHeight="1">
       <c r="A268" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B268" s="2">
         <v>8</v>
@@ -5586,13 +5550,13 @@
     </row>
     <row r="269" spans="1:5" ht="16.5" customHeight="1">
       <c r="A269" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B269" s="2">
         <v>9</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D269" s="4">
         <v>9783249</v>
@@ -5604,13 +5568,13 @@
     </row>
     <row r="270" spans="1:5" ht="16.5" customHeight="1">
       <c r="A270" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B270" s="2">
         <v>10</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D270" s="4">
         <v>9196550</v>
@@ -5622,7 +5586,7 @@
     </row>
     <row r="271" spans="1:5" ht="16.5" customHeight="1">
       <c r="A271" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B271" s="2">
         <v>11</v>
@@ -5640,13 +5604,13 @@
     </row>
     <row r="272" spans="1:5" ht="16.5" customHeight="1">
       <c r="A272" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B272" s="2">
         <v>12</v>
       </c>
-      <c r="C272" s="6" t="s">
-        <v>23</v>
+      <c r="C272" s="7" t="s">
+        <v>116</v>
       </c>
       <c r="D272" s="4">
         <v>8990350</v>
@@ -5658,13 +5622,13 @@
     </row>
     <row r="273" spans="1:5" ht="16.5" customHeight="1">
       <c r="A273" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B273" s="2">
         <v>13</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D273" s="4">
         <v>8798439</v>
@@ -5676,13 +5640,13 @@
     </row>
     <row r="274" spans="1:5" ht="16.5" customHeight="1">
       <c r="A274" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B274" s="2">
         <v>14</v>
       </c>
-      <c r="C274" s="6" t="s">
-        <v>30</v>
+      <c r="C274" s="7" t="s">
+        <v>117</v>
       </c>
       <c r="D274" s="4">
         <v>8797500</v>
@@ -5694,13 +5658,13 @@
     </row>
     <row r="275" spans="1:5" ht="16.5" customHeight="1">
       <c r="A275" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B275" s="2">
         <v>15</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D275" s="4">
         <v>8702111</v>
@@ -5712,13 +5676,13 @@
     </row>
     <row r="276" spans="1:5" ht="16.5" customHeight="1">
       <c r="A276" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B276" s="2">
         <v>16</v>
       </c>
       <c r="C276" s="7" t="s">
-        <v>131</v>
+        <v>22</v>
       </c>
       <c r="D276" s="4">
         <v>8594600</v>
@@ -5730,13 +5694,13 @@
     </row>
     <row r="277" spans="1:5" ht="16.5" customHeight="1">
       <c r="A277" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B277" s="2">
         <v>17</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D277" s="4">
         <v>8587682</v>
@@ -5748,13 +5712,13 @@
     </row>
     <row r="278" spans="1:5" ht="16.5" customHeight="1">
       <c r="A278" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B278" s="2">
         <v>18</v>
       </c>
-      <c r="C278" s="6" t="s">
-        <v>39</v>
+      <c r="C278" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="D278" s="4">
         <v>8525490</v>
@@ -5766,13 +5730,13 @@
     </row>
     <row r="279" spans="1:5" ht="16.5" customHeight="1">
       <c r="A279" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B279" s="2">
         <v>19</v>
       </c>
-      <c r="C279" s="6" t="s">
-        <v>85</v>
+      <c r="C279" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="D279" s="4">
         <v>8248525</v>
@@ -5784,13 +5748,13 @@
     </row>
     <row r="280" spans="1:5" ht="16.5" customHeight="1">
       <c r="A280" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B280" s="2">
         <v>20</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D280" s="4">
         <v>8177600</v>
@@ -5802,7 +5766,7 @@
     </row>
     <row r="281" spans="1:5" ht="16.5" customHeight="1">
       <c r="A281" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B281" s="2">
         <v>21</v>
@@ -5820,13 +5784,13 @@
     </row>
     <row r="282" spans="1:5" ht="16.5" customHeight="1">
       <c r="A282" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B282" s="2">
         <v>22</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D282" s="4">
         <v>8051401</v>
@@ -5838,13 +5802,13 @@
     </row>
     <row r="283" spans="1:5" ht="16.5" customHeight="1">
       <c r="A283" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B283" s="2">
         <v>23</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D283" s="4">
         <v>7776950</v>
@@ -5856,7 +5820,7 @@
     </row>
     <row r="284" spans="1:5" ht="16.5" customHeight="1">
       <c r="A284" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B284" s="2">
         <v>24</v>
@@ -5874,7 +5838,7 @@
     </row>
     <row r="285" spans="1:5" ht="16.5" customHeight="1">
       <c r="A285" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B285" s="2">
         <v>25</v>
@@ -5892,7 +5856,7 @@
     </row>
     <row r="286" spans="1:5" ht="16.5" customHeight="1">
       <c r="A286" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B286" s="2">
         <v>26</v>
@@ -5910,7 +5874,7 @@
     </row>
     <row r="287" spans="1:5" ht="16.5" customHeight="1">
       <c r="A287" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B287" s="2">
         <v>27</v>
@@ -5928,7 +5892,7 @@
     </row>
     <row r="288" spans="1:5" ht="16.5" customHeight="1">
       <c r="A288" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B288" s="2">
         <v>28</v>
@@ -5946,13 +5910,13 @@
     </row>
     <row r="289" spans="1:5" ht="16.5" customHeight="1">
       <c r="A289" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B289" s="2">
         <v>29</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D289" s="4">
         <v>7511676</v>
@@ -5964,7 +5928,7 @@
     </row>
     <row r="290" spans="1:5" ht="16.5" customHeight="1">
       <c r="A290" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B290" s="2">
         <v>30</v>
@@ -5982,13 +5946,13 @@
     </row>
     <row r="291" spans="1:5" ht="16.5" customHeight="1">
       <c r="A291" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B291" s="2">
         <v>31</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D291" s="4">
         <v>7435700</v>
@@ -6000,13 +5964,13 @@
     </row>
     <row r="292" spans="1:5" ht="16.5" customHeight="1">
       <c r="A292" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B292" s="2">
         <v>32</v>
       </c>
       <c r="C292" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D292" s="4">
         <v>7331000</v>
@@ -6018,13 +5982,13 @@
     </row>
     <row r="293" spans="1:5" ht="16.5" customHeight="1">
       <c r="A293" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B293" s="2">
         <v>33</v>
       </c>
-      <c r="C293" s="6" t="s">
-        <v>50</v>
+      <c r="C293" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="D293" s="4">
         <v>7321924</v>
@@ -6036,13 +6000,13 @@
     </row>
     <row r="294" spans="1:5" ht="16.5" customHeight="1">
       <c r="A294" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B294" s="2">
         <v>34</v>
       </c>
-      <c r="C294" s="6" t="s">
-        <v>34</v>
+      <c r="C294" s="7" t="s">
+        <v>118</v>
       </c>
       <c r="D294" s="4">
         <v>7318696</v>
@@ -6054,7 +6018,7 @@
     </row>
     <row r="295" spans="1:5" ht="16.5" customHeight="1">
       <c r="A295" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B295" s="2">
         <v>35</v>
@@ -6072,13 +6036,13 @@
     </row>
     <row r="296" spans="1:5" ht="16.5" customHeight="1">
       <c r="A296" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B296" s="2">
         <v>36</v>
       </c>
       <c r="C296" s="6" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D296" s="4">
         <v>7216687</v>
@@ -6090,13 +6054,13 @@
     </row>
     <row r="297" spans="1:5" ht="16.5" customHeight="1">
       <c r="A297" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B297" s="2">
         <v>37</v>
       </c>
       <c r="C297" s="6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D297" s="4">
         <v>6356548</v>
@@ -6108,13 +6072,13 @@
     </row>
     <row r="298" spans="1:5" ht="16.5" customHeight="1">
       <c r="A298" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B298" s="2">
         <v>38</v>
       </c>
       <c r="C298" s="6" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D298" s="4">
         <v>6347447</v>
@@ -6126,13 +6090,13 @@
     </row>
     <row r="299" spans="1:5" ht="16.5" customHeight="1">
       <c r="A299" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B299" s="2">
         <v>39</v>
       </c>
       <c r="C299" s="7" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D299" s="4">
         <v>5960246</v>
@@ -6144,13 +6108,13 @@
     </row>
     <row r="300" spans="1:5" ht="16.5" customHeight="1">
       <c r="A300" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B300" s="2">
         <v>40</v>
       </c>
       <c r="C300" s="6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D300" s="4">
         <v>5879538</v>
@@ -6162,7 +6126,7 @@
     </row>
     <row r="301" spans="1:5" ht="16.5" customHeight="1">
       <c r="A301" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B301" s="2">
         <v>41</v>
@@ -6180,13 +6144,13 @@
     </row>
     <row r="302" spans="1:5" ht="16.5" customHeight="1">
       <c r="A302" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B302" s="2">
         <v>42</v>
       </c>
       <c r="C302" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D302" s="4">
         <v>5376985</v>
@@ -6198,13 +6162,13 @@
     </row>
     <row r="303" spans="1:5" ht="16.5" customHeight="1">
       <c r="A303" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B303" s="2">
         <v>43</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D303" s="4">
         <v>5159999</v>
@@ -6216,13 +6180,13 @@
     </row>
     <row r="304" spans="1:5" ht="16.5" customHeight="1">
       <c r="A304" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B304" s="2">
         <v>44</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D304" s="4">
         <v>4816595</v>
@@ -6234,13 +6198,13 @@
     </row>
     <row r="305" spans="1:5" ht="16.5" customHeight="1">
       <c r="A305" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B305" s="2">
         <v>45</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D305" s="4">
         <v>4538649</v>
@@ -6252,13 +6216,13 @@
     </row>
     <row r="306" spans="1:5" ht="16.5" customHeight="1">
       <c r="A306" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B306" s="2">
         <v>46</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D306" s="4">
         <v>4493569</v>
@@ -6270,13 +6234,13 @@
     </row>
     <row r="307" spans="1:5" ht="16.5" customHeight="1">
       <c r="A307" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B307" s="2">
         <v>47</v>
       </c>
       <c r="C307" s="6" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D307" s="4">
         <v>4473170</v>
@@ -6288,13 +6252,13 @@
     </row>
     <row r="308" spans="1:5" ht="16.5" customHeight="1">
       <c r="A308" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B308" s="2">
         <v>48</v>
       </c>
       <c r="C308" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D308" s="4">
         <v>4398940</v>
@@ -6306,13 +6270,13 @@
     </row>
     <row r="309" spans="1:5" ht="16.5" customHeight="1">
       <c r="A309" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B309" s="2">
         <v>49</v>
       </c>
       <c r="C309" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D309" s="4">
         <v>4263500</v>
@@ -6324,13 +6288,13 @@
     </row>
     <row r="310" spans="1:5" ht="16.5" customHeight="1">
       <c r="A310" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B310" s="2">
         <v>50</v>
       </c>
       <c r="C310" s="7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D310" s="4">
         <v>4186720</v>
@@ -6342,13 +6306,13 @@
     </row>
     <row r="311" spans="1:5" ht="16.5" customHeight="1">
       <c r="A311" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B311" s="2">
         <v>51</v>
       </c>
       <c r="C311" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D311" s="4">
         <v>4155232</v>
@@ -6360,13 +6324,13 @@
     </row>
     <row r="312" spans="1:5" ht="16.5" customHeight="1">
       <c r="A312" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B312" s="2">
         <v>52</v>
       </c>
       <c r="C312" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D312" s="4">
         <v>4148173</v>
@@ -6378,13 +6342,13 @@
     </row>
     <row r="313" spans="1:5" ht="16.5" customHeight="1">
       <c r="A313" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B313" s="2">
         <v>53</v>
       </c>
       <c r="C313" s="6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D313" s="4">
         <v>3953623</v>
@@ -6396,13 +6360,13 @@
     </row>
     <row r="314" spans="1:5" ht="16.5" customHeight="1">
       <c r="A314" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B314" s="2">
         <v>54</v>
       </c>
       <c r="C314" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D314" s="4">
         <v>3841825</v>
@@ -6414,13 +6378,13 @@
     </row>
     <row r="315" spans="1:5" ht="16.5" customHeight="1">
       <c r="A315" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B315" s="2">
         <v>55</v>
       </c>
       <c r="C315" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D315" s="4">
         <v>3725748</v>
@@ -6432,13 +6396,13 @@
     </row>
     <row r="316" spans="1:5" ht="16.5" customHeight="1">
       <c r="A316" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B316" s="2">
         <v>56</v>
       </c>
       <c r="C316" s="6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D316" s="4">
         <v>3668126</v>
@@ -6450,13 +6414,13 @@
     </row>
     <row r="317" spans="1:5" ht="16.5" customHeight="1">
       <c r="A317" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B317" s="2">
         <v>57</v>
       </c>
       <c r="C317" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D317" s="4">
         <v>3655552</v>
@@ -6468,13 +6432,13 @@
     </row>
     <row r="318" spans="1:5" ht="16.5" customHeight="1">
       <c r="A318" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B318" s="2">
         <v>58</v>
       </c>
       <c r="C318" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D318" s="4">
         <v>3643670</v>
@@ -6486,13 +6450,13 @@
     </row>
     <row r="319" spans="1:5" ht="16.5" customHeight="1">
       <c r="A319" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B319" s="2">
         <v>59</v>
       </c>
       <c r="C319" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D319" s="4">
         <v>2973305</v>
@@ -6504,13 +6468,13 @@
     </row>
     <row r="320" spans="1:5" ht="16.5" customHeight="1">
       <c r="A320" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B320" s="2">
         <v>60</v>
       </c>
       <c r="C320" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D320" s="4">
         <v>2438490</v>
@@ -6522,13 +6486,13 @@
     </row>
     <row r="321" spans="1:5" ht="16.5" customHeight="1">
       <c r="A321" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B321" s="2">
         <v>61</v>
       </c>
       <c r="C321" s="6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D321" s="4">
         <v>2379290</v>
@@ -6540,13 +6504,13 @@
     </row>
     <row r="322" spans="1:5" ht="16.5" customHeight="1">
       <c r="A322" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B322" s="2">
         <v>62</v>
       </c>
       <c r="C322" s="6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D322" s="4">
         <v>2161578</v>
@@ -6558,13 +6522,13 @@
     </row>
     <row r="323" spans="1:5" ht="16.5" customHeight="1">
       <c r="A323" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B323" s="2">
         <v>63</v>
       </c>
       <c r="C323" s="6" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D323" s="4">
         <v>2130311</v>
@@ -6576,13 +6540,13 @@
     </row>
     <row r="324" spans="1:5" ht="16.5" customHeight="1">
       <c r="A324" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B324" s="2">
         <v>64</v>
       </c>
       <c r="C324" s="6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D324" s="4">
         <v>1272950</v>
@@ -6594,13 +6558,13 @@
     </row>
     <row r="325" spans="1:5" ht="16.5" customHeight="1">
       <c r="A325" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B325" s="2">
         <v>65</v>
       </c>
       <c r="C325" s="6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D325" s="4">
         <v>1207378</v>
@@ -6612,13 +6576,13 @@
     </row>
     <row r="326" spans="1:5" ht="16.5" customHeight="1">
       <c r="A326" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B326" s="2">
         <v>66</v>
       </c>
       <c r="C326" s="6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D326" s="4">
         <v>959773</v>
@@ -6630,13 +6594,13 @@
     </row>
     <row r="327" spans="1:5" ht="16.5" customHeight="1">
       <c r="A327" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B327" s="2">
         <v>67</v>
       </c>
       <c r="C327" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D327" s="4">
         <v>276650</v>
@@ -6648,7 +6612,7 @@
     </row>
     <row r="328" spans="1:5">
       <c r="A328" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B328" s="9">
         <v>1</v>
@@ -6659,50 +6623,47 @@
       <c r="D328" s="9">
         <v>51572469</v>
       </c>
-      <c r="E328" s="5" t="str">
-        <f>IF($D328="","",VLOOKUP($D328,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E328" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="329" spans="1:5">
       <c r="A329" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B329" s="9">
         <v>2</v>
       </c>
       <c r="C329" s="8" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D329" s="9">
         <v>45927381</v>
       </c>
-      <c r="E329" s="5" t="str">
-        <f>IF($D329="","",VLOOKUP($D329,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E329" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="330" spans="1:5">
       <c r="A330" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B330" s="9">
         <v>3</v>
       </c>
       <c r="C330" s="8" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D330" s="9">
-        <v>44792553</v>
-      </c>
-      <c r="E330" s="5" t="str">
-        <f>IF($D330="","",VLOOKUP($D330,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>44882553</v>
+      </c>
+      <c r="E330" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="331" spans="1:5">
       <c r="A331" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B331" s="9">
         <v>4</v>
@@ -6713,14 +6674,13 @@
       <c r="D331" s="9">
         <v>36401622</v>
       </c>
-      <c r="E331" s="5" t="str">
-        <f>IF($D331="","",VLOOKUP($D331,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E331" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="332" spans="1:5">
       <c r="A332" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B332" s="9">
         <v>5</v>
@@ -6731,14 +6691,13 @@
       <c r="D332" s="9">
         <v>32814024</v>
       </c>
-      <c r="E332" s="5" t="str">
-        <f>IF($D332="","",VLOOKUP($D332,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E332" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="333" spans="1:5">
       <c r="A333" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B333" s="9">
         <v>6</v>
@@ -6747,106 +6706,100 @@
         <v>18</v>
       </c>
       <c r="D333" s="9">
-        <v>29746875</v>
-      </c>
-      <c r="E333" s="5" t="str">
-        <f>IF($D333="","",VLOOKUP($D333,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>30352177</v>
+      </c>
+      <c r="E333" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="334" spans="1:5">
       <c r="A334" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B334" s="9">
         <v>7</v>
       </c>
       <c r="C334" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D334" s="9">
         <v>29064577</v>
       </c>
-      <c r="E334" s="5" t="str">
-        <f>IF($D334="","",VLOOKUP($D334,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E334" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="335" spans="1:5">
       <c r="A335" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B335" s="9">
         <v>8</v>
       </c>
       <c r="C335" s="8" t="s">
-        <v>30</v>
+        <v>117</v>
       </c>
       <c r="D335" s="9">
         <v>28830256</v>
       </c>
-      <c r="E335" s="5" t="str">
-        <f>IF($D335="","",VLOOKUP($D335,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E335" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="336" spans="1:5">
       <c r="A336" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B336" s="9">
         <v>9</v>
       </c>
       <c r="C336" s="8" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D336" s="9">
         <v>27963110</v>
       </c>
-      <c r="E336" s="5" t="str">
-        <f>IF($D336="","",VLOOKUP($D336,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E336" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="337" spans="1:5">
       <c r="A337" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B337" s="9">
         <v>10</v>
       </c>
       <c r="C337" s="8" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D337" s="9">
         <v>27716398</v>
       </c>
-      <c r="E337" s="5" t="str">
-        <f>IF($D337="","",VLOOKUP($D337,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E337" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="338" spans="1:5">
       <c r="A338" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B338" s="9">
         <v>11</v>
       </c>
       <c r="C338" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D338" s="9">
-        <v>27120602</v>
-      </c>
-      <c r="E338" s="5" t="str">
-        <f>IF($D338="","",VLOOKUP($D338,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>27125102</v>
+      </c>
+      <c r="E338" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="339" spans="1:5">
       <c r="A339" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B339" s="9">
         <v>12</v>
@@ -6857,14 +6810,13 @@
       <c r="D339" s="9">
         <v>26303031</v>
       </c>
-      <c r="E339" s="5" t="str">
-        <f>IF($D339="","",VLOOKUP($D339,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E339" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="340" spans="1:5">
       <c r="A340" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B340" s="9">
         <v>13</v>
@@ -6875,50 +6827,47 @@
       <c r="D340" s="9">
         <v>25598926</v>
       </c>
-      <c r="E340" s="5" t="str">
-        <f>IF($D340="","",VLOOKUP($D340,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E340" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="341" spans="1:5">
       <c r="A341" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B341" s="9">
         <v>14</v>
       </c>
       <c r="C341" s="8" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D341" s="9">
         <v>25275492</v>
       </c>
-      <c r="E341" s="5" t="str">
-        <f>IF($D341="","",VLOOKUP($D341,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E341" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="342" spans="1:5">
       <c r="A342" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B342" s="9">
         <v>15</v>
       </c>
       <c r="C342" s="8" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D342" s="9">
         <v>24620930</v>
       </c>
-      <c r="E342" s="5" t="str">
-        <f>IF($D342="","",VLOOKUP($D342,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E342" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="343" spans="1:5">
       <c r="A343" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B343" s="9">
         <v>16</v>
@@ -6929,14 +6878,13 @@
       <c r="D343" s="9">
         <v>24434321</v>
       </c>
-      <c r="E343" s="5" t="str">
-        <f>IF($D343="","",VLOOKUP($D343,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E343" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="344" spans="1:5">
       <c r="A344" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B344" s="9">
         <v>17</v>
@@ -6947,32 +6895,30 @@
       <c r="D344" s="9">
         <v>21605033</v>
       </c>
-      <c r="E344" s="5" t="str">
-        <f>IF($D344="","",VLOOKUP($D344,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E344" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="345" spans="1:5">
       <c r="A345" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B345" s="9">
         <v>18</v>
       </c>
       <c r="C345" s="8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D345" s="9">
         <v>21478397</v>
       </c>
-      <c r="E345" s="5" t="str">
-        <f>IF($D345="","",VLOOKUP($D345,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E345" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="346" spans="1:5">
       <c r="A346" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B346" s="9">
         <v>19</v>
@@ -6983,86 +6929,81 @@
       <c r="D346" s="9">
         <v>21123578</v>
       </c>
-      <c r="E346" s="5" t="str">
-        <f>IF($D346="","",VLOOKUP($D346,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E346" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="347" spans="1:5">
       <c r="A347" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B347" s="9">
         <v>20</v>
       </c>
       <c r="C347" s="8" t="s">
-        <v>130</v>
+        <v>38</v>
       </c>
       <c r="D347" s="9">
-        <v>19328458</v>
-      </c>
-      <c r="E347" s="5" t="str">
-        <f>IF($D347="","",VLOOKUP($D347,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>20055931</v>
+      </c>
+      <c r="E347" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="348" spans="1:5">
       <c r="A348" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B348" s="9">
         <v>21</v>
       </c>
       <c r="C348" s="8" t="s">
-        <v>118</v>
+        <v>22</v>
       </c>
       <c r="D348" s="9">
-        <v>18986692</v>
-      </c>
-      <c r="E348" s="5" t="str">
-        <f>IF($D348="","",VLOOKUP($D348,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>19328458</v>
+      </c>
+      <c r="E348" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="349" spans="1:5">
       <c r="A349" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B349" s="9">
         <v>22</v>
       </c>
       <c r="C349" s="8" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D349" s="9">
-        <v>18188828</v>
-      </c>
-      <c r="E349" s="5" t="str">
-        <f>IF($D349="","",VLOOKUP($D349,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>18197828</v>
+      </c>
+      <c r="E349" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="350" spans="1:5">
       <c r="A350" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B350" s="9">
         <v>23</v>
       </c>
       <c r="C350" s="8" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D350" s="9">
         <v>17545894</v>
       </c>
-      <c r="E350" s="5" t="str">
-        <f>IF($D350="","",VLOOKUP($D350,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E350" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="351" spans="1:5">
       <c r="A351" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B351" s="9">
         <v>24</v>
@@ -7073,122 +7014,115 @@
       <c r="D351" s="9">
         <v>17451192</v>
       </c>
-      <c r="E351" s="5" t="str">
-        <f>IF($D351="","",VLOOKUP($D351,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E351" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="352" spans="1:5">
       <c r="A352" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B352" s="9">
         <v>25</v>
       </c>
       <c r="C352" s="8" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D352" s="9">
         <v>17095537</v>
       </c>
-      <c r="E352" s="5" t="str">
-        <f>IF($D352="","",VLOOKUP($D352,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E352" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="353" spans="1:5">
       <c r="A353" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B353" s="9">
         <v>26</v>
       </c>
       <c r="C353" s="8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D353" s="9">
         <v>16940645</v>
       </c>
-      <c r="E353" s="5" t="str">
-        <f>IF($D353="","",VLOOKUP($D353,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E353" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="354" spans="1:5">
       <c r="A354" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B354" s="9">
         <v>27</v>
       </c>
       <c r="C354" s="8" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D354" s="9">
         <v>16625723</v>
       </c>
-      <c r="E354" s="5" t="str">
-        <f>IF($D354="","",VLOOKUP($D354,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E354" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="355" spans="1:5">
       <c r="A355" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B355" s="9">
         <v>28</v>
       </c>
       <c r="C355" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D355" s="9">
         <v>16582350</v>
       </c>
-      <c r="E355" s="5" t="str">
-        <f>IF($D355="","",VLOOKUP($D355,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E355" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="356" spans="1:5">
       <c r="A356" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B356" s="9">
         <v>29</v>
       </c>
       <c r="C356" s="8" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D356" s="9">
-        <v>16370099</v>
-      </c>
-      <c r="E356" s="5" t="str">
-        <f>IF($D356="","",VLOOKUP($D356,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>16374224</v>
+      </c>
+      <c r="E356" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="357" spans="1:5">
       <c r="A357" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B357" s="9">
         <v>30</v>
       </c>
       <c r="C357" s="8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D357" s="9">
         <v>15989772</v>
       </c>
-      <c r="E357" s="5" t="str">
-        <f>IF($D357="","",VLOOKUP($D357,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E357" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="358" spans="1:5">
       <c r="A358" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B358" s="9">
         <v>31</v>
@@ -7199,284 +7133,268 @@
       <c r="D358" s="9">
         <v>15124678</v>
       </c>
-      <c r="E358" s="5" t="str">
-        <f>IF($D358="","",VLOOKUP($D358,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E358" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="359" spans="1:5">
       <c r="A359" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B359" s="9">
         <v>32</v>
       </c>
       <c r="C359" s="8" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D359" s="9">
-        <v>14253593</v>
-      </c>
-      <c r="E359" s="5" t="str">
-        <f>IF($D359="","",VLOOKUP($D359,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>14388261</v>
+      </c>
+      <c r="E359" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="360" spans="1:5">
       <c r="A360" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B360" s="9">
         <v>33</v>
       </c>
       <c r="C360" s="8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D360" s="9">
-        <v>13958262</v>
-      </c>
-      <c r="E360" s="5" t="str">
-        <f>IF($D360="","",VLOOKUP($D360,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>14253593</v>
+      </c>
+      <c r="E360" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="361" spans="1:5">
       <c r="A361" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B361" s="9">
         <v>34</v>
       </c>
       <c r="C361" s="8" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D361" s="9">
         <v>13903501</v>
       </c>
-      <c r="E361" s="5" t="str">
-        <f>IF($D361="","",VLOOKUP($D361,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E361" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="362" spans="1:5">
       <c r="A362" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B362" s="9">
         <v>35</v>
       </c>
       <c r="C362" s="8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D362" s="9">
         <v>13791347</v>
       </c>
-      <c r="E362" s="5" t="str">
-        <f>IF($D362="","",VLOOKUP($D362,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E362" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="363" spans="1:5">
       <c r="A363" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B363" s="9">
         <v>36</v>
       </c>
       <c r="C363" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D363" s="9">
         <v>13310754</v>
       </c>
-      <c r="E363" s="5" t="str">
-        <f>IF($D363="","",VLOOKUP($D363,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E363" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="364" spans="1:5">
       <c r="A364" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B364" s="9">
         <v>37</v>
       </c>
       <c r="C364" s="8" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D364" s="9">
         <v>12684262</v>
       </c>
-      <c r="E364" s="5" t="str">
-        <f>IF($D364="","",VLOOKUP($D364,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E364" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="365" spans="1:5">
       <c r="A365" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B365" s="9">
         <v>38</v>
       </c>
       <c r="C365" s="8" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="D365" s="9">
         <v>12215462</v>
       </c>
-      <c r="E365" s="5" t="str">
-        <f>IF($D365="","",VLOOKUP($D365,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E365" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="366" spans="1:5">
       <c r="A366" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B366" s="9">
         <v>39</v>
       </c>
       <c r="C366" s="8" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D366" s="9">
         <v>11325863</v>
       </c>
-      <c r="E366" s="5" t="str">
-        <f>IF($D366="","",VLOOKUP($D366,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E366" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="367" spans="1:5">
       <c r="A367" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B367" s="9">
         <v>40</v>
       </c>
       <c r="C367" s="8" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D367" s="9">
         <v>10130369</v>
       </c>
-      <c r="E367" s="5" t="str">
-        <f>IF($D367="","",VLOOKUP($D367,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E367" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="368" spans="1:5">
       <c r="A368" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B368" s="9">
         <v>41</v>
       </c>
       <c r="C368" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D368" s="9">
         <v>10079600</v>
       </c>
-      <c r="E368" s="5" t="str">
-        <f>IF($D368="","",VLOOKUP($D368,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E368" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="369" spans="1:5">
       <c r="A369" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B369" s="9">
         <v>42</v>
       </c>
       <c r="C369" s="8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D369" s="9">
         <v>9578558</v>
       </c>
-      <c r="E369" s="5" t="str">
-        <f>IF($D369="","",VLOOKUP($D369,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E369" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="370" spans="1:5">
       <c r="A370" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B370" s="9">
         <v>43</v>
       </c>
       <c r="C370" s="8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D370" s="9">
-        <v>9476214</v>
-      </c>
-      <c r="E370" s="5" t="str">
-        <f>IF($D370="","",VLOOKUP($D370,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>9480264</v>
+      </c>
+      <c r="E370" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="371" spans="1:5">
       <c r="A371" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B371" s="9">
         <v>44</v>
       </c>
       <c r="C371" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D371" s="9">
         <v>9389063</v>
       </c>
-      <c r="E371" s="5" t="str">
-        <f>IF($D371="","",VLOOKUP($D371,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E371" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="372" spans="1:5">
       <c r="A372" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B372" s="9">
         <v>45</v>
       </c>
       <c r="C372" s="8" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D372" s="9">
         <v>9257137</v>
       </c>
-      <c r="E372" s="5" t="str">
-        <f>IF($D372="","",VLOOKUP($D372,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E372" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="373" spans="1:5">
       <c r="A373" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B373" s="9">
         <v>46</v>
       </c>
       <c r="C373" s="8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D373" s="9">
         <v>9172250</v>
       </c>
-      <c r="E373" s="5" t="str">
-        <f>IF($D373="","",VLOOKUP($D373,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E373" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="374" spans="1:5">
       <c r="A374" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B374" s="9">
         <v>47</v>
@@ -7487,351 +7405,348 @@
       <c r="D374" s="9">
         <v>8664783</v>
       </c>
-      <c r="E374" s="5" t="str">
-        <f>IF($D374="","",VLOOKUP($D374,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E374" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="375" spans="1:5">
       <c r="A375" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B375" s="9">
         <v>48</v>
       </c>
       <c r="C375" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D375" s="9">
         <v>8482806</v>
       </c>
-      <c r="E375" s="5" t="str">
-        <f>IF($D375="","",VLOOKUP($D375,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E375" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="376" spans="1:5">
       <c r="A376" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B376" s="9">
         <v>49</v>
       </c>
       <c r="C376" s="8" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="D376" s="9">
         <v>8449715</v>
       </c>
-      <c r="E376" s="5" t="str">
-        <f>IF($D376="","",VLOOKUP($D376,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E376" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="377" spans="1:5">
       <c r="A377" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B377" s="9">
         <v>50</v>
       </c>
       <c r="C377" s="8" t="s">
-        <v>125</v>
+        <v>39</v>
       </c>
       <c r="D377" s="9">
         <v>8167774</v>
       </c>
-      <c r="E377" s="5" t="str">
-        <f>IF($D377="","",VLOOKUP($D377,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E377" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="378" spans="1:5">
       <c r="A378" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B378" s="9">
         <v>51</v>
       </c>
       <c r="C378" s="8" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="D378" s="9">
         <v>7379637</v>
       </c>
-      <c r="E378" s="5" t="str">
-        <f>IF($D378="","",VLOOKUP($D378,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+      <c r="E378" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="379" spans="1:5">
       <c r="A379" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B379" s="9">
         <v>52</v>
       </c>
       <c r="C379" s="8" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="D379" s="9">
-        <v>6388100</v>
-      </c>
-      <c r="E379" s="5" t="str">
-        <f>IF($D379="","",VLOOKUP($D379,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>7351478</v>
+      </c>
+      <c r="E379" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="380" spans="1:5">
       <c r="A380" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B380" s="9">
         <v>53</v>
       </c>
       <c r="C380" s="8" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="D380" s="9">
-        <v>5666872</v>
-      </c>
-      <c r="E380" s="5" t="str">
-        <f>IF($D380="","",VLOOKUP($D380,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>6388100</v>
+      </c>
+      <c r="E380" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="381" spans="1:5">
       <c r="A381" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B381" s="9">
         <v>54</v>
       </c>
       <c r="C381" s="8" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="D381" s="9">
-        <v>5593709</v>
-      </c>
-      <c r="E381" s="5" t="str">
-        <f>IF($D381="","",VLOOKUP($D381,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>6032072</v>
+      </c>
+      <c r="E381" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="382" spans="1:5">
       <c r="A382" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B382" s="9">
         <v>55</v>
       </c>
       <c r="C382" s="8" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="D382" s="9">
-        <v>4942793</v>
-      </c>
-      <c r="E382" s="5" t="str">
-        <f>IF($D382="","",VLOOKUP($D382,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>5593709</v>
+      </c>
+      <c r="E382" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="383" spans="1:5">
       <c r="A383" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B383" s="9">
         <v>56</v>
       </c>
-      <c r="C383" s="8">
-        <v>1090</v>
+      <c r="C383" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="D383" s="9">
-        <v>4587543</v>
-      </c>
-      <c r="E383" s="5" t="str">
-        <f>IF($D383="","",VLOOKUP($D383,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>4942793</v>
+      </c>
+      <c r="E383" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="384" spans="1:5">
       <c r="A384" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B384" s="9">
         <v>57</v>
       </c>
       <c r="C384" s="8" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D384" s="9">
-        <v>4012455</v>
-      </c>
-      <c r="E384" s="5" t="str">
-        <f>IF($D384="","",VLOOKUP($D384,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>4587543</v>
+      </c>
+      <c r="E384" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="385" spans="1:5">
       <c r="A385" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B385" s="9">
         <v>58</v>
       </c>
       <c r="C385" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D385" s="9">
-        <v>3613479</v>
-      </c>
-      <c r="E385" s="5" t="str">
-        <f>IF($D385="","",VLOOKUP($D385,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>4012455</v>
+      </c>
+      <c r="E385" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="386" spans="1:5">
       <c r="A386" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B386" s="9">
         <v>59</v>
       </c>
       <c r="C386" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D386" s="9">
-        <v>2363818</v>
-      </c>
-      <c r="E386" s="5" t="str">
-        <f>IF($D386="","",VLOOKUP($D386,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>7단계</v>
+        <v>3613479</v>
+      </c>
+      <c r="E386" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="387" spans="1:5">
       <c r="A387" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B387" s="9">
         <v>60</v>
       </c>
       <c r="C387" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D387" s="9">
-        <v>2307050</v>
-      </c>
-      <c r="E387" s="5" t="str">
-        <f>IF($D387="","",VLOOKUP($D387,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>7단계</v>
+        <v>2363818</v>
+      </c>
+      <c r="E387" s="5" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="388" spans="1:5">
       <c r="A388" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B388" s="9">
         <v>61</v>
       </c>
       <c r="C388" s="8" t="s">
-        <v>127</v>
+        <v>55</v>
       </c>
       <c r="D388" s="9">
-        <v>2215136</v>
-      </c>
-      <c r="E388" s="5" t="str">
-        <f>IF($D388="","",VLOOKUP($D388,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
+        <v>2307050</v>
+      </c>
+      <c r="E388" s="5" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="389" spans="1:5">
       <c r="A389" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B389" s="9">
         <v>62</v>
       </c>
       <c r="C389" s="8" t="s">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="D389" s="9">
-        <v>2185908</v>
-      </c>
-      <c r="E389" s="5" t="str">
-        <f>IF($D389="","",VLOOKUP($D389,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
+        <v>2215136</v>
+      </c>
+      <c r="E389" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="390" spans="1:5">
       <c r="A390" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B390" s="9">
         <v>63</v>
       </c>
       <c r="C390" s="8" t="s">
-        <v>129</v>
+        <v>59</v>
       </c>
       <c r="D390" s="9">
-        <v>1109775</v>
-      </c>
-      <c r="E390" s="5" t="str">
-        <f>IF($D390="","",VLOOKUP($D390,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
+        <v>2185908</v>
+      </c>
+      <c r="E390" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="391" spans="1:5">
       <c r="A391" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B391" s="9">
         <v>64</v>
       </c>
       <c r="C391" s="8" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="D391" s="9">
-        <v>999218</v>
-      </c>
-      <c r="E391" s="5" t="str">
-        <f>IF($D391="","",VLOOKUP($D391,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>5단계</v>
+        <v>1109775</v>
+      </c>
+      <c r="E391" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="392" spans="1:5">
       <c r="A392" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B392" s="9">
         <v>65</v>
       </c>
       <c r="C392" s="8" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="D392" s="9">
-        <v>845000</v>
-      </c>
-      <c r="E392" s="5" t="str">
-        <f>IF($D392="","",VLOOKUP($D392,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>5단계</v>
+        <v>999218</v>
+      </c>
+      <c r="E392" s="5" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="393" spans="1:5">
       <c r="A393" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B393" s="9">
         <v>66</v>
       </c>
       <c r="C393" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D393" s="9">
+        <v>845000</v>
+      </c>
+      <c r="E393" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5">
+      <c r="A394" t="s">
+        <v>95</v>
+      </c>
+      <c r="B394" s="9">
+        <v>67</v>
+      </c>
+      <c r="C394" t="s">
+        <v>69</v>
+      </c>
+      <c r="D394" s="9">
         <v>364314</v>
       </c>
-      <c r="E393" s="5" t="str">
-        <f>IF($D393="","",VLOOKUP($D393,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>3단계</v>
+      <c r="E394" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -7848,7 +7763,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A66B3FC1-1F68-45EF-9776-AADA8BB5C0D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F69B92F-DA43-4EAE-AFC9-509F8231A4A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21600" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="기준표" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="120">
   <si>
     <t>📦 월별 보관 — 2026-06  (날짜별 길드전 랭킹 누적)</t>
   </si>
@@ -6623,8 +6623,9 @@
       <c r="D328" s="9">
         <v>51572469</v>
       </c>
-      <c r="E328" s="5" t="s">
-        <v>8</v>
+      <c r="E328" s="5" t="str">
+        <f>IF($D328="","",VLOOKUP($D328,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -6640,8 +6641,9 @@
       <c r="D329" s="9">
         <v>45927381</v>
       </c>
-      <c r="E329" s="5" t="s">
-        <v>8</v>
+      <c r="E329" s="5" t="str">
+        <f>IF($D329="","",VLOOKUP($D329,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="330" spans="1:5">
@@ -6657,8 +6659,9 @@
       <c r="D330" s="9">
         <v>44882553</v>
       </c>
-      <c r="E330" s="5" t="s">
-        <v>8</v>
+      <c r="E330" s="5" t="str">
+        <f>IF($D330="","",VLOOKUP($D330,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -6674,8 +6677,9 @@
       <c r="D331" s="9">
         <v>36401622</v>
       </c>
-      <c r="E331" s="5" t="s">
-        <v>8</v>
+      <c r="E331" s="5" t="str">
+        <f>IF($D331="","",VLOOKUP($D331,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -6691,8 +6695,9 @@
       <c r="D332" s="9">
         <v>32814024</v>
       </c>
-      <c r="E332" s="5" t="s">
-        <v>8</v>
+      <c r="E332" s="5" t="str">
+        <f>IF($D332="","",VLOOKUP($D332,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="333" spans="1:5">
@@ -6708,8 +6713,9 @@
       <c r="D333" s="9">
         <v>30352177</v>
       </c>
-      <c r="E333" s="5" t="s">
-        <v>8</v>
+      <c r="E333" s="5" t="str">
+        <f>IF($D333="","",VLOOKUP($D333,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="334" spans="1:5">
@@ -6725,8 +6731,9 @@
       <c r="D334" s="9">
         <v>29064577</v>
       </c>
-      <c r="E334" s="5" t="s">
-        <v>8</v>
+      <c r="E334" s="5" t="str">
+        <f>IF($D334="","",VLOOKUP($D334,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="335" spans="1:5">
@@ -6742,8 +6749,9 @@
       <c r="D335" s="9">
         <v>28830256</v>
       </c>
-      <c r="E335" s="5" t="s">
-        <v>8</v>
+      <c r="E335" s="5" t="str">
+        <f>IF($D335="","",VLOOKUP($D335,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="336" spans="1:5">
@@ -6759,8 +6767,9 @@
       <c r="D336" s="9">
         <v>27963110</v>
       </c>
-      <c r="E336" s="5" t="s">
-        <v>8</v>
+      <c r="E336" s="5" t="str">
+        <f>IF($D336="","",VLOOKUP($D336,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -6776,8 +6785,9 @@
       <c r="D337" s="9">
         <v>27716398</v>
       </c>
-      <c r="E337" s="5" t="s">
-        <v>8</v>
+      <c r="E337" s="5" t="str">
+        <f>IF($D337="","",VLOOKUP($D337,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -6793,8 +6803,9 @@
       <c r="D338" s="9">
         <v>27125102</v>
       </c>
-      <c r="E338" s="5" t="s">
-        <v>8</v>
+      <c r="E338" s="5" t="str">
+        <f>IF($D338="","",VLOOKUP($D338,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -6810,8 +6821,9 @@
       <c r="D339" s="9">
         <v>26303031</v>
       </c>
-      <c r="E339" s="5" t="s">
-        <v>8</v>
+      <c r="E339" s="5" t="str">
+        <f>IF($D339="","",VLOOKUP($D339,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -6827,8 +6839,9 @@
       <c r="D340" s="9">
         <v>25598926</v>
       </c>
-      <c r="E340" s="5" t="s">
-        <v>8</v>
+      <c r="E340" s="5" t="str">
+        <f>IF($D340="","",VLOOKUP($D340,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -6844,8 +6857,9 @@
       <c r="D341" s="9">
         <v>25275492</v>
       </c>
-      <c r="E341" s="5" t="s">
-        <v>8</v>
+      <c r="E341" s="5" t="str">
+        <f>IF($D341="","",VLOOKUP($D341,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="342" spans="1:5">
@@ -6861,8 +6875,9 @@
       <c r="D342" s="9">
         <v>24620930</v>
       </c>
-      <c r="E342" s="5" t="s">
-        <v>8</v>
+      <c r="E342" s="5" t="str">
+        <f>IF($D342="","",VLOOKUP($D342,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -6878,8 +6893,9 @@
       <c r="D343" s="9">
         <v>24434321</v>
       </c>
-      <c r="E343" s="5" t="s">
-        <v>8</v>
+      <c r="E343" s="5" t="str">
+        <f>IF($D343="","",VLOOKUP($D343,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -6895,8 +6911,9 @@
       <c r="D344" s="9">
         <v>21605033</v>
       </c>
-      <c r="E344" s="5" t="s">
-        <v>8</v>
+      <c r="E344" s="5" t="str">
+        <f>IF($D344="","",VLOOKUP($D344,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -6912,8 +6929,9 @@
       <c r="D345" s="9">
         <v>21478397</v>
       </c>
-      <c r="E345" s="5" t="s">
-        <v>8</v>
+      <c r="E345" s="5" t="str">
+        <f>IF($D345="","",VLOOKUP($D345,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -6929,8 +6947,9 @@
       <c r="D346" s="9">
         <v>21123578</v>
       </c>
-      <c r="E346" s="5" t="s">
-        <v>8</v>
+      <c r="E346" s="5" t="str">
+        <f>IF($D346="","",VLOOKUP($D346,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -6946,8 +6965,9 @@
       <c r="D347" s="9">
         <v>20055931</v>
       </c>
-      <c r="E347" s="5" t="s">
-        <v>8</v>
+      <c r="E347" s="5" t="str">
+        <f>IF($D347="","",VLOOKUP($D347,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -6963,8 +6983,9 @@
       <c r="D348" s="9">
         <v>19328458</v>
       </c>
-      <c r="E348" s="5" t="s">
-        <v>8</v>
+      <c r="E348" s="5" t="str">
+        <f>IF($D348="","",VLOOKUP($D348,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -6980,8 +7001,9 @@
       <c r="D349" s="9">
         <v>18197828</v>
       </c>
-      <c r="E349" s="5" t="s">
-        <v>8</v>
+      <c r="E349" s="5" t="str">
+        <f>IF($D349="","",VLOOKUP($D349,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -6997,8 +7019,9 @@
       <c r="D350" s="9">
         <v>17545894</v>
       </c>
-      <c r="E350" s="5" t="s">
-        <v>8</v>
+      <c r="E350" s="5" t="str">
+        <f>IF($D350="","",VLOOKUP($D350,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="351" spans="1:5">
@@ -7014,8 +7037,9 @@
       <c r="D351" s="9">
         <v>17451192</v>
       </c>
-      <c r="E351" s="5" t="s">
-        <v>8</v>
+      <c r="E351" s="5" t="str">
+        <f>IF($D351="","",VLOOKUP($D351,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="352" spans="1:5">
@@ -7031,8 +7055,9 @@
       <c r="D352" s="9">
         <v>17095537</v>
       </c>
-      <c r="E352" s="5" t="s">
-        <v>8</v>
+      <c r="E352" s="5" t="str">
+        <f>IF($D352="","",VLOOKUP($D352,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="353" spans="1:5">
@@ -7048,8 +7073,9 @@
       <c r="D353" s="9">
         <v>16940645</v>
       </c>
-      <c r="E353" s="5" t="s">
-        <v>8</v>
+      <c r="E353" s="5" t="str">
+        <f>IF($D353="","",VLOOKUP($D353,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="354" spans="1:5">
@@ -7065,8 +7091,9 @@
       <c r="D354" s="9">
         <v>16625723</v>
       </c>
-      <c r="E354" s="5" t="s">
-        <v>8</v>
+      <c r="E354" s="5" t="str">
+        <f>IF($D354="","",VLOOKUP($D354,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="355" spans="1:5">
@@ -7082,8 +7109,9 @@
       <c r="D355" s="9">
         <v>16582350</v>
       </c>
-      <c r="E355" s="5" t="s">
-        <v>8</v>
+      <c r="E355" s="5" t="str">
+        <f>IF($D355="","",VLOOKUP($D355,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -7099,8 +7127,9 @@
       <c r="D356" s="9">
         <v>16374224</v>
       </c>
-      <c r="E356" s="5" t="s">
-        <v>8</v>
+      <c r="E356" s="5" t="str">
+        <f>IF($D356="","",VLOOKUP($D356,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -7116,8 +7145,9 @@
       <c r="D357" s="9">
         <v>15989772</v>
       </c>
-      <c r="E357" s="5" t="s">
-        <v>8</v>
+      <c r="E357" s="5" t="str">
+        <f>IF($D357="","",VLOOKUP($D357,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -7133,8 +7163,9 @@
       <c r="D358" s="9">
         <v>15124678</v>
       </c>
-      <c r="E358" s="5" t="s">
-        <v>8</v>
+      <c r="E358" s="5" t="str">
+        <f>IF($D358="","",VLOOKUP($D358,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -7150,8 +7181,9 @@
       <c r="D359" s="9">
         <v>14388261</v>
       </c>
-      <c r="E359" s="5" t="s">
-        <v>8</v>
+      <c r="E359" s="5" t="str">
+        <f>IF($D359="","",VLOOKUP($D359,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -7167,8 +7199,9 @@
       <c r="D360" s="9">
         <v>14253593</v>
       </c>
-      <c r="E360" s="5" t="s">
-        <v>8</v>
+      <c r="E360" s="5" t="str">
+        <f>IF($D360="","",VLOOKUP($D360,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -7184,8 +7217,9 @@
       <c r="D361" s="9">
         <v>13903501</v>
       </c>
-      <c r="E361" s="5" t="s">
-        <v>8</v>
+      <c r="E361" s="5" t="str">
+        <f>IF($D361="","",VLOOKUP($D361,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="362" spans="1:5">
@@ -7201,8 +7235,9 @@
       <c r="D362" s="9">
         <v>13791347</v>
       </c>
-      <c r="E362" s="5" t="s">
-        <v>8</v>
+      <c r="E362" s="5" t="str">
+        <f>IF($D362="","",VLOOKUP($D362,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -7218,8 +7253,9 @@
       <c r="D363" s="9">
         <v>13310754</v>
       </c>
-      <c r="E363" s="5" t="s">
-        <v>8</v>
+      <c r="E363" s="5" t="str">
+        <f>IF($D363="","",VLOOKUP($D363,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="364" spans="1:5">
@@ -7235,8 +7271,9 @@
       <c r="D364" s="9">
         <v>12684262</v>
       </c>
-      <c r="E364" s="5" t="s">
-        <v>8</v>
+      <c r="E364" s="5" t="str">
+        <f>IF($D364="","",VLOOKUP($D364,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -7252,8 +7289,9 @@
       <c r="D365" s="9">
         <v>12215462</v>
       </c>
-      <c r="E365" s="5" t="s">
-        <v>8</v>
+      <c r="E365" s="5" t="str">
+        <f>IF($D365="","",VLOOKUP($D365,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -7269,8 +7307,9 @@
       <c r="D366" s="9">
         <v>11325863</v>
       </c>
-      <c r="E366" s="5" t="s">
-        <v>8</v>
+      <c r="E366" s="5" t="str">
+        <f>IF($D366="","",VLOOKUP($D366,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -7286,8 +7325,9 @@
       <c r="D367" s="9">
         <v>10130369</v>
       </c>
-      <c r="E367" s="5" t="s">
-        <v>8</v>
+      <c r="E367" s="5" t="str">
+        <f>IF($D367="","",VLOOKUP($D367,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -7303,8 +7343,9 @@
       <c r="D368" s="9">
         <v>10079600</v>
       </c>
-      <c r="E368" s="5" t="s">
-        <v>8</v>
+      <c r="E368" s="5" t="str">
+        <f>IF($D368="","",VLOOKUP($D368,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -7320,8 +7361,9 @@
       <c r="D369" s="9">
         <v>9578558</v>
       </c>
-      <c r="E369" s="5" t="s">
-        <v>8</v>
+      <c r="E369" s="5" t="str">
+        <f>IF($D369="","",VLOOKUP($D369,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -7337,8 +7379,9 @@
       <c r="D370" s="9">
         <v>9480264</v>
       </c>
-      <c r="E370" s="5" t="s">
-        <v>8</v>
+      <c r="E370" s="5" t="str">
+        <f>IF($D370="","",VLOOKUP($D370,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -7354,8 +7397,9 @@
       <c r="D371" s="9">
         <v>9389063</v>
       </c>
-      <c r="E371" s="5" t="s">
-        <v>8</v>
+      <c r="E371" s="5" t="str">
+        <f>IF($D371="","",VLOOKUP($D371,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="372" spans="1:5">
@@ -7371,8 +7415,9 @@
       <c r="D372" s="9">
         <v>9257137</v>
       </c>
-      <c r="E372" s="5" t="s">
-        <v>8</v>
+      <c r="E372" s="5" t="str">
+        <f>IF($D372="","",VLOOKUP($D372,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -7388,8 +7433,9 @@
       <c r="D373" s="9">
         <v>9172250</v>
       </c>
-      <c r="E373" s="5" t="s">
-        <v>8</v>
+      <c r="E373" s="5" t="str">
+        <f>IF($D373="","",VLOOKUP($D373,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="374" spans="1:5">
@@ -7405,8 +7451,9 @@
       <c r="D374" s="9">
         <v>8664783</v>
       </c>
-      <c r="E374" s="5" t="s">
-        <v>8</v>
+      <c r="E374" s="5" t="str">
+        <f>IF($D374="","",VLOOKUP($D374,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="375" spans="1:5">
@@ -7422,8 +7469,9 @@
       <c r="D375" s="9">
         <v>8482806</v>
       </c>
-      <c r="E375" s="5" t="s">
-        <v>8</v>
+      <c r="E375" s="5" t="str">
+        <f>IF($D375="","",VLOOKUP($D375,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -7439,8 +7487,9 @@
       <c r="D376" s="9">
         <v>8449715</v>
       </c>
-      <c r="E376" s="5" t="s">
-        <v>8</v>
+      <c r="E376" s="5" t="str">
+        <f>IF($D376="","",VLOOKUP($D376,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -7456,8 +7505,9 @@
       <c r="D377" s="9">
         <v>8167774</v>
       </c>
-      <c r="E377" s="5" t="s">
-        <v>8</v>
+      <c r="E377" s="5" t="str">
+        <f>IF($D377="","",VLOOKUP($D377,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -7473,8 +7523,9 @@
       <c r="D378" s="9">
         <v>7379637</v>
       </c>
-      <c r="E378" s="5" t="s">
-        <v>8</v>
+      <c r="E378" s="5" t="str">
+        <f>IF($D378="","",VLOOKUP($D378,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="379" spans="1:5">
@@ -7490,8 +7541,9 @@
       <c r="D379" s="9">
         <v>7351478</v>
       </c>
-      <c r="E379" s="5" t="s">
-        <v>8</v>
+      <c r="E379" s="5" t="str">
+        <f>IF($D379="","",VLOOKUP($D379,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
     <row r="380" spans="1:5">
@@ -7507,8 +7559,9 @@
       <c r="D380" s="9">
         <v>6388100</v>
       </c>
-      <c r="E380" s="5" t="s">
-        <v>35</v>
+      <c r="E380" s="5" t="str">
+        <f>IF($D380="","",VLOOKUP($D380,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -7524,8 +7577,9 @@
       <c r="D381" s="9">
         <v>6032072</v>
       </c>
-      <c r="E381" s="5" t="s">
-        <v>35</v>
+      <c r="E381" s="5" t="str">
+        <f>IF($D381="","",VLOOKUP($D381,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -7541,8 +7595,9 @@
       <c r="D382" s="9">
         <v>5593709</v>
       </c>
-      <c r="E382" s="5" t="s">
-        <v>35</v>
+      <c r="E382" s="5" t="str">
+        <f>IF($D382="","",VLOOKUP($D382,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -7558,8 +7613,9 @@
       <c r="D383" s="9">
         <v>4942793</v>
       </c>
-      <c r="E383" s="5" t="s">
-        <v>35</v>
+      <c r="E383" s="5" t="str">
+        <f>IF($D383="","",VLOOKUP($D383,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -7575,8 +7631,9 @@
       <c r="D384" s="9">
         <v>4587543</v>
       </c>
-      <c r="E384" s="5" t="s">
-        <v>35</v>
+      <c r="E384" s="5" t="str">
+        <f>IF($D384="","",VLOOKUP($D384,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -7592,8 +7649,9 @@
       <c r="D385" s="9">
         <v>4012455</v>
       </c>
-      <c r="E385" s="5" t="s">
-        <v>35</v>
+      <c r="E385" s="5" t="str">
+        <f>IF($D385="","",VLOOKUP($D385,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -7609,8 +7667,9 @@
       <c r="D386" s="9">
         <v>3613479</v>
       </c>
-      <c r="E386" s="5" t="s">
-        <v>35</v>
+      <c r="E386" s="5" t="str">
+        <f>IF($D386="","",VLOOKUP($D386,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -7626,8 +7685,9 @@
       <c r="D387" s="9">
         <v>2363818</v>
       </c>
-      <c r="E387" s="5" t="s">
-        <v>61</v>
+      <c r="E387" s="5" t="str">
+        <f>IF($D387="","",VLOOKUP($D387,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>7단계</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -7643,8 +7703,9 @@
       <c r="D388" s="9">
         <v>2307050</v>
       </c>
-      <c r="E388" s="5" t="s">
-        <v>61</v>
+      <c r="E388" s="5" t="str">
+        <f>IF($D388="","",VLOOKUP($D388,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>7단계</v>
       </c>
     </row>
     <row r="389" spans="1:5">
@@ -7660,8 +7721,9 @@
       <c r="D389" s="9">
         <v>2215136</v>
       </c>
-      <c r="E389" s="5" t="s">
-        <v>63</v>
+      <c r="E389" s="5" t="str">
+        <f>IF($D389="","",VLOOKUP($D389,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -7677,8 +7739,9 @@
       <c r="D390" s="9">
         <v>2185908</v>
       </c>
-      <c r="E390" s="5" t="s">
-        <v>63</v>
+      <c r="E390" s="5" t="str">
+        <f>IF($D390="","",VLOOKUP($D390,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
       </c>
     </row>
     <row r="391" spans="1:5">
@@ -7694,8 +7757,9 @@
       <c r="D391" s="9">
         <v>1109775</v>
       </c>
-      <c r="E391" s="5" t="s">
-        <v>63</v>
+      <c r="E391" s="5" t="str">
+        <f>IF($D391="","",VLOOKUP($D391,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
       </c>
     </row>
     <row r="392" spans="1:5">
@@ -7711,8 +7775,9 @@
       <c r="D392" s="9">
         <v>999218</v>
       </c>
-      <c r="E392" s="5" t="s">
-        <v>68</v>
+      <c r="E392" s="5" t="str">
+        <f>IF($D392="","",VLOOKUP($D392,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>5단계</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -7728,8 +7793,9 @@
       <c r="D393" s="9">
         <v>845000</v>
       </c>
-      <c r="E393" s="5" t="s">
-        <v>68</v>
+      <c r="E393" s="5" t="str">
+        <f>IF($D393="","",VLOOKUP($D393,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>5단계</v>
       </c>
     </row>
     <row r="394" spans="1:5">
@@ -7745,8 +7811,9 @@
       <c r="D394" s="9">
         <v>364314</v>
       </c>
-      <c r="E394" s="5" t="s">
-        <v>63</v>
+      <c r="E394" s="5" t="str">
+        <f>IF($D394="","",VLOOKUP($D394,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>3단계</v>
       </c>
     </row>
   </sheetData>

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F69B92F-DA43-4EAE-AFC9-509F8231A4A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB73774-617F-4D7B-B60D-02CF964DE0A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21600" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="기준표" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="121">
   <si>
     <t>📦 월별 보관 — 2026-06  (날짜별 길드전 랭킹 누적)</t>
   </si>
@@ -109,6 +109,9 @@
     <t>독로이지</t>
   </si>
   <si>
+    <t>습격이다개스키야</t>
+  </si>
+  <si>
     <t>핑도노-품치고-생각하는-편</t>
   </si>
   <si>
@@ -127,12 +130,21 @@
     <t>독그레핀</t>
   </si>
   <si>
+    <t>떠들어봐안들린다</t>
+  </si>
+  <si>
     <t>명령라하지마라</t>
   </si>
   <si>
+    <t>뮤지컬보러가서노래따라부르는놈</t>
+  </si>
+  <si>
     <t>독한다람쥐</t>
   </si>
   <si>
+    <t>영화관에서결말스포한냔</t>
+  </si>
+  <si>
     <t>독파민</t>
   </si>
   <si>
@@ -145,6 +157,9 @@
     <t>8단계</t>
   </si>
   <si>
+    <t>티거Ya드랍더튀어</t>
+  </si>
+  <si>
     <t>독눈누눈누</t>
   </si>
   <si>
@@ -175,69 +190,69 @@
     <t>독삼미</t>
   </si>
   <si>
+    <t>엘베닫힘연타법</t>
+  </si>
+  <si>
+    <t>독아크</t>
+  </si>
+  <si>
+    <t>독아윤</t>
+  </si>
+  <si>
+    <t>훔쳐뿟노</t>
+  </si>
+  <si>
+    <t>괴도하미</t>
+  </si>
+  <si>
+    <t>독후감상문</t>
+  </si>
+  <si>
+    <t>독고독</t>
+  </si>
+  <si>
+    <t>독철이</t>
+  </si>
+  <si>
+    <t>독계탕</t>
+  </si>
+  <si>
+    <t>독이즈</t>
+  </si>
+  <si>
+    <t>독과점</t>
+  </si>
+  <si>
+    <t>독터키캔씨Turkey1881</t>
+  </si>
+  <si>
+    <t>악마인데순둥소예</t>
+  </si>
+  <si>
+    <t>독팡팡</t>
+  </si>
+  <si>
+    <t>독독쿠롱</t>
+  </si>
+  <si>
+    <t>7단계</t>
+  </si>
+  <si>
+    <t>독골골</t>
+  </si>
+  <si>
+    <t>6단계</t>
+  </si>
+  <si>
+    <t>독주</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
     <t>엘베단힘연타법</t>
   </si>
   <si>
-    <t>독아크</t>
-  </si>
-  <si>
-    <t>독아윤</t>
-  </si>
-  <si>
-    <t>훔쳐뿟노</t>
-  </si>
-  <si>
-    <t>괴도하미</t>
-  </si>
-  <si>
-    <t>독후감상문</t>
-  </si>
-  <si>
-    <t>독고독</t>
-  </si>
-  <si>
-    <t>독철이</t>
-  </si>
-  <si>
-    <t>독계탕</t>
-  </si>
-  <si>
-    <t>독이즈</t>
-  </si>
-  <si>
-    <t>독과점</t>
-  </si>
-  <si>
-    <t>독터키캔씨Turkey1881</t>
-  </si>
-  <si>
-    <t>악마인데순둥소예</t>
-  </si>
-  <si>
-    <t>독팡팡</t>
-  </si>
-  <si>
-    <t>독독쿠롱</t>
-  </si>
-  <si>
-    <t>7단계</t>
-  </si>
-  <si>
-    <t>독골골</t>
-  </si>
-  <si>
-    <t>6단계</t>
-  </si>
-  <si>
-    <t>독주</t>
-  </si>
-  <si>
-    <t>2026-06-13</t>
-  </si>
-  <si>
-    <t>주니품</t>
-  </si>
-  <si>
     <t>1090</t>
   </si>
   <si>
@@ -280,6 +295,9 @@
     <t>아사히</t>
   </si>
   <si>
+    <t>미녀와야자수</t>
+  </si>
+  <si>
     <t>빡센공주</t>
   </si>
   <si>
@@ -328,6 +346,12 @@
     <t>입담터는단소빌런</t>
   </si>
   <si>
+    <t>뺙센공주</t>
+  </si>
+  <si>
+    <t>저썰고</t>
+  </si>
+  <si>
     <t>하한점수</t>
   </si>
   <si>
@@ -370,38 +394,10 @@
     <t>📦 월별 보관 — 2026-07  (날짜별 길드전 랭킹 누적)</t>
   </si>
   <si>
-    <t>뺙센공주</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>엘베닫힘연타법</t>
-  </si>
-  <si>
-    <t>엘베닫힘연타법</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>미녀와야자수</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>티거Ya드랍더튀어</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>습격이다개스키야</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>떠들어봐안들린다</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>영화관에서결말스포한냔</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>뮤지컬보러가서노래따라부르는놈</t>
+    <t>2026-06-19</t>
+  </si>
+  <si>
+    <t>주니쯤</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -503,7 +499,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -532,6 +528,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -801,13 +800,13 @@
   <sheetData>
     <row r="3" spans="2:4" ht="16.5" customHeight="1">
       <c r="B3" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="16.5" customHeight="1">
@@ -815,10 +814,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="16.5" customHeight="1">
@@ -826,10 +825,10 @@
         <v>38001</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="16.5" customHeight="1">
@@ -837,10 +836,10 @@
         <v>145001</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="16.5" customHeight="1">
@@ -848,10 +847,10 @@
         <v>550001</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="16.5" customHeight="1">
@@ -859,10 +858,10 @@
         <v>650001</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="16.5" customHeight="1">
@@ -870,10 +869,10 @@
         <v>1020001</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="16.5" customHeight="1">
@@ -881,10 +880,10 @@
         <v>2280001</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="16.5" customHeight="1">
@@ -892,10 +891,10 @@
         <v>2630001</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="16.5" customHeight="1">
@@ -906,7 +905,7 @@
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -918,10 +917,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E394"/>
+  <dimension ref="A1:E461"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="49.75" customWidth="1"/>
+    <col min="1" max="1" width="14.875" customWidth="1"/>
     <col min="2" max="2" width="5.25" customWidth="1"/>
     <col min="3" max="3" width="31.75" customWidth="1"/>
     <col min="4" max="4" width="15.125" customWidth="1"/>
@@ -1230,7 +1229,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="D19">
         <v>7972413</v>
@@ -1247,7 +1246,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D20">
         <v>7829890</v>
@@ -1264,7 +1263,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D21">
         <v>7747410</v>
@@ -1281,7 +1280,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D22">
         <v>7734457</v>
@@ -1298,7 +1297,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>7656699</v>
@@ -1315,7 +1314,7 @@
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D24">
         <v>7629930</v>
@@ -1332,7 +1331,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D25">
         <v>7629170</v>
@@ -1349,7 +1348,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="D26">
         <v>7530750</v>
@@ -1366,7 +1365,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D27">
         <v>7494390</v>
@@ -1383,7 +1382,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>119</v>
+        <v>33</v>
       </c>
       <c r="D28">
         <v>7425030</v>
@@ -1400,7 +1399,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D29">
         <v>7233630</v>
@@ -1417,7 +1416,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="D30">
         <v>7218568</v>
@@ -1434,7 +1433,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D31">
         <v>7215859</v>
@@ -1451,7 +1450,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D32">
         <v>7202018</v>
@@ -1468,13 +1467,13 @@
         <v>31</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D33">
         <v>5747056</v>
       </c>
       <c r="E33" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="16.5" customHeight="1">
@@ -1485,13 +1484,13 @@
         <v>32</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="D34">
         <v>5659102</v>
       </c>
       <c r="E34" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="16.5" customHeight="1">
@@ -1502,13 +1501,13 @@
         <v>33</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D35">
         <v>5575024</v>
       </c>
       <c r="E35" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="16.5" customHeight="1">
@@ -1519,13 +1518,13 @@
         <v>34</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D36">
         <v>5545974</v>
       </c>
       <c r="E36" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="16.5" customHeight="1">
@@ -1536,13 +1535,13 @@
         <v>35</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D37">
         <v>5391755</v>
       </c>
       <c r="E37" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="16.5" customHeight="1">
@@ -1553,13 +1552,13 @@
         <v>36</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D38">
         <v>5181490</v>
       </c>
       <c r="E38" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="16.5" customHeight="1">
@@ -1570,13 +1569,13 @@
         <v>37</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D39">
         <v>5131950</v>
       </c>
       <c r="E39" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="16.5" customHeight="1">
@@ -1587,13 +1586,13 @@
         <v>38</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D40">
         <v>4904007</v>
       </c>
       <c r="E40" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="16.5" customHeight="1">
@@ -1604,13 +1603,13 @@
         <v>39</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D41">
         <v>4573837</v>
       </c>
       <c r="E41" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="16.5" customHeight="1">
@@ -1621,13 +1620,13 @@
         <v>40</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D42">
         <v>4490575</v>
       </c>
       <c r="E42" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="16.5" customHeight="1">
@@ -1638,13 +1637,13 @@
         <v>41</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D43">
         <v>4397353</v>
       </c>
       <c r="E43" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="16.5" customHeight="1">
@@ -1655,13 +1654,13 @@
         <v>42</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D44">
         <v>4297031</v>
       </c>
       <c r="E44" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="16.5" customHeight="1">
@@ -1672,13 +1671,13 @@
         <v>43</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="D45">
         <v>4182965</v>
       </c>
       <c r="E45" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="16.5" customHeight="1">
@@ -1689,13 +1688,13 @@
         <v>44</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D46">
         <v>4030862</v>
       </c>
       <c r="E46" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="16.5" customHeight="1">
@@ -1706,13 +1705,13 @@
         <v>45</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D47">
         <v>3998435</v>
       </c>
       <c r="E47" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="16.5" customHeight="1">
@@ -1723,13 +1722,13 @@
         <v>46</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D48">
         <v>3927862</v>
       </c>
       <c r="E48" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="16.5" customHeight="1">
@@ -1740,13 +1739,13 @@
         <v>47</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D49">
         <v>3788029</v>
       </c>
       <c r="E49" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="16.5" customHeight="1">
@@ -1757,13 +1756,13 @@
         <v>48</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D50">
         <v>3775539</v>
       </c>
       <c r="E50" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="16.5" customHeight="1">
@@ -1774,13 +1773,13 @@
         <v>49</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D51">
         <v>3644353</v>
       </c>
       <c r="E51" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="16.5" customHeight="1">
@@ -1791,13 +1790,13 @@
         <v>50</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D52">
         <v>3436366</v>
       </c>
       <c r="E52" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="16.5" customHeight="1">
@@ -1808,13 +1807,13 @@
         <v>51</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D53">
         <v>3375232</v>
       </c>
       <c r="E53" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="16.5" customHeight="1">
@@ -1825,13 +1824,13 @@
         <v>52</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D54">
         <v>3219637</v>
       </c>
       <c r="E54" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="16.5" customHeight="1">
@@ -1842,13 +1841,13 @@
         <v>53</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D55">
         <v>3100693</v>
       </c>
       <c r="E55" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="16.5" customHeight="1">
@@ -1859,13 +1858,13 @@
         <v>54</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D56">
         <v>3087580</v>
       </c>
       <c r="E56" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="16.5" customHeight="1">
@@ -1876,13 +1875,13 @@
         <v>55</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D57">
         <v>2720000</v>
       </c>
       <c r="E57" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="16.5" customHeight="1">
@@ -1893,13 +1892,13 @@
         <v>56</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D58">
         <v>2670936</v>
       </c>
       <c r="E58" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="16.5" customHeight="1">
@@ -1910,13 +1909,13 @@
         <v>57</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D59">
         <v>2294961</v>
       </c>
       <c r="E59" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="16.5" customHeight="1">
@@ -1927,13 +1926,13 @@
         <v>58</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D60">
         <v>2202597</v>
       </c>
       <c r="E60" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="16.5" customHeight="1">
@@ -1944,24 +1943,24 @@
         <v>59</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D61">
         <v>2155923</v>
       </c>
       <c r="E61" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="16.5" customHeight="1">
       <c r="A62" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B62">
         <v>1</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="D62">
         <v>20124674</v>
@@ -1972,7 +1971,7 @@
     </row>
     <row r="63" spans="1:5" ht="16.5" customHeight="1">
       <c r="A63" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B63">
         <v>2</v>
@@ -1989,7 +1988,7 @@
     </row>
     <row r="64" spans="1:5" ht="16.5" customHeight="1">
       <c r="A64" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B64">
         <v>3</v>
@@ -2006,7 +2005,7 @@
     </row>
     <row r="65" spans="1:5" ht="16.5" customHeight="1">
       <c r="A65" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B65">
         <v>4</v>
@@ -2023,7 +2022,7 @@
     </row>
     <row r="66" spans="1:5" ht="16.5" customHeight="1">
       <c r="A66" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B66">
         <v>5</v>
@@ -2040,7 +2039,7 @@
     </row>
     <row r="67" spans="1:5" ht="16.5" customHeight="1">
       <c r="A67" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B67">
         <v>6</v>
@@ -2057,7 +2056,7 @@
     </row>
     <row r="68" spans="1:5" ht="16.5" customHeight="1">
       <c r="A68" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B68">
         <v>7</v>
@@ -2074,13 +2073,13 @@
     </row>
     <row r="69" spans="1:5" ht="16.5" customHeight="1">
       <c r="A69" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B69">
         <v>8</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="D69">
         <v>11050986</v>
@@ -2091,7 +2090,7 @@
     </row>
     <row r="70" spans="1:5" ht="16.5" customHeight="1">
       <c r="A70" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B70">
         <v>9</v>
@@ -2108,13 +2107,13 @@
     </row>
     <row r="71" spans="1:5" ht="16.5" customHeight="1">
       <c r="A71" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B71">
         <v>10</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D71">
         <v>10955529</v>
@@ -2125,13 +2124,13 @@
     </row>
     <row r="72" spans="1:5" ht="16.5" customHeight="1">
       <c r="A72" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B72">
         <v>11</v>
       </c>
       <c r="C72" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D72">
         <v>10698509</v>
@@ -2142,13 +2141,13 @@
     </row>
     <row r="73" spans="1:5" ht="16.5" customHeight="1">
       <c r="A73" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B73">
         <v>12</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D73">
         <v>10412961</v>
@@ -2159,7 +2158,7 @@
     </row>
     <row r="74" spans="1:5" ht="16.5" customHeight="1">
       <c r="A74" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B74">
         <v>13</v>
@@ -2176,7 +2175,7 @@
     </row>
     <row r="75" spans="1:5" ht="16.5" customHeight="1">
       <c r="A75" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B75">
         <v>14</v>
@@ -2193,13 +2192,13 @@
     </row>
     <row r="76" spans="1:5" ht="16.5" customHeight="1">
       <c r="A76" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B76">
         <v>15</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D76">
         <v>9099782</v>
@@ -2210,13 +2209,13 @@
     </row>
     <row r="77" spans="1:5" ht="16.5" customHeight="1">
       <c r="A77" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B77">
         <v>16</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D77">
         <v>8928749</v>
@@ -2227,7 +2226,7 @@
     </row>
     <row r="78" spans="1:5" ht="16.5" customHeight="1">
       <c r="A78" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B78">
         <v>17</v>
@@ -2244,13 +2243,13 @@
     </row>
     <row r="79" spans="1:5" ht="16.5" customHeight="1">
       <c r="A79" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B79">
         <v>18</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D79">
         <v>8453735</v>
@@ -2261,13 +2260,13 @@
     </row>
     <row r="80" spans="1:5" ht="16.5" customHeight="1">
       <c r="A80" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B80">
         <v>19</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D80">
         <v>8390684</v>
@@ -2278,13 +2277,13 @@
     </row>
     <row r="81" spans="1:5" ht="16.5" customHeight="1">
       <c r="A81" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B81">
         <v>20</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D81">
         <v>8385975</v>
@@ -2295,7 +2294,7 @@
     </row>
     <row r="82" spans="1:5" ht="16.5" customHeight="1">
       <c r="A82" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B82">
         <v>21</v>
@@ -2312,13 +2311,13 @@
     </row>
     <row r="83" spans="1:5" ht="16.5" customHeight="1">
       <c r="A83" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B83">
         <v>22</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D83">
         <v>7760606</v>
@@ -2329,13 +2328,13 @@
     </row>
     <row r="84" spans="1:5" ht="16.5" customHeight="1">
       <c r="A84" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B84">
         <v>23</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D84">
         <v>7534842</v>
@@ -2346,13 +2345,13 @@
     </row>
     <row r="85" spans="1:5" ht="16.5" customHeight="1">
       <c r="A85" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B85">
         <v>24</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D85">
         <v>7400843</v>
@@ -2363,13 +2362,13 @@
     </row>
     <row r="86" spans="1:5" ht="16.5" customHeight="1">
       <c r="A86" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B86">
         <v>25</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D86">
         <v>7282637</v>
@@ -2380,13 +2379,13 @@
     </row>
     <row r="87" spans="1:5" ht="16.5" customHeight="1">
       <c r="A87" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B87">
         <v>26</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="D87">
         <v>7281876</v>
@@ -2397,7 +2396,7 @@
     </row>
     <row r="88" spans="1:5" ht="16.5" customHeight="1">
       <c r="A88" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B88">
         <v>27</v>
@@ -2414,13 +2413,13 @@
     </row>
     <row r="89" spans="1:5" ht="16.5" customHeight="1">
       <c r="A89" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B89">
         <v>28</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>119</v>
+        <v>33</v>
       </c>
       <c r="D89">
         <v>7272828</v>
@@ -2431,13 +2430,13 @@
     </row>
     <row r="90" spans="1:5" ht="16.5" customHeight="1">
       <c r="A90" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B90">
         <v>29</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D90">
         <v>7236458</v>
@@ -2448,24 +2447,24 @@
     </row>
     <row r="91" spans="1:5" ht="16.5" customHeight="1">
       <c r="A91" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B91">
         <v>30</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="D91">
         <v>6986371</v>
       </c>
       <c r="E91" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="16.5" customHeight="1">
       <c r="A92" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B92">
         <v>31</v>
@@ -2477,63 +2476,63 @@
         <v>5884130</v>
       </c>
       <c r="E92" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="16.5" customHeight="1">
       <c r="A93" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B93">
         <v>32</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D93">
         <v>5813157</v>
       </c>
       <c r="E93" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="16.5" customHeight="1">
       <c r="A94" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B94">
         <v>33</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D94">
         <v>5275134</v>
       </c>
       <c r="E94" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="16.5" customHeight="1">
       <c r="A95" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B95">
         <v>34</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D95">
         <v>4876688</v>
       </c>
       <c r="E95" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="16.5" customHeight="1">
       <c r="A96" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B96">
         <v>35</v>
@@ -2545,63 +2544,63 @@
         <v>4842063</v>
       </c>
       <c r="E96" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="16.5" customHeight="1">
       <c r="A97" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B97">
         <v>36</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D97">
         <v>4668195</v>
       </c>
       <c r="E97" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="16.5" customHeight="1">
       <c r="A98" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B98">
         <v>37</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D98">
         <v>4616477</v>
       </c>
       <c r="E98" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="16.5" customHeight="1">
       <c r="A99" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B99">
         <v>38</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D99">
         <v>4498125</v>
       </c>
       <c r="E99" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="16.5" customHeight="1">
       <c r="A100" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B100">
         <v>39</v>
@@ -2613,165 +2612,165 @@
         <v>3687186</v>
       </c>
       <c r="E100" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="16.5" customHeight="1">
       <c r="A101" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B101">
         <v>40</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D101">
         <v>3611227</v>
       </c>
       <c r="E101" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="16.5" customHeight="1">
       <c r="A102" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B102">
         <v>41</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D102">
         <v>3189920</v>
       </c>
       <c r="E102" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="16.5" customHeight="1">
       <c r="A103" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B103">
         <v>42</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D103">
         <v>3120139</v>
       </c>
       <c r="E103" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="16.5" customHeight="1">
       <c r="A104" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B104">
         <v>43</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D104">
         <v>3108728</v>
       </c>
       <c r="E104" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="16.5" customHeight="1">
       <c r="A105" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B105">
         <v>44</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>66</v>
+      <c r="C105" s="10" t="s">
+        <v>120</v>
       </c>
       <c r="D105">
         <v>3077202</v>
       </c>
       <c r="E105" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="16.5" customHeight="1">
       <c r="A106" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B106">
         <v>45</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D106">
         <v>2968639</v>
       </c>
       <c r="E106" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="16.5" customHeight="1">
       <c r="A107" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B107">
         <v>46</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D107">
         <v>2968603</v>
       </c>
       <c r="E107" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="16.5" customHeight="1">
       <c r="A108" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B108">
         <v>47</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="D108">
         <v>2953979</v>
       </c>
       <c r="E108" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="16.5" customHeight="1">
       <c r="A109" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B109">
         <v>48</v>
       </c>
       <c r="C109" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D109">
         <v>2772649</v>
       </c>
       <c r="E109" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="16.5" customHeight="1">
       <c r="A110" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B110">
         <v>49</v>
@@ -2783,273 +2782,273 @@
         <v>2738331</v>
       </c>
       <c r="E110" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="16.5" customHeight="1">
       <c r="A111" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B111">
         <v>50</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D111">
         <v>2460723</v>
       </c>
       <c r="E111" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="16.5" customHeight="1">
       <c r="A112" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B112">
         <v>51</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D112">
         <v>2165388</v>
       </c>
       <c r="E112" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="16.5" customHeight="1">
       <c r="A113" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B113">
         <v>52</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D113">
         <v>2028076</v>
       </c>
       <c r="E113" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="16.5" customHeight="1">
       <c r="A114" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B114">
         <v>53</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D114">
         <v>1829852</v>
       </c>
       <c r="E114" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="16.5" customHeight="1">
       <c r="A115" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B115">
         <v>54</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D115">
         <v>1765395</v>
       </c>
       <c r="E115" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="16.5" customHeight="1">
       <c r="A116" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B116">
         <v>55</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D116">
         <v>1693947</v>
       </c>
       <c r="E116" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="16.5" customHeight="1">
       <c r="A117" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B117">
         <v>56</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D117">
         <v>1288077</v>
       </c>
       <c r="E117" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="16.5" customHeight="1">
       <c r="A118" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B118">
         <v>57</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D118">
         <v>1207196</v>
       </c>
       <c r="E118" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="16.5" customHeight="1">
       <c r="A119" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B119">
         <v>58</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D119">
         <v>963718</v>
       </c>
       <c r="E119" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="16.5" customHeight="1">
       <c r="A120" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B120">
         <v>59</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D120">
         <v>700489</v>
       </c>
       <c r="E120" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="16.5" customHeight="1">
       <c r="A121" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B121">
         <v>60</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D121">
         <v>659256</v>
       </c>
       <c r="E121" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="16.5" customHeight="1">
       <c r="A122" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B122">
         <v>61</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D122">
         <v>384395</v>
       </c>
       <c r="E122" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="16.5" customHeight="1">
       <c r="A123" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B123">
         <v>62</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D123">
         <v>327964</v>
       </c>
       <c r="E123" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="16.5" customHeight="1">
       <c r="A124" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B124">
         <v>63</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D124">
         <v>266932</v>
       </c>
       <c r="E124" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="16.5" customHeight="1">
       <c r="A125" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B125">
         <v>64</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D125">
         <v>89508</v>
       </c>
       <c r="E125" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="16.5" customHeight="1">
       <c r="A126" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D126">
         <v>76513151</v>
@@ -3060,13 +3059,13 @@
     </row>
     <row r="127" spans="1:5" ht="16.5" customHeight="1">
       <c r="A127" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B127">
         <v>2</v>
       </c>
       <c r="C127" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D127">
         <v>62254586</v>
@@ -3077,13 +3076,13 @@
     </row>
     <row r="128" spans="1:5" ht="16.5" customHeight="1">
       <c r="A128" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B128">
         <v>3</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>119</v>
+        <v>33</v>
       </c>
       <c r="D128">
         <v>36598969</v>
@@ -3094,7 +3093,7 @@
     </row>
     <row r="129" spans="1:5" ht="16.5" customHeight="1">
       <c r="A129" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B129">
         <v>4</v>
@@ -3111,13 +3110,13 @@
     </row>
     <row r="130" spans="1:5" ht="16.5" customHeight="1">
       <c r="A130" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B130">
         <v>5</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D130">
         <v>22027625</v>
@@ -3128,7 +3127,7 @@
     </row>
     <row r="131" spans="1:5" ht="16.5" customHeight="1">
       <c r="A131" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B131">
         <v>6</v>
@@ -3145,7 +3144,7 @@
     </row>
     <row r="132" spans="1:5" ht="16.5" customHeight="1">
       <c r="A132" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B132">
         <v>7</v>
@@ -3162,7 +3161,7 @@
     </row>
     <row r="133" spans="1:5" ht="16.5" customHeight="1">
       <c r="A133" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B133">
         <v>8</v>
@@ -3179,13 +3178,13 @@
     </row>
     <row r="134" spans="1:5" ht="16.5" customHeight="1">
       <c r="A134" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B134">
         <v>9</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D134">
         <v>15971399</v>
@@ -3196,7 +3195,7 @@
     </row>
     <row r="135" spans="1:5" ht="16.5" customHeight="1">
       <c r="A135" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B135">
         <v>10</v>
@@ -3213,13 +3212,13 @@
     </row>
     <row r="136" spans="1:5" ht="16.5" customHeight="1">
       <c r="A136" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B136">
         <v>11</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="D136">
         <v>15166835</v>
@@ -3230,13 +3229,13 @@
     </row>
     <row r="137" spans="1:5" ht="16.5" customHeight="1">
       <c r="A137" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B137">
         <v>12</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D137">
         <v>15136017</v>
@@ -3247,13 +3246,13 @@
     </row>
     <row r="138" spans="1:5" ht="16.5" customHeight="1">
       <c r="A138" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B138">
         <v>13</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D138">
         <v>15045625</v>
@@ -3264,13 +3263,13 @@
     </row>
     <row r="139" spans="1:5" ht="16.5" customHeight="1">
       <c r="A139" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B139">
         <v>14</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D139">
         <v>11929975</v>
@@ -3281,7 +3280,7 @@
     </row>
     <row r="140" spans="1:5" ht="16.5" customHeight="1">
       <c r="A140" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B140">
         <v>15</v>
@@ -3298,13 +3297,13 @@
     </row>
     <row r="141" spans="1:5" ht="16.5" customHeight="1">
       <c r="A141" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B141">
         <v>16</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D141">
         <v>11641804</v>
@@ -3315,13 +3314,13 @@
     </row>
     <row r="142" spans="1:5" ht="16.5" customHeight="1">
       <c r="A142" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B142">
         <v>17</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="D142">
         <v>11224132</v>
@@ -3332,13 +3331,13 @@
     </row>
     <row r="143" spans="1:5" ht="16.5" customHeight="1">
       <c r="A143" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B143">
         <v>18</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="D143">
         <v>11128193</v>
@@ -3349,7 +3348,7 @@
     </row>
     <row r="144" spans="1:5" ht="16.5" customHeight="1">
       <c r="A144" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B144">
         <v>19</v>
@@ -3366,7 +3365,7 @@
     </row>
     <row r="145" spans="1:5" ht="16.5" customHeight="1">
       <c r="A145" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B145">
         <v>20</v>
@@ -3383,7 +3382,7 @@
     </row>
     <row r="146" spans="1:5" ht="16.5" customHeight="1">
       <c r="A146" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B146">
         <v>21</v>
@@ -3400,7 +3399,7 @@
     </row>
     <row r="147" spans="1:5" ht="16.5" customHeight="1">
       <c r="A147" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B147">
         <v>22</v>
@@ -3417,13 +3416,13 @@
     </row>
     <row r="148" spans="1:5" ht="16.5" customHeight="1">
       <c r="A148" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B148">
         <v>23</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D148">
         <v>10128124</v>
@@ -3434,13 +3433,13 @@
     </row>
     <row r="149" spans="1:5" ht="16.5" customHeight="1">
       <c r="A149" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B149">
         <v>24</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D149">
         <v>9706739</v>
@@ -3451,13 +3450,13 @@
     </row>
     <row r="150" spans="1:5" ht="16.5" customHeight="1">
       <c r="A150" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B150">
         <v>25</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D150">
         <v>9164119</v>
@@ -3468,13 +3467,13 @@
     </row>
     <row r="151" spans="1:5" ht="16.5" customHeight="1">
       <c r="A151" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B151">
         <v>26</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D151">
         <v>8999382</v>
@@ -3485,13 +3484,13 @@
     </row>
     <row r="152" spans="1:5" ht="16.5" customHeight="1">
       <c r="A152" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B152">
         <v>27</v>
       </c>
       <c r="C152" s="10" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="D152">
         <v>8596217</v>
@@ -3502,13 +3501,13 @@
     </row>
     <row r="153" spans="1:5" ht="16.5" customHeight="1">
       <c r="A153" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B153">
         <v>28</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D153">
         <v>8456726</v>
@@ -3519,13 +3518,13 @@
     </row>
     <row r="154" spans="1:5" ht="16.5" customHeight="1">
       <c r="A154" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B154">
         <v>29</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D154">
         <v>8220352</v>
@@ -3536,13 +3535,13 @@
     </row>
     <row r="155" spans="1:5" ht="16.5" customHeight="1">
       <c r="A155" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B155">
         <v>30</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D155">
         <v>8154156</v>
@@ -3553,13 +3552,13 @@
     </row>
     <row r="156" spans="1:5" ht="16.5" customHeight="1">
       <c r="A156" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B156">
         <v>31</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D156">
         <v>8127020</v>
@@ -3570,13 +3569,13 @@
     </row>
     <row r="157" spans="1:5" ht="16.5" customHeight="1">
       <c r="A157" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B157">
         <v>32</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D157">
         <v>7952273</v>
@@ -3587,13 +3586,13 @@
     </row>
     <row r="158" spans="1:5" ht="16.5" customHeight="1">
       <c r="A158" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B158">
         <v>33</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D158">
         <v>7918857</v>
@@ -3604,13 +3603,13 @@
     </row>
     <row r="159" spans="1:5" ht="16.5" customHeight="1">
       <c r="A159" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B159">
         <v>34</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D159">
         <v>7909501</v>
@@ -3621,13 +3620,13 @@
     </row>
     <row r="160" spans="1:5" ht="16.5" customHeight="1">
       <c r="A160" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B160">
         <v>35</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D160">
         <v>7876636</v>
@@ -3638,13 +3637,13 @@
     </row>
     <row r="161" spans="1:5" ht="16.5" customHeight="1">
       <c r="A161" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B161">
         <v>36</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D161">
         <v>7824653</v>
@@ -3655,7 +3654,7 @@
     </row>
     <row r="162" spans="1:5" ht="16.5" customHeight="1">
       <c r="A162" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B162">
         <v>37</v>
@@ -3672,13 +3671,13 @@
     </row>
     <row r="163" spans="1:5" ht="16.5" customHeight="1">
       <c r="A163" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B163">
         <v>38</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D163">
         <v>7679597</v>
@@ -3689,13 +3688,13 @@
     </row>
     <row r="164" spans="1:5" ht="16.5" customHeight="1">
       <c r="A164" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B164">
         <v>39</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D164">
         <v>7635056</v>
@@ -3706,13 +3705,13 @@
     </row>
     <row r="165" spans="1:5" ht="16.5" customHeight="1">
       <c r="A165" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B165">
         <v>40</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D165">
         <v>7579677</v>
@@ -3723,13 +3722,13 @@
     </row>
     <row r="166" spans="1:5" ht="16.5" customHeight="1">
       <c r="A166" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B166">
         <v>41</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D166">
         <v>7552044</v>
@@ -3740,13 +3739,13 @@
     </row>
     <row r="167" spans="1:5" ht="16.5" customHeight="1">
       <c r="A167" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B167">
         <v>42</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D167">
         <v>7462230</v>
@@ -3757,13 +3756,13 @@
     </row>
     <row r="168" spans="1:5" ht="16.5" customHeight="1">
       <c r="A168" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B168">
         <v>43</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D168">
         <v>7423633</v>
@@ -3774,13 +3773,13 @@
     </row>
     <row r="169" spans="1:5" ht="16.5" customHeight="1">
       <c r="A169" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B169">
         <v>44</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D169">
         <v>7327050</v>
@@ -3791,160 +3790,160 @@
     </row>
     <row r="170" spans="1:5" ht="16.5" customHeight="1">
       <c r="A170" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B170">
         <v>45</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D170">
         <v>6678842</v>
       </c>
       <c r="E170" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="16.5" customHeight="1">
       <c r="A171" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B171">
         <v>46</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D171">
         <v>6177989</v>
       </c>
       <c r="E171" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="16.5" customHeight="1">
       <c r="A172" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B172">
         <v>47</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D172">
         <v>5901298</v>
       </c>
       <c r="E172" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="16.5" customHeight="1">
       <c r="A173" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B173">
         <v>48</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D173">
         <v>5097585</v>
       </c>
       <c r="E173" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="16.5" customHeight="1">
       <c r="A174" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B174">
         <v>49</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D174">
         <v>5036088</v>
       </c>
       <c r="E174" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="16.5" customHeight="1">
       <c r="A175" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B175">
         <v>50</v>
       </c>
       <c r="C175" s="11" t="s">
-        <v>112</v>
+        <v>51</v>
       </c>
       <c r="D175">
         <v>4821347</v>
       </c>
       <c r="E175" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="16.5" customHeight="1">
       <c r="A176" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B176">
         <v>51</v>
       </c>
       <c r="C176" s="10" t="s">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="D176">
         <v>4599953</v>
       </c>
       <c r="E176" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="16.5" customHeight="1">
       <c r="A177" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B177">
         <v>52</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D177">
         <v>4332112</v>
       </c>
       <c r="E177" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="16.5" customHeight="1">
       <c r="A178" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B178">
         <v>53</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D178">
         <v>4235009</v>
       </c>
       <c r="E178" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="16.5" customHeight="1">
       <c r="A179" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B179">
         <v>54</v>
@@ -3956,12 +3955,12 @@
         <v>4226803</v>
       </c>
       <c r="E179" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="16.5" customHeight="1">
       <c r="A180" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B180">
         <v>55</v>
@@ -3973,216 +3972,216 @@
         <v>3992666</v>
       </c>
       <c r="E180" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="16.5" customHeight="1">
       <c r="A181" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B181">
         <v>56</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D181">
         <v>3935236</v>
       </c>
       <c r="E181" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="16.5" customHeight="1">
       <c r="A182" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B182">
         <v>57</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D182">
         <v>3819189</v>
       </c>
       <c r="E182" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="16.5" customHeight="1">
       <c r="A183" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B183">
         <v>58</v>
       </c>
-      <c r="C183" s="1" t="s">
-        <v>66</v>
+      <c r="C183" s="10" t="s">
+        <v>120</v>
       </c>
       <c r="D183">
         <v>2896389</v>
       </c>
       <c r="E183" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="184" spans="1:5" ht="16.5" customHeight="1">
       <c r="A184" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B184">
         <v>59</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D184">
         <v>2645896</v>
       </c>
       <c r="E184" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="185" spans="1:5" ht="16.5" customHeight="1">
       <c r="A185" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B185">
         <v>60</v>
       </c>
       <c r="C185" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D185">
         <v>2195612</v>
       </c>
       <c r="E185" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="16.5" customHeight="1">
       <c r="A186" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B186">
         <v>61</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D186">
         <v>1908787</v>
       </c>
       <c r="E186" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="16.5" customHeight="1">
       <c r="A187" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B187">
         <v>62</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D187">
         <v>1890847</v>
       </c>
       <c r="E187" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="16.5" customHeight="1">
       <c r="A188" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B188">
         <v>63</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D188">
         <v>1772463</v>
       </c>
       <c r="E188" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="189" spans="1:5" ht="16.5" customHeight="1">
       <c r="A189" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B189">
         <v>64</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D189">
         <v>1472500</v>
       </c>
       <c r="E189" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="16.5" customHeight="1">
       <c r="A190" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B190">
         <v>65</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D190">
         <v>1425274</v>
       </c>
       <c r="E190" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="191" spans="1:5" ht="16.5" customHeight="1">
       <c r="A191" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B191">
         <v>66</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D191">
         <v>1226829</v>
       </c>
       <c r="E191" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="16.5" customHeight="1">
       <c r="A192" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B192">
         <v>67</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D192">
         <v>460000</v>
       </c>
       <c r="E192" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="193" spans="1:5" ht="16.5" customHeight="1">
       <c r="A193" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B193" s="2">
         <v>1</v>
@@ -4200,13 +4199,13 @@
     </row>
     <row r="194" spans="1:5" ht="16.5" customHeight="1">
       <c r="A194" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B194" s="2">
         <v>2</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D194" s="4">
         <v>12925350</v>
@@ -4218,13 +4217,13 @@
     </row>
     <row r="195" spans="1:5" ht="16.5" customHeight="1">
       <c r="A195" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B195" s="2">
         <v>3</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D195" s="4">
         <v>12016650</v>
@@ -4236,13 +4235,13 @@
     </row>
     <row r="196" spans="1:5" ht="16.5" customHeight="1">
       <c r="A196" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B196" s="2">
         <v>4</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D196" s="4">
         <v>9907350</v>
@@ -4254,13 +4253,13 @@
     </row>
     <row r="197" spans="1:5" ht="16.5" customHeight="1">
       <c r="A197" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B197" s="2">
         <v>5</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="D197" s="4">
         <v>9868650</v>
@@ -4272,13 +4271,13 @@
     </row>
     <row r="198" spans="1:5" ht="16.5" customHeight="1">
       <c r="A198" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B198" s="2">
         <v>6</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>119</v>
+        <v>33</v>
       </c>
       <c r="D198" s="4">
         <v>9143700</v>
@@ -4290,7 +4289,7 @@
     </row>
     <row r="199" spans="1:5" ht="16.5" customHeight="1">
       <c r="A199" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B199" s="2">
         <v>7</v>
@@ -4308,13 +4307,13 @@
     </row>
     <row r="200" spans="1:5" ht="16.5" customHeight="1">
       <c r="A200" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B200" s="2">
         <v>8</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D200" s="4">
         <v>9065250</v>
@@ -4326,13 +4325,13 @@
     </row>
     <row r="201" spans="1:5" ht="16.5" customHeight="1">
       <c r="A201" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B201" s="2">
         <v>9</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D201" s="4">
         <v>9017250</v>
@@ -4344,13 +4343,13 @@
     </row>
     <row r="202" spans="1:5" ht="16.5" customHeight="1">
       <c r="A202" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B202" s="2">
         <v>10</v>
       </c>
       <c r="C202" s="7" t="s">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="D202" s="4">
         <v>8908800</v>
@@ -4362,7 +4361,7 @@
     </row>
     <row r="203" spans="1:5" ht="16.5" customHeight="1">
       <c r="A203" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B203" s="2">
         <v>11</v>
@@ -4380,7 +4379,7 @@
     </row>
     <row r="204" spans="1:5" ht="16.5" customHeight="1">
       <c r="A204" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B204" s="2">
         <v>12</v>
@@ -4398,13 +4397,13 @@
     </row>
     <row r="205" spans="1:5" ht="16.5" customHeight="1">
       <c r="A205" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B205" s="2">
         <v>13</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D205" s="4">
         <v>8125259</v>
@@ -4416,7 +4415,7 @@
     </row>
     <row r="206" spans="1:5" ht="16.5" customHeight="1">
       <c r="A206" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B206" s="2">
         <v>14</v>
@@ -4434,13 +4433,13 @@
     </row>
     <row r="207" spans="1:5" ht="16.5" customHeight="1">
       <c r="A207" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B207" s="2">
         <v>15</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D207" s="4">
         <v>7740750</v>
@@ -4452,7 +4451,7 @@
     </row>
     <row r="208" spans="1:5" ht="16.5" customHeight="1">
       <c r="A208" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B208" s="2">
         <v>16</v>
@@ -4470,7 +4469,7 @@
     </row>
     <row r="209" spans="1:5" ht="16.5" customHeight="1">
       <c r="A209" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B209" s="2">
         <v>17</v>
@@ -4488,13 +4487,13 @@
     </row>
     <row r="210" spans="1:5" ht="16.5" customHeight="1">
       <c r="A210" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B210" s="2">
         <v>18</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D210" s="4">
         <v>7694109</v>
@@ -4506,13 +4505,13 @@
     </row>
     <row r="211" spans="1:5" ht="16.5" customHeight="1">
       <c r="A211" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B211" s="2">
         <v>19</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D211" s="4">
         <v>7624294</v>
@@ -4524,13 +4523,13 @@
     </row>
     <row r="212" spans="1:5" ht="16.5" customHeight="1">
       <c r="A212" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B212" s="2">
         <v>20</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D212" s="4">
         <v>7548021</v>
@@ -4542,13 +4541,13 @@
     </row>
     <row r="213" spans="1:5" ht="16.5" customHeight="1">
       <c r="A213" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B213" s="2">
         <v>21</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D213" s="4">
         <v>7514973</v>
@@ -4560,13 +4559,13 @@
     </row>
     <row r="214" spans="1:5" ht="16.5" customHeight="1">
       <c r="A214" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B214" s="2">
         <v>22</v>
       </c>
       <c r="C214" s="7" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="D214" s="4">
         <v>7392720</v>
@@ -4578,7 +4577,7 @@
     </row>
     <row r="215" spans="1:5" ht="16.5" customHeight="1">
       <c r="A215" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B215" s="2">
         <v>23</v>
@@ -4596,7 +4595,7 @@
     </row>
     <row r="216" spans="1:5" ht="16.5" customHeight="1">
       <c r="A216" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B216" s="2">
         <v>24</v>
@@ -4614,13 +4613,13 @@
     </row>
     <row r="217" spans="1:5" ht="16.5" customHeight="1">
       <c r="A217" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B217" s="2">
         <v>25</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D217" s="4">
         <v>7285842</v>
@@ -4632,13 +4631,13 @@
     </row>
     <row r="218" spans="1:5" ht="16.5" customHeight="1">
       <c r="A218" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B218" s="2">
         <v>26</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D218" s="4">
         <v>7252456</v>
@@ -4650,7 +4649,7 @@
     </row>
     <row r="219" spans="1:5" ht="16.5" customHeight="1">
       <c r="A219" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B219" s="2">
         <v>27</v>
@@ -4668,13 +4667,13 @@
     </row>
     <row r="220" spans="1:5" ht="16.5" customHeight="1">
       <c r="A220" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B220" s="2">
         <v>28</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D220" s="4">
         <v>7095450</v>
@@ -4686,13 +4685,13 @@
     </row>
     <row r="221" spans="1:5" ht="16.5" customHeight="1">
       <c r="A221" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B221" s="2">
         <v>29</v>
       </c>
       <c r="C221" s="7" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D221" s="4">
         <v>5739081</v>
@@ -4704,13 +4703,13 @@
     </row>
     <row r="222" spans="1:5" ht="16.5" customHeight="1">
       <c r="A222" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B222" s="2">
         <v>30</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D222" s="4">
         <v>5561285</v>
@@ -4722,13 +4721,13 @@
     </row>
     <row r="223" spans="1:5" ht="16.5" customHeight="1">
       <c r="A223" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B223" s="2">
         <v>31</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D223" s="4">
         <v>5434650</v>
@@ -4740,13 +4739,13 @@
     </row>
     <row r="224" spans="1:5" ht="16.5" customHeight="1">
       <c r="A224" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B224" s="2">
         <v>32</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D224" s="4">
         <v>5171951</v>
@@ -4758,13 +4757,13 @@
     </row>
     <row r="225" spans="1:5" ht="16.5" customHeight="1">
       <c r="A225" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B225" s="2">
         <v>33</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D225" s="4">
         <v>5091005</v>
@@ -4776,13 +4775,13 @@
     </row>
     <row r="226" spans="1:5" ht="16.5" customHeight="1">
       <c r="A226" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B226" s="2">
         <v>34</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D226" s="4">
         <v>5016847</v>
@@ -4794,7 +4793,7 @@
     </row>
     <row r="227" spans="1:5" ht="16.5" customHeight="1">
       <c r="A227" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B227" s="2">
         <v>35</v>
@@ -4812,13 +4811,13 @@
     </row>
     <row r="228" spans="1:5" ht="16.5" customHeight="1">
       <c r="A228" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B228" s="2">
         <v>36</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D228" s="4">
         <v>4537987</v>
@@ -4830,13 +4829,13 @@
     </row>
     <row r="229" spans="1:5" ht="16.5" customHeight="1">
       <c r="A229" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B229" s="2">
         <v>37</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D229" s="4">
         <v>4444305</v>
@@ -4848,13 +4847,13 @@
     </row>
     <row r="230" spans="1:5" ht="16.5" customHeight="1">
       <c r="A230" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B230" s="2">
         <v>38</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D230" s="4">
         <v>4393558</v>
@@ -4866,13 +4865,13 @@
     </row>
     <row r="231" spans="1:5" ht="16.5" customHeight="1">
       <c r="A231" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B231" s="2">
         <v>39</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D231" s="4">
         <v>4361685</v>
@@ -4884,13 +4883,13 @@
     </row>
     <row r="232" spans="1:5" ht="16.5" customHeight="1">
       <c r="A232" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B232" s="2">
         <v>40</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D232" s="4">
         <v>4314000</v>
@@ -4902,13 +4901,13 @@
     </row>
     <row r="233" spans="1:5" ht="16.5" customHeight="1">
       <c r="A233" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B233" s="2">
         <v>41</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D233" s="4">
         <v>4305372</v>
@@ -4920,13 +4919,13 @@
     </row>
     <row r="234" spans="1:5" ht="16.5" customHeight="1">
       <c r="A234" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B234" s="2">
         <v>42</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D234" s="4">
         <v>4250088</v>
@@ -4938,13 +4937,13 @@
     </row>
     <row r="235" spans="1:5" ht="16.5" customHeight="1">
       <c r="A235" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B235" s="2">
         <v>43</v>
       </c>
       <c r="C235" s="7" t="s">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="D235" s="4">
         <v>4174414</v>
@@ -4956,13 +4955,13 @@
     </row>
     <row r="236" spans="1:5" ht="16.5" customHeight="1">
       <c r="A236" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B236" s="2">
         <v>44</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D236" s="4">
         <v>4151246</v>
@@ -4974,13 +4973,13 @@
     </row>
     <row r="237" spans="1:5" ht="16.5" customHeight="1">
       <c r="A237" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B237" s="2">
         <v>45</v>
       </c>
       <c r="C237" s="7" t="s">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="D237" s="4">
         <v>4081096</v>
@@ -4992,13 +4991,13 @@
     </row>
     <row r="238" spans="1:5" ht="16.5" customHeight="1">
       <c r="A238" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B238" s="2">
         <v>46</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D238" s="4">
         <v>4033323</v>
@@ -5010,7 +5009,7 @@
     </row>
     <row r="239" spans="1:5" ht="16.5" customHeight="1">
       <c r="A239" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B239" s="2">
         <v>47</v>
@@ -5028,13 +5027,13 @@
     </row>
     <row r="240" spans="1:5" ht="16.5" customHeight="1">
       <c r="A240" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B240" s="2">
         <v>48</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D240" s="4">
         <v>4000500</v>
@@ -5046,13 +5045,13 @@
     </row>
     <row r="241" spans="1:5" ht="16.5" customHeight="1">
       <c r="A241" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B241" s="2">
         <v>49</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D241" s="4">
         <v>3893926</v>
@@ -5064,13 +5063,13 @@
     </row>
     <row r="242" spans="1:5" ht="16.5" customHeight="1">
       <c r="A242" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B242" s="2">
         <v>50</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D242" s="4">
         <v>3892915</v>
@@ -5082,13 +5081,13 @@
     </row>
     <row r="243" spans="1:5" ht="16.5" customHeight="1">
       <c r="A243" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B243" s="2">
         <v>51</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D243" s="4">
         <v>3817624</v>
@@ -5100,13 +5099,13 @@
     </row>
     <row r="244" spans="1:5" ht="16.5" customHeight="1">
       <c r="A244" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B244" s="2">
         <v>52</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D244" s="4">
         <v>3776295</v>
@@ -5118,7 +5117,7 @@
     </row>
     <row r="245" spans="1:5" ht="16.5" customHeight="1">
       <c r="A245" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B245" s="2">
         <v>53</v>
@@ -5136,13 +5135,13 @@
     </row>
     <row r="246" spans="1:5" ht="16.5" customHeight="1">
       <c r="A246" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B246" s="2">
         <v>54</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D246" s="4">
         <v>3620200</v>
@@ -5154,13 +5153,13 @@
     </row>
     <row r="247" spans="1:5" ht="16.5" customHeight="1">
       <c r="A247" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B247" s="2">
         <v>55</v>
       </c>
       <c r="C247" s="7" t="s">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="D247" s="4">
         <v>3414335</v>
@@ -5172,13 +5171,13 @@
     </row>
     <row r="248" spans="1:5" ht="16.5" customHeight="1">
       <c r="A248" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B248" s="2">
         <v>56</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D248" s="4">
         <v>3164754</v>
@@ -5190,13 +5189,13 @@
     </row>
     <row r="249" spans="1:5" ht="16.5" customHeight="1">
       <c r="A249" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B249" s="2">
         <v>57</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D249" s="4">
         <v>3063699</v>
@@ -5208,13 +5207,13 @@
     </row>
     <row r="250" spans="1:5" ht="16.5" customHeight="1">
       <c r="A250" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B250" s="2">
         <v>58</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D250" s="4">
         <v>2777032</v>
@@ -5226,13 +5225,13 @@
     </row>
     <row r="251" spans="1:5" ht="16.5" customHeight="1">
       <c r="A251" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B251" s="2">
         <v>59</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D251" s="4">
         <v>2391014</v>
@@ -5244,13 +5243,13 @@
     </row>
     <row r="252" spans="1:5" ht="16.5" customHeight="1">
       <c r="A252" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B252" s="2">
         <v>60</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D252" s="4">
         <v>2371425</v>
@@ -5262,13 +5261,13 @@
     </row>
     <row r="253" spans="1:5" ht="16.5" customHeight="1">
       <c r="A253" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B253" s="2">
         <v>61</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D253" s="4">
         <v>2022500</v>
@@ -5280,13 +5279,13 @@
     </row>
     <row r="254" spans="1:5" ht="16.5" customHeight="1">
       <c r="A254" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B254" s="2">
         <v>62</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D254" s="4">
         <v>1764375</v>
@@ -5298,13 +5297,13 @@
     </row>
     <row r="255" spans="1:5" ht="16.5" customHeight="1">
       <c r="A255" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B255" s="2">
         <v>63</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D255" s="4">
         <v>1739773</v>
@@ -5316,13 +5315,13 @@
     </row>
     <row r="256" spans="1:5" ht="16.5" customHeight="1">
       <c r="A256" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B256" s="2">
         <v>64</v>
       </c>
-      <c r="C256" s="3" t="s">
-        <v>66</v>
+      <c r="C256" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="D256" s="4">
         <v>1685105</v>
@@ -5334,7 +5333,7 @@
     </row>
     <row r="257" spans="1:5" ht="16.5" customHeight="1">
       <c r="A257" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B257" s="2">
         <v>65</v>
@@ -5352,13 +5351,13 @@
     </row>
     <row r="258" spans="1:5" ht="16.5" customHeight="1">
       <c r="A258" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B258" s="2">
         <v>66</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D258" s="4">
         <v>1116967</v>
@@ -5370,13 +5369,13 @@
     </row>
     <row r="259" spans="1:5" ht="16.5" customHeight="1">
       <c r="A259" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B259" s="2">
         <v>67</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D259" s="4">
         <v>481250</v>
@@ -5388,13 +5387,13 @@
     </row>
     <row r="260" spans="1:5" ht="16.5" customHeight="1">
       <c r="A260" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B260" s="2">
         <v>68</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D260" s="4">
         <v>368750</v>
@@ -5406,13 +5405,13 @@
     </row>
     <row r="261" spans="1:5" ht="16.5" customHeight="1">
       <c r="A261" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B261" s="2">
         <v>1</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D261" s="4">
         <v>32997950</v>
@@ -5424,13 +5423,13 @@
     </row>
     <row r="262" spans="1:5" ht="16.5" customHeight="1">
       <c r="A262" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B262" s="2">
         <v>2</v>
       </c>
       <c r="C262" s="7" t="s">
-        <v>119</v>
+        <v>33</v>
       </c>
       <c r="D262" s="4">
         <v>15520250</v>
@@ -5442,7 +5441,7 @@
     </row>
     <row r="263" spans="1:5" ht="16.5" customHeight="1">
       <c r="A263" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B263" s="2">
         <v>3</v>
@@ -5460,13 +5459,13 @@
     </row>
     <row r="264" spans="1:5" ht="16.5" customHeight="1">
       <c r="A264" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B264" s="2">
         <v>4</v>
       </c>
       <c r="C264" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D264" s="4">
         <v>12803400</v>
@@ -5478,13 +5477,13 @@
     </row>
     <row r="265" spans="1:5" ht="16.5" customHeight="1">
       <c r="A265" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B265" s="2">
         <v>5</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D265" s="4">
         <v>11730150</v>
@@ -5496,7 +5495,7 @@
     </row>
     <row r="266" spans="1:5" ht="16.5" customHeight="1">
       <c r="A266" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B266" s="2">
         <v>6</v>
@@ -5514,13 +5513,13 @@
     </row>
     <row r="267" spans="1:5" ht="16.5" customHeight="1">
       <c r="A267" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B267" s="2">
         <v>7</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D267" s="4">
         <v>10310343</v>
@@ -5532,13 +5531,13 @@
     </row>
     <row r="268" spans="1:5" ht="16.5" customHeight="1">
       <c r="A268" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B268" s="2">
         <v>8</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D268" s="4">
         <v>9826000</v>
@@ -5550,13 +5549,13 @@
     </row>
     <row r="269" spans="1:5" ht="16.5" customHeight="1">
       <c r="A269" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B269" s="2">
         <v>9</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D269" s="4">
         <v>9783249</v>
@@ -5568,13 +5567,13 @@
     </row>
     <row r="270" spans="1:5" ht="16.5" customHeight="1">
       <c r="A270" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B270" s="2">
         <v>10</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D270" s="4">
         <v>9196550</v>
@@ -5586,7 +5585,7 @@
     </row>
     <row r="271" spans="1:5" ht="16.5" customHeight="1">
       <c r="A271" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B271" s="2">
         <v>11</v>
@@ -5604,13 +5603,13 @@
     </row>
     <row r="272" spans="1:5" ht="16.5" customHeight="1">
       <c r="A272" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B272" s="2">
         <v>12</v>
       </c>
       <c r="C272" s="7" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="D272" s="4">
         <v>8990350</v>
@@ -5622,13 +5621,13 @@
     </row>
     <row r="273" spans="1:5" ht="16.5" customHeight="1">
       <c r="A273" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B273" s="2">
         <v>13</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D273" s="4">
         <v>8798439</v>
@@ -5640,13 +5639,13 @@
     </row>
     <row r="274" spans="1:5" ht="16.5" customHeight="1">
       <c r="A274" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B274" s="2">
         <v>14</v>
       </c>
       <c r="C274" s="7" t="s">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="D274" s="4">
         <v>8797500</v>
@@ -5658,13 +5657,13 @@
     </row>
     <row r="275" spans="1:5" ht="16.5" customHeight="1">
       <c r="A275" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B275" s="2">
         <v>15</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D275" s="4">
         <v>8702111</v>
@@ -5676,7 +5675,7 @@
     </row>
     <row r="276" spans="1:5" ht="16.5" customHeight="1">
       <c r="A276" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B276" s="2">
         <v>16</v>
@@ -5694,7 +5693,7 @@
     </row>
     <row r="277" spans="1:5" ht="16.5" customHeight="1">
       <c r="A277" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B277" s="2">
         <v>17</v>
@@ -5712,13 +5711,13 @@
     </row>
     <row r="278" spans="1:5" ht="16.5" customHeight="1">
       <c r="A278" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B278" s="2">
         <v>18</v>
       </c>
       <c r="C278" s="7" t="s">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="D278" s="4">
         <v>8525490</v>
@@ -5730,13 +5729,13 @@
     </row>
     <row r="279" spans="1:5" ht="16.5" customHeight="1">
       <c r="A279" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B279" s="2">
         <v>19</v>
       </c>
       <c r="C279" s="7" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="D279" s="4">
         <v>8248525</v>
@@ -5748,13 +5747,13 @@
     </row>
     <row r="280" spans="1:5" ht="16.5" customHeight="1">
       <c r="A280" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B280" s="2">
         <v>20</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D280" s="4">
         <v>8177600</v>
@@ -5766,7 +5765,7 @@
     </row>
     <row r="281" spans="1:5" ht="16.5" customHeight="1">
       <c r="A281" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B281" s="2">
         <v>21</v>
@@ -5784,13 +5783,13 @@
     </row>
     <row r="282" spans="1:5" ht="16.5" customHeight="1">
       <c r="A282" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B282" s="2">
         <v>22</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D282" s="4">
         <v>8051401</v>
@@ -5802,13 +5801,13 @@
     </row>
     <row r="283" spans="1:5" ht="16.5" customHeight="1">
       <c r="A283" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B283" s="2">
         <v>23</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D283" s="4">
         <v>7776950</v>
@@ -5820,7 +5819,7 @@
     </row>
     <row r="284" spans="1:5" ht="16.5" customHeight="1">
       <c r="A284" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B284" s="2">
         <v>24</v>
@@ -5838,7 +5837,7 @@
     </row>
     <row r="285" spans="1:5" ht="16.5" customHeight="1">
       <c r="A285" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B285" s="2">
         <v>25</v>
@@ -5856,13 +5855,13 @@
     </row>
     <row r="286" spans="1:5" ht="16.5" customHeight="1">
       <c r="A286" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B286" s="2">
         <v>26</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D286" s="4">
         <v>7645595</v>
@@ -5874,7 +5873,7 @@
     </row>
     <row r="287" spans="1:5" ht="16.5" customHeight="1">
       <c r="A287" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B287" s="2">
         <v>27</v>
@@ -5892,7 +5891,7 @@
     </row>
     <row r="288" spans="1:5" ht="16.5" customHeight="1">
       <c r="A288" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B288" s="2">
         <v>28</v>
@@ -5910,13 +5909,13 @@
     </row>
     <row r="289" spans="1:5" ht="16.5" customHeight="1">
       <c r="A289" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B289" s="2">
         <v>29</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D289" s="4">
         <v>7511676</v>
@@ -5928,7 +5927,7 @@
     </row>
     <row r="290" spans="1:5" ht="16.5" customHeight="1">
       <c r="A290" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B290" s="2">
         <v>30</v>
@@ -5946,13 +5945,13 @@
     </row>
     <row r="291" spans="1:5" ht="16.5" customHeight="1">
       <c r="A291" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B291" s="2">
         <v>31</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D291" s="4">
         <v>7435700</v>
@@ -5964,13 +5963,13 @@
     </row>
     <row r="292" spans="1:5" ht="16.5" customHeight="1">
       <c r="A292" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B292" s="2">
         <v>32</v>
       </c>
       <c r="C292" s="6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D292" s="4">
         <v>7331000</v>
@@ -5982,13 +5981,13 @@
     </row>
     <row r="293" spans="1:5" ht="16.5" customHeight="1">
       <c r="A293" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B293" s="2">
         <v>33</v>
       </c>
       <c r="C293" s="7" t="s">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="D293" s="4">
         <v>7321924</v>
@@ -6000,13 +5999,13 @@
     </row>
     <row r="294" spans="1:5" ht="16.5" customHeight="1">
       <c r="A294" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B294" s="2">
         <v>34</v>
       </c>
       <c r="C294" s="7" t="s">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="D294" s="4">
         <v>7318696</v>
@@ -6018,7 +6017,7 @@
     </row>
     <row r="295" spans="1:5" ht="16.5" customHeight="1">
       <c r="A295" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B295" s="2">
         <v>35</v>
@@ -6036,13 +6035,13 @@
     </row>
     <row r="296" spans="1:5" ht="16.5" customHeight="1">
       <c r="A296" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B296" s="2">
         <v>36</v>
       </c>
       <c r="C296" s="6" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D296" s="4">
         <v>7216687</v>
@@ -6054,13 +6053,13 @@
     </row>
     <row r="297" spans="1:5" ht="16.5" customHeight="1">
       <c r="A297" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B297" s="2">
         <v>37</v>
       </c>
       <c r="C297" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D297" s="4">
         <v>6356548</v>
@@ -6072,13 +6071,13 @@
     </row>
     <row r="298" spans="1:5" ht="16.5" customHeight="1">
       <c r="A298" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B298" s="2">
         <v>38</v>
       </c>
       <c r="C298" s="6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D298" s="4">
         <v>6347447</v>
@@ -6090,13 +6089,13 @@
     </row>
     <row r="299" spans="1:5" ht="16.5" customHeight="1">
       <c r="A299" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B299" s="2">
         <v>39</v>
       </c>
       <c r="C299" s="7" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D299" s="4">
         <v>5960246</v>
@@ -6108,13 +6107,13 @@
     </row>
     <row r="300" spans="1:5" ht="16.5" customHeight="1">
       <c r="A300" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B300" s="2">
         <v>40</v>
       </c>
       <c r="C300" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D300" s="4">
         <v>5879538</v>
@@ -6126,7 +6125,7 @@
     </row>
     <row r="301" spans="1:5" ht="16.5" customHeight="1">
       <c r="A301" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B301" s="2">
         <v>41</v>
@@ -6144,13 +6143,13 @@
     </row>
     <row r="302" spans="1:5" ht="16.5" customHeight="1">
       <c r="A302" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B302" s="2">
         <v>42</v>
       </c>
       <c r="C302" s="6" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D302" s="4">
         <v>5376985</v>
@@ -6162,13 +6161,13 @@
     </row>
     <row r="303" spans="1:5" ht="16.5" customHeight="1">
       <c r="A303" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B303" s="2">
         <v>43</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D303" s="4">
         <v>5159999</v>
@@ -6180,13 +6179,13 @@
     </row>
     <row r="304" spans="1:5" ht="16.5" customHeight="1">
       <c r="A304" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B304" s="2">
         <v>44</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D304" s="4">
         <v>4816595</v>
@@ -6198,13 +6197,13 @@
     </row>
     <row r="305" spans="1:5" ht="16.5" customHeight="1">
       <c r="A305" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B305" s="2">
         <v>45</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D305" s="4">
         <v>4538649</v>
@@ -6216,13 +6215,13 @@
     </row>
     <row r="306" spans="1:5" ht="16.5" customHeight="1">
       <c r="A306" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B306" s="2">
         <v>46</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D306" s="4">
         <v>4493569</v>
@@ -6234,13 +6233,13 @@
     </row>
     <row r="307" spans="1:5" ht="16.5" customHeight="1">
       <c r="A307" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B307" s="2">
         <v>47</v>
       </c>
       <c r="C307" s="6" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D307" s="4">
         <v>4473170</v>
@@ -6252,13 +6251,13 @@
     </row>
     <row r="308" spans="1:5" ht="16.5" customHeight="1">
       <c r="A308" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B308" s="2">
         <v>48</v>
       </c>
       <c r="C308" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D308" s="4">
         <v>4398940</v>
@@ -6270,13 +6269,13 @@
     </row>
     <row r="309" spans="1:5" ht="16.5" customHeight="1">
       <c r="A309" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B309" s="2">
         <v>49</v>
       </c>
       <c r="C309" s="6" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D309" s="4">
         <v>4263500</v>
@@ -6288,13 +6287,13 @@
     </row>
     <row r="310" spans="1:5" ht="16.5" customHeight="1">
       <c r="A310" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B310" s="2">
         <v>50</v>
       </c>
       <c r="C310" s="7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D310" s="4">
         <v>4186720</v>
@@ -6306,13 +6305,13 @@
     </row>
     <row r="311" spans="1:5" ht="16.5" customHeight="1">
       <c r="A311" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B311" s="2">
         <v>51</v>
       </c>
       <c r="C311" s="6" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D311" s="4">
         <v>4155232</v>
@@ -6324,13 +6323,13 @@
     </row>
     <row r="312" spans="1:5" ht="16.5" customHeight="1">
       <c r="A312" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B312" s="2">
         <v>52</v>
       </c>
       <c r="C312" s="6" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D312" s="4">
         <v>4148173</v>
@@ -6342,13 +6341,13 @@
     </row>
     <row r="313" spans="1:5" ht="16.5" customHeight="1">
       <c r="A313" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B313" s="2">
         <v>53</v>
       </c>
       <c r="C313" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D313" s="4">
         <v>3953623</v>
@@ -6360,13 +6359,13 @@
     </row>
     <row r="314" spans="1:5" ht="16.5" customHeight="1">
       <c r="A314" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B314" s="2">
         <v>54</v>
       </c>
       <c r="C314" s="6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D314" s="4">
         <v>3841825</v>
@@ -6378,13 +6377,13 @@
     </row>
     <row r="315" spans="1:5" ht="16.5" customHeight="1">
       <c r="A315" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B315" s="2">
         <v>55</v>
       </c>
       <c r="C315" s="6" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D315" s="4">
         <v>3725748</v>
@@ -6396,13 +6395,13 @@
     </row>
     <row r="316" spans="1:5" ht="16.5" customHeight="1">
       <c r="A316" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B316" s="2">
         <v>56</v>
       </c>
       <c r="C316" s="6" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D316" s="4">
         <v>3668126</v>
@@ -6414,13 +6413,13 @@
     </row>
     <row r="317" spans="1:5" ht="16.5" customHeight="1">
       <c r="A317" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B317" s="2">
         <v>57</v>
       </c>
       <c r="C317" s="6" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D317" s="4">
         <v>3655552</v>
@@ -6432,13 +6431,13 @@
     </row>
     <row r="318" spans="1:5" ht="16.5" customHeight="1">
       <c r="A318" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B318" s="2">
         <v>58</v>
       </c>
       <c r="C318" s="6" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D318" s="4">
         <v>3643670</v>
@@ -6450,13 +6449,13 @@
     </row>
     <row r="319" spans="1:5" ht="16.5" customHeight="1">
       <c r="A319" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B319" s="2">
         <v>59</v>
       </c>
       <c r="C319" s="6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D319" s="4">
         <v>2973305</v>
@@ -6468,13 +6467,13 @@
     </row>
     <row r="320" spans="1:5" ht="16.5" customHeight="1">
       <c r="A320" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B320" s="2">
         <v>60</v>
       </c>
       <c r="C320" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D320" s="4">
         <v>2438490</v>
@@ -6486,13 +6485,13 @@
     </row>
     <row r="321" spans="1:5" ht="16.5" customHeight="1">
       <c r="A321" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B321" s="2">
         <v>61</v>
       </c>
       <c r="C321" s="6" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D321" s="4">
         <v>2379290</v>
@@ -6504,13 +6503,13 @@
     </row>
     <row r="322" spans="1:5" ht="16.5" customHeight="1">
       <c r="A322" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B322" s="2">
         <v>62</v>
       </c>
       <c r="C322" s="6" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D322" s="4">
         <v>2161578</v>
@@ -6522,13 +6521,13 @@
     </row>
     <row r="323" spans="1:5" ht="16.5" customHeight="1">
       <c r="A323" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B323" s="2">
         <v>63</v>
       </c>
       <c r="C323" s="6" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D323" s="4">
         <v>2130311</v>
@@ -6540,13 +6539,13 @@
     </row>
     <row r="324" spans="1:5" ht="16.5" customHeight="1">
       <c r="A324" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B324" s="2">
         <v>64</v>
       </c>
       <c r="C324" s="6" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D324" s="4">
         <v>1272950</v>
@@ -6558,13 +6557,13 @@
     </row>
     <row r="325" spans="1:5" ht="16.5" customHeight="1">
       <c r="A325" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B325" s="2">
         <v>65</v>
       </c>
       <c r="C325" s="6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D325" s="4">
         <v>1207378</v>
@@ -6576,13 +6575,13 @@
     </row>
     <row r="326" spans="1:5" ht="16.5" customHeight="1">
       <c r="A326" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B326" s="2">
         <v>66</v>
       </c>
-      <c r="C326" s="6" t="s">
-        <v>66</v>
+      <c r="C326" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="D326" s="4">
         <v>959773</v>
@@ -6594,13 +6593,13 @@
     </row>
     <row r="327" spans="1:5" ht="16.5" customHeight="1">
       <c r="A327" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B327" s="2">
         <v>67</v>
       </c>
       <c r="C327" s="6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D327" s="4">
         <v>276650</v>
@@ -6612,13 +6611,13 @@
     </row>
     <row r="328" spans="1:5">
       <c r="A328" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B328" s="9">
         <v>1</v>
       </c>
       <c r="C328" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D328" s="9">
         <v>51572469</v>
@@ -6630,13 +6629,13 @@
     </row>
     <row r="329" spans="1:5">
       <c r="A329" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B329" s="9">
         <v>2</v>
       </c>
       <c r="C329" s="8" t="s">
-        <v>119</v>
+        <v>33</v>
       </c>
       <c r="D329" s="9">
         <v>45927381</v>
@@ -6648,13 +6647,13 @@
     </row>
     <row r="330" spans="1:5">
       <c r="A330" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B330" s="9">
         <v>3</v>
       </c>
       <c r="C330" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D330" s="9">
         <v>44882553</v>
@@ -6666,7 +6665,7 @@
     </row>
     <row r="331" spans="1:5">
       <c r="A331" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B331" s="9">
         <v>4</v>
@@ -6684,7 +6683,7 @@
     </row>
     <row r="332" spans="1:5">
       <c r="A332" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B332" s="9">
         <v>5</v>
@@ -6702,7 +6701,7 @@
     </row>
     <row r="333" spans="1:5">
       <c r="A333" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B333" s="9">
         <v>6</v>
@@ -6720,13 +6719,13 @@
     </row>
     <row r="334" spans="1:5">
       <c r="A334" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B334" s="9">
         <v>7</v>
       </c>
       <c r="C334" s="8" t="s">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="D334" s="9">
         <v>29064577</v>
@@ -6738,13 +6737,13 @@
     </row>
     <row r="335" spans="1:5">
       <c r="A335" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B335" s="9">
         <v>8</v>
       </c>
       <c r="C335" s="8" t="s">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="D335" s="9">
         <v>28830256</v>
@@ -6756,13 +6755,13 @@
     </row>
     <row r="336" spans="1:5">
       <c r="A336" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B336" s="9">
         <v>9</v>
       </c>
       <c r="C336" s="8" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D336" s="9">
         <v>27963110</v>
@@ -6774,13 +6773,13 @@
     </row>
     <row r="337" spans="1:5">
       <c r="A337" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B337" s="9">
         <v>10</v>
       </c>
       <c r="C337" s="8" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D337" s="9">
         <v>27716398</v>
@@ -6792,13 +6791,13 @@
     </row>
     <row r="338" spans="1:5">
       <c r="A338" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B338" s="9">
         <v>11</v>
       </c>
       <c r="C338" s="8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D338" s="9">
         <v>27125102</v>
@@ -6810,7 +6809,7 @@
     </row>
     <row r="339" spans="1:5">
       <c r="A339" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B339" s="9">
         <v>12</v>
@@ -6828,7 +6827,7 @@
     </row>
     <row r="340" spans="1:5">
       <c r="A340" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B340" s="9">
         <v>13</v>
@@ -6846,13 +6845,13 @@
     </row>
     <row r="341" spans="1:5">
       <c r="A341" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B341" s="9">
         <v>14</v>
       </c>
       <c r="C341" s="8" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D341" s="9">
         <v>25275492</v>
@@ -6864,13 +6863,13 @@
     </row>
     <row r="342" spans="1:5">
       <c r="A342" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B342" s="9">
         <v>15</v>
       </c>
       <c r="C342" s="8" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D342" s="9">
         <v>24620930</v>
@@ -6882,7 +6881,7 @@
     </row>
     <row r="343" spans="1:5">
       <c r="A343" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B343" s="9">
         <v>16</v>
@@ -6900,13 +6899,13 @@
     </row>
     <row r="344" spans="1:5">
       <c r="A344" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B344" s="9">
         <v>17</v>
       </c>
       <c r="C344" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D344" s="9">
         <v>21605033</v>
@@ -6918,13 +6917,13 @@
     </row>
     <row r="345" spans="1:5">
       <c r="A345" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B345" s="9">
         <v>18</v>
       </c>
       <c r="C345" s="8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D345" s="9">
         <v>21478397</v>
@@ -6936,13 +6935,13 @@
     </row>
     <row r="346" spans="1:5">
       <c r="A346" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B346" s="9">
         <v>19</v>
       </c>
       <c r="C346" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D346" s="9">
         <v>21123578</v>
@@ -6954,13 +6953,13 @@
     </row>
     <row r="347" spans="1:5">
       <c r="A347" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B347" s="9">
         <v>20</v>
       </c>
       <c r="C347" s="8" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D347" s="9">
         <v>20055931</v>
@@ -6972,7 +6971,7 @@
     </row>
     <row r="348" spans="1:5">
       <c r="A348" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B348" s="9">
         <v>21</v>
@@ -6990,13 +6989,13 @@
     </row>
     <row r="349" spans="1:5">
       <c r="A349" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B349" s="9">
         <v>22</v>
       </c>
       <c r="C349" s="8" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="D349" s="9">
         <v>18197828</v>
@@ -7008,13 +7007,13 @@
     </row>
     <row r="350" spans="1:5">
       <c r="A350" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B350" s="9">
         <v>23</v>
       </c>
       <c r="C350" s="8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D350" s="9">
         <v>17545894</v>
@@ -7026,7 +7025,7 @@
     </row>
     <row r="351" spans="1:5">
       <c r="A351" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B351" s="9">
         <v>24</v>
@@ -7044,13 +7043,13 @@
     </row>
     <row r="352" spans="1:5">
       <c r="A352" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B352" s="9">
         <v>25</v>
       </c>
       <c r="C352" s="8" t="s">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="D352" s="9">
         <v>17095537</v>
@@ -7062,13 +7061,13 @@
     </row>
     <row r="353" spans="1:5">
       <c r="A353" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B353" s="9">
         <v>26</v>
       </c>
       <c r="C353" s="8" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D353" s="9">
         <v>16940645</v>
@@ -7080,13 +7079,13 @@
     </row>
     <row r="354" spans="1:5">
       <c r="A354" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B354" s="9">
         <v>27</v>
       </c>
       <c r="C354" s="8" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D354" s="9">
         <v>16625723</v>
@@ -7098,7 +7097,7 @@
     </row>
     <row r="355" spans="1:5">
       <c r="A355" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B355" s="9">
         <v>28</v>
@@ -7116,13 +7115,13 @@
     </row>
     <row r="356" spans="1:5">
       <c r="A356" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B356" s="9">
         <v>29</v>
       </c>
       <c r="C356" s="8" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="D356" s="9">
         <v>16374224</v>
@@ -7134,13 +7133,13 @@
     </row>
     <row r="357" spans="1:5">
       <c r="A357" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B357" s="9">
         <v>30</v>
       </c>
       <c r="C357" s="8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D357" s="9">
         <v>15989772</v>
@@ -7152,7 +7151,7 @@
     </row>
     <row r="358" spans="1:5">
       <c r="A358" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B358" s="9">
         <v>31</v>
@@ -7170,13 +7169,13 @@
     </row>
     <row r="359" spans="1:5">
       <c r="A359" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B359" s="9">
         <v>32</v>
       </c>
       <c r="C359" s="8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D359" s="9">
         <v>14388261</v>
@@ -7188,13 +7187,13 @@
     </row>
     <row r="360" spans="1:5">
       <c r="A360" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B360" s="9">
         <v>33</v>
       </c>
       <c r="C360" s="8" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D360" s="9">
         <v>14253593</v>
@@ -7206,13 +7205,13 @@
     </row>
     <row r="361" spans="1:5">
       <c r="A361" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B361" s="9">
         <v>34</v>
       </c>
       <c r="C361" s="8" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D361" s="9">
         <v>13903501</v>
@@ -7224,13 +7223,13 @@
     </row>
     <row r="362" spans="1:5">
       <c r="A362" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B362" s="9">
         <v>35</v>
       </c>
       <c r="C362" s="8" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D362" s="9">
         <v>13791347</v>
@@ -7242,13 +7241,13 @@
     </row>
     <row r="363" spans="1:5">
       <c r="A363" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B363" s="9">
         <v>36</v>
       </c>
       <c r="C363" s="8" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D363" s="9">
         <v>13310754</v>
@@ -7260,13 +7259,13 @@
     </row>
     <row r="364" spans="1:5">
       <c r="A364" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B364" s="9">
         <v>37</v>
       </c>
       <c r="C364" s="8" t="s">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="D364" s="9">
         <v>12684262</v>
@@ -7278,13 +7277,13 @@
     </row>
     <row r="365" spans="1:5">
       <c r="A365" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B365" s="9">
         <v>38</v>
       </c>
       <c r="C365" s="8" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D365" s="9">
         <v>12215462</v>
@@ -7296,13 +7295,13 @@
     </row>
     <row r="366" spans="1:5">
       <c r="A366" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B366" s="9">
         <v>39</v>
       </c>
       <c r="C366" s="8" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D366" s="9">
         <v>11325863</v>
@@ -7314,13 +7313,13 @@
     </row>
     <row r="367" spans="1:5">
       <c r="A367" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B367" s="9">
         <v>40</v>
       </c>
       <c r="C367" s="8" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D367" s="9">
         <v>10130369</v>
@@ -7332,13 +7331,13 @@
     </row>
     <row r="368" spans="1:5">
       <c r="A368" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B368" s="9">
         <v>41</v>
       </c>
       <c r="C368" s="8" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D368" s="9">
         <v>10079600</v>
@@ -7350,13 +7349,13 @@
     </row>
     <row r="369" spans="1:5">
       <c r="A369" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B369" s="9">
         <v>42</v>
       </c>
       <c r="C369" s="8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D369" s="9">
         <v>9578558</v>
@@ -7368,13 +7367,13 @@
     </row>
     <row r="370" spans="1:5">
       <c r="A370" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B370" s="9">
         <v>43</v>
       </c>
       <c r="C370" s="8" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D370" s="9">
         <v>9480264</v>
@@ -7386,13 +7385,13 @@
     </row>
     <row r="371" spans="1:5">
       <c r="A371" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B371" s="9">
         <v>44</v>
       </c>
       <c r="C371" s="8" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D371" s="9">
         <v>9389063</v>
@@ -7404,13 +7403,13 @@
     </row>
     <row r="372" spans="1:5">
       <c r="A372" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B372" s="9">
         <v>45</v>
       </c>
       <c r="C372" s="8" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D372" s="9">
         <v>9257137</v>
@@ -7422,13 +7421,13 @@
     </row>
     <row r="373" spans="1:5">
       <c r="A373" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B373" s="9">
         <v>46</v>
       </c>
       <c r="C373" s="8" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D373" s="9">
         <v>9172250</v>
@@ -7440,7 +7439,7 @@
     </row>
     <row r="374" spans="1:5">
       <c r="A374" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B374" s="9">
         <v>47</v>
@@ -7458,13 +7457,13 @@
     </row>
     <row r="375" spans="1:5">
       <c r="A375" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B375" s="9">
         <v>48</v>
       </c>
       <c r="C375" s="8" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D375" s="9">
         <v>8482806</v>
@@ -7476,13 +7475,13 @@
     </row>
     <row r="376" spans="1:5">
       <c r="A376" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B376" s="9">
         <v>49</v>
       </c>
       <c r="C376" s="8" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D376" s="9">
         <v>8449715</v>
@@ -7494,13 +7493,13 @@
     </row>
     <row r="377" spans="1:5">
       <c r="A377" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B377" s="9">
         <v>50</v>
       </c>
       <c r="C377" s="8" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D377" s="9">
         <v>8167774</v>
@@ -7512,13 +7511,13 @@
     </row>
     <row r="378" spans="1:5">
       <c r="A378" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B378" s="9">
         <v>51</v>
       </c>
       <c r="C378" s="8" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D378" s="9">
         <v>7379637</v>
@@ -7530,13 +7529,13 @@
     </row>
     <row r="379" spans="1:5">
       <c r="A379" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B379" s="9">
         <v>52</v>
       </c>
       <c r="C379" s="8" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D379" s="9">
         <v>7351478</v>
@@ -7548,7 +7547,7 @@
     </row>
     <row r="380" spans="1:5">
       <c r="A380" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B380" s="9">
         <v>53</v>
@@ -7566,13 +7565,13 @@
     </row>
     <row r="381" spans="1:5">
       <c r="A381" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B381" s="9">
         <v>54</v>
       </c>
       <c r="C381" s="8" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D381" s="9">
         <v>6032072</v>
@@ -7584,13 +7583,13 @@
     </row>
     <row r="382" spans="1:5">
       <c r="A382" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B382" s="9">
         <v>55</v>
       </c>
       <c r="C382" s="8" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D382" s="9">
         <v>5593709</v>
@@ -7602,13 +7601,13 @@
     </row>
     <row r="383" spans="1:5">
       <c r="A383" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B383" s="9">
         <v>56</v>
       </c>
       <c r="C383" s="8" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D383" s="9">
         <v>4942793</v>
@@ -7620,13 +7619,13 @@
     </row>
     <row r="384" spans="1:5">
       <c r="A384" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B384" s="9">
         <v>57</v>
       </c>
       <c r="C384" s="8" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D384" s="9">
         <v>4587543</v>
@@ -7638,13 +7637,13 @@
     </row>
     <row r="385" spans="1:5">
       <c r="A385" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B385" s="9">
         <v>58</v>
       </c>
       <c r="C385" s="8" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D385" s="9">
         <v>4012455</v>
@@ -7656,13 +7655,13 @@
     </row>
     <row r="386" spans="1:5">
       <c r="A386" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B386" s="9">
         <v>59</v>
       </c>
       <c r="C386" s="8" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D386" s="9">
         <v>3613479</v>
@@ -7674,13 +7673,13 @@
     </row>
     <row r="387" spans="1:5">
       <c r="A387" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B387" s="9">
         <v>60</v>
       </c>
       <c r="C387" s="8" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D387" s="9">
         <v>2363818</v>
@@ -7692,13 +7691,13 @@
     </row>
     <row r="388" spans="1:5">
       <c r="A388" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B388" s="9">
         <v>61</v>
       </c>
       <c r="C388" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D388" s="9">
         <v>2307050</v>
@@ -7710,13 +7709,13 @@
     </row>
     <row r="389" spans="1:5">
       <c r="A389" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B389" s="9">
         <v>62</v>
       </c>
       <c r="C389" s="8" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="D389" s="9">
         <v>2215136</v>
@@ -7728,13 +7727,13 @@
     </row>
     <row r="390" spans="1:5">
       <c r="A390" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B390" s="9">
         <v>63</v>
       </c>
       <c r="C390" s="8" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D390" s="9">
         <v>2185908</v>
@@ -7746,13 +7745,13 @@
     </row>
     <row r="391" spans="1:5">
       <c r="A391" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B391" s="9">
         <v>64</v>
       </c>
       <c r="C391" s="8" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D391" s="9">
         <v>1109775</v>
@@ -7764,13 +7763,13 @@
     </row>
     <row r="392" spans="1:5">
       <c r="A392" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B392" s="9">
         <v>65</v>
       </c>
       <c r="C392" s="8" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D392" s="9">
         <v>999218</v>
@@ -7782,13 +7781,13 @@
     </row>
     <row r="393" spans="1:5">
       <c r="A393" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B393" s="9">
         <v>66</v>
       </c>
       <c r="C393" s="8" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D393" s="9">
         <v>845000</v>
@@ -7800,13 +7799,13 @@
     </row>
     <row r="394" spans="1:5">
       <c r="A394" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B394" s="9">
         <v>67</v>
       </c>
       <c r="C394" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D394" s="9">
         <v>364314</v>
@@ -7814,6 +7813,1212 @@
       <c r="E394" s="5" t="str">
         <f>IF($D394="","",VLOOKUP($D394,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>3단계</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5">
+      <c r="A395" t="s">
+        <v>119</v>
+      </c>
+      <c r="B395" s="9">
+        <v>1</v>
+      </c>
+      <c r="C395" t="s">
+        <v>7</v>
+      </c>
+      <c r="D395" s="9">
+        <v>15645750</v>
+      </c>
+      <c r="E395" s="5" t="str">
+        <f>IF($D395="","",VLOOKUP($D395,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5">
+      <c r="A396" t="s">
+        <v>119</v>
+      </c>
+      <c r="B396" s="9">
+        <v>2</v>
+      </c>
+      <c r="C396" t="s">
+        <v>15</v>
+      </c>
+      <c r="D396" s="9">
+        <v>13978410</v>
+      </c>
+      <c r="E396" s="5" t="str">
+        <f>IF($D396="","",VLOOKUP($D396,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5">
+      <c r="A397" t="s">
+        <v>119</v>
+      </c>
+      <c r="B397" s="9">
+        <v>3</v>
+      </c>
+      <c r="C397" t="s">
+        <v>93</v>
+      </c>
+      <c r="D397" s="9">
+        <v>13088206</v>
+      </c>
+      <c r="E397" s="5" t="str">
+        <f>IF($D397="","",VLOOKUP($D397,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5">
+      <c r="A398" t="s">
+        <v>119</v>
+      </c>
+      <c r="B398" s="9">
+        <v>4</v>
+      </c>
+      <c r="C398" t="s">
+        <v>25</v>
+      </c>
+      <c r="D398" s="9">
+        <v>12744509</v>
+      </c>
+      <c r="E398" s="5" t="str">
+        <f>IF($D398="","",VLOOKUP($D398,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5">
+      <c r="A399" t="s">
+        <v>119</v>
+      </c>
+      <c r="B399" s="9">
+        <v>5</v>
+      </c>
+      <c r="C399" t="s">
+        <v>24</v>
+      </c>
+      <c r="D399" s="9">
+        <v>11777730</v>
+      </c>
+      <c r="E399" s="5" t="str">
+        <f>IF($D399="","",VLOOKUP($D399,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5">
+      <c r="A400" t="s">
+        <v>119</v>
+      </c>
+      <c r="B400" s="9">
+        <v>6</v>
+      </c>
+      <c r="C400" t="s">
+        <v>81</v>
+      </c>
+      <c r="D400" s="9">
+        <v>11191350</v>
+      </c>
+      <c r="E400" s="5" t="str">
+        <f>IF($D400="","",VLOOKUP($D400,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5">
+      <c r="A401" t="s">
+        <v>119</v>
+      </c>
+      <c r="B401" s="9">
+        <v>7</v>
+      </c>
+      <c r="C401" t="s">
+        <v>33</v>
+      </c>
+      <c r="D401" s="9">
+        <v>10909500</v>
+      </c>
+      <c r="E401" s="5" t="str">
+        <f>IF($D401="","",VLOOKUP($D401,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5">
+      <c r="A402" t="s">
+        <v>119</v>
+      </c>
+      <c r="B402" s="9">
+        <v>8</v>
+      </c>
+      <c r="C402" t="s">
+        <v>86</v>
+      </c>
+      <c r="D402" s="9">
+        <v>10720108</v>
+      </c>
+      <c r="E402" s="5" t="str">
+        <f>IF($D402="","",VLOOKUP($D402,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5">
+      <c r="A403" t="s">
+        <v>119</v>
+      </c>
+      <c r="B403" s="9">
+        <v>9</v>
+      </c>
+      <c r="C403" t="s">
+        <v>102</v>
+      </c>
+      <c r="D403" s="9">
+        <v>10500995</v>
+      </c>
+      <c r="E403" s="5" t="str">
+        <f>IF($D403="","",VLOOKUP($D403,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5">
+      <c r="A404" t="s">
+        <v>119</v>
+      </c>
+      <c r="B404" s="9">
+        <v>10</v>
+      </c>
+      <c r="C404" t="s">
+        <v>19</v>
+      </c>
+      <c r="D404" s="9">
+        <v>10489590</v>
+      </c>
+      <c r="E404" s="5" t="str">
+        <f>IF($D404="","",VLOOKUP($D404,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5">
+      <c r="A405" t="s">
+        <v>119</v>
+      </c>
+      <c r="B405" s="9">
+        <v>11</v>
+      </c>
+      <c r="C405" t="s">
+        <v>14</v>
+      </c>
+      <c r="D405" s="9">
+        <v>10320090</v>
+      </c>
+      <c r="E405" s="5" t="str">
+        <f>IF($D405="","",VLOOKUP($D405,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5">
+      <c r="A406" t="s">
+        <v>119</v>
+      </c>
+      <c r="B406" s="9">
+        <v>12</v>
+      </c>
+      <c r="C406" t="s">
+        <v>94</v>
+      </c>
+      <c r="D406" s="9">
+        <v>9391223</v>
+      </c>
+      <c r="E406" s="5" t="str">
+        <f>IF($D406="","",VLOOKUP($D406,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5">
+      <c r="A407" t="s">
+        <v>119</v>
+      </c>
+      <c r="B407" s="9">
+        <v>13</v>
+      </c>
+      <c r="C407" t="s">
+        <v>11</v>
+      </c>
+      <c r="D407" s="9">
+        <v>9042210</v>
+      </c>
+      <c r="E407" s="5" t="str">
+        <f>IF($D407="","",VLOOKUP($D407,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5">
+      <c r="A408" t="s">
+        <v>119</v>
+      </c>
+      <c r="B408" s="9">
+        <v>14</v>
+      </c>
+      <c r="C408" t="s">
+        <v>98</v>
+      </c>
+      <c r="D408" s="9">
+        <v>8691306</v>
+      </c>
+      <c r="E408" s="5" t="str">
+        <f>IF($D408="","",VLOOKUP($D408,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5">
+      <c r="A409" t="s">
+        <v>119</v>
+      </c>
+      <c r="B409" s="9">
+        <v>15</v>
+      </c>
+      <c r="C409" t="s">
+        <v>22</v>
+      </c>
+      <c r="D409" s="9">
+        <v>8350410</v>
+      </c>
+      <c r="E409" s="5" t="str">
+        <f>IF($D409="","",VLOOKUP($D409,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5">
+      <c r="A410" t="s">
+        <v>119</v>
+      </c>
+      <c r="B410" s="9">
+        <v>16</v>
+      </c>
+      <c r="C410" t="s">
+        <v>34</v>
+      </c>
+      <c r="D410" s="9">
+        <v>8286570</v>
+      </c>
+      <c r="E410" s="5" t="str">
+        <f>IF($D410="","",VLOOKUP($D410,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5">
+      <c r="A411" t="s">
+        <v>119</v>
+      </c>
+      <c r="B411" s="9">
+        <v>17</v>
+      </c>
+      <c r="C411" t="s">
+        <v>43</v>
+      </c>
+      <c r="D411" s="9">
+        <v>8219625</v>
+      </c>
+      <c r="E411" s="5" t="str">
+        <f>IF($D411="","",VLOOKUP($D411,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5">
+      <c r="A412" t="s">
+        <v>119</v>
+      </c>
+      <c r="B412" s="9">
+        <v>18</v>
+      </c>
+      <c r="C412" t="s">
+        <v>45</v>
+      </c>
+      <c r="D412" s="9">
+        <v>8111520</v>
+      </c>
+      <c r="E412" s="5" t="str">
+        <f>IF($D412="","",VLOOKUP($D412,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5">
+      <c r="A413" t="s">
+        <v>119</v>
+      </c>
+      <c r="B413" s="9">
+        <v>19</v>
+      </c>
+      <c r="C413" t="s">
+        <v>85</v>
+      </c>
+      <c r="D413" s="9">
+        <v>8105430</v>
+      </c>
+      <c r="E413" s="5" t="str">
+        <f>IF($D413="","",VLOOKUP($D413,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5">
+      <c r="A414" t="s">
+        <v>119</v>
+      </c>
+      <c r="B414" s="9">
+        <v>20</v>
+      </c>
+      <c r="C414" t="s">
+        <v>88</v>
+      </c>
+      <c r="D414" s="9">
+        <v>7975410</v>
+      </c>
+      <c r="E414" s="5" t="str">
+        <f>IF($D414="","",VLOOKUP($D414,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5">
+      <c r="A415" t="s">
+        <v>119</v>
+      </c>
+      <c r="B415" s="9">
+        <v>21</v>
+      </c>
+      <c r="C415" t="s">
+        <v>27</v>
+      </c>
+      <c r="D415" s="9">
+        <v>7852200</v>
+      </c>
+      <c r="E415" s="5" t="str">
+        <f>IF($D415="","",VLOOKUP($D415,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5">
+      <c r="A416" t="s">
+        <v>119</v>
+      </c>
+      <c r="B416" s="9">
+        <v>22</v>
+      </c>
+      <c r="C416" t="s">
+        <v>82</v>
+      </c>
+      <c r="D416" s="9">
+        <v>7715220</v>
+      </c>
+      <c r="E416" s="5" t="str">
+        <f>IF($D416="","",VLOOKUP($D416,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5">
+      <c r="A417" t="s">
+        <v>119</v>
+      </c>
+      <c r="B417" s="9">
+        <v>23</v>
+      </c>
+      <c r="C417" t="s">
+        <v>21</v>
+      </c>
+      <c r="D417" s="9">
+        <v>7610714</v>
+      </c>
+      <c r="E417" s="5" t="str">
+        <f>IF($D417="","",VLOOKUP($D417,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5">
+      <c r="A418" t="s">
+        <v>119</v>
+      </c>
+      <c r="B418" s="9">
+        <v>24</v>
+      </c>
+      <c r="C418" t="s">
+        <v>23</v>
+      </c>
+      <c r="D418" s="9">
+        <v>7602658</v>
+      </c>
+      <c r="E418" s="5" t="str">
+        <f>IF($D418="","",VLOOKUP($D418,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5">
+      <c r="A419" t="s">
+        <v>119</v>
+      </c>
+      <c r="B419" s="9">
+        <v>25</v>
+      </c>
+      <c r="C419" t="s">
+        <v>84</v>
+      </c>
+      <c r="D419" s="9">
+        <v>7503696</v>
+      </c>
+      <c r="E419" s="5" t="str">
+        <f>IF($D419="","",VLOOKUP($D419,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5">
+      <c r="A420" t="s">
+        <v>119</v>
+      </c>
+      <c r="B420" s="9">
+        <v>26</v>
+      </c>
+      <c r="C420" t="s">
+        <v>90</v>
+      </c>
+      <c r="D420" s="9">
+        <v>7449306</v>
+      </c>
+      <c r="E420" s="5" t="str">
+        <f>IF($D420="","",VLOOKUP($D420,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5">
+      <c r="A421" t="s">
+        <v>119</v>
+      </c>
+      <c r="B421" s="9">
+        <v>27</v>
+      </c>
+      <c r="C421" t="s">
+        <v>18</v>
+      </c>
+      <c r="D421" s="9">
+        <v>7398360</v>
+      </c>
+      <c r="E421" s="5" t="str">
+        <f>IF($D421="","",VLOOKUP($D421,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5">
+      <c r="A422" t="s">
+        <v>119</v>
+      </c>
+      <c r="B422" s="9">
+        <v>28</v>
+      </c>
+      <c r="C422" t="s">
+        <v>103</v>
+      </c>
+      <c r="D422" s="9">
+        <v>7390802</v>
+      </c>
+      <c r="E422" s="5" t="str">
+        <f>IF($D422="","",VLOOKUP($D422,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5">
+      <c r="A423" t="s">
+        <v>119</v>
+      </c>
+      <c r="B423" s="9">
+        <v>29</v>
+      </c>
+      <c r="C423" t="s">
+        <v>31</v>
+      </c>
+      <c r="D423" s="9">
+        <v>7314780</v>
+      </c>
+      <c r="E423" s="5" t="str">
+        <f>IF($D423="","",VLOOKUP($D423,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5">
+      <c r="A424" t="s">
+        <v>119</v>
+      </c>
+      <c r="B424" s="9">
+        <v>30</v>
+      </c>
+      <c r="C424" t="s">
+        <v>29</v>
+      </c>
+      <c r="D424" s="9">
+        <v>7242120</v>
+      </c>
+      <c r="E424" s="5" t="str">
+        <f>IF($D424="","",VLOOKUP($D424,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5">
+      <c r="A425" t="s">
+        <v>119</v>
+      </c>
+      <c r="B425" s="9">
+        <v>31</v>
+      </c>
+      <c r="C425" t="s">
+        <v>83</v>
+      </c>
+      <c r="D425" s="9">
+        <v>7227828</v>
+      </c>
+      <c r="E425" s="5" t="str">
+        <f>IF($D425="","",VLOOKUP($D425,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5">
+      <c r="A426" t="s">
+        <v>119</v>
+      </c>
+      <c r="B426" s="9">
+        <v>32</v>
+      </c>
+      <c r="C426" t="s">
+        <v>13</v>
+      </c>
+      <c r="D426" s="9">
+        <v>7191540</v>
+      </c>
+      <c r="E426" s="5" t="str">
+        <f>IF($D426="","",VLOOKUP($D426,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5">
+      <c r="A427" t="s">
+        <v>119</v>
+      </c>
+      <c r="B427" s="9">
+        <v>33</v>
+      </c>
+      <c r="C427" t="s">
+        <v>92</v>
+      </c>
+      <c r="D427" s="9">
+        <v>6893512</v>
+      </c>
+      <c r="E427" s="5" t="str">
+        <f>IF($D427="","",VLOOKUP($D427,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5">
+      <c r="A428" t="s">
+        <v>119</v>
+      </c>
+      <c r="B428" s="9">
+        <v>34</v>
+      </c>
+      <c r="C428" t="s">
+        <v>35</v>
+      </c>
+      <c r="D428" s="9">
+        <v>6830397</v>
+      </c>
+      <c r="E428" s="5" t="str">
+        <f>IF($D428="","",VLOOKUP($D428,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5">
+      <c r="A429" t="s">
+        <v>119</v>
+      </c>
+      <c r="B429" s="9">
+        <v>35</v>
+      </c>
+      <c r="C429" t="s">
+        <v>100</v>
+      </c>
+      <c r="D429" s="9">
+        <v>6123133</v>
+      </c>
+      <c r="E429" s="5" t="str">
+        <f>IF($D429="","",VLOOKUP($D429,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5">
+      <c r="A430" t="s">
+        <v>119</v>
+      </c>
+      <c r="B430" s="9">
+        <v>36</v>
+      </c>
+      <c r="C430" t="s">
+        <v>42</v>
+      </c>
+      <c r="D430" s="9">
+        <v>5690876</v>
+      </c>
+      <c r="E430" s="5" t="str">
+        <f>IF($D430="","",VLOOKUP($D430,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5">
+      <c r="A431" t="s">
+        <v>119</v>
+      </c>
+      <c r="B431" s="9">
+        <v>37</v>
+      </c>
+      <c r="C431" t="s">
+        <v>47</v>
+      </c>
+      <c r="D431" s="9">
+        <v>5540207</v>
+      </c>
+      <c r="E431" s="5" t="str">
+        <f>IF($D431="","",VLOOKUP($D431,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5">
+      <c r="A432" t="s">
+        <v>119</v>
+      </c>
+      <c r="B432" s="9">
+        <v>38</v>
+      </c>
+      <c r="C432" t="s">
+        <v>91</v>
+      </c>
+      <c r="D432" s="9">
+        <v>5079780</v>
+      </c>
+      <c r="E432" s="5" t="str">
+        <f>IF($D432="","",VLOOKUP($D432,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5">
+      <c r="A433" t="s">
+        <v>119</v>
+      </c>
+      <c r="B433" s="9">
+        <v>39</v>
+      </c>
+      <c r="C433" t="s">
+        <v>44</v>
+      </c>
+      <c r="D433" s="9">
+        <v>4997779</v>
+      </c>
+      <c r="E433" s="5" t="str">
+        <f>IF($D433="","",VLOOKUP($D433,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5">
+      <c r="A434" t="s">
+        <v>119</v>
+      </c>
+      <c r="B434" s="9">
+        <v>40</v>
+      </c>
+      <c r="C434" t="s">
+        <v>51</v>
+      </c>
+      <c r="D434" s="9">
+        <v>4937750</v>
+      </c>
+      <c r="E434" s="5" t="str">
+        <f>IF($D434="","",VLOOKUP($D434,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5">
+      <c r="A435" t="s">
+        <v>119</v>
+      </c>
+      <c r="B435" s="9">
+        <v>41</v>
+      </c>
+      <c r="C435" t="s">
+        <v>40</v>
+      </c>
+      <c r="D435" s="9">
+        <v>4896569</v>
+      </c>
+      <c r="E435" s="5" t="str">
+        <f>IF($D435="","",VLOOKUP($D435,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5">
+      <c r="A436" t="s">
+        <v>119</v>
+      </c>
+      <c r="B436" s="9">
+        <v>42</v>
+      </c>
+      <c r="C436" t="s">
+        <v>54</v>
+      </c>
+      <c r="D436" s="9">
+        <v>4585763</v>
+      </c>
+      <c r="E436" s="5" t="str">
+        <f>IF($D436="","",VLOOKUP($D436,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5">
+      <c r="A437" t="s">
+        <v>119</v>
+      </c>
+      <c r="B437" s="9">
+        <v>43</v>
+      </c>
+      <c r="C437" t="s">
+        <v>67</v>
+      </c>
+      <c r="D437" s="9">
+        <v>4520490</v>
+      </c>
+      <c r="E437" s="5" t="str">
+        <f>IF($D437="","",VLOOKUP($D437,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5">
+      <c r="A438" t="s">
+        <v>119</v>
+      </c>
+      <c r="B438" s="9">
+        <v>44</v>
+      </c>
+      <c r="C438" t="s">
+        <v>69</v>
+      </c>
+      <c r="D438" s="9">
+        <v>4472197</v>
+      </c>
+      <c r="E438" s="5" t="str">
+        <f>IF($D438="","",VLOOKUP($D438,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5">
+      <c r="A439" t="s">
+        <v>119</v>
+      </c>
+      <c r="B439" s="9">
+        <v>45</v>
+      </c>
+      <c r="C439" t="s">
+        <v>38</v>
+      </c>
+      <c r="D439" s="9">
+        <v>4454646</v>
+      </c>
+      <c r="E439" s="5" t="str">
+        <f>IF($D439="","",VLOOKUP($D439,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5">
+      <c r="A440" t="s">
+        <v>119</v>
+      </c>
+      <c r="B440" s="9">
+        <v>46</v>
+      </c>
+      <c r="C440" t="s">
+        <v>37</v>
+      </c>
+      <c r="D440" s="9">
+        <v>4432064</v>
+      </c>
+      <c r="E440" s="5" t="str">
+        <f>IF($D440="","",VLOOKUP($D440,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5">
+      <c r="A441" t="s">
+        <v>119</v>
+      </c>
+      <c r="B441" s="9">
+        <v>47</v>
+      </c>
+      <c r="C441" t="s">
+        <v>41</v>
+      </c>
+      <c r="D441" s="9">
+        <v>4264172</v>
+      </c>
+      <c r="E441" s="5" t="str">
+        <f>IF($D441="","",VLOOKUP($D441,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5">
+      <c r="A442" t="s">
+        <v>119</v>
+      </c>
+      <c r="B442" s="9">
+        <v>48</v>
+      </c>
+      <c r="C442" t="s">
+        <v>53</v>
+      </c>
+      <c r="D442" s="9">
+        <v>4118340</v>
+      </c>
+      <c r="E442" s="5" t="str">
+        <f>IF($D442="","",VLOOKUP($D442,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5">
+      <c r="A443" t="s">
+        <v>119</v>
+      </c>
+      <c r="B443" s="9">
+        <v>49</v>
+      </c>
+      <c r="C443" t="s">
+        <v>20</v>
+      </c>
+      <c r="D443" s="9">
+        <v>3936283</v>
+      </c>
+      <c r="E443" s="5" t="str">
+        <f>IF($D443="","",VLOOKUP($D443,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5">
+      <c r="A444" t="s">
+        <v>119</v>
+      </c>
+      <c r="B444" s="9">
+        <v>50</v>
+      </c>
+      <c r="C444" t="s">
+        <v>61</v>
+      </c>
+      <c r="D444" s="9">
+        <v>3811500</v>
+      </c>
+      <c r="E444" s="5" t="str">
+        <f>IF($D444="","",VLOOKUP($D444,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5">
+      <c r="A445" t="s">
+        <v>119</v>
+      </c>
+      <c r="B445" s="9">
+        <v>51</v>
+      </c>
+      <c r="C445" t="s">
+        <v>55</v>
+      </c>
+      <c r="D445" s="9">
+        <v>3741493</v>
+      </c>
+      <c r="E445" s="5" t="str">
+        <f>IF($D445="","",VLOOKUP($D445,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5">
+      <c r="A446" t="s">
+        <v>119</v>
+      </c>
+      <c r="B446" s="9">
+        <v>52</v>
+      </c>
+      <c r="C446" t="s">
+        <v>57</v>
+      </c>
+      <c r="D446" s="9">
+        <v>3713921</v>
+      </c>
+      <c r="E446" s="5" t="str">
+        <f>IF($D446="","",VLOOKUP($D446,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5">
+      <c r="A447" t="s">
+        <v>119</v>
+      </c>
+      <c r="B447" s="9">
+        <v>53</v>
+      </c>
+      <c r="C447" t="s">
+        <v>120</v>
+      </c>
+      <c r="D447" s="9">
+        <v>3610131</v>
+      </c>
+      <c r="E447" s="5" t="str">
+        <f>IF($D447="","",VLOOKUP($D447,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5">
+      <c r="A448" t="s">
+        <v>119</v>
+      </c>
+      <c r="B448" s="9">
+        <v>54</v>
+      </c>
+      <c r="C448" s="12">
+        <v>1090</v>
+      </c>
+      <c r="D448" s="9">
+        <v>3471939</v>
+      </c>
+      <c r="E448" s="5" t="str">
+        <f>IF($D448="","",VLOOKUP($D448,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5">
+      <c r="A449" t="s">
+        <v>119</v>
+      </c>
+      <c r="B449" s="9">
+        <v>55</v>
+      </c>
+      <c r="C449" t="s">
+        <v>65</v>
+      </c>
+      <c r="D449" s="9">
+        <v>3449277</v>
+      </c>
+      <c r="E449" s="5" t="str">
+        <f>IF($D449="","",VLOOKUP($D449,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="450" spans="1:5">
+      <c r="A450" t="s">
+        <v>119</v>
+      </c>
+      <c r="B450" s="9">
+        <v>56</v>
+      </c>
+      <c r="C450" t="s">
+        <v>89</v>
+      </c>
+      <c r="D450" s="9">
+        <v>3355011</v>
+      </c>
+      <c r="E450" s="5" t="str">
+        <f>IF($D450="","",VLOOKUP($D450,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5">
+      <c r="A451" t="s">
+        <v>119</v>
+      </c>
+      <c r="B451" s="9">
+        <v>57</v>
+      </c>
+      <c r="C451" t="s">
+        <v>56</v>
+      </c>
+      <c r="D451" s="9">
+        <v>3348356</v>
+      </c>
+      <c r="E451" s="5" t="str">
+        <f>IF($D451="","",VLOOKUP($D451,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5">
+      <c r="A452" t="s">
+        <v>119</v>
+      </c>
+      <c r="B452" s="9">
+        <v>58</v>
+      </c>
+      <c r="C452" t="s">
+        <v>16</v>
+      </c>
+      <c r="D452" s="9">
+        <v>2818744</v>
+      </c>
+      <c r="E452" s="5" t="str">
+        <f>IF($D452="","",VLOOKUP($D452,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5">
+      <c r="A453" t="s">
+        <v>119</v>
+      </c>
+      <c r="B453" s="9">
+        <v>59</v>
+      </c>
+      <c r="C453" t="s">
+        <v>60</v>
+      </c>
+      <c r="D453" s="9">
+        <v>2676764</v>
+      </c>
+      <c r="E453" s="5" t="str">
+        <f>IF($D453="","",VLOOKUP($D453,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5">
+      <c r="A454" t="s">
+        <v>119</v>
+      </c>
+      <c r="B454" s="9">
+        <v>60</v>
+      </c>
+      <c r="C454" t="s">
+        <v>49</v>
+      </c>
+      <c r="D454" s="9">
+        <v>2595175</v>
+      </c>
+      <c r="E454" s="5" t="str">
+        <f>IF($D454="","",VLOOKUP($D454,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>7단계</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5">
+      <c r="A455" t="s">
+        <v>119</v>
+      </c>
+      <c r="B455" s="9">
+        <v>61</v>
+      </c>
+      <c r="C455" t="s">
+        <v>46</v>
+      </c>
+      <c r="D455" s="9">
+        <v>2505960</v>
+      </c>
+      <c r="E455" s="5" t="str">
+        <f>IF($D455="","",VLOOKUP($D455,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>7단계</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5">
+      <c r="A456" t="s">
+        <v>119</v>
+      </c>
+      <c r="B456" s="9">
+        <v>62</v>
+      </c>
+      <c r="C456" t="s">
+        <v>74</v>
+      </c>
+      <c r="D456" s="9">
+        <v>2181924</v>
+      </c>
+      <c r="E456" s="5" t="str">
+        <f>IF($D456="","",VLOOKUP($D456,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5">
+      <c r="A457" t="s">
+        <v>119</v>
+      </c>
+      <c r="B457" s="9">
+        <v>63</v>
+      </c>
+      <c r="C457" t="s">
+        <v>64</v>
+      </c>
+      <c r="D457" s="9">
+        <v>2020453</v>
+      </c>
+      <c r="E457" s="5" t="str">
+        <f>IF($D457="","",VLOOKUP($D457,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5">
+      <c r="A458" t="s">
+        <v>119</v>
+      </c>
+      <c r="B458" s="9">
+        <v>64</v>
+      </c>
+      <c r="C458" t="s">
+        <v>99</v>
+      </c>
+      <c r="D458" s="9">
+        <v>1951212</v>
+      </c>
+      <c r="E458" s="5" t="str">
+        <f>IF($D458="","",VLOOKUP($D458,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5">
+      <c r="A459" t="s">
+        <v>119</v>
+      </c>
+      <c r="B459" s="9">
+        <v>65</v>
+      </c>
+      <c r="C459" t="s">
+        <v>62</v>
+      </c>
+      <c r="D459" s="9">
+        <v>1775577</v>
+      </c>
+      <c r="E459" s="5" t="str">
+        <f>IF($D459="","",VLOOKUP($D459,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5">
+      <c r="A460" t="s">
+        <v>119</v>
+      </c>
+      <c r="B460" s="9">
+        <v>66</v>
+      </c>
+      <c r="C460" t="s">
+        <v>104</v>
+      </c>
+      <c r="D460" s="9">
+        <v>1535970</v>
+      </c>
+      <c r="E460" s="5" t="str">
+        <f>IF($D460="","",VLOOKUP($D460,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5">
+      <c r="A461" t="s">
+        <v>119</v>
+      </c>
+      <c r="B461" s="9">
+        <v>67</v>
+      </c>
+      <c r="C461" t="s">
+        <v>77</v>
+      </c>
+      <c r="D461" s="9">
+        <v>1235026</v>
+      </c>
+      <c r="E461" s="5" t="str">
+        <f>IF($D461="","",VLOOKUP($D461,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
       </c>
     </row>
   </sheetData>
@@ -7830,7 +9035,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF72E96B-BFB2-4F0A-87C0-94BB6F0899A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11139F7-C97E-43C4-B1C2-8154FA20792C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="149">
   <si>
     <t>하한점수</t>
   </si>
@@ -934,6 +934,14 @@
   </si>
   <si>
     <t>📦 월별 보관 — 2026-07  (날짜별 길드전 랭킹 누적)</t>
+  </si>
+  <si>
+    <t>guild</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>HARU</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -10786,6 +10794,12 @@
       <c r="A530" s="12">
         <v>46195</v>
       </c>
+      <c r="B530" t="s">
+        <v>147</v>
+      </c>
+      <c r="C530" s="2" t="s">
+        <v>148</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11139F7-C97E-43C4-B1C2-8154FA20792C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095657BE-13FD-4460-B255-B1A2E0740586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="131">
   <si>
     <t>하한점수</t>
   </si>
@@ -877,60 +877,6 @@
   </si>
   <si>
     <t>저썰고</t>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>독여울</t>
-  </si>
-  <si>
-    <t>핑도노•훔치고•생각하는•편</t>
-  </si>
-  <si>
-    <t>뉴스나온그사람</t>
-  </si>
-  <si>
-    <t>빠쎈공주</t>
-  </si>
-  <si>
-    <t>Gardiss</t>
-  </si>
-  <si>
-    <t>♣Reaper♣</t>
-  </si>
-  <si>
-    <t>FREDfre</t>
-  </si>
-  <si>
-    <t>PAMPALIS</t>
-  </si>
-  <si>
-    <t>Llumeta</t>
-  </si>
-  <si>
-    <t>Hikari09</t>
-  </si>
-  <si>
-    <t>해녜도앤댈리는뭬</t>
-  </si>
-  <si>
-    <t>Chief-Sidd</t>
-  </si>
-  <si>
-    <t>BarbarianROK</t>
-  </si>
-  <si>
-    <t>Synfull</t>
-  </si>
-  <si>
-    <t>Lizarbara</t>
-  </si>
-  <si>
-    <t>M1NTDRAGON</t>
-  </si>
-  <si>
-    <t>Sin4ez</t>
   </si>
   <si>
     <t>📦 월별 보관 — 2026-07  (날짜별 길드전 랭킹 누적)</t>
@@ -1462,7 +1408,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E530"/>
+  <dimension ref="A1:E462"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="14.875" customWidth="1"/>
@@ -9567,1238 +9513,14 @@
       </c>
     </row>
     <row r="462" spans="1:5">
-      <c r="A462" t="s">
-        <v>128</v>
-      </c>
-      <c r="B462">
-        <v>1</v>
+      <c r="A462" s="12">
+        <v>46195</v>
+      </c>
+      <c r="B462" t="s">
+        <v>129</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D462">
-        <v>23307444</v>
-      </c>
-      <c r="E462" t="str">
-        <f>IF($D462="","",VLOOKUP($D462,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="463" spans="1:5">
-      <c r="A463" t="s">
-        <v>128</v>
-      </c>
-      <c r="B463">
-        <v>2</v>
-      </c>
-      <c r="C463" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D463">
-        <v>19396950</v>
-      </c>
-      <c r="E463" t="str">
-        <f>IF($D463="","",VLOOKUP($D463,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="464" spans="1:5">
-      <c r="A464" t="s">
-        <v>128</v>
-      </c>
-      <c r="B464">
-        <v>3</v>
-      </c>
-      <c r="C464" t="s">
-        <v>34</v>
-      </c>
-      <c r="D464">
-        <v>18095408</v>
-      </c>
-      <c r="E464" t="str">
-        <f>IF($D464="","",VLOOKUP($D464,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="465" spans="1:5">
-      <c r="A465" t="s">
-        <v>128</v>
-      </c>
-      <c r="B465">
-        <v>4</v>
-      </c>
-      <c r="C465" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D465">
-        <v>17119393</v>
-      </c>
-      <c r="E465" t="str">
-        <f>IF($D465="","",VLOOKUP($D465,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="466" spans="1:5">
-      <c r="A466" t="s">
-        <v>128</v>
-      </c>
-      <c r="B466">
-        <v>5</v>
-      </c>
-      <c r="C466" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D466">
-        <v>13828925</v>
-      </c>
-      <c r="E466" t="str">
-        <f>IF($D466="","",VLOOKUP($D466,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="467" spans="1:5">
-      <c r="A467" t="s">
-        <v>128</v>
-      </c>
-      <c r="B467">
-        <v>6</v>
-      </c>
-      <c r="C467" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D467">
-        <v>13309076</v>
-      </c>
-      <c r="E467" t="str">
-        <f>IF($D467="","",VLOOKUP($D467,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="468" spans="1:5">
-      <c r="A468" t="s">
-        <v>128</v>
-      </c>
-      <c r="B468">
-        <v>7</v>
-      </c>
-      <c r="C468" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D468">
-        <v>13181412</v>
-      </c>
-      <c r="E468" t="str">
-        <f>IF($D468="","",VLOOKUP($D468,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="469" spans="1:5">
-      <c r="A469" t="s">
-        <v>128</v>
-      </c>
-      <c r="B469">
-        <v>8</v>
-      </c>
-      <c r="C469" t="s">
-        <v>48</v>
-      </c>
-      <c r="D469">
-        <v>12545033</v>
-      </c>
-      <c r="E469" t="str">
-        <f>IF($D469="","",VLOOKUP($D469,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="470" spans="1:5">
-      <c r="A470" t="s">
-        <v>128</v>
-      </c>
-      <c r="B470">
-        <v>9</v>
-      </c>
-      <c r="C470" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D470">
-        <v>12397090</v>
-      </c>
-      <c r="E470" t="str">
-        <f>IF($D470="","",VLOOKUP($D470,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="471" spans="1:5">
-      <c r="A471" t="s">
-        <v>128</v>
-      </c>
-      <c r="B471">
-        <v>10</v>
-      </c>
-      <c r="C471" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D471">
-        <v>12207359</v>
-      </c>
-      <c r="E471" t="str">
-        <f>IF($D471="","",VLOOKUP($D471,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="472" spans="1:5">
-      <c r="A472" t="s">
-        <v>128</v>
-      </c>
-      <c r="B472">
-        <v>11</v>
-      </c>
-      <c r="C472" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="D472">
-        <v>11650664</v>
-      </c>
-      <c r="E472" t="str">
-        <f>IF($D472="","",VLOOKUP($D472,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="473" spans="1:5">
-      <c r="A473" t="s">
-        <v>128</v>
-      </c>
-      <c r="B473">
-        <v>12</v>
-      </c>
-      <c r="C473" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D473">
-        <v>10515222</v>
-      </c>
-      <c r="E473" t="str">
-        <f>IF($D473="","",VLOOKUP($D473,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="474" spans="1:5">
-      <c r="A474" t="s">
-        <v>128</v>
-      </c>
-      <c r="B474">
-        <v>13</v>
-      </c>
-      <c r="C474" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D474">
-        <v>10446187</v>
-      </c>
-      <c r="E474" t="str">
-        <f>IF($D474="","",VLOOKUP($D474,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="475" spans="1:5">
-      <c r="A475" t="s">
-        <v>128</v>
-      </c>
-      <c r="B475">
-        <v>14</v>
-      </c>
-      <c r="C475" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D475">
-        <v>10294723</v>
-      </c>
-      <c r="E475" t="str">
-        <f>IF($D475="","",VLOOKUP($D475,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="476" spans="1:5">
-      <c r="A476" t="s">
-        <v>128</v>
-      </c>
-      <c r="B476">
-        <v>15</v>
-      </c>
-      <c r="C476" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D476">
-        <v>9738825</v>
-      </c>
-      <c r="E476" t="str">
-        <f>IF($D476="","",VLOOKUP($D476,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="477" spans="1:5">
-      <c r="A477" t="s">
-        <v>128</v>
-      </c>
-      <c r="B477">
-        <v>16</v>
-      </c>
-      <c r="C477" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D477">
-        <v>9634748</v>
-      </c>
-      <c r="E477" t="str">
-        <f>IF($D477="","",VLOOKUP($D477,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="478" spans="1:5">
-      <c r="A478" t="s">
-        <v>128</v>
-      </c>
-      <c r="B478">
-        <v>17</v>
-      </c>
-      <c r="C478" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D478">
-        <v>9313376</v>
-      </c>
-      <c r="E478" t="str">
-        <f>IF($D478="","",VLOOKUP($D478,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="479" spans="1:5">
-      <c r="A479" t="s">
-        <v>128</v>
-      </c>
-      <c r="B479">
-        <v>18</v>
-      </c>
-      <c r="C479" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D479">
-        <v>9283612</v>
-      </c>
-      <c r="E479" t="str">
-        <f>IF($D479="","",VLOOKUP($D479,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="480" spans="1:5">
-      <c r="A480" t="s">
-        <v>128</v>
-      </c>
-      <c r="B480">
-        <v>19</v>
-      </c>
-      <c r="C480" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D480">
-        <v>9103063</v>
-      </c>
-      <c r="E480" t="str">
-        <f>IF($D480="","",VLOOKUP($D480,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="481" spans="1:5">
-      <c r="A481" t="s">
-        <v>128</v>
-      </c>
-      <c r="B481">
-        <v>20</v>
-      </c>
-      <c r="C481" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D481">
-        <v>9099286</v>
-      </c>
-      <c r="E481" t="str">
-        <f>IF($D481="","",VLOOKUP($D481,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="482" spans="1:5">
-      <c r="A482" t="s">
-        <v>128</v>
-      </c>
-      <c r="B482">
-        <v>21</v>
-      </c>
-      <c r="C482" t="s">
-        <v>133</v>
-      </c>
-      <c r="D482">
-        <v>9071411</v>
-      </c>
-      <c r="E482" t="str">
-        <f>IF($D482="","",VLOOKUP($D482,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="483" spans="1:5">
-      <c r="A483" t="s">
-        <v>128</v>
-      </c>
-      <c r="B483">
-        <v>22</v>
-      </c>
-      <c r="C483" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D483">
-        <v>8888947</v>
-      </c>
-      <c r="E483" t="str">
-        <f>IF($D483="","",VLOOKUP($D483,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="484" spans="1:5">
-      <c r="A484" t="s">
-        <v>128</v>
-      </c>
-      <c r="B484">
-        <v>23</v>
-      </c>
-      <c r="C484" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D484">
-        <v>8537633</v>
-      </c>
-      <c r="E484" t="str">
-        <f>IF($D484="","",VLOOKUP($D484,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="485" spans="1:5">
-      <c r="A485" t="s">
-        <v>128</v>
-      </c>
-      <c r="B485">
-        <v>24</v>
-      </c>
-      <c r="C485" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D485">
-        <v>8369231</v>
-      </c>
-      <c r="E485" t="str">
-        <f>IF($D485="","",VLOOKUP($D485,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="486" spans="1:5">
-      <c r="A486" t="s">
-        <v>128</v>
-      </c>
-      <c r="B486">
-        <v>25</v>
-      </c>
-      <c r="C486" t="s">
-        <v>134</v>
-      </c>
-      <c r="D486">
-        <v>8139316</v>
-      </c>
-      <c r="E486" t="str">
-        <f>IF($D486="","",VLOOKUP($D486,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="487" spans="1:5">
-      <c r="A487" t="s">
-        <v>128</v>
-      </c>
-      <c r="B487">
-        <v>26</v>
-      </c>
-      <c r="C487" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D487">
-        <v>8056645</v>
-      </c>
-      <c r="E487" t="str">
-        <f>IF($D487="","",VLOOKUP($D487,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="488" spans="1:5">
-      <c r="A488" t="s">
-        <v>128</v>
-      </c>
-      <c r="B488">
-        <v>27</v>
-      </c>
-      <c r="C488" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D488">
-        <v>8010939</v>
-      </c>
-      <c r="E488" t="str">
-        <f>IF($D488="","",VLOOKUP($D488,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="489" spans="1:5">
-      <c r="A489" t="s">
-        <v>128</v>
-      </c>
-      <c r="B489">
-        <v>28</v>
-      </c>
-      <c r="C489" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D489">
-        <v>7916094</v>
-      </c>
-      <c r="E489" t="str">
-        <f>IF($D489="","",VLOOKUP($D489,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="490" spans="1:5">
-      <c r="A490" t="s">
-        <v>128</v>
-      </c>
-      <c r="B490">
-        <v>29</v>
-      </c>
-      <c r="C490" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D490">
-        <v>7860992</v>
-      </c>
-      <c r="E490" t="str">
-        <f>IF($D490="","",VLOOKUP($D490,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="491" spans="1:5">
-      <c r="A491" t="s">
-        <v>128</v>
-      </c>
-      <c r="B491">
-        <v>30</v>
-      </c>
-      <c r="C491" t="s">
-        <v>135</v>
-      </c>
-      <c r="D491">
-        <v>7856398</v>
-      </c>
-      <c r="E491" t="str">
-        <f>IF($D491="","",VLOOKUP($D491,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="492" spans="1:5">
-      <c r="A492" t="s">
-        <v>128</v>
-      </c>
-      <c r="B492">
-        <v>31</v>
-      </c>
-      <c r="C492" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D492">
-        <v>7680143</v>
-      </c>
-      <c r="E492" t="str">
-        <f>IF($D492="","",VLOOKUP($D492,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="493" spans="1:5">
-      <c r="A493" t="s">
-        <v>128</v>
-      </c>
-      <c r="B493">
-        <v>32</v>
-      </c>
-      <c r="C493" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D493">
-        <v>7533387</v>
-      </c>
-      <c r="E493" t="str">
-        <f>IF($D493="","",VLOOKUP($D493,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="494" spans="1:5">
-      <c r="A494" t="s">
-        <v>128</v>
-      </c>
-      <c r="B494">
-        <v>33</v>
-      </c>
-      <c r="C494" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D494">
-        <v>7423111</v>
-      </c>
-      <c r="E494" t="str">
-        <f>IF($D494="","",VLOOKUP($D494,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="495" spans="1:5">
-      <c r="A495" t="s">
-        <v>128</v>
-      </c>
-      <c r="B495">
-        <v>34</v>
-      </c>
-      <c r="C495" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D495">
-        <v>7363396</v>
-      </c>
-      <c r="E495" t="str">
-        <f>IF($D495="","",VLOOKUP($D495,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="496" spans="1:5">
-      <c r="A496" t="s">
-        <v>128</v>
-      </c>
-      <c r="B496">
-        <v>35</v>
-      </c>
-      <c r="C496" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D496">
-        <v>7140609</v>
-      </c>
-      <c r="E496" t="str">
-        <f>IF($D496="","",VLOOKUP($D496,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="497" spans="1:5">
-      <c r="A497" t="s">
-        <v>128</v>
-      </c>
-      <c r="B497">
-        <v>36</v>
-      </c>
-      <c r="C497" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D497">
-        <v>7000332</v>
-      </c>
-      <c r="E497" t="str">
-        <f>IF($D497="","",VLOOKUP($D497,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="498" spans="1:5">
-      <c r="A498" t="s">
-        <v>128</v>
-      </c>
-      <c r="B498">
-        <v>37</v>
-      </c>
-      <c r="C498" t="s">
-        <v>136</v>
-      </c>
-      <c r="D498">
-        <v>6462016</v>
-      </c>
-      <c r="E498" t="str">
-        <f>IF($D498="","",VLOOKUP($D498,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="499" spans="1:5">
-      <c r="A499" t="s">
-        <v>128</v>
-      </c>
-      <c r="B499">
-        <v>38</v>
-      </c>
-      <c r="C499" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D499">
-        <v>6270014</v>
-      </c>
-      <c r="E499" t="str">
-        <f>IF($D499="","",VLOOKUP($D499,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="500" spans="1:5">
-      <c r="A500" t="s">
-        <v>128</v>
-      </c>
-      <c r="B500">
-        <v>39</v>
-      </c>
-      <c r="C500" t="s">
-        <v>137</v>
-      </c>
-      <c r="D500">
-        <v>5417347</v>
-      </c>
-      <c r="E500" t="str">
-        <f>IF($D500="","",VLOOKUP($D500,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="501" spans="1:5">
-      <c r="A501" t="s">
-        <v>128</v>
-      </c>
-      <c r="B501">
-        <v>40</v>
-      </c>
-      <c r="C501" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D501">
-        <v>5071879</v>
-      </c>
-      <c r="E501" t="str">
-        <f>IF($D501="","",VLOOKUP($D501,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="502" spans="1:5">
-      <c r="A502" t="s">
-        <v>128</v>
-      </c>
-      <c r="B502">
-        <v>41</v>
-      </c>
-      <c r="C502" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D502">
-        <v>4841861</v>
-      </c>
-      <c r="E502" t="str">
-        <f>IF($D502="","",VLOOKUP($D502,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="503" spans="1:5">
-      <c r="A503" t="s">
-        <v>128</v>
-      </c>
-      <c r="B503">
-        <v>42</v>
-      </c>
-      <c r="C503" t="s">
-        <v>138</v>
-      </c>
-      <c r="D503">
-        <v>4700789</v>
-      </c>
-      <c r="E503" t="str">
-        <f>IF($D503="","",VLOOKUP($D503,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="504" spans="1:5">
-      <c r="A504" t="s">
-        <v>128</v>
-      </c>
-      <c r="B504">
-        <v>43</v>
-      </c>
-      <c r="C504" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D504">
-        <v>4671946</v>
-      </c>
-      <c r="E504" t="str">
-        <f>IF($D504="","",VLOOKUP($D504,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="505" spans="1:5">
-      <c r="A505" t="s">
-        <v>128</v>
-      </c>
-      <c r="B505">
-        <v>44</v>
-      </c>
-      <c r="C505" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D505">
-        <v>4548374</v>
-      </c>
-      <c r="E505" t="str">
-        <f>IF($D505="","",VLOOKUP($D505,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="506" spans="1:5">
-      <c r="A506" t="s">
-        <v>128</v>
-      </c>
-      <c r="B506">
-        <v>45</v>
-      </c>
-      <c r="C506" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D506">
-        <v>4512303</v>
-      </c>
-      <c r="E506" t="str">
-        <f>IF($D506="","",VLOOKUP($D506,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="507" spans="1:5">
-      <c r="A507" t="s">
-        <v>128</v>
-      </c>
-      <c r="B507">
-        <v>46</v>
-      </c>
-      <c r="C507" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D507">
-        <v>4291108</v>
-      </c>
-      <c r="E507" t="str">
-        <f>IF($D507="","",VLOOKUP($D507,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="508" spans="1:5">
-      <c r="A508" t="s">
-        <v>128</v>
-      </c>
-      <c r="B508">
-        <v>47</v>
-      </c>
-      <c r="C508" t="s">
-        <v>140</v>
-      </c>
-      <c r="D508">
-        <v>4210423</v>
-      </c>
-      <c r="E508" t="str">
-        <f>IF($D508="","",VLOOKUP($D508,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="509" spans="1:5">
-      <c r="A509" t="s">
-        <v>128</v>
-      </c>
-      <c r="B509">
-        <v>48</v>
-      </c>
-      <c r="C509" t="s">
-        <v>141</v>
-      </c>
-      <c r="D509">
-        <v>4137894</v>
-      </c>
-      <c r="E509" t="str">
-        <f>IF($D509="","",VLOOKUP($D509,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="510" spans="1:5">
-      <c r="A510" t="s">
-        <v>128</v>
-      </c>
-      <c r="B510">
-        <v>49</v>
-      </c>
-      <c r="C510" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D510">
-        <v>4108074</v>
-      </c>
-      <c r="E510" t="str">
-        <f>IF($D510="","",VLOOKUP($D510,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="511" spans="1:5">
-      <c r="A511" t="s">
-        <v>128</v>
-      </c>
-      <c r="B511">
-        <v>50</v>
-      </c>
-      <c r="C511" t="s">
-        <v>142</v>
-      </c>
-      <c r="D511">
-        <v>3819359</v>
-      </c>
-      <c r="E511" t="str">
-        <f>IF($D511="","",VLOOKUP($D511,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="512" spans="1:5">
-      <c r="A512" t="s">
-        <v>128</v>
-      </c>
-      <c r="B512">
-        <v>51</v>
-      </c>
-      <c r="C512" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D512">
-        <v>3716764</v>
-      </c>
-      <c r="E512" t="str">
-        <f>IF($D512="","",VLOOKUP($D512,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="513" spans="1:5">
-      <c r="A513" t="s">
-        <v>128</v>
-      </c>
-      <c r="B513">
-        <v>52</v>
-      </c>
-      <c r="C513" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D513">
-        <v>3673701</v>
-      </c>
-      <c r="E513" t="str">
-        <f>IF($D513="","",VLOOKUP($D513,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="514" spans="1:5">
-      <c r="A514" t="s">
-        <v>128</v>
-      </c>
-      <c r="B514">
-        <v>53</v>
-      </c>
-      <c r="C514" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D514">
-        <v>3661187</v>
-      </c>
-      <c r="E514" t="str">
-        <f>IF($D514="","",VLOOKUP($D514,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="515" spans="1:5">
-      <c r="A515" t="s">
-        <v>128</v>
-      </c>
-      <c r="B515">
-        <v>54</v>
-      </c>
-      <c r="C515" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D515">
-        <v>3610343</v>
-      </c>
-      <c r="E515" t="str">
-        <f>IF($D515="","",VLOOKUP($D515,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="516" spans="1:5">
-      <c r="A516" t="s">
-        <v>128</v>
-      </c>
-      <c r="B516">
-        <v>55</v>
-      </c>
-      <c r="C516" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D516">
-        <v>3447259</v>
-      </c>
-      <c r="E516" t="str">
-        <f>IF($D516="","",VLOOKUP($D516,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="517" spans="1:5">
-      <c r="A517" t="s">
-        <v>128</v>
-      </c>
-      <c r="B517">
-        <v>56</v>
-      </c>
-      <c r="C517" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D517">
-        <v>3395092</v>
-      </c>
-      <c r="E517" t="str">
-        <f>IF($D517="","",VLOOKUP($D517,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="518" spans="1:5">
-      <c r="A518" t="s">
-        <v>128</v>
-      </c>
-      <c r="B518">
-        <v>57</v>
-      </c>
-      <c r="C518" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D518">
-        <v>3243612</v>
-      </c>
-      <c r="E518" t="str">
-        <f>IF($D518="","",VLOOKUP($D518,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="519" spans="1:5">
-      <c r="A519" t="s">
-        <v>128</v>
-      </c>
-      <c r="B519">
-        <v>58</v>
-      </c>
-      <c r="C519" t="s">
-        <v>143</v>
-      </c>
-      <c r="D519">
-        <v>3204977</v>
-      </c>
-      <c r="E519" t="str">
-        <f>IF($D519="","",VLOOKUP($D519,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="520" spans="1:5">
-      <c r="A520" t="s">
-        <v>128</v>
-      </c>
-      <c r="B520">
-        <v>59</v>
-      </c>
-      <c r="C520" t="s">
-        <v>144</v>
-      </c>
-      <c r="D520">
-        <v>2990540</v>
-      </c>
-      <c r="E520" t="str">
-        <f>IF($D520="","",VLOOKUP($D520,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="521" spans="1:5">
-      <c r="A521" t="s">
-        <v>128</v>
-      </c>
-      <c r="B521">
-        <v>60</v>
-      </c>
-      <c r="C521" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D521">
-        <v>2988780</v>
-      </c>
-      <c r="E521" t="str">
-        <f>IF($D521="","",VLOOKUP($D521,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="522" spans="1:5">
-      <c r="A522" t="s">
-        <v>128</v>
-      </c>
-      <c r="B522">
-        <v>61</v>
-      </c>
-      <c r="C522" t="s">
-        <v>145</v>
-      </c>
-      <c r="D522">
-        <v>2798723</v>
-      </c>
-      <c r="E522" t="str">
-        <f>IF($D522="","",VLOOKUP($D522,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
-      </c>
-    </row>
-    <row r="523" spans="1:5">
-      <c r="A523" t="s">
-        <v>128</v>
-      </c>
-      <c r="B523">
-        <v>62</v>
-      </c>
-      <c r="C523" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D523">
-        <v>1364975</v>
-      </c>
-      <c r="E523" t="str">
-        <f>IF($D523="","",VLOOKUP($D523,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
-      </c>
-    </row>
-    <row r="524" spans="1:5">
-      <c r="A524" t="s">
-        <v>128</v>
-      </c>
-      <c r="B524">
-        <v>63</v>
-      </c>
-      <c r="C524" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D524">
-        <v>1228212</v>
-      </c>
-      <c r="E524" t="str">
-        <f>IF($D524="","",VLOOKUP($D524,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
-      </c>
-    </row>
-    <row r="525" spans="1:5">
-      <c r="A525" t="s">
-        <v>128</v>
-      </c>
-      <c r="B525">
-        <v>64</v>
-      </c>
-      <c r="C525" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D525">
-        <v>1223730</v>
-      </c>
-      <c r="E525" t="str">
-        <f>IF($D525="","",VLOOKUP($D525,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
-      </c>
-    </row>
-    <row r="526" spans="1:5">
-      <c r="A526" t="s">
-        <v>128</v>
-      </c>
-      <c r="B526">
-        <v>65</v>
-      </c>
-      <c r="C526" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D526">
-        <v>1133672</v>
-      </c>
-      <c r="E526" t="str">
-        <f>IF($D526="","",VLOOKUP($D526,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
-      </c>
-    </row>
-    <row r="527" spans="1:5">
-      <c r="A527" t="s">
-        <v>128</v>
-      </c>
-      <c r="B527">
-        <v>66</v>
-      </c>
-      <c r="C527" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D527">
-        <v>462900</v>
-      </c>
-      <c r="E527" t="str">
-        <f>IF($D527="","",VLOOKUP($D527,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>3단계</v>
-      </c>
-    </row>
-    <row r="528" spans="1:5">
-      <c r="A528" t="s">
-        <v>128</v>
-      </c>
-      <c r="B528">
-        <v>67</v>
-      </c>
-      <c r="C528" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D528">
-        <v>98750</v>
-      </c>
-      <c r="E528" t="str">
-        <f>IF($D528="","",VLOOKUP($D528,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>2단계</v>
-      </c>
-    </row>
-    <row r="529" spans="1:5">
-      <c r="A529" t="s">
-        <v>128</v>
-      </c>
-      <c r="B529">
-        <v>68</v>
-      </c>
-      <c r="C529" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D529">
-        <v>8032</v>
-      </c>
-      <c r="E529" t="str">
-        <f>IF($D529="","",VLOOKUP($D529,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>1단계</v>
-      </c>
-    </row>
-    <row r="530" spans="1:5">
-      <c r="A530" s="12">
-        <v>46195</v>
-      </c>
-      <c r="B530" t="s">
-        <v>147</v>
-      </c>
-      <c r="C530" s="2" t="s">
-        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -10815,7 +9537,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095657BE-13FD-4460-B255-B1A2E0740586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C99B5EE-8ADD-406F-BE35-8A0F8756829F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="131">
   <si>
     <t>하한점수</t>
   </si>
@@ -1408,7 +1408,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E462"/>
+  <dimension ref="A1:E465"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="14.875" customWidth="1"/>
@@ -9521,6 +9521,60 @@
       </c>
       <c r="C462" s="2" t="s">
         <v>130</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5">
+      <c r="A463" t="s">
+        <v>126</v>
+      </c>
+      <c r="B463" s="9">
+        <v>1</v>
+      </c>
+      <c r="C463" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D463" s="9">
+        <v>15645750</v>
+      </c>
+      <c r="E463" s="6" t="str">
+        <f>IF($D463="","",VLOOKUP($D463,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5">
+      <c r="A464" t="s">
+        <v>126</v>
+      </c>
+      <c r="B464" s="9">
+        <v>2</v>
+      </c>
+      <c r="C464" t="s">
+        <v>34</v>
+      </c>
+      <c r="D464" s="9">
+        <v>13978410</v>
+      </c>
+      <c r="E464" s="6" t="str">
+        <f>IF($D464="","",VLOOKUP($D464,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5">
+      <c r="A465" t="s">
+        <v>126</v>
+      </c>
+      <c r="B465" s="9">
+        <v>3</v>
+      </c>
+      <c r="C465" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D465" s="9">
+        <v>13088206</v>
+      </c>
+      <c r="E465" s="6" t="str">
+        <f>IF($D465="","",VLOOKUP($D465,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
       </c>
     </row>
   </sheetData>

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C99B5EE-8ADD-406F-BE35-8A0F8756829F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4DB6FE-00C3-409F-8E40-C8872AD63937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -886,7 +886,7 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>HARU</t>
+    <t>[ HARU ] 春ぽかぽか</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4DB6FE-00C3-409F-8E40-C8872AD63937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{518664C2-3642-4EF6-B6B5-7DAE88932722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="131">
   <si>
     <t>하한점수</t>
   </si>
@@ -9524,8 +9524,8 @@
       </c>
     </row>
     <row r="463" spans="1:5">
-      <c r="A463" t="s">
-        <v>126</v>
+      <c r="A463" s="12">
+        <v>46195</v>
       </c>
       <c r="B463" s="9">
         <v>1</v>
@@ -9542,8 +9542,8 @@
       </c>
     </row>
     <row r="464" spans="1:5">
-      <c r="A464" t="s">
-        <v>126</v>
+      <c r="A464" s="12">
+        <v>46195</v>
       </c>
       <c r="B464" s="9">
         <v>2</v>
@@ -9560,8 +9560,8 @@
       </c>
     </row>
     <row r="465" spans="1:5">
-      <c r="A465" t="s">
-        <v>126</v>
+      <c r="A465" s="12">
+        <v>46195</v>
       </c>
       <c r="B465" s="9">
         <v>3</v>

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{518664C2-3642-4EF6-B6B5-7DAE88932722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A2C673C-A07D-4600-95F7-FF8EF2B0D263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="132">
   <si>
     <t>하한점수</t>
   </si>
@@ -887,6 +887,10 @@
   </si>
   <si>
     <t>[ HARU ] 春ぽかぽか</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ Vx3 ] Veni,Vidi,Vici</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1408,7 +1412,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E465"/>
+  <dimension ref="A1:E466"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="14.875" customWidth="1"/>
@@ -8310,32 +8314,27 @@
       <c r="A395" t="s">
         <v>126</v>
       </c>
-      <c r="B395" s="9">
-        <v>1</v>
+      <c r="B395" t="s">
+        <v>129</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D395" s="9">
-        <v>15645750</v>
-      </c>
-      <c r="E395" s="6" t="str">
-        <f>IF($D395="","",VLOOKUP($D395,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="D395" s="9"/>
+      <c r="E395" s="6"/>
     </row>
     <row r="396" spans="1:5">
       <c r="A396" t="s">
         <v>126</v>
       </c>
       <c r="B396" s="9">
-        <v>2</v>
-      </c>
-      <c r="C396" t="s">
-        <v>34</v>
+        <v>1</v>
+      </c>
+      <c r="C396" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="D396" s="9">
-        <v>13978410</v>
+        <v>15645750</v>
       </c>
       <c r="E396" s="6" t="str">
         <f>IF($D396="","",VLOOKUP($D396,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8347,13 +8346,13 @@
         <v>126</v>
       </c>
       <c r="B397" s="9">
-        <v>3</v>
-      </c>
-      <c r="C397" s="2" t="s">
-        <v>107</v>
+        <v>2</v>
+      </c>
+      <c r="C397" t="s">
+        <v>34</v>
       </c>
       <c r="D397" s="9">
-        <v>13088206</v>
+        <v>13978410</v>
       </c>
       <c r="E397" s="6" t="str">
         <f>IF($D397="","",VLOOKUP($D397,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8365,13 +8364,13 @@
         <v>126</v>
       </c>
       <c r="B398" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="D398" s="9">
-        <v>12744509</v>
+        <v>13088206</v>
       </c>
       <c r="E398" s="6" t="str">
         <f>IF($D398="","",VLOOKUP($D398,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8383,13 +8382,13 @@
         <v>126</v>
       </c>
       <c r="B399" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>43</v>
+        <v>121</v>
       </c>
       <c r="D399" s="9">
-        <v>11777730</v>
+        <v>12744509</v>
       </c>
       <c r="E399" s="6" t="str">
         <f>IF($D399="","",VLOOKUP($D399,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8401,13 +8400,13 @@
         <v>126</v>
       </c>
       <c r="B400" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="D400" s="9">
-        <v>11191350</v>
+        <v>11777730</v>
       </c>
       <c r="E400" s="6" t="str">
         <f>IF($D400="","",VLOOKUP($D400,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8419,13 +8418,13 @@
         <v>126</v>
       </c>
       <c r="B401" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="D401" s="9">
-        <v>10909500</v>
+        <v>11191350</v>
       </c>
       <c r="E401" s="6" t="str">
         <f>IF($D401="","",VLOOKUP($D401,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8437,13 +8436,13 @@
         <v>126</v>
       </c>
       <c r="B402" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="D402" s="9">
-        <v>10720108</v>
+        <v>10909500</v>
       </c>
       <c r="E402" s="6" t="str">
         <f>IF($D402="","",VLOOKUP($D402,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8455,13 +8454,13 @@
         <v>126</v>
       </c>
       <c r="B403" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D403" s="9">
-        <v>10500995</v>
+        <v>10720108</v>
       </c>
       <c r="E403" s="6" t="str">
         <f>IF($D403="","",VLOOKUP($D403,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8473,13 +8472,13 @@
         <v>126</v>
       </c>
       <c r="B404" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="D404" s="9">
-        <v>10489590</v>
+        <v>10500995</v>
       </c>
       <c r="E404" s="6" t="str">
         <f>IF($D404="","",VLOOKUP($D404,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8491,13 +8490,13 @@
         <v>126</v>
       </c>
       <c r="B405" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D405" s="9">
-        <v>10320090</v>
+        <v>10489590</v>
       </c>
       <c r="E405" s="6" t="str">
         <f>IF($D405="","",VLOOKUP($D405,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8509,13 +8508,13 @@
         <v>126</v>
       </c>
       <c r="B406" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="D406" s="9">
-        <v>9391223</v>
+        <v>10320090</v>
       </c>
       <c r="E406" s="6" t="str">
         <f>IF($D406="","",VLOOKUP($D406,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8527,13 +8526,13 @@
         <v>126</v>
       </c>
       <c r="B407" s="9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>30</v>
+        <v>108</v>
       </c>
       <c r="D407" s="9">
-        <v>9042210</v>
+        <v>9391223</v>
       </c>
       <c r="E407" s="6" t="str">
         <f>IF($D407="","",VLOOKUP($D407,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8545,13 +8544,13 @@
         <v>126</v>
       </c>
       <c r="B408" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>116</v>
+        <v>30</v>
       </c>
       <c r="D408" s="9">
-        <v>8691306</v>
+        <v>9042210</v>
       </c>
       <c r="E408" s="6" t="str">
         <f>IF($D408="","",VLOOKUP($D408,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8563,13 +8562,13 @@
         <v>126</v>
       </c>
       <c r="B409" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>41</v>
+        <v>116</v>
       </c>
       <c r="D409" s="9">
-        <v>8350410</v>
+        <v>8691306</v>
       </c>
       <c r="E409" s="6" t="str">
         <f>IF($D409="","",VLOOKUP($D409,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8581,13 +8580,13 @@
         <v>126</v>
       </c>
       <c r="B410" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="D410" s="9">
-        <v>8286570</v>
+        <v>8350410</v>
       </c>
       <c r="E410" s="6" t="str">
         <f>IF($D410="","",VLOOKUP($D410,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8599,13 +8598,13 @@
         <v>126</v>
       </c>
       <c r="B411" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D411" s="9">
-        <v>8219625</v>
+        <v>8286570</v>
       </c>
       <c r="E411" s="6" t="str">
         <f>IF($D411="","",VLOOKUP($D411,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8617,13 +8616,13 @@
         <v>126</v>
       </c>
       <c r="B412" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D412" s="9">
-        <v>8111520</v>
+        <v>8219625</v>
       </c>
       <c r="E412" s="6" t="str">
         <f>IF($D412="","",VLOOKUP($D412,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8635,13 +8634,13 @@
         <v>126</v>
       </c>
       <c r="B413" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="D413" s="9">
-        <v>8105430</v>
+        <v>8111520</v>
       </c>
       <c r="E413" s="6" t="str">
         <f>IF($D413="","",VLOOKUP($D413,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8653,13 +8652,13 @@
         <v>126</v>
       </c>
       <c r="B414" s="9">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D414" s="9">
-        <v>7975410</v>
+        <v>8105430</v>
       </c>
       <c r="E414" s="6" t="str">
         <f>IF($D414="","",VLOOKUP($D414,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8671,13 +8670,13 @@
         <v>126</v>
       </c>
       <c r="B415" s="9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="D415" s="9">
-        <v>7852200</v>
+        <v>7975410</v>
       </c>
       <c r="E415" s="6" t="str">
         <f>IF($D415="","",VLOOKUP($D415,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8689,13 +8688,13 @@
         <v>126</v>
       </c>
       <c r="B416" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="D416" s="9">
-        <v>7715220</v>
+        <v>7852200</v>
       </c>
       <c r="E416" s="6" t="str">
         <f>IF($D416="","",VLOOKUP($D416,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8707,13 +8706,13 @@
         <v>126</v>
       </c>
       <c r="B417" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="D417" s="9">
-        <v>7610714</v>
+        <v>7715220</v>
       </c>
       <c r="E417" s="6" t="str">
         <f>IF($D417="","",VLOOKUP($D417,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8725,13 +8724,13 @@
         <v>126</v>
       </c>
       <c r="B418" s="9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D418" s="9">
-        <v>7602658</v>
+        <v>7610714</v>
       </c>
       <c r="E418" s="6" t="str">
         <f>IF($D418="","",VLOOKUP($D418,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8743,13 +8742,13 @@
         <v>126</v>
       </c>
       <c r="B419" s="9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="D419" s="9">
-        <v>7503696</v>
+        <v>7602658</v>
       </c>
       <c r="E419" s="6" t="str">
         <f>IF($D419="","",VLOOKUP($D419,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8761,13 +8760,13 @@
         <v>126</v>
       </c>
       <c r="B420" s="9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D420" s="9">
-        <v>7449306</v>
+        <v>7503696</v>
       </c>
       <c r="E420" s="6" t="str">
         <f>IF($D420="","",VLOOKUP($D420,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8779,13 +8778,13 @@
         <v>126</v>
       </c>
       <c r="B421" s="9">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
       <c r="D421" s="9">
-        <v>7398360</v>
+        <v>7449306</v>
       </c>
       <c r="E421" s="6" t="str">
         <f>IF($D421="","",VLOOKUP($D421,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8797,13 +8796,13 @@
         <v>126</v>
       </c>
       <c r="B422" s="9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>123</v>
+        <v>37</v>
       </c>
       <c r="D422" s="9">
-        <v>7390802</v>
+        <v>7398360</v>
       </c>
       <c r="E422" s="6" t="str">
         <f>IF($D422="","",VLOOKUP($D422,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8815,13 +8814,13 @@
         <v>126</v>
       </c>
       <c r="B423" s="9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="D423" s="9">
-        <v>7314780</v>
+        <v>7390802</v>
       </c>
       <c r="E423" s="6" t="str">
         <f>IF($D423="","",VLOOKUP($D423,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8833,13 +8832,13 @@
         <v>126</v>
       </c>
       <c r="B424" s="9">
-        <v>30</v>
-      </c>
-      <c r="C424" t="s">
-        <v>48</v>
+        <v>29</v>
+      </c>
+      <c r="C424" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="D424" s="9">
-        <v>7242120</v>
+        <v>7314780</v>
       </c>
       <c r="E424" s="6" t="str">
         <f>IF($D424="","",VLOOKUP($D424,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8851,13 +8850,13 @@
         <v>126</v>
       </c>
       <c r="B425" s="9">
-        <v>31</v>
-      </c>
-      <c r="C425" s="2" t="s">
-        <v>97</v>
+        <v>30</v>
+      </c>
+      <c r="C425" t="s">
+        <v>48</v>
       </c>
       <c r="D425" s="9">
-        <v>7227828</v>
+        <v>7242120</v>
       </c>
       <c r="E425" s="6" t="str">
         <f>IF($D425="","",VLOOKUP($D425,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8869,13 +8868,13 @@
         <v>126</v>
       </c>
       <c r="B426" s="9">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="D426" s="9">
-        <v>7191540</v>
+        <v>7227828</v>
       </c>
       <c r="E426" s="6" t="str">
         <f>IF($D426="","",VLOOKUP($D426,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8887,17 +8886,17 @@
         <v>126</v>
       </c>
       <c r="B427" s="9">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="D427" s="9">
-        <v>6893512</v>
+        <v>7191540</v>
       </c>
       <c r="E427" s="6" t="str">
         <f>IF($D427="","",VLOOKUP($D427,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>9단계</v>
       </c>
     </row>
     <row r="428" spans="1:5">
@@ -8905,13 +8904,13 @@
         <v>126</v>
       </c>
       <c r="B428" s="9">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="D428" s="9">
-        <v>6830397</v>
+        <v>6893512</v>
       </c>
       <c r="E428" s="6" t="str">
         <f>IF($D428="","",VLOOKUP($D428,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8923,13 +8922,13 @@
         <v>126</v>
       </c>
       <c r="B429" s="9">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="D429" s="9">
-        <v>6123133</v>
+        <v>6830397</v>
       </c>
       <c r="E429" s="6" t="str">
         <f>IF($D429="","",VLOOKUP($D429,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8941,13 +8940,13 @@
         <v>126</v>
       </c>
       <c r="B430" s="9">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="D430" s="9">
-        <v>5690876</v>
+        <v>6123133</v>
       </c>
       <c r="E430" s="6" t="str">
         <f>IF($D430="","",VLOOKUP($D430,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8959,13 +8958,13 @@
         <v>126</v>
       </c>
       <c r="B431" s="9">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D431" s="9">
-        <v>5540207</v>
+        <v>5690876</v>
       </c>
       <c r="E431" s="6" t="str">
         <f>IF($D431="","",VLOOKUP($D431,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8977,13 +8976,13 @@
         <v>126</v>
       </c>
       <c r="B432" s="9">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="D432" s="9">
-        <v>5079780</v>
+        <v>5540207</v>
       </c>
       <c r="E432" s="6" t="str">
         <f>IF($D432="","",VLOOKUP($D432,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8995,13 +8994,13 @@
         <v>126</v>
       </c>
       <c r="B433" s="9">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="D433" s="9">
-        <v>4997779</v>
+        <v>5079780</v>
       </c>
       <c r="E433" s="6" t="str">
         <f>IF($D433="","",VLOOKUP($D433,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9013,13 +9012,13 @@
         <v>126</v>
       </c>
       <c r="B434" s="9">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>69</v>
+        <v>124</v>
       </c>
       <c r="D434" s="9">
-        <v>4937750</v>
+        <v>4997779</v>
       </c>
       <c r="E434" s="6" t="str">
         <f>IF($D434="","",VLOOKUP($D434,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9031,13 +9030,13 @@
         <v>126</v>
       </c>
       <c r="B435" s="9">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>122</v>
+        <v>69</v>
       </c>
       <c r="D435" s="9">
-        <v>4896569</v>
+        <v>4937750</v>
       </c>
       <c r="E435" s="6" t="str">
         <f>IF($D435="","",VLOOKUP($D435,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9049,13 +9048,13 @@
         <v>126</v>
       </c>
       <c r="B436" s="9">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="D436" s="9">
-        <v>4585763</v>
+        <v>4896569</v>
       </c>
       <c r="E436" s="6" t="str">
         <f>IF($D436="","",VLOOKUP($D436,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9067,13 +9066,13 @@
         <v>126</v>
       </c>
       <c r="B437" s="9">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D437" s="9">
-        <v>4520490</v>
+        <v>4585763</v>
       </c>
       <c r="E437" s="6" t="str">
         <f>IF($D437="","",VLOOKUP($D437,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9085,13 +9084,13 @@
         <v>126</v>
       </c>
       <c r="B438" s="9">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D438" s="9">
-        <v>4472197</v>
+        <v>4520490</v>
       </c>
       <c r="E438" s="6" t="str">
         <f>IF($D438="","",VLOOKUP($D438,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9103,13 +9102,13 @@
         <v>126</v>
       </c>
       <c r="B439" s="9">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="D439" s="9">
-        <v>4454646</v>
+        <v>4472197</v>
       </c>
       <c r="E439" s="6" t="str">
         <f>IF($D439="","",VLOOKUP($D439,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9121,13 +9120,13 @@
         <v>126</v>
       </c>
       <c r="B440" s="9">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D440" s="9">
-        <v>4432064</v>
+        <v>4454646</v>
       </c>
       <c r="E440" s="6" t="str">
         <f>IF($D440="","",VLOOKUP($D440,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9139,13 +9138,13 @@
         <v>126</v>
       </c>
       <c r="B441" s="9">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D441" s="9">
-        <v>4264172</v>
+        <v>4432064</v>
       </c>
       <c r="E441" s="6" t="str">
         <f>IF($D441="","",VLOOKUP($D441,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9157,13 +9156,13 @@
         <v>126</v>
       </c>
       <c r="B442" s="9">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="D442" s="9">
-        <v>4118340</v>
+        <v>4264172</v>
       </c>
       <c r="E442" s="6" t="str">
         <f>IF($D442="","",VLOOKUP($D442,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9175,13 +9174,13 @@
         <v>126</v>
       </c>
       <c r="B443" s="9">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="D443" s="9">
-        <v>3936283</v>
+        <v>4118340</v>
       </c>
       <c r="E443" s="6" t="str">
         <f>IF($D443="","",VLOOKUP($D443,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9193,13 +9192,13 @@
         <v>126</v>
       </c>
       <c r="B444" s="9">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="D444" s="9">
-        <v>3811500</v>
+        <v>3936283</v>
       </c>
       <c r="E444" s="6" t="str">
         <f>IF($D444="","",VLOOKUP($D444,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9211,13 +9210,13 @@
         <v>126</v>
       </c>
       <c r="B445" s="9">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D445" s="9">
-        <v>3741493</v>
+        <v>3811500</v>
       </c>
       <c r="E445" s="6" t="str">
         <f>IF($D445="","",VLOOKUP($D445,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9229,13 +9228,13 @@
         <v>126</v>
       </c>
       <c r="B446" s="9">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D446" s="9">
-        <v>3713921</v>
+        <v>3741493</v>
       </c>
       <c r="E446" s="6" t="str">
         <f>IF($D446="","",VLOOKUP($D446,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9247,13 +9246,13 @@
         <v>126</v>
       </c>
       <c r="B447" s="9">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="D447" s="9">
-        <v>3610131</v>
+        <v>3713921</v>
       </c>
       <c r="E447" s="6" t="str">
         <f>IF($D447="","",VLOOKUP($D447,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9265,13 +9264,13 @@
         <v>126</v>
       </c>
       <c r="B448" s="9">
-        <v>54</v>
-      </c>
-      <c r="C448" s="10">
-        <v>1090</v>
+        <v>53</v>
+      </c>
+      <c r="C448" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="D448" s="9">
-        <v>3471939</v>
+        <v>3610131</v>
       </c>
       <c r="E448" s="6" t="str">
         <f>IF($D448="","",VLOOKUP($D448,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9283,13 +9282,13 @@
         <v>126</v>
       </c>
       <c r="B449" s="9">
-        <v>55</v>
-      </c>
-      <c r="C449" s="2" t="s">
-        <v>83</v>
+        <v>54</v>
+      </c>
+      <c r="C449" s="10">
+        <v>1090</v>
       </c>
       <c r="D449" s="9">
-        <v>3449277</v>
+        <v>3471939</v>
       </c>
       <c r="E449" s="6" t="str">
         <f>IF($D449="","",VLOOKUP($D449,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9301,13 +9300,13 @@
         <v>126</v>
       </c>
       <c r="B450" s="9">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="D450" s="9">
-        <v>3355011</v>
+        <v>3449277</v>
       </c>
       <c r="E450" s="6" t="str">
         <f>IF($D450="","",VLOOKUP($D450,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9319,13 +9318,13 @@
         <v>126</v>
       </c>
       <c r="B451" s="9">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="D451" s="9">
-        <v>3348356</v>
+        <v>3355011</v>
       </c>
       <c r="E451" s="6" t="str">
         <f>IF($D451="","",VLOOKUP($D451,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9337,13 +9336,13 @@
         <v>126</v>
       </c>
       <c r="B452" s="9">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="D452" s="9">
-        <v>2818744</v>
+        <v>3348356</v>
       </c>
       <c r="E452" s="6" t="str">
         <f>IF($D452="","",VLOOKUP($D452,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9355,13 +9354,13 @@
         <v>126</v>
       </c>
       <c r="B453" s="9">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="D453" s="9">
-        <v>2676764</v>
+        <v>2818744</v>
       </c>
       <c r="E453" s="6" t="str">
         <f>IF($D453="","",VLOOKUP($D453,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9373,17 +9372,17 @@
         <v>126</v>
       </c>
       <c r="B454" s="9">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="D454" s="9">
-        <v>2595175</v>
+        <v>2676764</v>
       </c>
       <c r="E454" s="6" t="str">
         <f>IF($D454="","",VLOOKUP($D454,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>7단계</v>
+        <v>8단계</v>
       </c>
     </row>
     <row r="455" spans="1:5">
@@ -9391,13 +9390,13 @@
         <v>126</v>
       </c>
       <c r="B455" s="9">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D455" s="9">
-        <v>2505960</v>
+        <v>2595175</v>
       </c>
       <c r="E455" s="6" t="str">
         <f>IF($D455="","",VLOOKUP($D455,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9409,17 +9408,17 @@
         <v>126</v>
       </c>
       <c r="B456" s="9">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="D456" s="9">
-        <v>2181924</v>
+        <v>2505960</v>
       </c>
       <c r="E456" s="6" t="str">
         <f>IF($D456="","",VLOOKUP($D456,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
+        <v>7단계</v>
       </c>
     </row>
     <row r="457" spans="1:5">
@@ -9427,13 +9426,13 @@
         <v>126</v>
       </c>
       <c r="B457" s="9">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D457" s="9">
-        <v>2020453</v>
+        <v>2181924</v>
       </c>
       <c r="E457" s="6" t="str">
         <f>IF($D457="","",VLOOKUP($D457,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9445,13 +9444,13 @@
         <v>126</v>
       </c>
       <c r="B458" s="9">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="D458" s="9">
-        <v>1951212</v>
+        <v>2020453</v>
       </c>
       <c r="E458" s="6" t="str">
         <f>IF($D458="","",VLOOKUP($D458,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9463,13 +9462,13 @@
         <v>126</v>
       </c>
       <c r="B459" s="9">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D459" s="9">
-        <v>1775577</v>
+        <v>1951212</v>
       </c>
       <c r="E459" s="6" t="str">
         <f>IF($D459="","",VLOOKUP($D459,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9481,13 +9480,13 @@
         <v>126</v>
       </c>
       <c r="B460" s="9">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D460" s="9">
-        <v>1535970</v>
+        <v>1775577</v>
       </c>
       <c r="E460" s="6" t="str">
         <f>IF($D460="","",VLOOKUP($D460,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9499,13 +9498,13 @@
         <v>126</v>
       </c>
       <c r="B461" s="9">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="D461" s="9">
-        <v>1235026</v>
+        <v>1535970</v>
       </c>
       <c r="E461" s="6" t="str">
         <f>IF($D461="","",VLOOKUP($D461,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9513,32 +9512,32 @@
       </c>
     </row>
     <row r="462" spans="1:5">
-      <c r="A462" s="12">
-        <v>46195</v>
-      </c>
-      <c r="B462" t="s">
-        <v>129</v>
+      <c r="A462" t="s">
+        <v>126</v>
+      </c>
+      <c r="B462" s="9">
+        <v>67</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>130</v>
+        <v>92</v>
+      </c>
+      <c r="D462" s="9">
+        <v>1235026</v>
+      </c>
+      <c r="E462" s="6" t="str">
+        <f>IF($D462="","",VLOOKUP($D462,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
       </c>
     </row>
     <row r="463" spans="1:5">
       <c r="A463" s="12">
         <v>46195</v>
       </c>
-      <c r="B463" s="9">
-        <v>1</v>
+      <c r="B463" t="s">
+        <v>129</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D463" s="9">
-        <v>15645750</v>
-      </c>
-      <c r="E463" s="6" t="str">
-        <f>IF($D463="","",VLOOKUP($D463,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>130</v>
       </c>
     </row>
     <row r="464" spans="1:5">
@@ -9546,13 +9545,13 @@
         <v>46195</v>
       </c>
       <c r="B464" s="9">
-        <v>2</v>
-      </c>
-      <c r="C464" t="s">
-        <v>34</v>
+        <v>1</v>
+      </c>
+      <c r="C464" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="D464" s="9">
-        <v>13978410</v>
+        <v>15645750</v>
       </c>
       <c r="E464" s="6" t="str">
         <f>IF($D464="","",VLOOKUP($D464,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -9564,16 +9563,34 @@
         <v>46195</v>
       </c>
       <c r="B465" s="9">
-        <v>3</v>
-      </c>
-      <c r="C465" s="2" t="s">
-        <v>107</v>
+        <v>2</v>
+      </c>
+      <c r="C465" t="s">
+        <v>34</v>
       </c>
       <c r="D465" s="9">
-        <v>13088206</v>
+        <v>13978410</v>
       </c>
       <c r="E465" s="6" t="str">
         <f>IF($D465="","",VLOOKUP($D465,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5">
+      <c r="A466" s="12">
+        <v>46195</v>
+      </c>
+      <c r="B466" s="9">
+        <v>3</v>
+      </c>
+      <c r="C466" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D466" s="9">
+        <v>13088206</v>
+      </c>
+      <c r="E466" s="6" t="str">
+        <f>IF($D466="","",VLOOKUP($D466,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
     </row>

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A2C673C-A07D-4600-95F7-FF8EF2B0D263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D3862A-518A-4712-9855-79132DCB83F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="132">
   <si>
     <t>하한점수</t>
   </si>
@@ -1412,7 +1412,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E466"/>
+  <dimension ref="A1:E463"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="14.875" customWidth="1"/>
@@ -3535,35 +3535,31 @@
         <v>5</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="16.5" customHeight="1">
+    <row r="126" spans="1:5">
       <c r="A126" t="s">
         <v>94</v>
       </c>
-      <c r="B126">
-        <v>1</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D126">
-        <v>76513151</v>
-      </c>
-      <c r="E126" t="s">
-        <v>19</v>
-      </c>
+      <c r="B126" t="s">
+        <v>129</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D126" s="9"/>
+      <c r="E126" s="6"/>
     </row>
     <row r="127" spans="1:5" ht="16.5" customHeight="1">
       <c r="A127" t="s">
         <v>94</v>
       </c>
       <c r="B127">
-        <v>2</v>
-      </c>
-      <c r="C127" t="s">
-        <v>48</v>
+        <v>1</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="D127">
-        <v>62254586</v>
+        <v>76513151</v>
       </c>
       <c r="E127" t="s">
         <v>19</v>
@@ -3574,13 +3570,13 @@
         <v>94</v>
       </c>
       <c r="B128">
-        <v>3</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>52</v>
+        <v>2</v>
+      </c>
+      <c r="C128" t="s">
+        <v>48</v>
       </c>
       <c r="D128">
-        <v>36598969</v>
+        <v>62254586</v>
       </c>
       <c r="E128" t="s">
         <v>19</v>
@@ -3591,13 +3587,13 @@
         <v>94</v>
       </c>
       <c r="B129">
-        <v>4</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>32</v>
+        <v>3</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="D129">
-        <v>26859795</v>
+        <v>36598969</v>
       </c>
       <c r="E129" t="s">
         <v>19</v>
@@ -3608,13 +3604,13 @@
         <v>94</v>
       </c>
       <c r="B130">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="D130">
-        <v>22027625</v>
+        <v>26859795</v>
       </c>
       <c r="E130" t="s">
         <v>19</v>
@@ -3625,13 +3621,13 @@
         <v>94</v>
       </c>
       <c r="B131">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="D131">
-        <v>19336746</v>
+        <v>22027625</v>
       </c>
       <c r="E131" t="s">
         <v>19</v>
@@ -3642,13 +3638,13 @@
         <v>94</v>
       </c>
       <c r="B132">
-        <v>7</v>
-      </c>
-      <c r="C132" t="s">
-        <v>34</v>
+        <v>6</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="D132">
-        <v>17008882</v>
+        <v>19336746</v>
       </c>
       <c r="E132" t="s">
         <v>19</v>
@@ -3659,13 +3655,13 @@
         <v>94</v>
       </c>
       <c r="B133">
-        <v>8</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>38</v>
+        <v>7</v>
+      </c>
+      <c r="C133" t="s">
+        <v>34</v>
       </c>
       <c r="D133">
-        <v>16620269</v>
+        <v>17008882</v>
       </c>
       <c r="E133" t="s">
         <v>19</v>
@@ -3676,13 +3672,13 @@
         <v>94</v>
       </c>
       <c r="B134">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="D134">
-        <v>15971399</v>
+        <v>16620269</v>
       </c>
       <c r="E134" t="s">
         <v>19</v>
@@ -3693,13 +3689,13 @@
         <v>94</v>
       </c>
       <c r="B135">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="D135">
-        <v>15579579</v>
+        <v>15971399</v>
       </c>
       <c r="E135" t="s">
         <v>19</v>
@@ -3710,13 +3706,13 @@
         <v>94</v>
       </c>
       <c r="B136">
-        <v>11</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>50</v>
+        <v>10</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="D136">
-        <v>15166835</v>
+        <v>15579579</v>
       </c>
       <c r="E136" t="s">
         <v>19</v>
@@ -3727,13 +3723,13 @@
         <v>94</v>
       </c>
       <c r="B137">
-        <v>12</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>61</v>
+        <v>11</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="D137">
-        <v>15136017</v>
+        <v>15166835</v>
       </c>
       <c r="E137" t="s">
         <v>19</v>
@@ -3744,13 +3740,13 @@
         <v>94</v>
       </c>
       <c r="B138">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="D138">
-        <v>15045625</v>
+        <v>15136017</v>
       </c>
       <c r="E138" t="s">
         <v>19</v>
@@ -3761,13 +3757,13 @@
         <v>94</v>
       </c>
       <c r="B139">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="D139">
-        <v>11929975</v>
+        <v>15045625</v>
       </c>
       <c r="E139" t="s">
         <v>19</v>
@@ -3778,13 +3774,13 @@
         <v>94</v>
       </c>
       <c r="B140">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="D140">
-        <v>11703867</v>
+        <v>11929975</v>
       </c>
       <c r="E140" t="s">
         <v>19</v>
@@ -3795,13 +3791,13 @@
         <v>94</v>
       </c>
       <c r="B141">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="D141">
-        <v>11641804</v>
+        <v>11703867</v>
       </c>
       <c r="E141" t="s">
         <v>19</v>
@@ -3812,13 +3808,13 @@
         <v>94</v>
       </c>
       <c r="B142">
-        <v>17</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>54</v>
+        <v>16</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="D142">
-        <v>11224132</v>
+        <v>11641804</v>
       </c>
       <c r="E142" t="s">
         <v>19</v>
@@ -3829,13 +3825,13 @@
         <v>94</v>
       </c>
       <c r="B143">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="D143">
-        <v>11128193</v>
+        <v>11224132</v>
       </c>
       <c r="E143" t="s">
         <v>19</v>
@@ -3846,13 +3842,13 @@
         <v>94</v>
       </c>
       <c r="B144">
-        <v>19</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>37</v>
+        <v>18</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="D144">
-        <v>10907771</v>
+        <v>11128193</v>
       </c>
       <c r="E144" t="s">
         <v>19</v>
@@ -3863,13 +3859,13 @@
         <v>94</v>
       </c>
       <c r="B145">
-        <v>20</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>41</v>
+        <v>19</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="D145">
-        <v>10606882</v>
+        <v>10907771</v>
       </c>
       <c r="E145" t="s">
         <v>19</v>
@@ -3880,13 +3876,13 @@
         <v>94</v>
       </c>
       <c r="B146">
-        <v>21</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="D146">
-        <v>10422796</v>
+        <v>10606882</v>
       </c>
       <c r="E146" t="s">
         <v>19</v>
@@ -3897,13 +3893,13 @@
         <v>94</v>
       </c>
       <c r="B147">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D147">
-        <v>10412768</v>
+        <v>10422796</v>
       </c>
       <c r="E147" t="s">
         <v>19</v>
@@ -3914,13 +3910,13 @@
         <v>94</v>
       </c>
       <c r="B148">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="D148">
-        <v>10128124</v>
+        <v>10412768</v>
       </c>
       <c r="E148" t="s">
         <v>19</v>
@@ -3931,13 +3927,13 @@
         <v>94</v>
       </c>
       <c r="B149">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="D149">
-        <v>9706739</v>
+        <v>10128124</v>
       </c>
       <c r="E149" t="s">
         <v>19</v>
@@ -3948,13 +3944,13 @@
         <v>94</v>
       </c>
       <c r="B150">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>102</v>
+        <v>47</v>
       </c>
       <c r="D150">
-        <v>9164119</v>
+        <v>9706739</v>
       </c>
       <c r="E150" t="s">
         <v>19</v>
@@ -3965,13 +3961,13 @@
         <v>94</v>
       </c>
       <c r="B151">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D151">
-        <v>8999382</v>
+        <v>9164119</v>
       </c>
       <c r="E151" t="s">
         <v>19</v>
@@ -3982,13 +3978,13 @@
         <v>94</v>
       </c>
       <c r="B152">
-        <v>27</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="D152">
-        <v>8596217</v>
+        <v>8999382</v>
       </c>
       <c r="E152" t="s">
         <v>19</v>
@@ -3999,13 +3995,13 @@
         <v>94</v>
       </c>
       <c r="B153">
-        <v>28</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>79</v>
+        <v>27</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="D153">
-        <v>8456726</v>
+        <v>8596217</v>
       </c>
       <c r="E153" t="s">
         <v>19</v>
@@ -4016,13 +4012,13 @@
         <v>94</v>
       </c>
       <c r="B154">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D154">
-        <v>8220352</v>
+        <v>8456726</v>
       </c>
       <c r="E154" t="s">
         <v>19</v>
@@ -4033,13 +4029,13 @@
         <v>94</v>
       </c>
       <c r="B155">
-        <v>30</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>103</v>
+        <v>29</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="D155">
-        <v>8154156</v>
+        <v>8220352</v>
       </c>
       <c r="E155" t="s">
         <v>19</v>
@@ -4050,13 +4046,13 @@
         <v>94</v>
       </c>
       <c r="B156">
-        <v>31</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>72</v>
+        <v>30</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="D156">
-        <v>8127020</v>
+        <v>8154156</v>
       </c>
       <c r="E156" t="s">
         <v>19</v>
@@ -4067,13 +4063,13 @@
         <v>94</v>
       </c>
       <c r="B157">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="D157">
-        <v>7952273</v>
+        <v>8127020</v>
       </c>
       <c r="E157" t="s">
         <v>19</v>
@@ -4084,13 +4080,13 @@
         <v>94</v>
       </c>
       <c r="B158">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D158">
-        <v>7918857</v>
+        <v>7952273</v>
       </c>
       <c r="E158" t="s">
         <v>19</v>
@@ -4101,13 +4097,13 @@
         <v>94</v>
       </c>
       <c r="B159">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="D159">
-        <v>7909501</v>
+        <v>7918857</v>
       </c>
       <c r="E159" t="s">
         <v>19</v>
@@ -4118,13 +4114,13 @@
         <v>94</v>
       </c>
       <c r="B160">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="D160">
-        <v>7876636</v>
+        <v>7909501</v>
       </c>
       <c r="E160" t="s">
         <v>19</v>
@@ -4135,13 +4131,13 @@
         <v>94</v>
       </c>
       <c r="B161">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="D161">
-        <v>7824653</v>
+        <v>7876636</v>
       </c>
       <c r="E161" t="s">
         <v>19</v>
@@ -4152,13 +4148,13 @@
         <v>94</v>
       </c>
       <c r="B162">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>42</v>
+        <v>106</v>
       </c>
       <c r="D162">
-        <v>7823884</v>
+        <v>7824653</v>
       </c>
       <c r="E162" t="s">
         <v>19</v>
@@ -4169,13 +4165,13 @@
         <v>94</v>
       </c>
       <c r="B163">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="D163">
-        <v>7679597</v>
+        <v>7823884</v>
       </c>
       <c r="E163" t="s">
         <v>19</v>
@@ -4186,13 +4182,13 @@
         <v>94</v>
       </c>
       <c r="B164">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D164">
-        <v>7635056</v>
+        <v>7679597</v>
       </c>
       <c r="E164" t="s">
         <v>19</v>
@@ -4203,13 +4199,13 @@
         <v>94</v>
       </c>
       <c r="B165">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D165">
-        <v>7579677</v>
+        <v>7635056</v>
       </c>
       <c r="E165" t="s">
         <v>19</v>
@@ -4220,13 +4216,13 @@
         <v>94</v>
       </c>
       <c r="B166">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="D166">
-        <v>7552044</v>
+        <v>7579677</v>
       </c>
       <c r="E166" t="s">
         <v>19</v>
@@ -4237,13 +4233,13 @@
         <v>94</v>
       </c>
       <c r="B167">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D167">
-        <v>7462230</v>
+        <v>7552044</v>
       </c>
       <c r="E167" t="s">
         <v>19</v>
@@ -4254,13 +4250,13 @@
         <v>94</v>
       </c>
       <c r="B168">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D168">
-        <v>7423633</v>
+        <v>7462230</v>
       </c>
       <c r="E168" t="s">
         <v>19</v>
@@ -4271,13 +4267,13 @@
         <v>94</v>
       </c>
       <c r="B169">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="D169">
-        <v>7327050</v>
+        <v>7423633</v>
       </c>
       <c r="E169" t="s">
         <v>19</v>
@@ -4288,16 +4284,16 @@
         <v>94</v>
       </c>
       <c r="B170">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D170">
-        <v>6678842</v>
+        <v>7327050</v>
       </c>
       <c r="E170" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="16.5" customHeight="1">
@@ -4305,13 +4301,13 @@
         <v>94</v>
       </c>
       <c r="B171">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="D171">
-        <v>6177989</v>
+        <v>6678842</v>
       </c>
       <c r="E171" t="s">
         <v>17</v>
@@ -4322,13 +4318,13 @@
         <v>94</v>
       </c>
       <c r="B172">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="D172">
-        <v>5901298</v>
+        <v>6177989</v>
       </c>
       <c r="E172" t="s">
         <v>17</v>
@@ -4339,13 +4335,13 @@
         <v>94</v>
       </c>
       <c r="B173">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="D173">
-        <v>5097585</v>
+        <v>5901298</v>
       </c>
       <c r="E173" t="s">
         <v>17</v>
@@ -4356,13 +4352,13 @@
         <v>94</v>
       </c>
       <c r="B174">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="D174">
-        <v>5036088</v>
+        <v>5097585</v>
       </c>
       <c r="E174" t="s">
         <v>17</v>
@@ -4373,13 +4369,13 @@
         <v>94</v>
       </c>
       <c r="B175">
-        <v>50</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>69</v>
+        <v>49</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="D175">
-        <v>4821347</v>
+        <v>5036088</v>
       </c>
       <c r="E175" t="s">
         <v>17</v>
@@ -4390,13 +4386,13 @@
         <v>94</v>
       </c>
       <c r="B176">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D176">
-        <v>4599953</v>
+        <v>4821347</v>
       </c>
       <c r="E176" t="s">
         <v>17</v>
@@ -4407,13 +4403,13 @@
         <v>94</v>
       </c>
       <c r="B177">
-        <v>52</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>65</v>
+        <v>51</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="D177">
-        <v>4332112</v>
+        <v>4599953</v>
       </c>
       <c r="E177" t="s">
         <v>17</v>
@@ -4424,13 +4420,13 @@
         <v>94</v>
       </c>
       <c r="B178">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D178">
-        <v>4235009</v>
+        <v>4332112</v>
       </c>
       <c r="E178" t="s">
         <v>17</v>
@@ -4441,13 +4437,13 @@
         <v>94</v>
       </c>
       <c r="B179">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="D179">
-        <v>4226803</v>
+        <v>4235009</v>
       </c>
       <c r="E179" t="s">
         <v>17</v>
@@ -4458,13 +4454,13 @@
         <v>94</v>
       </c>
       <c r="B180">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D180">
-        <v>3992666</v>
+        <v>4226803</v>
       </c>
       <c r="E180" t="s">
         <v>17</v>
@@ -4475,13 +4471,13 @@
         <v>94</v>
       </c>
       <c r="B181">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="D181">
-        <v>3935236</v>
+        <v>3992666</v>
       </c>
       <c r="E181" t="s">
         <v>17</v>
@@ -4492,13 +4488,13 @@
         <v>94</v>
       </c>
       <c r="B182">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="D182">
-        <v>3819189</v>
+        <v>3935236</v>
       </c>
       <c r="E182" t="s">
         <v>17</v>
@@ -4509,13 +4505,13 @@
         <v>94</v>
       </c>
       <c r="B183">
-        <v>58</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>88</v>
+        <v>57</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="D183">
-        <v>2896389</v>
+        <v>3819189</v>
       </c>
       <c r="E183" t="s">
         <v>17</v>
@@ -4526,13 +4522,13 @@
         <v>94</v>
       </c>
       <c r="B184">
-        <v>59</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>82</v>
+        <v>58</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="D184">
-        <v>2645896</v>
+        <v>2896389</v>
       </c>
       <c r="E184" t="s">
         <v>17</v>
@@ -4543,16 +4539,16 @@
         <v>94</v>
       </c>
       <c r="B185">
-        <v>60</v>
-      </c>
-      <c r="C185" t="s">
-        <v>89</v>
+        <v>59</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="D185">
-        <v>2195612</v>
+        <v>2645896</v>
       </c>
       <c r="E185" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="16.5" customHeight="1">
@@ -4560,13 +4556,13 @@
         <v>94</v>
       </c>
       <c r="B186">
-        <v>61</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>71</v>
+        <v>60</v>
+      </c>
+      <c r="C186" t="s">
+        <v>89</v>
       </c>
       <c r="D186">
-        <v>1908787</v>
+        <v>2195612</v>
       </c>
       <c r="E186" t="s">
         <v>13</v>
@@ -4577,13 +4573,13 @@
         <v>94</v>
       </c>
       <c r="B187">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D187">
-        <v>1890847</v>
+        <v>1908787</v>
       </c>
       <c r="E187" t="s">
         <v>13</v>
@@ -4594,13 +4590,13 @@
         <v>94</v>
       </c>
       <c r="B188">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D188">
-        <v>1772463</v>
+        <v>1890847</v>
       </c>
       <c r="E188" t="s">
         <v>13</v>
@@ -4611,13 +4607,13 @@
         <v>94</v>
       </c>
       <c r="B189">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D189">
-        <v>1472500</v>
+        <v>1772463</v>
       </c>
       <c r="E189" t="s">
         <v>13</v>
@@ -4628,13 +4624,13 @@
         <v>94</v>
       </c>
       <c r="B190">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D190">
-        <v>1425274</v>
+        <v>1472500</v>
       </c>
       <c r="E190" t="s">
         <v>13</v>
@@ -4645,13 +4641,13 @@
         <v>94</v>
       </c>
       <c r="B191">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D191">
-        <v>1226829</v>
+        <v>1425274</v>
       </c>
       <c r="E191" t="s">
         <v>13</v>
@@ -4662,34 +4658,33 @@
         <v>94</v>
       </c>
       <c r="B192">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D192">
-        <v>460000</v>
+        <v>1226829</v>
       </c>
       <c r="E192" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="193" spans="1:5" ht="16.5" customHeight="1">
       <c r="A193" t="s">
-        <v>110</v>
-      </c>
-      <c r="B193" s="3">
-        <v>1</v>
-      </c>
-      <c r="C193" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D193" s="5">
-        <v>15915600</v>
-      </c>
-      <c r="E193" s="6" t="str">
-        <f>IF($D193="","",VLOOKUP($D193,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>94</v>
+      </c>
+      <c r="B193">
+        <v>67</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D193">
+        <v>460000</v>
+      </c>
+      <c r="E193" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="194" spans="1:5" ht="16.5" customHeight="1">
@@ -4697,13 +4692,13 @@
         <v>110</v>
       </c>
       <c r="B194" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="D194" s="5">
-        <v>12925350</v>
+        <v>15915600</v>
       </c>
       <c r="E194" s="6" t="str">
         <f>IF($D194="","",VLOOKUP($D194,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -4715,13 +4710,13 @@
         <v>110</v>
       </c>
       <c r="B195" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D195" s="5">
-        <v>12016650</v>
+        <v>12925350</v>
       </c>
       <c r="E195" s="6" t="str">
         <f>IF($D195="","",VLOOKUP($D195,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -4733,13 +4728,13 @@
         <v>110</v>
       </c>
       <c r="B196" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="D196" s="5">
-        <v>9907350</v>
+        <v>12016650</v>
       </c>
       <c r="E196" s="6" t="str">
         <f>IF($D196="","",VLOOKUP($D196,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -4751,13 +4746,13 @@
         <v>110</v>
       </c>
       <c r="B197" s="3">
-        <v>5</v>
-      </c>
-      <c r="C197" s="7" t="s">
-        <v>43</v>
+        <v>4</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="D197" s="5">
-        <v>9868650</v>
+        <v>9907350</v>
       </c>
       <c r="E197" s="6" t="str">
         <f>IF($D197="","",VLOOKUP($D197,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -4769,13 +4764,13 @@
         <v>110</v>
       </c>
       <c r="B198" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D198" s="5">
-        <v>9143700</v>
+        <v>9868650</v>
       </c>
       <c r="E198" s="6" t="str">
         <f>IF($D198="","",VLOOKUP($D198,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -4787,13 +4782,13 @@
         <v>110</v>
       </c>
       <c r="B199" s="3">
-        <v>7</v>
-      </c>
-      <c r="C199" s="8" t="s">
-        <v>111</v>
+        <v>6</v>
+      </c>
+      <c r="C199" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="D199" s="5">
-        <v>9141450</v>
+        <v>9143700</v>
       </c>
       <c r="E199" s="6" t="str">
         <f>IF($D199="","",VLOOKUP($D199,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -4805,13 +4800,13 @@
         <v>110</v>
       </c>
       <c r="B200" s="3">
-        <v>8</v>
-      </c>
-      <c r="C200" s="4" t="s">
-        <v>46</v>
+        <v>7</v>
+      </c>
+      <c r="C200" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="D200" s="5">
-        <v>9065250</v>
+        <v>9141450</v>
       </c>
       <c r="E200" s="6" t="str">
         <f>IF($D200="","",VLOOKUP($D200,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -4823,13 +4818,13 @@
         <v>110</v>
       </c>
       <c r="B201" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="D201" s="5">
-        <v>9017250</v>
+        <v>9065250</v>
       </c>
       <c r="E201" s="6" t="str">
         <f>IF($D201="","",VLOOKUP($D201,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -4841,13 +4836,13 @@
         <v>110</v>
       </c>
       <c r="B202" s="3">
-        <v>10</v>
-      </c>
-      <c r="C202" s="7" t="s">
-        <v>50</v>
+        <v>9</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="D202" s="5">
-        <v>8908800</v>
+        <v>9017250</v>
       </c>
       <c r="E202" s="6" t="str">
         <f>IF($D202="","",VLOOKUP($D202,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -4859,13 +4854,13 @@
         <v>110</v>
       </c>
       <c r="B203" s="3">
-        <v>11</v>
-      </c>
-      <c r="C203" s="4" t="s">
-        <v>37</v>
+        <v>10</v>
+      </c>
+      <c r="C203" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D203" s="5">
-        <v>8266050</v>
+        <v>8908800</v>
       </c>
       <c r="E203" s="6" t="str">
         <f>IF($D203="","",VLOOKUP($D203,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -4877,13 +4872,13 @@
         <v>110</v>
       </c>
       <c r="B204" s="3">
-        <v>12</v>
-      </c>
-      <c r="C204" s="7" t="s">
-        <v>41</v>
+        <v>11</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="D204" s="5">
-        <v>8226750</v>
+        <v>8266050</v>
       </c>
       <c r="E204" s="6" t="str">
         <f>IF($D204="","",VLOOKUP($D204,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -4895,13 +4890,13 @@
         <v>110</v>
       </c>
       <c r="B205" s="3">
-        <v>13</v>
-      </c>
-      <c r="C205" s="4" t="s">
-        <v>104</v>
+        <v>12</v>
+      </c>
+      <c r="C205" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="D205" s="5">
-        <v>8125259</v>
+        <v>8226750</v>
       </c>
       <c r="E205" s="6" t="str">
         <f>IF($D205="","",VLOOKUP($D205,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -4913,13 +4908,13 @@
         <v>110</v>
       </c>
       <c r="B206" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="D206" s="5">
-        <v>7855412</v>
+        <v>8125259</v>
       </c>
       <c r="E206" s="6" t="str">
         <f>IF($D206="","",VLOOKUP($D206,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -4931,13 +4926,13 @@
         <v>110</v>
       </c>
       <c r="B207" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="D207" s="5">
-        <v>7740750</v>
+        <v>7855412</v>
       </c>
       <c r="E207" s="6" t="str">
         <f>IF($D207="","",VLOOKUP($D207,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -4949,13 +4944,13 @@
         <v>110</v>
       </c>
       <c r="B208" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="D208" s="5">
-        <v>7716900</v>
+        <v>7740750</v>
       </c>
       <c r="E208" s="6" t="str">
         <f>IF($D208="","",VLOOKUP($D208,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -4967,13 +4962,13 @@
         <v>110</v>
       </c>
       <c r="B209" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D209" s="5">
-        <v>7697397</v>
+        <v>7716900</v>
       </c>
       <c r="E209" s="6" t="str">
         <f>IF($D209="","",VLOOKUP($D209,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -4985,13 +4980,13 @@
         <v>110</v>
       </c>
       <c r="B210" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="D210" s="5">
-        <v>7694109</v>
+        <v>7697397</v>
       </c>
       <c r="E210" s="6" t="str">
         <f>IF($D210="","",VLOOKUP($D210,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5003,13 +4998,13 @@
         <v>110</v>
       </c>
       <c r="B211" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D211" s="5">
-        <v>7624294</v>
+        <v>7694109</v>
       </c>
       <c r="E211" s="6" t="str">
         <f>IF($D211="","",VLOOKUP($D211,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5021,13 +5016,13 @@
         <v>110</v>
       </c>
       <c r="B212" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="D212" s="5">
-        <v>7548021</v>
+        <v>7624294</v>
       </c>
       <c r="E212" s="6" t="str">
         <f>IF($D212="","",VLOOKUP($D212,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5039,13 +5034,13 @@
         <v>110</v>
       </c>
       <c r="B213" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="D213" s="5">
-        <v>7514973</v>
+        <v>7548021</v>
       </c>
       <c r="E213" s="6" t="str">
         <f>IF($D213="","",VLOOKUP($D213,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5057,13 +5052,13 @@
         <v>110</v>
       </c>
       <c r="B214" s="3">
-        <v>22</v>
-      </c>
-      <c r="C214" s="7" t="s">
-        <v>100</v>
+        <v>21</v>
+      </c>
+      <c r="C214" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="D214" s="5">
-        <v>7392720</v>
+        <v>7514973</v>
       </c>
       <c r="E214" s="6" t="str">
         <f>IF($D214="","",VLOOKUP($D214,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5075,13 +5070,13 @@
         <v>110</v>
       </c>
       <c r="B215" s="3">
-        <v>23</v>
-      </c>
-      <c r="C215" s="4" t="s">
-        <v>40</v>
+        <v>22</v>
+      </c>
+      <c r="C215" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="D215" s="5">
-        <v>7368735</v>
+        <v>7392720</v>
       </c>
       <c r="E215" s="6" t="str">
         <f>IF($D215="","",VLOOKUP($D215,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5093,13 +5088,13 @@
         <v>110</v>
       </c>
       <c r="B216" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D216" s="5">
-        <v>7299150</v>
+        <v>7368735</v>
       </c>
       <c r="E216" s="6" t="str">
         <f>IF($D216="","",VLOOKUP($D216,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5111,13 +5106,13 @@
         <v>110</v>
       </c>
       <c r="B217" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>107</v>
+        <v>38</v>
       </c>
       <c r="D217" s="5">
-        <v>7285842</v>
+        <v>7299150</v>
       </c>
       <c r="E217" s="6" t="str">
         <f>IF($D217="","",VLOOKUP($D217,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5129,13 +5124,13 @@
         <v>110</v>
       </c>
       <c r="B218" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>47</v>
+        <v>107</v>
       </c>
       <c r="D218" s="5">
-        <v>7252456</v>
+        <v>7285842</v>
       </c>
       <c r="E218" s="6" t="str">
         <f>IF($D218="","",VLOOKUP($D218,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5147,13 +5142,13 @@
         <v>110</v>
       </c>
       <c r="B219" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="D219" s="5">
-        <v>7210500</v>
+        <v>7252456</v>
       </c>
       <c r="E219" s="6" t="str">
         <f>IF($D219="","",VLOOKUP($D219,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5165,17 +5160,17 @@
         <v>110</v>
       </c>
       <c r="B220" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="D220" s="5">
-        <v>7095450</v>
+        <v>7210500</v>
       </c>
       <c r="E220" s="6" t="str">
         <f>IF($D220="","",VLOOKUP($D220,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>9단계</v>
       </c>
     </row>
     <row r="221" spans="1:5" ht="16.5" customHeight="1">
@@ -5183,13 +5178,13 @@
         <v>110</v>
       </c>
       <c r="B221" s="3">
-        <v>29</v>
-      </c>
-      <c r="C221" s="7" t="s">
-        <v>103</v>
+        <v>28</v>
+      </c>
+      <c r="C221" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="D221" s="5">
-        <v>5739081</v>
+        <v>7095450</v>
       </c>
       <c r="E221" s="6" t="str">
         <f>IF($D221="","",VLOOKUP($D221,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5201,13 +5196,13 @@
         <v>110</v>
       </c>
       <c r="B222" s="3">
-        <v>30</v>
-      </c>
-      <c r="C222" s="4" t="s">
-        <v>101</v>
+        <v>29</v>
+      </c>
+      <c r="C222" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="D222" s="5">
-        <v>5561285</v>
+        <v>5739081</v>
       </c>
       <c r="E222" s="6" t="str">
         <f>IF($D222="","",VLOOKUP($D222,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5219,13 +5214,13 @@
         <v>110</v>
       </c>
       <c r="B223" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D223" s="5">
-        <v>5434650</v>
+        <v>5561285</v>
       </c>
       <c r="E223" s="6" t="str">
         <f>IF($D223="","",VLOOKUP($D223,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5237,13 +5232,13 @@
         <v>110</v>
       </c>
       <c r="B224" s="3">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D224" s="5">
-        <v>5171951</v>
+        <v>5434650</v>
       </c>
       <c r="E224" s="6" t="str">
         <f>IF($D224="","",VLOOKUP($D224,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5255,13 +5250,13 @@
         <v>110</v>
       </c>
       <c r="B225" s="3">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="D225" s="5">
-        <v>5091005</v>
+        <v>5171951</v>
       </c>
       <c r="E225" s="6" t="str">
         <f>IF($D225="","",VLOOKUP($D225,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5273,13 +5268,13 @@
         <v>110</v>
       </c>
       <c r="B226" s="3">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="D226" s="5">
-        <v>5016847</v>
+        <v>5091005</v>
       </c>
       <c r="E226" s="6" t="str">
         <f>IF($D226="","",VLOOKUP($D226,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5291,13 +5286,13 @@
         <v>110</v>
       </c>
       <c r="B227" s="3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="D227" s="5">
-        <v>4630800</v>
+        <v>5016847</v>
       </c>
       <c r="E227" s="6" t="str">
         <f>IF($D227="","",VLOOKUP($D227,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5309,13 +5304,13 @@
         <v>110</v>
       </c>
       <c r="B228" s="3">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="D228" s="5">
-        <v>4537987</v>
+        <v>4630800</v>
       </c>
       <c r="E228" s="6" t="str">
         <f>IF($D228="","",VLOOKUP($D228,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5327,13 +5322,13 @@
         <v>110</v>
       </c>
       <c r="B229" s="3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>60</v>
+        <v>106</v>
       </c>
       <c r="D229" s="5">
-        <v>4444305</v>
+        <v>4537987</v>
       </c>
       <c r="E229" s="6" t="str">
         <f>IF($D229="","",VLOOKUP($D229,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5345,13 +5340,13 @@
         <v>110</v>
       </c>
       <c r="B230" s="3">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="D230" s="5">
-        <v>4393558</v>
+        <v>4444305</v>
       </c>
       <c r="E230" s="6" t="str">
         <f>IF($D230="","",VLOOKUP($D230,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5363,13 +5358,13 @@
         <v>110</v>
       </c>
       <c r="B231" s="3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C231" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D231" s="5">
-        <v>4361685</v>
+        <v>4393558</v>
       </c>
       <c r="E231" s="6" t="str">
         <f>IF($D231="","",VLOOKUP($D231,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5381,13 +5376,13 @@
         <v>110</v>
       </c>
       <c r="B232" s="3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="D232" s="5">
-        <v>4314000</v>
+        <v>4361685</v>
       </c>
       <c r="E232" s="6" t="str">
         <f>IF($D232="","",VLOOKUP($D232,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5399,13 +5394,13 @@
         <v>110</v>
       </c>
       <c r="B233" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C233" s="4" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="D233" s="5">
-        <v>4305372</v>
+        <v>4314000</v>
       </c>
       <c r="E233" s="6" t="str">
         <f>IF($D233="","",VLOOKUP($D233,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5417,13 +5412,13 @@
         <v>110</v>
       </c>
       <c r="B234" s="3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="D234" s="5">
-        <v>4250088</v>
+        <v>4305372</v>
       </c>
       <c r="E234" s="6" t="str">
         <f>IF($D234="","",VLOOKUP($D234,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5435,13 +5430,13 @@
         <v>110</v>
       </c>
       <c r="B235" s="3">
-        <v>43</v>
-      </c>
-      <c r="C235" s="7" t="s">
-        <v>54</v>
+        <v>42</v>
+      </c>
+      <c r="C235" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="D235" s="5">
-        <v>4174414</v>
+        <v>4250088</v>
       </c>
       <c r="E235" s="6" t="str">
         <f>IF($D235="","",VLOOKUP($D235,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5453,13 +5448,13 @@
         <v>110</v>
       </c>
       <c r="B236" s="3">
-        <v>44</v>
-      </c>
-      <c r="C236" s="4" t="s">
-        <v>59</v>
+        <v>43</v>
+      </c>
+      <c r="C236" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="D236" s="5">
-        <v>4151246</v>
+        <v>4174414</v>
       </c>
       <c r="E236" s="6" t="str">
         <f>IF($D236="","",VLOOKUP($D236,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5471,13 +5466,13 @@
         <v>110</v>
       </c>
       <c r="B237" s="3">
-        <v>45</v>
-      </c>
-      <c r="C237" s="7" t="s">
-        <v>113</v>
+        <v>44</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>59</v>
       </c>
       <c r="D237" s="5">
-        <v>4081096</v>
+        <v>4151246</v>
       </c>
       <c r="E237" s="6" t="str">
         <f>IF($D237="","",VLOOKUP($D237,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5489,13 +5484,13 @@
         <v>110</v>
       </c>
       <c r="B238" s="3">
-        <v>46</v>
-      </c>
-      <c r="C238" s="4" t="s">
-        <v>83</v>
+        <v>45</v>
+      </c>
+      <c r="C238" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="D238" s="5">
-        <v>4033323</v>
+        <v>4081096</v>
       </c>
       <c r="E238" s="6" t="str">
         <f>IF($D238="","",VLOOKUP($D238,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5507,13 +5502,13 @@
         <v>110</v>
       </c>
       <c r="B239" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C239" s="4" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="D239" s="5">
-        <v>4029200</v>
+        <v>4033323</v>
       </c>
       <c r="E239" s="6" t="str">
         <f>IF($D239="","",VLOOKUP($D239,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5525,13 +5520,13 @@
         <v>110</v>
       </c>
       <c r="B240" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="D240" s="5">
-        <v>4000500</v>
+        <v>4029200</v>
       </c>
       <c r="E240" s="6" t="str">
         <f>IF($D240="","",VLOOKUP($D240,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5543,13 +5538,13 @@
         <v>110</v>
       </c>
       <c r="B241" s="3">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C241" s="4" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="D241" s="5">
-        <v>3893926</v>
+        <v>4000500</v>
       </c>
       <c r="E241" s="6" t="str">
         <f>IF($D241="","",VLOOKUP($D241,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5561,13 +5556,13 @@
         <v>110</v>
       </c>
       <c r="B242" s="3">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D242" s="5">
-        <v>3892915</v>
+        <v>3893926</v>
       </c>
       <c r="E242" s="6" t="str">
         <f>IF($D242="","",VLOOKUP($D242,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5579,13 +5574,13 @@
         <v>110</v>
       </c>
       <c r="B243" s="3">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C243" s="4" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="D243" s="5">
-        <v>3817624</v>
+        <v>3892915</v>
       </c>
       <c r="E243" s="6" t="str">
         <f>IF($D243="","",VLOOKUP($D243,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5597,13 +5592,13 @@
         <v>110</v>
       </c>
       <c r="B244" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D244" s="5">
-        <v>3776295</v>
+        <v>3817624</v>
       </c>
       <c r="E244" s="6" t="str">
         <f>IF($D244="","",VLOOKUP($D244,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5615,13 +5610,13 @@
         <v>110</v>
       </c>
       <c r="B245" s="3">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C245" s="4" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="D245" s="5">
-        <v>3636629</v>
+        <v>3776295</v>
       </c>
       <c r="E245" s="6" t="str">
         <f>IF($D245="","",VLOOKUP($D245,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5633,13 +5628,13 @@
         <v>110</v>
       </c>
       <c r="B246" s="3">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C246" s="4" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="D246" s="5">
-        <v>3620200</v>
+        <v>3636629</v>
       </c>
       <c r="E246" s="6" t="str">
         <f>IF($D246="","",VLOOKUP($D246,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5651,13 +5646,13 @@
         <v>110</v>
       </c>
       <c r="B247" s="3">
-        <v>55</v>
-      </c>
-      <c r="C247" s="7" t="s">
-        <v>69</v>
+        <v>54</v>
+      </c>
+      <c r="C247" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="D247" s="5">
-        <v>3414335</v>
+        <v>3620200</v>
       </c>
       <c r="E247" s="6" t="str">
         <f>IF($D247="","",VLOOKUP($D247,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5669,13 +5664,13 @@
         <v>110</v>
       </c>
       <c r="B248" s="3">
-        <v>56</v>
-      </c>
-      <c r="C248" s="4" t="s">
-        <v>74</v>
+        <v>55</v>
+      </c>
+      <c r="C248" s="7" t="s">
+        <v>69</v>
       </c>
       <c r="D248" s="5">
-        <v>3164754</v>
+        <v>3414335</v>
       </c>
       <c r="E248" s="6" t="str">
         <f>IF($D248="","",VLOOKUP($D248,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5687,13 +5682,13 @@
         <v>110</v>
       </c>
       <c r="B249" s="3">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C249" s="4" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D249" s="5">
-        <v>3063699</v>
+        <v>3164754</v>
       </c>
       <c r="E249" s="6" t="str">
         <f>IF($D249="","",VLOOKUP($D249,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5705,13 +5700,13 @@
         <v>110</v>
       </c>
       <c r="B250" s="3">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D250" s="5">
-        <v>2777032</v>
+        <v>3063699</v>
       </c>
       <c r="E250" s="6" t="str">
         <f>IF($D250="","",VLOOKUP($D250,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5723,17 +5718,17 @@
         <v>110</v>
       </c>
       <c r="B251" s="3">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C251" s="4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D251" s="5">
-        <v>2391014</v>
+        <v>2777032</v>
       </c>
       <c r="E251" s="6" t="str">
         <f>IF($D251="","",VLOOKUP($D251,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>7단계</v>
+        <v>8단계</v>
       </c>
     </row>
     <row r="252" spans="1:5" ht="16.5" customHeight="1">
@@ -5741,13 +5736,13 @@
         <v>110</v>
       </c>
       <c r="B252" s="3">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D252" s="5">
-        <v>2371425</v>
+        <v>2391014</v>
       </c>
       <c r="E252" s="6" t="str">
         <f>IF($D252="","",VLOOKUP($D252,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5759,17 +5754,17 @@
         <v>110</v>
       </c>
       <c r="B253" s="3">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C253" s="4" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="D253" s="5">
-        <v>2022500</v>
+        <v>2371425</v>
       </c>
       <c r="E253" s="6" t="str">
         <f>IF($D253="","",VLOOKUP($D253,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
+        <v>7단계</v>
       </c>
     </row>
     <row r="254" spans="1:5" ht="16.5" customHeight="1">
@@ -5777,13 +5772,13 @@
         <v>110</v>
       </c>
       <c r="B254" s="3">
+        <v>61</v>
+      </c>
+      <c r="C254" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C254" s="4" t="s">
-        <v>81</v>
-      </c>
       <c r="D254" s="5">
-        <v>1764375</v>
+        <v>2022500</v>
       </c>
       <c r="E254" s="6" t="str">
         <f>IF($D254="","",VLOOKUP($D254,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5795,13 +5790,13 @@
         <v>110</v>
       </c>
       <c r="B255" s="3">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C255" s="4" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="D255" s="5">
-        <v>1739773</v>
+        <v>1764375</v>
       </c>
       <c r="E255" s="6" t="str">
         <f>IF($D255="","",VLOOKUP($D255,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5813,13 +5808,13 @@
         <v>110</v>
       </c>
       <c r="B256" s="3">
-        <v>64</v>
-      </c>
-      <c r="C256" s="7" t="s">
-        <v>88</v>
+        <v>63</v>
+      </c>
+      <c r="C256" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="D256" s="5">
-        <v>1685105</v>
+        <v>1739773</v>
       </c>
       <c r="E256" s="6" t="str">
         <f>IF($D256="","",VLOOKUP($D256,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5831,13 +5826,13 @@
         <v>110</v>
       </c>
       <c r="B257" s="3">
-        <v>65</v>
-      </c>
-      <c r="C257" s="4">
-        <v>1090</v>
+        <v>64</v>
+      </c>
+      <c r="C257" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="D257" s="5">
-        <v>1619227</v>
+        <v>1685105</v>
       </c>
       <c r="E257" s="6" t="str">
         <f>IF($D257="","",VLOOKUP($D257,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5849,13 +5844,13 @@
         <v>110</v>
       </c>
       <c r="B258" s="3">
-        <v>66</v>
-      </c>
-      <c r="C258" s="4" t="s">
-        <v>85</v>
+        <v>65</v>
+      </c>
+      <c r="C258" s="4">
+        <v>1090</v>
       </c>
       <c r="D258" s="5">
-        <v>1116967</v>
+        <v>1619227</v>
       </c>
       <c r="E258" s="6" t="str">
         <f>IF($D258="","",VLOOKUP($D258,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5867,17 +5862,17 @@
         <v>110</v>
       </c>
       <c r="B259" s="3">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C259" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D259" s="5">
-        <v>481250</v>
+        <v>1116967</v>
       </c>
       <c r="E259" s="6" t="str">
         <f>IF($D259="","",VLOOKUP($D259,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>3단계</v>
+        <v>6단계</v>
       </c>
     </row>
     <row r="260" spans="1:5" ht="16.5" customHeight="1">
@@ -5885,13 +5880,13 @@
         <v>110</v>
       </c>
       <c r="B260" s="3">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D260" s="5">
-        <v>368750</v>
+        <v>481250</v>
       </c>
       <c r="E260" s="6" t="str">
         <f>IF($D260="","",VLOOKUP($D260,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5900,20 +5895,20 @@
     </row>
     <row r="261" spans="1:5" ht="16.5" customHeight="1">
       <c r="A261" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B261" s="3">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C261" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D261" s="5">
-        <v>32997950</v>
+        <v>368750</v>
       </c>
       <c r="E261" s="6" t="str">
         <f>IF($D261="","",VLOOKUP($D261,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>3단계</v>
       </c>
     </row>
     <row r="262" spans="1:5" ht="16.5" customHeight="1">
@@ -5921,13 +5916,13 @@
         <v>114</v>
       </c>
       <c r="B262" s="3">
-        <v>2</v>
-      </c>
-      <c r="C262" s="7" t="s">
-        <v>52</v>
+        <v>1</v>
+      </c>
+      <c r="C262" s="4" t="s">
+        <v>95</v>
       </c>
       <c r="D262" s="5">
-        <v>15520250</v>
+        <v>32997950</v>
       </c>
       <c r="E262" s="6" t="str">
         <f>IF($D262="","",VLOOKUP($D262,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5939,13 +5934,13 @@
         <v>114</v>
       </c>
       <c r="B263" s="3">
-        <v>3</v>
-      </c>
-      <c r="C263" s="4" t="s">
-        <v>27</v>
+        <v>2</v>
+      </c>
+      <c r="C263" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="D263" s="5">
-        <v>14318400</v>
+        <v>15520250</v>
       </c>
       <c r="E263" s="6" t="str">
         <f>IF($D263="","",VLOOKUP($D263,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5957,13 +5952,13 @@
         <v>114</v>
       </c>
       <c r="B264" s="3">
-        <v>4</v>
-      </c>
-      <c r="C264" s="8" t="s">
-        <v>115</v>
+        <v>3</v>
+      </c>
+      <c r="C264" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="D264" s="5">
-        <v>12803400</v>
+        <v>14318400</v>
       </c>
       <c r="E264" s="6" t="str">
         <f>IF($D264="","",VLOOKUP($D264,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5975,13 +5970,13 @@
         <v>114</v>
       </c>
       <c r="B265" s="3">
-        <v>5</v>
-      </c>
-      <c r="C265" s="4" t="s">
-        <v>53</v>
+        <v>4</v>
+      </c>
+      <c r="C265" s="8" t="s">
+        <v>115</v>
       </c>
       <c r="D265" s="5">
-        <v>11730150</v>
+        <v>12803400</v>
       </c>
       <c r="E265" s="6" t="str">
         <f>IF($D265="","",VLOOKUP($D265,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -5993,13 +5988,13 @@
         <v>114</v>
       </c>
       <c r="B266" s="3">
-        <v>6</v>
-      </c>
-      <c r="C266" s="8" t="s">
-        <v>111</v>
+        <v>5</v>
+      </c>
+      <c r="C266" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="D266" s="5">
-        <v>10776300</v>
+        <v>11730150</v>
       </c>
       <c r="E266" s="6" t="str">
         <f>IF($D266="","",VLOOKUP($D266,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6011,13 +6006,13 @@
         <v>114</v>
       </c>
       <c r="B267" s="3">
-        <v>7</v>
-      </c>
-      <c r="C267" s="4" t="s">
-        <v>61</v>
+        <v>6</v>
+      </c>
+      <c r="C267" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="D267" s="5">
-        <v>10310343</v>
+        <v>10776300</v>
       </c>
       <c r="E267" s="6" t="str">
         <f>IF($D267="","",VLOOKUP($D267,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6029,13 +6024,13 @@
         <v>114</v>
       </c>
       <c r="B268" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C268" s="4" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="D268" s="5">
-        <v>9826000</v>
+        <v>10310343</v>
       </c>
       <c r="E268" s="6" t="str">
         <f>IF($D268="","",VLOOKUP($D268,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6047,13 +6042,13 @@
         <v>114</v>
       </c>
       <c r="B269" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C269" s="4" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D269" s="5">
-        <v>9783249</v>
+        <v>9826000</v>
       </c>
       <c r="E269" s="6" t="str">
         <f>IF($D269="","",VLOOKUP($D269,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6065,13 +6060,13 @@
         <v>114</v>
       </c>
       <c r="B270" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C270" s="4" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="D270" s="5">
-        <v>9196550</v>
+        <v>9783249</v>
       </c>
       <c r="E270" s="6" t="str">
         <f>IF($D270="","",VLOOKUP($D270,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6083,13 +6078,13 @@
         <v>114</v>
       </c>
       <c r="B271" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C271" s="4" t="s">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="D271" s="5">
-        <v>9100150</v>
+        <v>9196550</v>
       </c>
       <c r="E271" s="6" t="str">
         <f>IF($D271="","",VLOOKUP($D271,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6101,13 +6096,13 @@
         <v>114</v>
       </c>
       <c r="B272" s="3">
-        <v>12</v>
-      </c>
-      <c r="C272" s="7" t="s">
-        <v>43</v>
+        <v>11</v>
+      </c>
+      <c r="C272" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="D272" s="5">
-        <v>8990350</v>
+        <v>9100150</v>
       </c>
       <c r="E272" s="6" t="str">
         <f>IF($D272="","",VLOOKUP($D272,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6119,13 +6114,13 @@
         <v>114</v>
       </c>
       <c r="B273" s="3">
-        <v>13</v>
-      </c>
-      <c r="C273" s="4" t="s">
-        <v>106</v>
+        <v>12</v>
+      </c>
+      <c r="C273" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="D273" s="5">
-        <v>8798439</v>
+        <v>8990350</v>
       </c>
       <c r="E273" s="6" t="str">
         <f>IF($D273="","",VLOOKUP($D273,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6137,13 +6132,13 @@
         <v>114</v>
       </c>
       <c r="B274" s="3">
-        <v>14</v>
-      </c>
-      <c r="C274" s="7" t="s">
-        <v>50</v>
+        <v>13</v>
+      </c>
+      <c r="C274" s="4" t="s">
+        <v>106</v>
       </c>
       <c r="D274" s="5">
-        <v>8797500</v>
+        <v>8798439</v>
       </c>
       <c r="E274" s="6" t="str">
         <f>IF($D274="","",VLOOKUP($D274,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6155,13 +6150,13 @@
         <v>114</v>
       </c>
       <c r="B275" s="3">
-        <v>15</v>
-      </c>
-      <c r="C275" s="4" t="s">
-        <v>98</v>
+        <v>14</v>
+      </c>
+      <c r="C275" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D275" s="5">
-        <v>8702111</v>
+        <v>8797500</v>
       </c>
       <c r="E275" s="6" t="str">
         <f>IF($D275="","",VLOOKUP($D275,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6173,13 +6168,13 @@
         <v>114</v>
       </c>
       <c r="B276" s="3">
-        <v>16</v>
-      </c>
-      <c r="C276" s="7" t="s">
-        <v>41</v>
+        <v>15</v>
+      </c>
+      <c r="C276" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="D276" s="5">
-        <v>8594600</v>
+        <v>8702111</v>
       </c>
       <c r="E276" s="6" t="str">
         <f>IF($D276="","",VLOOKUP($D276,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6191,13 +6186,13 @@
         <v>114</v>
       </c>
       <c r="B277" s="3">
-        <v>17</v>
-      </c>
-      <c r="C277" s="4" t="s">
-        <v>42</v>
+        <v>16</v>
+      </c>
+      <c r="C277" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="D277" s="5">
-        <v>8587682</v>
+        <v>8594600</v>
       </c>
       <c r="E277" s="6" t="str">
         <f>IF($D277="","",VLOOKUP($D277,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6209,13 +6204,13 @@
         <v>114</v>
       </c>
       <c r="B278" s="3">
-        <v>18</v>
-      </c>
-      <c r="C278" s="7" t="s">
-        <v>113</v>
+        <v>17</v>
+      </c>
+      <c r="C278" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="D278" s="5">
-        <v>8525490</v>
+        <v>8587682</v>
       </c>
       <c r="E278" s="6" t="str">
         <f>IF($D278="","",VLOOKUP($D278,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6227,13 +6222,13 @@
         <v>114</v>
       </c>
       <c r="B279" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C279" s="7" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="D279" s="5">
-        <v>8248525</v>
+        <v>8525490</v>
       </c>
       <c r="E279" s="6" t="str">
         <f>IF($D279="","",VLOOKUP($D279,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6245,13 +6240,13 @@
         <v>114</v>
       </c>
       <c r="B280" s="3">
-        <v>20</v>
-      </c>
-      <c r="C280" s="4" t="s">
-        <v>99</v>
+        <v>19</v>
+      </c>
+      <c r="C280" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="D280" s="5">
-        <v>8177600</v>
+        <v>8248525</v>
       </c>
       <c r="E280" s="6" t="str">
         <f>IF($D280="","",VLOOKUP($D280,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6263,13 +6258,13 @@
         <v>114</v>
       </c>
       <c r="B281" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C281" s="4" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="D281" s="5">
-        <v>8138300</v>
+        <v>8177600</v>
       </c>
       <c r="E281" s="6" t="str">
         <f>IF($D281="","",VLOOKUP($D281,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6281,13 +6276,13 @@
         <v>114</v>
       </c>
       <c r="B282" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C282" s="4" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="D282" s="5">
-        <v>8051401</v>
+        <v>8138300</v>
       </c>
       <c r="E282" s="6" t="str">
         <f>IF($D282="","",VLOOKUP($D282,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6299,13 +6294,13 @@
         <v>114</v>
       </c>
       <c r="B283" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C283" s="4" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="D283" s="5">
-        <v>7776950</v>
+        <v>8051401</v>
       </c>
       <c r="E283" s="6" t="str">
         <f>IF($D283="","",VLOOKUP($D283,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6317,13 +6312,13 @@
         <v>114</v>
       </c>
       <c r="B284" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C284" s="4" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="D284" s="5">
-        <v>7656300</v>
+        <v>7776950</v>
       </c>
       <c r="E284" s="6" t="str">
         <f>IF($D284="","",VLOOKUP($D284,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6335,13 +6330,13 @@
         <v>114</v>
       </c>
       <c r="B285" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C285" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D285" s="5">
-        <v>7654875</v>
+        <v>7656300</v>
       </c>
       <c r="E285" s="6" t="str">
         <f>IF($D285="","",VLOOKUP($D285,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6353,13 +6348,13 @@
         <v>114</v>
       </c>
       <c r="B286" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C286" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D286" s="5">
-        <v>7645595</v>
+        <v>7654875</v>
       </c>
       <c r="E286" s="6" t="str">
         <f>IF($D286="","",VLOOKUP($D286,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6371,13 +6366,13 @@
         <v>114</v>
       </c>
       <c r="B287" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C287" s="4" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D287" s="5">
-        <v>7625700</v>
+        <v>7645595</v>
       </c>
       <c r="E287" s="6" t="str">
         <f>IF($D287="","",VLOOKUP($D287,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6389,13 +6384,13 @@
         <v>114</v>
       </c>
       <c r="B288" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C288" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D288" s="5">
-        <v>7572000</v>
+        <v>7625700</v>
       </c>
       <c r="E288" s="6" t="str">
         <f>IF($D288="","",VLOOKUP($D288,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6407,13 +6402,13 @@
         <v>114</v>
       </c>
       <c r="B289" s="3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C289" s="4" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="D289" s="5">
-        <v>7511676</v>
+        <v>7572000</v>
       </c>
       <c r="E289" s="6" t="str">
         <f>IF($D289="","",VLOOKUP($D289,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6425,13 +6420,13 @@
         <v>114</v>
       </c>
       <c r="B290" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C290" s="4" t="s">
-        <v>29</v>
+        <v>116</v>
       </c>
       <c r="D290" s="5">
-        <v>7445477</v>
+        <v>7511676</v>
       </c>
       <c r="E290" s="6" t="str">
         <f>IF($D290="","",VLOOKUP($D290,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6443,13 +6438,13 @@
         <v>114</v>
       </c>
       <c r="B291" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C291" s="4" t="s">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c r="D291" s="5">
-        <v>7435700</v>
+        <v>7445477</v>
       </c>
       <c r="E291" s="6" t="str">
         <f>IF($D291="","",VLOOKUP($D291,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6461,13 +6456,13 @@
         <v>114</v>
       </c>
       <c r="B292" s="3">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D292" s="5">
-        <v>7331000</v>
+        <v>7435700</v>
       </c>
       <c r="E292" s="6" t="str">
         <f>IF($D292="","",VLOOKUP($D292,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6479,13 +6474,13 @@
         <v>114</v>
       </c>
       <c r="B293" s="3">
-        <v>33</v>
-      </c>
-      <c r="C293" s="7" t="s">
-        <v>69</v>
+        <v>32</v>
+      </c>
+      <c r="C293" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="D293" s="5">
-        <v>7321924</v>
+        <v>7331000</v>
       </c>
       <c r="E293" s="6" t="str">
         <f>IF($D293="","",VLOOKUP($D293,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6497,13 +6492,13 @@
         <v>114</v>
       </c>
       <c r="B294" s="3">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C294" s="7" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D294" s="5">
-        <v>7318696</v>
+        <v>7321924</v>
       </c>
       <c r="E294" s="6" t="str">
         <f>IF($D294="","",VLOOKUP($D294,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6515,13 +6510,13 @@
         <v>114</v>
       </c>
       <c r="B295" s="3">
-        <v>35</v>
-      </c>
-      <c r="C295" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="C295" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="D295" s="5">
-        <v>7241850</v>
+        <v>7318696</v>
       </c>
       <c r="E295" s="6" t="str">
         <f>IF($D295="","",VLOOKUP($D295,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6533,13 +6528,13 @@
         <v>114</v>
       </c>
       <c r="B296" s="3">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>108</v>
+        <v>32</v>
       </c>
       <c r="D296" s="5">
-        <v>7216687</v>
+        <v>7241850</v>
       </c>
       <c r="E296" s="6" t="str">
         <f>IF($D296="","",VLOOKUP($D296,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6551,17 +6546,17 @@
         <v>114</v>
       </c>
       <c r="B297" s="3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C297" s="4" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="D297" s="5">
-        <v>6356548</v>
+        <v>7216687</v>
       </c>
       <c r="E297" s="6" t="str">
         <f>IF($D297="","",VLOOKUP($D297,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>9단계</v>
       </c>
     </row>
     <row r="298" spans="1:5" ht="16.5" customHeight="1">
@@ -6569,13 +6564,13 @@
         <v>114</v>
       </c>
       <c r="B298" s="3">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D298" s="5">
-        <v>6347447</v>
+        <v>6356548</v>
       </c>
       <c r="E298" s="6" t="str">
         <f>IF($D298="","",VLOOKUP($D298,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6587,13 +6582,13 @@
         <v>114</v>
       </c>
       <c r="B299" s="3">
-        <v>39</v>
-      </c>
-      <c r="C299" s="7" t="s">
-        <v>103</v>
+        <v>38</v>
+      </c>
+      <c r="C299" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="D299" s="5">
-        <v>5960246</v>
+        <v>6347447</v>
       </c>
       <c r="E299" s="6" t="str">
         <f>IF($D299="","",VLOOKUP($D299,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6605,13 +6600,13 @@
         <v>114</v>
       </c>
       <c r="B300" s="3">
-        <v>40</v>
-      </c>
-      <c r="C300" s="4" t="s">
-        <v>85</v>
+        <v>39</v>
+      </c>
+      <c r="C300" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="D300" s="5">
-        <v>5879538</v>
+        <v>5960246</v>
       </c>
       <c r="E300" s="6" t="str">
         <f>IF($D300="","",VLOOKUP($D300,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6623,13 +6618,13 @@
         <v>114</v>
       </c>
       <c r="B301" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C301" s="4" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="D301" s="5">
-        <v>5722760</v>
+        <v>5879538</v>
       </c>
       <c r="E301" s="6" t="str">
         <f>IF($D301="","",VLOOKUP($D301,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6641,13 +6636,13 @@
         <v>114</v>
       </c>
       <c r="B302" s="3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C302" s="4" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="D302" s="5">
-        <v>5376985</v>
+        <v>5722760</v>
       </c>
       <c r="E302" s="6" t="str">
         <f>IF($D302="","",VLOOKUP($D302,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6659,13 +6654,13 @@
         <v>114</v>
       </c>
       <c r="B303" s="3">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C303" s="4" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="D303" s="5">
-        <v>5159999</v>
+        <v>5376985</v>
       </c>
       <c r="E303" s="6" t="str">
         <f>IF($D303="","",VLOOKUP($D303,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6677,13 +6672,13 @@
         <v>114</v>
       </c>
       <c r="B304" s="3">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="D304" s="5">
-        <v>4816595</v>
+        <v>5159999</v>
       </c>
       <c r="E304" s="6" t="str">
         <f>IF($D304="","",VLOOKUP($D304,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6695,13 +6690,13 @@
         <v>114</v>
       </c>
       <c r="B305" s="3">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C305" s="4" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D305" s="5">
-        <v>4538649</v>
+        <v>4816595</v>
       </c>
       <c r="E305" s="6" t="str">
         <f>IF($D305="","",VLOOKUP($D305,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6713,13 +6708,13 @@
         <v>114</v>
       </c>
       <c r="B306" s="3">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="D306" s="5">
-        <v>4493569</v>
+        <v>4538649</v>
       </c>
       <c r="E306" s="6" t="str">
         <f>IF($D306="","",VLOOKUP($D306,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6731,13 +6726,13 @@
         <v>114</v>
       </c>
       <c r="B307" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C307" s="4" t="s">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="D307" s="5">
-        <v>4473170</v>
+        <v>4493569</v>
       </c>
       <c r="E307" s="6" t="str">
         <f>IF($D307="","",VLOOKUP($D307,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6749,13 +6744,13 @@
         <v>114</v>
       </c>
       <c r="B308" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C308" s="4" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="D308" s="5">
-        <v>4398940</v>
+        <v>4473170</v>
       </c>
       <c r="E308" s="6" t="str">
         <f>IF($D308="","",VLOOKUP($D308,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6767,13 +6762,13 @@
         <v>114</v>
       </c>
       <c r="B309" s="3">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C309" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D309" s="5">
-        <v>4263500</v>
+        <v>4398940</v>
       </c>
       <c r="E309" s="6" t="str">
         <f>IF($D309="","",VLOOKUP($D309,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6785,13 +6780,13 @@
         <v>114</v>
       </c>
       <c r="B310" s="3">
-        <v>50</v>
-      </c>
-      <c r="C310" s="8" t="s">
-        <v>89</v>
+        <v>49</v>
+      </c>
+      <c r="C310" s="4" t="s">
+        <v>71</v>
       </c>
       <c r="D310" s="5">
-        <v>4186720</v>
+        <v>4263500</v>
       </c>
       <c r="E310" s="6" t="str">
         <f>IF($D310="","",VLOOKUP($D310,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6803,13 +6798,13 @@
         <v>114</v>
       </c>
       <c r="B311" s="3">
-        <v>51</v>
-      </c>
-      <c r="C311" s="4" t="s">
-        <v>84</v>
+        <v>50</v>
+      </c>
+      <c r="C311" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="D311" s="5">
-        <v>4155232</v>
+        <v>4186720</v>
       </c>
       <c r="E311" s="6" t="str">
         <f>IF($D311="","",VLOOKUP($D311,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6821,13 +6816,13 @@
         <v>114</v>
       </c>
       <c r="B312" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C312" s="4" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D312" s="5">
-        <v>4148173</v>
+        <v>4155232</v>
       </c>
       <c r="E312" s="6" t="str">
         <f>IF($D312="","",VLOOKUP($D312,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6839,13 +6834,13 @@
         <v>114</v>
       </c>
       <c r="B313" s="3">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C313" s="4" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="D313" s="5">
-        <v>3953623</v>
+        <v>4148173</v>
       </c>
       <c r="E313" s="6" t="str">
         <f>IF($D313="","",VLOOKUP($D313,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6857,13 +6852,13 @@
         <v>114</v>
       </c>
       <c r="B314" s="3">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C314" s="4" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D314" s="5">
-        <v>3841825</v>
+        <v>3953623</v>
       </c>
       <c r="E314" s="6" t="str">
         <f>IF($D314="","",VLOOKUP($D314,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6875,13 +6870,13 @@
         <v>114</v>
       </c>
       <c r="B315" s="3">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C315" s="4" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="D315" s="5">
-        <v>3725748</v>
+        <v>3841825</v>
       </c>
       <c r="E315" s="6" t="str">
         <f>IF($D315="","",VLOOKUP($D315,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6893,13 +6888,13 @@
         <v>114</v>
       </c>
       <c r="B316" s="3">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C316" s="4" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D316" s="5">
-        <v>3668126</v>
+        <v>3725748</v>
       </c>
       <c r="E316" s="6" t="str">
         <f>IF($D316="","",VLOOKUP($D316,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6911,13 +6906,13 @@
         <v>114</v>
       </c>
       <c r="B317" s="3">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C317" s="4" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D317" s="5">
-        <v>3655552</v>
+        <v>3668126</v>
       </c>
       <c r="E317" s="6" t="str">
         <f>IF($D317="","",VLOOKUP($D317,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6929,13 +6924,13 @@
         <v>114</v>
       </c>
       <c r="B318" s="3">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C318" s="4" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D318" s="5">
-        <v>3643670</v>
+        <v>3655552</v>
       </c>
       <c r="E318" s="6" t="str">
         <f>IF($D318="","",VLOOKUP($D318,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6947,13 +6942,13 @@
         <v>114</v>
       </c>
       <c r="B319" s="3">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C319" s="4" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="D319" s="5">
-        <v>2973305</v>
+        <v>3643670</v>
       </c>
       <c r="E319" s="6" t="str">
         <f>IF($D319="","",VLOOKUP($D319,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -6965,17 +6960,17 @@
         <v>114</v>
       </c>
       <c r="B320" s="3">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C320" s="4" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="D320" s="5">
-        <v>2438490</v>
+        <v>2973305</v>
       </c>
       <c r="E320" s="6" t="str">
         <f>IF($D320="","",VLOOKUP($D320,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>7단계</v>
+        <v>8단계</v>
       </c>
     </row>
     <row r="321" spans="1:5" ht="16.5" customHeight="1">
@@ -6983,13 +6978,13 @@
         <v>114</v>
       </c>
       <c r="B321" s="3">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C321" s="4" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D321" s="5">
-        <v>2379290</v>
+        <v>2438490</v>
       </c>
       <c r="E321" s="6" t="str">
         <f>IF($D321="","",VLOOKUP($D321,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7001,17 +6996,17 @@
         <v>114</v>
       </c>
       <c r="B322" s="3">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C322" s="4" t="s">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="D322" s="5">
-        <v>2161578</v>
+        <v>2379290</v>
       </c>
       <c r="E322" s="6" t="str">
         <f>IF($D322="","",VLOOKUP($D322,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
+        <v>7단계</v>
       </c>
     </row>
     <row r="323" spans="1:5" ht="16.5" customHeight="1">
@@ -7019,13 +7014,13 @@
         <v>114</v>
       </c>
       <c r="B323" s="3">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C323" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D323" s="5">
-        <v>2130311</v>
+        <v>2161578</v>
       </c>
       <c r="E323" s="6" t="str">
         <f>IF($D323="","",VLOOKUP($D323,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7037,13 +7032,13 @@
         <v>114</v>
       </c>
       <c r="B324" s="3">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C324" s="4" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="D324" s="5">
-        <v>1272950</v>
+        <v>2130311</v>
       </c>
       <c r="E324" s="6" t="str">
         <f>IF($D324="","",VLOOKUP($D324,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7055,13 +7050,13 @@
         <v>114</v>
       </c>
       <c r="B325" s="3">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C325" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D325" s="5">
-        <v>1207378</v>
+        <v>1272950</v>
       </c>
       <c r="E325" s="6" t="str">
         <f>IF($D325="","",VLOOKUP($D325,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7073,17 +7068,17 @@
         <v>114</v>
       </c>
       <c r="B326" s="3">
-        <v>66</v>
-      </c>
-      <c r="C326" s="7" t="s">
-        <v>88</v>
+        <v>65</v>
+      </c>
+      <c r="C326" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="D326" s="5">
-        <v>959773</v>
+        <v>1207378</v>
       </c>
       <c r="E326" s="6" t="str">
         <f>IF($D326="","",VLOOKUP($D326,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>5단계</v>
+        <v>6단계</v>
       </c>
     </row>
     <row r="327" spans="1:5" ht="16.5" customHeight="1">
@@ -7091,35 +7086,35 @@
         <v>114</v>
       </c>
       <c r="B327" s="3">
-        <v>67</v>
-      </c>
-      <c r="C327" s="4" t="s">
-        <v>92</v>
+        <v>66</v>
+      </c>
+      <c r="C327" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="D327" s="5">
-        <v>276650</v>
+        <v>959773</v>
       </c>
       <c r="E327" s="6" t="str">
         <f>IF($D327="","",VLOOKUP($D327,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>3단계</v>
-      </c>
-    </row>
-    <row r="328" spans="1:5">
+        <v>5단계</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" ht="16.5" customHeight="1">
       <c r="A328" t="s">
-        <v>119</v>
-      </c>
-      <c r="B328" s="9">
-        <v>1</v>
-      </c>
-      <c r="C328" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D328" s="9">
-        <v>51572469</v>
+        <v>114</v>
+      </c>
+      <c r="B328" s="3">
+        <v>67</v>
+      </c>
+      <c r="C328" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D328" s="5">
+        <v>276650</v>
       </c>
       <c r="E328" s="6" t="str">
         <f>IF($D328="","",VLOOKUP($D328,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
+        <v>3단계</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -7127,13 +7122,13 @@
         <v>119</v>
       </c>
       <c r="B329" s="9">
-        <v>2</v>
-      </c>
-      <c r="C329" s="11" t="s">
-        <v>52</v>
+        <v>1</v>
+      </c>
+      <c r="C329" s="10" t="s">
+        <v>48</v>
       </c>
       <c r="D329" s="9">
-        <v>45927381</v>
+        <v>51572469</v>
       </c>
       <c r="E329" s="6" t="str">
         <f>IF($D329="","",VLOOKUP($D329,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7145,13 +7140,13 @@
         <v>119</v>
       </c>
       <c r="B330" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C330" s="11" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="D330" s="9">
-        <v>44882553</v>
+        <v>45927381</v>
       </c>
       <c r="E330" s="6" t="str">
         <f>IF($D330="","",VLOOKUP($D330,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7163,13 +7158,13 @@
         <v>119</v>
       </c>
       <c r="B331" s="9">
-        <v>4</v>
-      </c>
-      <c r="C331" s="10" t="s">
-        <v>34</v>
+        <v>3</v>
+      </c>
+      <c r="C331" s="11" t="s">
+        <v>102</v>
       </c>
       <c r="D331" s="9">
-        <v>36401622</v>
+        <v>44882553</v>
       </c>
       <c r="E331" s="6" t="str">
         <f>IF($D331="","",VLOOKUP($D331,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7181,13 +7176,13 @@
         <v>119</v>
       </c>
       <c r="B332" s="9">
-        <v>5</v>
-      </c>
-      <c r="C332" s="11" t="s">
-        <v>27</v>
+        <v>4</v>
+      </c>
+      <c r="C332" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="D332" s="9">
-        <v>32814024</v>
+        <v>36401622</v>
       </c>
       <c r="E332" s="6" t="str">
         <f>IF($D332="","",VLOOKUP($D332,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7199,13 +7194,13 @@
         <v>119</v>
       </c>
       <c r="B333" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C333" s="11" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D333" s="9">
-        <v>30352177</v>
+        <v>32814024</v>
       </c>
       <c r="E333" s="6" t="str">
         <f>IF($D333="","",VLOOKUP($D333,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7217,13 +7212,13 @@
         <v>119</v>
       </c>
       <c r="B334" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C334" s="11" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="D334" s="9">
-        <v>29064577</v>
+        <v>30352177</v>
       </c>
       <c r="E334" s="6" t="str">
         <f>IF($D334="","",VLOOKUP($D334,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7235,13 +7230,13 @@
         <v>119</v>
       </c>
       <c r="B335" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C335" s="11" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D335" s="9">
-        <v>28830256</v>
+        <v>29064577</v>
       </c>
       <c r="E335" s="6" t="str">
         <f>IF($D335="","",VLOOKUP($D335,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7253,13 +7248,13 @@
         <v>119</v>
       </c>
       <c r="B336" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C336" s="11" t="s">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="D336" s="9">
-        <v>27963110</v>
+        <v>28830256</v>
       </c>
       <c r="E336" s="6" t="str">
         <f>IF($D336="","",VLOOKUP($D336,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7271,13 +7266,13 @@
         <v>119</v>
       </c>
       <c r="B337" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C337" s="11" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D337" s="9">
-        <v>27716398</v>
+        <v>27963110</v>
       </c>
       <c r="E337" s="6" t="str">
         <f>IF($D337="","",VLOOKUP($D337,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7289,13 +7284,13 @@
         <v>119</v>
       </c>
       <c r="B338" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C338" s="11" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="D338" s="9">
-        <v>27125102</v>
+        <v>27716398</v>
       </c>
       <c r="E338" s="6" t="str">
         <f>IF($D338="","",VLOOKUP($D338,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7307,13 +7302,13 @@
         <v>119</v>
       </c>
       <c r="B339" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C339" s="11" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="D339" s="9">
-        <v>26303031</v>
+        <v>27125102</v>
       </c>
       <c r="E339" s="6" t="str">
         <f>IF($D339="","",VLOOKUP($D339,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7325,13 +7320,13 @@
         <v>119</v>
       </c>
       <c r="B340" s="9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C340" s="11" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D340" s="9">
-        <v>25598926</v>
+        <v>26303031</v>
       </c>
       <c r="E340" s="6" t="str">
         <f>IF($D340="","",VLOOKUP($D340,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7343,13 +7338,13 @@
         <v>119</v>
       </c>
       <c r="B341" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C341" s="11" t="s">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="D341" s="9">
-        <v>25275492</v>
+        <v>25598926</v>
       </c>
       <c r="E341" s="6" t="str">
         <f>IF($D341="","",VLOOKUP($D341,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7361,13 +7356,13 @@
         <v>119</v>
       </c>
       <c r="B342" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C342" s="11" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="D342" s="9">
-        <v>24620930</v>
+        <v>25275492</v>
       </c>
       <c r="E342" s="6" t="str">
         <f>IF($D342="","",VLOOKUP($D342,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7379,13 +7374,13 @@
         <v>119</v>
       </c>
       <c r="B343" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C343" s="11" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="D343" s="9">
-        <v>24434321</v>
+        <v>24620930</v>
       </c>
       <c r="E343" s="6" t="str">
         <f>IF($D343="","",VLOOKUP($D343,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7397,13 +7392,13 @@
         <v>119</v>
       </c>
       <c r="B344" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C344" s="11" t="s">
-        <v>121</v>
+        <v>30</v>
       </c>
       <c r="D344" s="9">
-        <v>21605033</v>
+        <v>24434321</v>
       </c>
       <c r="E344" s="6" t="str">
         <f>IF($D344="","",VLOOKUP($D344,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7415,13 +7410,13 @@
         <v>119</v>
       </c>
       <c r="B345" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C345" s="11" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="D345" s="9">
-        <v>21478397</v>
+        <v>21605033</v>
       </c>
       <c r="E345" s="6" t="str">
         <f>IF($D345="","",VLOOKUP($D345,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7433,13 +7428,13 @@
         <v>119</v>
       </c>
       <c r="B346" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C346" s="11" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="D346" s="9">
-        <v>21123578</v>
+        <v>21478397</v>
       </c>
       <c r="E346" s="6" t="str">
         <f>IF($D346="","",VLOOKUP($D346,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7451,13 +7446,13 @@
         <v>119</v>
       </c>
       <c r="B347" s="9">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C347" s="11" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="D347" s="9">
-        <v>20055931</v>
+        <v>21123578</v>
       </c>
       <c r="E347" s="6" t="str">
         <f>IF($D347="","",VLOOKUP($D347,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7469,13 +7464,13 @@
         <v>119</v>
       </c>
       <c r="B348" s="9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C348" s="11" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="D348" s="9">
-        <v>19328458</v>
+        <v>20055931</v>
       </c>
       <c r="E348" s="6" t="str">
         <f>IF($D348="","",VLOOKUP($D348,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7487,13 +7482,13 @@
         <v>119</v>
       </c>
       <c r="B349" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C349" s="11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D349" s="9">
-        <v>18197828</v>
+        <v>19328458</v>
       </c>
       <c r="E349" s="6" t="str">
         <f>IF($D349="","",VLOOKUP($D349,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7505,13 +7500,13 @@
         <v>119</v>
       </c>
       <c r="B350" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C350" s="11" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="D350" s="9">
-        <v>17545894</v>
+        <v>18197828</v>
       </c>
       <c r="E350" s="6" t="str">
         <f>IF($D350="","",VLOOKUP($D350,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7523,13 +7518,13 @@
         <v>119</v>
       </c>
       <c r="B351" s="9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C351" s="11" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="D351" s="9">
-        <v>17451192</v>
+        <v>17545894</v>
       </c>
       <c r="E351" s="6" t="str">
         <f>IF($D351="","",VLOOKUP($D351,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7541,13 +7536,13 @@
         <v>119</v>
       </c>
       <c r="B352" s="9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C352" s="11" t="s">
-        <v>122</v>
+        <v>32</v>
       </c>
       <c r="D352" s="9">
-        <v>17095537</v>
+        <v>17451192</v>
       </c>
       <c r="E352" s="6" t="str">
         <f>IF($D352="","",VLOOKUP($D352,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7559,13 +7554,13 @@
         <v>119</v>
       </c>
       <c r="B353" s="9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C353" s="11" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="D353" s="9">
-        <v>16940645</v>
+        <v>17095537</v>
       </c>
       <c r="E353" s="6" t="str">
         <f>IF($D353="","",VLOOKUP($D353,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7577,13 +7572,13 @@
         <v>119</v>
       </c>
       <c r="B354" s="9">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C354" s="11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D354" s="9">
-        <v>16625723</v>
+        <v>16940645</v>
       </c>
       <c r="E354" s="6" t="str">
         <f>IF($D354="","",VLOOKUP($D354,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7595,13 +7590,13 @@
         <v>119</v>
       </c>
       <c r="B355" s="9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C355" s="11" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="D355" s="9">
-        <v>16582350</v>
+        <v>16625723</v>
       </c>
       <c r="E355" s="6" t="str">
         <f>IF($D355="","",VLOOKUP($D355,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7613,13 +7608,13 @@
         <v>119</v>
       </c>
       <c r="B356" s="9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C356" s="11" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="D356" s="9">
-        <v>16374224</v>
+        <v>16582350</v>
       </c>
       <c r="E356" s="6" t="str">
         <f>IF($D356="","",VLOOKUP($D356,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7631,13 +7626,13 @@
         <v>119</v>
       </c>
       <c r="B357" s="9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C357" s="11" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="D357" s="9">
-        <v>15989772</v>
+        <v>16374224</v>
       </c>
       <c r="E357" s="6" t="str">
         <f>IF($D357="","",VLOOKUP($D357,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7649,13 +7644,13 @@
         <v>119</v>
       </c>
       <c r="B358" s="9">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C358" s="11" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D358" s="9">
-        <v>15124678</v>
+        <v>15989772</v>
       </c>
       <c r="E358" s="6" t="str">
         <f>IF($D358="","",VLOOKUP($D358,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7667,13 +7662,13 @@
         <v>119</v>
       </c>
       <c r="B359" s="9">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C359" s="11" t="s">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="D359" s="9">
-        <v>14388261</v>
+        <v>15124678</v>
       </c>
       <c r="E359" s="6" t="str">
         <f>IF($D359="","",VLOOKUP($D359,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7685,13 +7680,13 @@
         <v>119</v>
       </c>
       <c r="B360" s="9">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C360" s="11" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="D360" s="9">
-        <v>14253593</v>
+        <v>14388261</v>
       </c>
       <c r="E360" s="6" t="str">
         <f>IF($D360="","",VLOOKUP($D360,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7703,13 +7698,13 @@
         <v>119</v>
       </c>
       <c r="B361" s="9">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C361" s="11" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="D361" s="9">
-        <v>13903501</v>
+        <v>14253593</v>
       </c>
       <c r="E361" s="6" t="str">
         <f>IF($D361="","",VLOOKUP($D361,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7721,13 +7716,13 @@
         <v>119</v>
       </c>
       <c r="B362" s="9">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C362" s="11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D362" s="9">
-        <v>13791347</v>
+        <v>13903501</v>
       </c>
       <c r="E362" s="6" t="str">
         <f>IF($D362="","",VLOOKUP($D362,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7739,13 +7734,13 @@
         <v>119</v>
       </c>
       <c r="B363" s="9">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C363" s="11" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D363" s="9">
-        <v>13310754</v>
+        <v>13791347</v>
       </c>
       <c r="E363" s="6" t="str">
         <f>IF($D363="","",VLOOKUP($D363,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7757,13 +7752,13 @@
         <v>119</v>
       </c>
       <c r="B364" s="9">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C364" s="11" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="D364" s="9">
-        <v>12684262</v>
+        <v>13310754</v>
       </c>
       <c r="E364" s="6" t="str">
         <f>IF($D364="","",VLOOKUP($D364,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7775,13 +7770,13 @@
         <v>119</v>
       </c>
       <c r="B365" s="9">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C365" s="11" t="s">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="D365" s="9">
-        <v>12215462</v>
+        <v>12684262</v>
       </c>
       <c r="E365" s="6" t="str">
         <f>IF($D365="","",VLOOKUP($D365,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7793,13 +7788,13 @@
         <v>119</v>
       </c>
       <c r="B366" s="9">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C366" s="11" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="D366" s="9">
-        <v>11325863</v>
+        <v>12215462</v>
       </c>
       <c r="E366" s="6" t="str">
         <f>IF($D366="","",VLOOKUP($D366,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7811,13 +7806,13 @@
         <v>119</v>
       </c>
       <c r="B367" s="9">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C367" s="11" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="D367" s="9">
-        <v>10130369</v>
+        <v>11325863</v>
       </c>
       <c r="E367" s="6" t="str">
         <f>IF($D367="","",VLOOKUP($D367,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7829,13 +7824,13 @@
         <v>119</v>
       </c>
       <c r="B368" s="9">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C368" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D368" s="9">
-        <v>10079600</v>
+        <v>10130369</v>
       </c>
       <c r="E368" s="6" t="str">
         <f>IF($D368="","",VLOOKUP($D368,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7847,13 +7842,13 @@
         <v>119</v>
       </c>
       <c r="B369" s="9">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C369" s="11" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D369" s="9">
-        <v>9578558</v>
+        <v>10079600</v>
       </c>
       <c r="E369" s="6" t="str">
         <f>IF($D369="","",VLOOKUP($D369,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7865,13 +7860,13 @@
         <v>119</v>
       </c>
       <c r="B370" s="9">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C370" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D370" s="9">
-        <v>9480264</v>
+        <v>9578558</v>
       </c>
       <c r="E370" s="6" t="str">
         <f>IF($D370="","",VLOOKUP($D370,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7883,13 +7878,13 @@
         <v>119</v>
       </c>
       <c r="B371" s="9">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C371" s="11" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D371" s="9">
-        <v>9389063</v>
+        <v>9480264</v>
       </c>
       <c r="E371" s="6" t="str">
         <f>IF($D371="","",VLOOKUP($D371,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7901,13 +7896,13 @@
         <v>119</v>
       </c>
       <c r="B372" s="9">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C372" s="11" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="D372" s="9">
-        <v>9257137</v>
+        <v>9389063</v>
       </c>
       <c r="E372" s="6" t="str">
         <f>IF($D372="","",VLOOKUP($D372,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7919,13 +7914,13 @@
         <v>119</v>
       </c>
       <c r="B373" s="9">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C373" s="11" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="D373" s="9">
-        <v>9172250</v>
+        <v>9257137</v>
       </c>
       <c r="E373" s="6" t="str">
         <f>IF($D373="","",VLOOKUP($D373,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7937,13 +7932,13 @@
         <v>119</v>
       </c>
       <c r="B374" s="9">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C374" s="11" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="D374" s="9">
-        <v>8664783</v>
+        <v>9172250</v>
       </c>
       <c r="E374" s="6" t="str">
         <f>IF($D374="","",VLOOKUP($D374,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7955,13 +7950,13 @@
         <v>119</v>
       </c>
       <c r="B375" s="9">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C375" s="11" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="D375" s="9">
-        <v>8482806</v>
+        <v>8664783</v>
       </c>
       <c r="E375" s="6" t="str">
         <f>IF($D375="","",VLOOKUP($D375,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7973,13 +7968,13 @@
         <v>119</v>
       </c>
       <c r="B376" s="9">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C376" s="11" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="D376" s="9">
-        <v>8449715</v>
+        <v>8482806</v>
       </c>
       <c r="E376" s="6" t="str">
         <f>IF($D376="","",VLOOKUP($D376,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -7991,13 +7986,13 @@
         <v>119</v>
       </c>
       <c r="B377" s="9">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C377" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D377" s="9">
-        <v>8167774</v>
+        <v>8449715</v>
       </c>
       <c r="E377" s="6" t="str">
         <f>IF($D377="","",VLOOKUP($D377,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8009,13 +8004,13 @@
         <v>119</v>
       </c>
       <c r="B378" s="9">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C378" s="11" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="D378" s="9">
-        <v>7379637</v>
+        <v>8167774</v>
       </c>
       <c r="E378" s="6" t="str">
         <f>IF($D378="","",VLOOKUP($D378,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8027,13 +8022,13 @@
         <v>119</v>
       </c>
       <c r="B379" s="9">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C379" s="11" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D379" s="9">
-        <v>7351478</v>
+        <v>7379637</v>
       </c>
       <c r="E379" s="6" t="str">
         <f>IF($D379="","",VLOOKUP($D379,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8045,17 +8040,17 @@
         <v>119</v>
       </c>
       <c r="B380" s="9">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C380" s="11" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="D380" s="9">
-        <v>6388100</v>
+        <v>7351478</v>
       </c>
       <c r="E380" s="6" t="str">
         <f>IF($D380="","",VLOOKUP($D380,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>8단계</v>
+        <v>9단계</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -8063,13 +8058,13 @@
         <v>119</v>
       </c>
       <c r="B381" s="9">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C381" s="11" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="D381" s="9">
-        <v>6032072</v>
+        <v>6388100</v>
       </c>
       <c r="E381" s="6" t="str">
         <f>IF($D381="","",VLOOKUP($D381,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8081,13 +8076,13 @@
         <v>119</v>
       </c>
       <c r="B382" s="9">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C382" s="11" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D382" s="9">
-        <v>5593709</v>
+        <v>6032072</v>
       </c>
       <c r="E382" s="6" t="str">
         <f>IF($D382="","",VLOOKUP($D382,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8099,13 +8094,13 @@
         <v>119</v>
       </c>
       <c r="B383" s="9">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C383" s="11" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="D383" s="9">
-        <v>4942793</v>
+        <v>5593709</v>
       </c>
       <c r="E383" s="6" t="str">
         <f>IF($D383="","",VLOOKUP($D383,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8117,13 +8112,13 @@
         <v>119</v>
       </c>
       <c r="B384" s="9">
-        <v>57</v>
-      </c>
-      <c r="C384" s="10" t="s">
-        <v>89</v>
+        <v>56</v>
+      </c>
+      <c r="C384" s="11" t="s">
+        <v>67</v>
       </c>
       <c r="D384" s="9">
-        <v>4587543</v>
+        <v>4942793</v>
       </c>
       <c r="E384" s="6" t="str">
         <f>IF($D384="","",VLOOKUP($D384,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8135,13 +8130,13 @@
         <v>119</v>
       </c>
       <c r="B385" s="9">
-        <v>58</v>
-      </c>
-      <c r="C385" s="11" t="s">
-        <v>75</v>
+        <v>57</v>
+      </c>
+      <c r="C385" s="10" t="s">
+        <v>89</v>
       </c>
       <c r="D385" s="9">
-        <v>4012455</v>
+        <v>4587543</v>
       </c>
       <c r="E385" s="6" t="str">
         <f>IF($D385="","",VLOOKUP($D385,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8153,13 +8148,13 @@
         <v>119</v>
       </c>
       <c r="B386" s="9">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C386" s="11" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D386" s="9">
-        <v>3613479</v>
+        <v>4012455</v>
       </c>
       <c r="E386" s="6" t="str">
         <f>IF($D386="","",VLOOKUP($D386,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8171,17 +8166,17 @@
         <v>119</v>
       </c>
       <c r="B387" s="9">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C387" s="11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D387" s="9">
-        <v>2363818</v>
+        <v>3613479</v>
       </c>
       <c r="E387" s="6" t="str">
         <f>IF($D387="","",VLOOKUP($D387,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>7단계</v>
+        <v>8단계</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -8189,13 +8184,13 @@
         <v>119</v>
       </c>
       <c r="B388" s="9">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C388" s="11" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D388" s="9">
-        <v>2307050</v>
+        <v>2363818</v>
       </c>
       <c r="E388" s="6" t="str">
         <f>IF($D388="","",VLOOKUP($D388,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8207,17 +8202,17 @@
         <v>119</v>
       </c>
       <c r="B389" s="9">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C389" s="11" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D389" s="9">
-        <v>2215136</v>
+        <v>2307050</v>
       </c>
       <c r="E389" s="6" t="str">
         <f>IF($D389="","",VLOOKUP($D389,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>6단계</v>
+        <v>7단계</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -8225,13 +8220,13 @@
         <v>119</v>
       </c>
       <c r="B390" s="9">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C390" s="11" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D390" s="9">
-        <v>2185908</v>
+        <v>2215136</v>
       </c>
       <c r="E390" s="6" t="str">
         <f>IF($D390="","",VLOOKUP($D390,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8243,13 +8238,13 @@
         <v>119</v>
       </c>
       <c r="B391" s="9">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C391" s="11" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="D391" s="9">
-        <v>1109775</v>
+        <v>2185908</v>
       </c>
       <c r="E391" s="6" t="str">
         <f>IF($D391="","",VLOOKUP($D391,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8261,17 +8256,17 @@
         <v>119</v>
       </c>
       <c r="B392" s="9">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C392" s="11" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D392" s="9">
-        <v>999218</v>
+        <v>1109775</v>
       </c>
       <c r="E392" s="6" t="str">
         <f>IF($D392="","",VLOOKUP($D392,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>5단계</v>
+        <v>6단계</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -8279,13 +8274,13 @@
         <v>119</v>
       </c>
       <c r="B393" s="9">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C393" s="11" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="D393" s="9">
-        <v>845000</v>
+        <v>999218</v>
       </c>
       <c r="E393" s="6" t="str">
         <f>IF($D393="","",VLOOKUP($D393,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -8297,31 +8292,36 @@
         <v>119</v>
       </c>
       <c r="B394" s="9">
-        <v>67</v>
-      </c>
-      <c r="C394" s="2" t="s">
-        <v>90</v>
+        <v>66</v>
+      </c>
+      <c r="C394" s="11" t="s">
+        <v>92</v>
       </c>
       <c r="D394" s="9">
-        <v>364314</v>
+        <v>845000</v>
       </c>
       <c r="E394" s="6" t="str">
         <f>IF($D394="","",VLOOKUP($D394,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>3단계</v>
+        <v>5단계</v>
       </c>
     </row>
     <row r="395" spans="1:5">
       <c r="A395" t="s">
-        <v>126</v>
-      </c>
-      <c r="B395" t="s">
-        <v>129</v>
+        <v>119</v>
+      </c>
+      <c r="B395" s="9">
+        <v>67</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D395" s="9"/>
-      <c r="E395" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="D395" s="9">
+        <v>364314</v>
+      </c>
+      <c r="E395" s="6" t="str">
+        <f>IF($D395="","",VLOOKUP($D395,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>3단계</v>
+      </c>
     </row>
     <row r="396" spans="1:5">
       <c r="A396" t="s">
@@ -9538,60 +9538,6 @@
       </c>
       <c r="C463" s="2" t="s">
         <v>130</v>
-      </c>
-    </row>
-    <row r="464" spans="1:5">
-      <c r="A464" s="12">
-        <v>46195</v>
-      </c>
-      <c r="B464" s="9">
-        <v>1</v>
-      </c>
-      <c r="C464" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D464" s="9">
-        <v>15645750</v>
-      </c>
-      <c r="E464" s="6" t="str">
-        <f>IF($D464="","",VLOOKUP($D464,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="465" spans="1:5">
-      <c r="A465" s="12">
-        <v>46195</v>
-      </c>
-      <c r="B465" s="9">
-        <v>2</v>
-      </c>
-      <c r="C465" t="s">
-        <v>34</v>
-      </c>
-      <c r="D465" s="9">
-        <v>13978410</v>
-      </c>
-      <c r="E465" s="6" t="str">
-        <f>IF($D465="","",VLOOKUP($D465,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
-      </c>
-    </row>
-    <row r="466" spans="1:5">
-      <c r="A466" s="12">
-        <v>46195</v>
-      </c>
-      <c r="B466" s="9">
-        <v>3</v>
-      </c>
-      <c r="C466" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D466" s="9">
-        <v>13088206</v>
-      </c>
-      <c r="E466" s="6" t="str">
-        <f>IF($D466="","",VLOOKUP($D466,기준표!$B$4:$C$12,2,TRUE()))</f>
-        <v>9단계</v>
       </c>
     </row>
   </sheetData>

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A7C2F6A-AFEC-4EF0-8B89-E502FEEE06F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D1D581-140A-4C7A-8DD4-E916C6A30ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="기준표" sheetId="1" r:id="rId1"/>
     <sheet name="2026-06" sheetId="2" r:id="rId2"/>
     <sheet name="2026-07" sheetId="3" r:id="rId3"/>
+    <sheet name="별칭" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1986" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="144">
   <si>
     <t>하한점수</t>
   </si>
@@ -721,72 +722,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>핑도노</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>훔치고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>생각하는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>편</t>
-    </r>
+    <t>핑도노·훔치고·생각하는·편</t>
   </si>
   <si>
     <t>해네도앤댈리는뒈</t>
@@ -822,87 +758,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>티거</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>Ya</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>드랍더튀어</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>자르반</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>84</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>세</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>독터키캔씨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>Turkey1881</t>
-    </r>
-  </si>
-  <si>
     <t>2026-06-24</t>
   </si>
   <si>
@@ -914,6 +769,12 @@
   <si>
     <t>📦 월별 보관 — 2026-07  (날짜별 길드전 랭킹 누적)</t>
   </si>
+  <si>
+    <t>과거닉네임</t>
+  </si>
+  <si>
+    <t>현재닉네임</t>
+  </si>
 </sst>
 </file>
 
@@ -922,7 +783,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -968,6 +829,21 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF999999"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
       <sz val="8"/>
       <name val="돋움"/>
       <family val="3"/>
@@ -1009,7 +885,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1039,7 +915,8 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1095,7 +972,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF999999"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -1418,7 +1295,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -10776,7 +10653,7 @@
       <c r="B483">
         <v>20</v>
       </c>
-      <c r="C483" s="11" t="s">
+      <c r="C483" s="1" t="s">
         <v>99</v>
       </c>
       <c r="D483">
@@ -11007,7 +10884,7 @@
       <c r="B494">
         <v>31</v>
       </c>
-      <c r="C494" s="11" t="s">
+      <c r="C494" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D494">
@@ -11175,7 +11052,7 @@
       <c r="B502">
         <v>39</v>
       </c>
-      <c r="C502" s="11" t="s">
+      <c r="C502" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D502">
@@ -11217,7 +11094,7 @@
       <c r="B504">
         <v>41</v>
       </c>
-      <c r="C504" s="11" t="s">
+      <c r="C504" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D504">
@@ -11694,7 +11571,7 @@
       <c r="B527">
         <v>1</v>
       </c>
-      <c r="C527" s="11" t="s">
+      <c r="C527" s="1" t="s">
         <v>122</v>
       </c>
       <c r="D527">
@@ -11704,7 +11581,7 @@
         <f>IF($D527="","",VLOOKUP($D527,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F527" s="11" t="s">
+      <c r="F527" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -11715,7 +11592,7 @@
       <c r="B528">
         <v>2</v>
       </c>
-      <c r="C528" s="11" t="s">
+      <c r="C528" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D528">
@@ -11725,7 +11602,7 @@
         <f>IF($D528="","",VLOOKUP($D528,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F528" s="11" t="s">
+      <c r="F528" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -11736,7 +11613,7 @@
       <c r="B529">
         <v>3</v>
       </c>
-      <c r="C529" s="11" t="s">
+      <c r="C529" s="1" t="s">
         <v>109</v>
       </c>
       <c r="D529">
@@ -11746,7 +11623,7 @@
         <f>IF($D529="","",VLOOKUP($D529,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F529" s="11" t="s">
+      <c r="F529" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -11757,7 +11634,7 @@
       <c r="B530">
         <v>4</v>
       </c>
-      <c r="C530" s="11" t="s">
+      <c r="C530" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D530">
@@ -11767,7 +11644,7 @@
         <f>IF($D530="","",VLOOKUP($D530,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F530" s="11" t="s">
+      <c r="F530" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -11778,7 +11655,7 @@
       <c r="B531">
         <v>5</v>
       </c>
-      <c r="C531" s="11" t="s">
+      <c r="C531" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D531">
@@ -11788,7 +11665,7 @@
         <f>IF($D531="","",VLOOKUP($D531,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F531" s="11" t="s">
+      <c r="F531" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -11799,7 +11676,7 @@
       <c r="B532">
         <v>6</v>
       </c>
-      <c r="C532" s="11" t="s">
+      <c r="C532" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D532">
@@ -11809,7 +11686,7 @@
         <f>IF($D532="","",VLOOKUP($D532,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F532" s="11" t="s">
+      <c r="F532" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -11820,7 +11697,7 @@
       <c r="B533">
         <v>7</v>
       </c>
-      <c r="C533" s="11" t="s">
+      <c r="C533" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D533">
@@ -11830,7 +11707,7 @@
         <f>IF($D533="","",VLOOKUP($D533,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F533" s="11" t="s">
+      <c r="F533" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -11841,7 +11718,7 @@
       <c r="B534">
         <v>8</v>
       </c>
-      <c r="C534" s="11" t="s">
+      <c r="C534" s="1" t="s">
         <v>105</v>
       </c>
       <c r="D534">
@@ -11851,7 +11728,7 @@
         <f>IF($D534="","",VLOOKUP($D534,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F534" s="11" t="s">
+      <c r="F534" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -11872,7 +11749,7 @@
         <f>IF($D535="","",VLOOKUP($D535,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F535" s="11" t="s">
+      <c r="F535" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -11883,7 +11760,7 @@
       <c r="B536">
         <v>10</v>
       </c>
-      <c r="C536" s="11" t="s">
+      <c r="C536" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D536">
@@ -11893,7 +11770,7 @@
         <f>IF($D536="","",VLOOKUP($D536,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F536" s="11" t="s">
+      <c r="F536" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -11904,7 +11781,7 @@
       <c r="B537">
         <v>11</v>
       </c>
-      <c r="C537" s="11" t="s">
+      <c r="C537" s="1" t="s">
         <v>59</v>
       </c>
       <c r="D537">
@@ -11914,7 +11791,7 @@
         <f>IF($D537="","",VLOOKUP($D537,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F537" s="11" t="s">
+      <c r="F537" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -11925,7 +11802,7 @@
       <c r="B538">
         <v>12</v>
       </c>
-      <c r="C538" s="11" t="s">
+      <c r="C538" s="1" t="s">
         <v>61</v>
       </c>
       <c r="D538">
@@ -11935,7 +11812,7 @@
         <f>IF($D538="","",VLOOKUP($D538,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F538" s="11" t="s">
+      <c r="F538" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -11946,7 +11823,7 @@
       <c r="B539">
         <v>13</v>
       </c>
-      <c r="C539" s="11" t="s">
+      <c r="C539" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D539">
@@ -11956,7 +11833,7 @@
         <f>IF($D539="","",VLOOKUP($D539,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F539" s="11" t="s">
+      <c r="F539" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -11967,7 +11844,7 @@
       <c r="B540">
         <v>14</v>
       </c>
-      <c r="C540" s="11" t="s">
+      <c r="C540" s="1" t="s">
         <v>102</v>
       </c>
       <c r="D540">
@@ -11977,7 +11854,7 @@
         <f>IF($D540="","",VLOOKUP($D540,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F540" s="11" t="s">
+      <c r="F540" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -11988,7 +11865,7 @@
       <c r="B541">
         <v>15</v>
       </c>
-      <c r="C541" s="11" t="s">
+      <c r="C541" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D541">
@@ -11998,7 +11875,7 @@
         <f>IF($D541="","",VLOOKUP($D541,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F541" s="11" t="s">
+      <c r="F541" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12009,7 +11886,7 @@
       <c r="B542">
         <v>16</v>
       </c>
-      <c r="C542" s="11" t="s">
+      <c r="C542" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D542">
@@ -12019,7 +11896,7 @@
         <f>IF($D542="","",VLOOKUP($D542,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F542" s="11" t="s">
+      <c r="F542" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12030,7 +11907,7 @@
       <c r="B543">
         <v>17</v>
       </c>
-      <c r="C543" s="11" t="s">
+      <c r="C543" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D543">
@@ -12040,7 +11917,7 @@
         <f>IF($D543="","",VLOOKUP($D543,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F543" s="11" t="s">
+      <c r="F543" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12061,7 +11938,7 @@
         <f>IF($D544="","",VLOOKUP($D544,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F544" s="11" t="s">
+      <c r="F544" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12072,7 +11949,7 @@
       <c r="B545">
         <v>19</v>
       </c>
-      <c r="C545" s="11" t="s">
+      <c r="C545" s="1" t="s">
         <v>110</v>
       </c>
       <c r="D545">
@@ -12082,7 +11959,7 @@
         <f>IF($D545="","",VLOOKUP($D545,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F545" s="11" t="s">
+      <c r="F545" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12093,7 +11970,7 @@
       <c r="B546">
         <v>20</v>
       </c>
-      <c r="C546" s="11" t="s">
+      <c r="C546" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D546">
@@ -12103,7 +11980,7 @@
         <f>IF($D546="","",VLOOKUP($D546,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F546" s="11" t="s">
+      <c r="F546" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12114,7 +11991,7 @@
       <c r="B547">
         <v>21</v>
       </c>
-      <c r="C547" s="11" t="s">
+      <c r="C547" s="1" t="s">
         <v>132</v>
       </c>
       <c r="D547">
@@ -12124,7 +12001,7 @@
         <f>IF($D547="","",VLOOKUP($D547,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F547" s="11" t="s">
+      <c r="F547" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12135,7 +12012,7 @@
       <c r="B548">
         <v>22</v>
       </c>
-      <c r="C548" s="11" t="s">
+      <c r="C548" s="1" t="s">
         <v>133</v>
       </c>
       <c r="D548">
@@ -12145,7 +12022,7 @@
         <f>IF($D548="","",VLOOKUP($D548,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F548" s="11" t="s">
+      <c r="F548" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12156,7 +12033,7 @@
       <c r="B549">
         <v>23</v>
       </c>
-      <c r="C549" s="11" t="s">
+      <c r="C549" s="1" t="s">
         <v>56</v>
       </c>
       <c r="D549">
@@ -12166,7 +12043,7 @@
         <f>IF($D549="","",VLOOKUP($D549,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F549" s="11" t="s">
+      <c r="F549" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12177,7 +12054,7 @@
       <c r="B550">
         <v>24</v>
       </c>
-      <c r="C550" s="11" t="s">
+      <c r="C550" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D550">
@@ -12187,7 +12064,7 @@
         <f>IF($D550="","",VLOOKUP($D550,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F550" s="11" t="s">
+      <c r="F550" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12198,7 +12075,7 @@
       <c r="B551">
         <v>25</v>
       </c>
-      <c r="C551" s="11" t="s">
+      <c r="C551" s="1" t="s">
         <v>134</v>
       </c>
       <c r="D551">
@@ -12208,7 +12085,7 @@
         <f>IF($D551="","",VLOOKUP($D551,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F551" s="11" t="s">
+      <c r="F551" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12219,7 +12096,7 @@
       <c r="B552">
         <v>26</v>
       </c>
-      <c r="C552" s="11" t="s">
+      <c r="C552" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D552">
@@ -12229,7 +12106,7 @@
         <f>IF($D552="","",VLOOKUP($D552,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F552" s="11" t="s">
+      <c r="F552" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12240,7 +12117,7 @@
       <c r="B553">
         <v>27</v>
       </c>
-      <c r="C553" s="11" t="s">
+      <c r="C553" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D553">
@@ -12250,7 +12127,7 @@
         <f>IF($D553="","",VLOOKUP($D553,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F553" s="11" t="s">
+      <c r="F553" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12261,7 +12138,7 @@
       <c r="B554">
         <v>28</v>
       </c>
-      <c r="C554" s="11" t="s">
+      <c r="C554" s="1" t="s">
         <v>135</v>
       </c>
       <c r="D554">
@@ -12271,7 +12148,7 @@
         <f>IF($D554="","",VLOOKUP($D554,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F554" s="11" t="s">
+      <c r="F554" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12282,7 +12159,7 @@
       <c r="B555">
         <v>29</v>
       </c>
-      <c r="C555" s="11" t="s">
+      <c r="C555" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D555">
@@ -12292,7 +12169,7 @@
         <f>IF($D555="","",VLOOKUP($D555,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F555" s="11" t="s">
+      <c r="F555" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12303,7 +12180,7 @@
       <c r="B556">
         <v>30</v>
       </c>
-      <c r="C556" s="11" t="s">
+      <c r="C556" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D556">
@@ -12313,7 +12190,7 @@
         <f>IF($D556="","",VLOOKUP($D556,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F556" s="11" t="s">
+      <c r="F556" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12324,7 +12201,7 @@
       <c r="B557">
         <v>31</v>
       </c>
-      <c r="C557" s="11" t="s">
+      <c r="C557" s="1" t="s">
         <v>101</v>
       </c>
       <c r="D557">
@@ -12334,7 +12211,7 @@
         <f>IF($D557="","",VLOOKUP($D557,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F557" s="11" t="s">
+      <c r="F557" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12345,7 +12222,7 @@
       <c r="B558">
         <v>32</v>
       </c>
-      <c r="C558" s="11" t="s">
+      <c r="C558" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D558">
@@ -12355,7 +12232,7 @@
         <f>IF($D558="","",VLOOKUP($D558,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F558" s="11" t="s">
+      <c r="F558" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12366,7 +12243,7 @@
       <c r="B559">
         <v>33</v>
       </c>
-      <c r="C559" s="11" t="s">
+      <c r="C559" s="1" t="s">
         <v>136</v>
       </c>
       <c r="D559">
@@ -12376,7 +12253,7 @@
         <f>IF($D559="","",VLOOKUP($D559,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F559" s="11" t="s">
+      <c r="F559" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12387,7 +12264,7 @@
       <c r="B560">
         <v>34</v>
       </c>
-      <c r="C560" s="11" t="s">
+      <c r="C560" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D560">
@@ -12397,7 +12274,7 @@
         <f>IF($D560="","",VLOOKUP($D560,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F560" s="11" t="s">
+      <c r="F560" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12418,7 +12295,7 @@
         <f>IF($D561="","",VLOOKUP($D561,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F561" s="11" t="s">
+      <c r="F561" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12429,7 +12306,7 @@
       <c r="B562">
         <v>36</v>
       </c>
-      <c r="C562" s="11" t="s">
+      <c r="C562" s="1" t="s">
         <v>118</v>
       </c>
       <c r="D562">
@@ -12439,7 +12316,7 @@
         <f>IF($D562="","",VLOOKUP($D562,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F562" s="11" t="s">
+      <c r="F562" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12450,7 +12327,7 @@
       <c r="B563">
         <v>37</v>
       </c>
-      <c r="C563" s="11" t="s">
+      <c r="C563" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D563">
@@ -12460,7 +12337,7 @@
         <f>IF($D563="","",VLOOKUP($D563,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F563" s="11" t="s">
+      <c r="F563" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12471,7 +12348,7 @@
       <c r="B564">
         <v>38</v>
       </c>
-      <c r="C564" s="11" t="s">
+      <c r="C564" s="1" t="s">
         <v>60</v>
       </c>
       <c r="D564">
@@ -12481,7 +12358,7 @@
         <f>IF($D564="","",VLOOKUP($D564,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F564" s="11" t="s">
+      <c r="F564" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12492,7 +12369,7 @@
       <c r="B565">
         <v>39</v>
       </c>
-      <c r="C565" s="11" t="s">
+      <c r="C565" s="1" t="s">
         <v>73</v>
       </c>
       <c r="D565">
@@ -12502,7 +12379,7 @@
         <f>IF($D565="","",VLOOKUP($D565,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F565" s="11" t="s">
+      <c r="F565" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12513,7 +12390,7 @@
       <c r="B566">
         <v>40</v>
       </c>
-      <c r="C566" s="11" t="s">
+      <c r="C566" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D566">
@@ -12523,7 +12400,7 @@
         <f>IF($D566="","",VLOOKUP($D566,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F566" s="11" t="s">
+      <c r="F566" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12534,7 +12411,7 @@
       <c r="B567">
         <v>41</v>
       </c>
-      <c r="C567" s="11" t="s">
+      <c r="C567" s="1" t="s">
         <v>108</v>
       </c>
       <c r="D567">
@@ -12544,7 +12421,7 @@
         <f>IF($D567="","",VLOOKUP($D567,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F567" s="11" t="s">
+      <c r="F567" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12555,7 +12432,7 @@
       <c r="B568">
         <v>42</v>
       </c>
-      <c r="C568" s="11" t="s">
+      <c r="C568" s="1" t="s">
         <v>74</v>
       </c>
       <c r="D568">
@@ -12565,7 +12442,7 @@
         <f>IF($D568="","",VLOOKUP($D568,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F568" s="11" t="s">
+      <c r="F568" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12576,7 +12453,7 @@
       <c r="B569">
         <v>43</v>
       </c>
-      <c r="C569" s="11" t="s">
+      <c r="C569" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D569">
@@ -12586,7 +12463,7 @@
         <f>IF($D569="","",VLOOKUP($D569,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F569" s="11" t="s">
+      <c r="F569" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12597,7 +12474,7 @@
       <c r="B570">
         <v>44</v>
       </c>
-      <c r="C570" s="11" t="s">
+      <c r="C570" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D570">
@@ -12607,7 +12484,7 @@
         <f>IF($D570="","",VLOOKUP($D570,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F570" s="11" t="s">
+      <c r="F570" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12618,7 +12495,7 @@
       <c r="B571">
         <v>45</v>
       </c>
-      <c r="C571" s="11" t="s">
+      <c r="C571" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D571">
@@ -12628,7 +12505,7 @@
         <f>IF($D571="","",VLOOKUP($D571,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F571" s="11" t="s">
+      <c r="F571" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12639,8 +12516,8 @@
       <c r="B572">
         <v>46</v>
       </c>
-      <c r="C572" s="11" t="s">
-        <v>138</v>
+      <c r="C572" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="D572">
         <v>3831557</v>
@@ -12649,7 +12526,7 @@
         <f>IF($D572="","",VLOOKUP($D572,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F572" s="11" t="s">
+      <c r="F572" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12660,7 +12537,7 @@
       <c r="B573">
         <v>47</v>
       </c>
-      <c r="C573" s="11" t="s">
+      <c r="C573" s="1" t="s">
         <v>99</v>
       </c>
       <c r="D573">
@@ -12670,7 +12547,7 @@
         <f>IF($D573="","",VLOOKUP($D573,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F573" s="11" t="s">
+      <c r="F573" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12681,7 +12558,7 @@
       <c r="B574">
         <v>48</v>
       </c>
-      <c r="C574" s="11" t="s">
+      <c r="C574" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D574">
@@ -12691,7 +12568,7 @@
         <f>IF($D574="","",VLOOKUP($D574,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F574" s="11" t="s">
+      <c r="F574" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12702,7 +12579,7 @@
       <c r="B575">
         <v>49</v>
       </c>
-      <c r="C575" s="11" t="s">
+      <c r="C575" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D575">
@@ -12712,7 +12589,7 @@
         <f>IF($D575="","",VLOOKUP($D575,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F575" s="11" t="s">
+      <c r="F575" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12723,7 +12600,7 @@
       <c r="B576">
         <v>50</v>
       </c>
-      <c r="C576" s="11" t="s">
+      <c r="C576" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D576">
@@ -12733,7 +12610,7 @@
         <f>IF($D576="","",VLOOKUP($D576,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F576" s="11" t="s">
+      <c r="F576" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12744,7 +12621,7 @@
       <c r="B577">
         <v>51</v>
       </c>
-      <c r="C577" s="11" t="s">
+      <c r="C577" s="1" t="s">
         <v>65</v>
       </c>
       <c r="D577">
@@ -12754,7 +12631,7 @@
         <f>IF($D577="","",VLOOKUP($D577,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F577" s="11" t="s">
+      <c r="F577" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12765,7 +12642,7 @@
       <c r="B578">
         <v>52</v>
       </c>
-      <c r="C578" s="11" t="s">
+      <c r="C578" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D578">
@@ -12775,7 +12652,7 @@
         <f>IF($D578="","",VLOOKUP($D578,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F578" s="11" t="s">
+      <c r="F578" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12786,7 +12663,7 @@
       <c r="B579">
         <v>53</v>
       </c>
-      <c r="C579" s="11" t="s">
+      <c r="C579" s="1" t="s">
         <v>125</v>
       </c>
       <c r="D579">
@@ -12796,7 +12673,7 @@
         <f>IF($D579="","",VLOOKUP($D579,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F579" s="11" t="s">
+      <c r="F579" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12807,7 +12684,7 @@
       <c r="B580">
         <v>54</v>
       </c>
-      <c r="C580" s="11" t="s">
+      <c r="C580" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D580">
@@ -12817,7 +12694,7 @@
         <f>IF($D580="","",VLOOKUP($D580,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F580" s="11" t="s">
+      <c r="F580" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12828,8 +12705,8 @@
       <c r="B581">
         <v>55</v>
       </c>
-      <c r="C581" s="11" t="s">
-        <v>139</v>
+      <c r="C581" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="D581">
         <v>2525220</v>
@@ -12838,7 +12715,7 @@
         <f>IF($D581="","",VLOOKUP($D581,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>7단계</v>
       </c>
-      <c r="F581" s="11" t="s">
+      <c r="F581" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12849,7 +12726,7 @@
       <c r="B582">
         <v>56</v>
       </c>
-      <c r="C582" s="11" t="s">
+      <c r="C582" s="1" t="s">
         <v>119</v>
       </c>
       <c r="D582">
@@ -12859,7 +12736,7 @@
         <f>IF($D582="","",VLOOKUP($D582,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>7단계</v>
       </c>
-      <c r="F582" s="11" t="s">
+      <c r="F582" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12870,7 +12747,7 @@
       <c r="B583">
         <v>57</v>
       </c>
-      <c r="C583" s="11" t="s">
+      <c r="C583" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D583">
@@ -12880,7 +12757,7 @@
         <f>IF($D583="","",VLOOKUP($D583,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>6단계</v>
       </c>
-      <c r="F583" s="11" t="s">
+      <c r="F583" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12891,8 +12768,8 @@
       <c r="B584">
         <v>58</v>
       </c>
-      <c r="C584" s="11" t="s">
-        <v>140</v>
+      <c r="C584" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="D584">
         <v>1972712</v>
@@ -12901,7 +12778,7 @@
         <f>IF($D584="","",VLOOKUP($D584,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>6단계</v>
       </c>
-      <c r="F584" s="11" t="s">
+      <c r="F584" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12922,7 +12799,7 @@
         <f>IF($D585="","",VLOOKUP($D585,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>6단계</v>
       </c>
-      <c r="F585" s="11" t="s">
+      <c r="F585" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12933,7 +12810,7 @@
       <c r="B586">
         <v>60</v>
       </c>
-      <c r="C586" s="11" t="s">
+      <c r="C586" s="1" t="s">
         <v>81</v>
       </c>
       <c r="D586">
@@ -12943,7 +12820,7 @@
         <f>IF($D586="","",VLOOKUP($D586,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>6단계</v>
       </c>
-      <c r="F586" s="11" t="s">
+      <c r="F586" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12954,7 +12831,7 @@
       <c r="B587">
         <v>61</v>
       </c>
-      <c r="C587" s="11" t="s">
+      <c r="C587" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D587">
@@ -12964,7 +12841,7 @@
         <f>IF($D587="","",VLOOKUP($D587,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>6단계</v>
       </c>
-      <c r="F587" s="11" t="s">
+      <c r="F587" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12975,7 +12852,7 @@
       <c r="B588">
         <v>62</v>
       </c>
-      <c r="C588" s="11" t="s">
+      <c r="C588" s="1" t="s">
         <v>92</v>
       </c>
       <c r="D588">
@@ -12985,7 +12862,7 @@
         <f>IF($D588="","",VLOOKUP($D588,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>6단계</v>
       </c>
-      <c r="F588" s="11" t="s">
+      <c r="F588" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -12996,7 +12873,7 @@
       <c r="B589">
         <v>63</v>
       </c>
-      <c r="C589" s="11" t="s">
+      <c r="C589" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D589">
@@ -13006,13 +12883,13 @@
         <f>IF($D589="","",VLOOKUP($D589,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>5단계</v>
       </c>
-      <c r="F589" s="11" t="s">
+      <c r="F589" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="590" spans="1:6">
       <c r="A590" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B590" t="s">
         <v>95</v>
@@ -13024,18 +12901,18 @@
         <f>IF($D590="","",VLOOKUP($D590,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v/>
       </c>
-      <c r="F590" s="11" t="s">
+      <c r="F590" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="591" spans="1:6">
       <c r="A591" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B591">
         <v>1</v>
       </c>
-      <c r="C591" s="11" t="s">
+      <c r="C591" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D591">
@@ -13045,13 +12922,13 @@
         <f>IF($D591="","",VLOOKUP($D591,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F591" s="11" t="s">
+      <c r="F591" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="592" spans="1:6">
       <c r="A592" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B592">
         <v>2</v>
@@ -13066,18 +12943,18 @@
         <f>IF($D592="","",VLOOKUP($D592,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F592" s="11" t="s">
+      <c r="F592" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="593" spans="1:6">
       <c r="A593" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B593">
         <v>3</v>
       </c>
-      <c r="C593" s="11" t="s">
+      <c r="C593" s="1" t="s">
         <v>99</v>
       </c>
       <c r="D593">
@@ -13087,18 +12964,18 @@
         <f>IF($D593="","",VLOOKUP($D593,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F593" s="11" t="s">
+      <c r="F593" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="594" spans="1:6">
       <c r="A594" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B594">
         <v>4</v>
       </c>
-      <c r="C594" s="11" t="s">
+      <c r="C594" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D594">
@@ -13108,18 +12985,18 @@
         <f>IF($D594="","",VLOOKUP($D594,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F594" s="11" t="s">
+      <c r="F594" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="595" spans="1:6">
       <c r="A595" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B595">
         <v>5</v>
       </c>
-      <c r="C595" s="11" t="s">
+      <c r="C595" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D595">
@@ -13129,18 +13006,18 @@
         <f>IF($D595="","",VLOOKUP($D595,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F595" s="11" t="s">
+      <c r="F595" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="596" spans="1:6">
       <c r="A596" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B596">
         <v>6</v>
       </c>
-      <c r="C596" s="11" t="s">
+      <c r="C596" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D596">
@@ -13150,18 +13027,18 @@
         <f>IF($D596="","",VLOOKUP($D596,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F596" s="11" t="s">
+      <c r="F596" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="597" spans="1:6">
       <c r="A597" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B597">
         <v>7</v>
       </c>
-      <c r="C597" s="11" t="s">
+      <c r="C597" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D597">
@@ -13171,19 +13048,19 @@
         <f>IF($D597="","",VLOOKUP($D597,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F597" s="11" t="s">
+      <c r="F597" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="598" spans="1:6">
       <c r="A598" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B598">
         <v>8</v>
       </c>
-      <c r="C598" s="11" t="s">
-        <v>142</v>
+      <c r="C598" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="D598">
         <v>11921560</v>
@@ -13192,13 +13069,13 @@
         <f>IF($D598="","",VLOOKUP($D598,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F598" s="11" t="s">
+      <c r="F598" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="599" spans="1:6">
       <c r="A599" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B599">
         <v>9</v>
@@ -13213,18 +13090,18 @@
         <f>IF($D599="","",VLOOKUP($D599,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F599" s="11" t="s">
+      <c r="F599" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="600" spans="1:6">
       <c r="A600" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B600">
         <v>10</v>
       </c>
-      <c r="C600" s="11" t="s">
+      <c r="C600" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D600">
@@ -13234,18 +13111,18 @@
         <f>IF($D600="","",VLOOKUP($D600,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F600" s="11" t="s">
+      <c r="F600" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="601" spans="1:6">
       <c r="A601" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B601">
         <v>11</v>
       </c>
-      <c r="C601" s="11" t="s">
+      <c r="C601" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D601">
@@ -13255,18 +13132,18 @@
         <f>IF($D601="","",VLOOKUP($D601,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F601" s="11" t="s">
+      <c r="F601" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="602" spans="1:6">
       <c r="A602" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B602">
         <v>12</v>
       </c>
-      <c r="C602" s="11" t="s">
+      <c r="C602" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D602">
@@ -13276,18 +13153,18 @@
         <f>IF($D602="","",VLOOKUP($D602,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F602" s="11" t="s">
+      <c r="F602" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="603" spans="1:6">
       <c r="A603" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B603">
         <v>13</v>
       </c>
-      <c r="C603" s="11" t="s">
+      <c r="C603" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D603">
@@ -13297,18 +13174,18 @@
         <f>IF($D603="","",VLOOKUP($D603,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F603" s="11" t="s">
+      <c r="F603" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="604" spans="1:6">
       <c r="A604" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B604">
         <v>14</v>
       </c>
-      <c r="C604" s="11" t="s">
+      <c r="C604" s="1" t="s">
         <v>73</v>
       </c>
       <c r="D604">
@@ -13318,18 +13195,18 @@
         <f>IF($D604="","",VLOOKUP($D604,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F604" s="11" t="s">
+      <c r="F604" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="605" spans="1:6">
       <c r="A605" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B605">
         <v>15</v>
       </c>
-      <c r="C605" s="11" t="s">
+      <c r="C605" s="1" t="s">
         <v>105</v>
       </c>
       <c r="D605">
@@ -13339,18 +13216,18 @@
         <f>IF($D605="","",VLOOKUP($D605,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F605" s="11" t="s">
+      <c r="F605" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="606" spans="1:6">
       <c r="A606" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B606">
         <v>16</v>
       </c>
-      <c r="C606" s="11" t="s">
+      <c r="C606" s="1" t="s">
         <v>102</v>
       </c>
       <c r="D606">
@@ -13360,19 +13237,19 @@
         <f>IF($D606="","",VLOOKUP($D606,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F606" s="11" t="s">
+      <c r="F606" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="607" spans="1:6">
       <c r="A607" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B607">
         <v>17</v>
       </c>
-      <c r="C607" s="11" t="s">
-        <v>138</v>
+      <c r="C607" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="D607">
         <v>9002723</v>
@@ -13381,18 +13258,18 @@
         <f>IF($D607="","",VLOOKUP($D607,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F607" s="11" t="s">
+      <c r="F607" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="608" spans="1:6">
       <c r="A608" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B608">
         <v>18</v>
       </c>
-      <c r="C608" s="11" t="s">
+      <c r="C608" s="1" t="s">
         <v>109</v>
       </c>
       <c r="D608">
@@ -13402,18 +13279,18 @@
         <f>IF($D608="","",VLOOKUP($D608,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F608" s="11" t="s">
+      <c r="F608" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="609" spans="1:6">
       <c r="A609" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B609">
         <v>19</v>
       </c>
-      <c r="C609" s="11" t="s">
+      <c r="C609" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D609">
@@ -13423,18 +13300,18 @@
         <f>IF($D609="","",VLOOKUP($D609,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F609" s="11" t="s">
+      <c r="F609" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="610" spans="1:6">
       <c r="A610" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B610">
         <v>20</v>
       </c>
-      <c r="C610" s="11" t="s">
+      <c r="C610" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D610">
@@ -13444,18 +13321,18 @@
         <f>IF($D610="","",VLOOKUP($D610,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F610" s="11" t="s">
+      <c r="F610" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="611" spans="1:6">
       <c r="A611" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B611">
         <v>21</v>
       </c>
-      <c r="C611" s="11" t="s">
+      <c r="C611" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D611">
@@ -13465,18 +13342,18 @@
         <f>IF($D611="","",VLOOKUP($D611,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F611" s="11" t="s">
+      <c r="F611" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="612" spans="1:6">
       <c r="A612" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B612">
         <v>22</v>
       </c>
-      <c r="C612" s="11" t="s">
+      <c r="C612" s="1" t="s">
         <v>101</v>
       </c>
       <c r="D612">
@@ -13486,18 +13363,18 @@
         <f>IF($D612="","",VLOOKUP($D612,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F612" s="11" t="s">
+      <c r="F612" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="613" spans="1:6">
       <c r="A613" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B613">
         <v>23</v>
       </c>
-      <c r="C613" s="11" t="s">
+      <c r="C613" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D613">
@@ -13507,18 +13384,18 @@
         <f>IF($D613="","",VLOOKUP($D613,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F613" s="11" t="s">
+      <c r="F613" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="614" spans="1:6">
       <c r="A614" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B614">
         <v>24</v>
       </c>
-      <c r="C614" s="11" t="s">
+      <c r="C614" s="1" t="s">
         <v>134</v>
       </c>
       <c r="D614">
@@ -13528,18 +13405,18 @@
         <f>IF($D614="","",VLOOKUP($D614,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F614" s="11" t="s">
+      <c r="F614" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="615" spans="1:6">
       <c r="A615" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B615">
         <v>25</v>
       </c>
-      <c r="C615" s="11" t="s">
+      <c r="C615" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D615">
@@ -13549,19 +13426,19 @@
         <f>IF($D615="","",VLOOKUP($D615,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F615" s="11" t="s">
+      <c r="F615" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="616" spans="1:6">
       <c r="A616" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B616">
         <v>26</v>
       </c>
-      <c r="C616" s="11" t="s">
-        <v>143</v>
+      <c r="C616" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D616">
         <v>7670475</v>
@@ -13570,18 +13447,18 @@
         <f>IF($D616="","",VLOOKUP($D616,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F616" s="11" t="s">
+      <c r="F616" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="617" spans="1:6">
       <c r="A617" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B617">
         <v>27</v>
       </c>
-      <c r="C617" s="11" t="s">
+      <c r="C617" s="1" t="s">
         <v>135</v>
       </c>
       <c r="D617">
@@ -13591,18 +13468,18 @@
         <f>IF($D617="","",VLOOKUP($D617,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F617" s="11" t="s">
+      <c r="F617" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="618" spans="1:6">
       <c r="A618" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B618">
         <v>28</v>
       </c>
-      <c r="C618" s="11" t="s">
+      <c r="C618" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D618">
@@ -13612,18 +13489,18 @@
         <f>IF($D618="","",VLOOKUP($D618,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F618" s="11" t="s">
+      <c r="F618" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="619" spans="1:6">
       <c r="A619" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B619">
         <v>29</v>
       </c>
-      <c r="C619" s="11" t="s">
+      <c r="C619" s="1" t="s">
         <v>132</v>
       </c>
       <c r="D619">
@@ -13633,18 +13510,18 @@
         <f>IF($D619="","",VLOOKUP($D619,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F619" s="11" t="s">
+      <c r="F619" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="620" spans="1:6">
       <c r="A620" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B620">
         <v>30</v>
       </c>
-      <c r="C620" s="11" t="s">
+      <c r="C620" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D620">
@@ -13654,18 +13531,18 @@
         <f>IF($D620="","",VLOOKUP($D620,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F620" s="11" t="s">
+      <c r="F620" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="621" spans="1:6">
       <c r="A621" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B621">
         <v>31</v>
       </c>
-      <c r="C621" s="11" t="s">
+      <c r="C621" s="1" t="s">
         <v>108</v>
       </c>
       <c r="D621">
@@ -13675,18 +13552,18 @@
         <f>IF($D621="","",VLOOKUP($D621,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F621" s="11" t="s">
+      <c r="F621" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="622" spans="1:6">
       <c r="A622" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B622">
         <v>32</v>
       </c>
-      <c r="C622" s="11" t="s">
+      <c r="C622" s="1" t="s">
         <v>118</v>
       </c>
       <c r="D622">
@@ -13696,18 +13573,18 @@
         <f>IF($D622="","",VLOOKUP($D622,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-      <c r="F622" s="11" t="s">
+      <c r="F622" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="623" spans="1:6">
       <c r="A623" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B623">
         <v>33</v>
       </c>
-      <c r="C623" s="11" t="s">
+      <c r="C623" s="1" t="s">
         <v>133</v>
       </c>
       <c r="D623">
@@ -13717,18 +13594,18 @@
         <f>IF($D623="","",VLOOKUP($D623,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F623" s="11" t="s">
+      <c r="F623" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="624" spans="1:6">
       <c r="A624" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B624">
         <v>34</v>
       </c>
-      <c r="C624" s="11" t="s">
+      <c r="C624" s="1" t="s">
         <v>61</v>
       </c>
       <c r="D624">
@@ -13738,18 +13615,18 @@
         <f>IF($D624="","",VLOOKUP($D624,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F624" s="11" t="s">
+      <c r="F624" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="625" spans="1:6">
       <c r="A625" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B625">
         <v>35</v>
       </c>
-      <c r="C625" s="11" t="s">
+      <c r="C625" s="1" t="s">
         <v>56</v>
       </c>
       <c r="D625">
@@ -13759,18 +13636,18 @@
         <f>IF($D625="","",VLOOKUP($D625,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F625" s="11" t="s">
+      <c r="F625" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="626" spans="1:6">
       <c r="A626" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B626">
         <v>36</v>
       </c>
-      <c r="C626" s="11" t="s">
+      <c r="C626" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D626">
@@ -13780,18 +13657,18 @@
         <f>IF($D626="","",VLOOKUP($D626,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F626" s="11" t="s">
+      <c r="F626" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="627" spans="1:6">
       <c r="A627" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B627">
         <v>37</v>
       </c>
-      <c r="C627" s="11" t="s">
+      <c r="C627" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D627">
@@ -13801,18 +13678,18 @@
         <f>IF($D627="","",VLOOKUP($D627,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F627" s="11" t="s">
+      <c r="F627" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="628" spans="1:6">
       <c r="A628" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B628">
         <v>38</v>
       </c>
-      <c r="C628" s="11" t="s">
+      <c r="C628" s="1" t="s">
         <v>60</v>
       </c>
       <c r="D628">
@@ -13822,18 +13699,18 @@
         <f>IF($D628="","",VLOOKUP($D628,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F628" s="11" t="s">
+      <c r="F628" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="629" spans="1:6">
       <c r="A629" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B629">
         <v>39</v>
       </c>
-      <c r="C629" s="11" t="s">
+      <c r="C629" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D629">
@@ -13843,13 +13720,13 @@
         <f>IF($D629="","",VLOOKUP($D629,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F629" s="11" t="s">
+      <c r="F629" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="630" spans="1:6">
       <c r="A630" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B630">
         <v>40</v>
@@ -13864,13 +13741,13 @@
         <f>IF($D630="","",VLOOKUP($D630,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F630" s="11" t="s">
+      <c r="F630" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="631" spans="1:6">
       <c r="A631" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B631">
         <v>41</v>
@@ -13885,18 +13762,18 @@
         <f>IF($D631="","",VLOOKUP($D631,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F631" s="11" t="s">
+      <c r="F631" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="632" spans="1:6">
       <c r="A632" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B632">
         <v>42</v>
       </c>
-      <c r="C632" s="11" t="s">
+      <c r="C632" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D632">
@@ -13906,18 +13783,18 @@
         <f>IF($D632="","",VLOOKUP($D632,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F632" s="11" t="s">
+      <c r="F632" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="633" spans="1:6">
       <c r="A633" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B633">
         <v>43</v>
       </c>
-      <c r="C633" s="11" t="s">
+      <c r="C633" s="1" t="s">
         <v>59</v>
       </c>
       <c r="D633">
@@ -13927,18 +13804,18 @@
         <f>IF($D633="","",VLOOKUP($D633,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F633" s="11" t="s">
+      <c r="F633" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="634" spans="1:6">
       <c r="A634" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B634">
         <v>44</v>
       </c>
-      <c r="C634" s="11" t="s">
+      <c r="C634" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D634">
@@ -13948,18 +13825,18 @@
         <f>IF($D634="","",VLOOKUP($D634,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F634" s="11" t="s">
+      <c r="F634" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="635" spans="1:6">
       <c r="A635" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B635">
         <v>45</v>
       </c>
-      <c r="C635" s="11" t="s">
+      <c r="C635" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D635">
@@ -13969,18 +13846,18 @@
         <f>IF($D635="","",VLOOKUP($D635,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F635" s="11" t="s">
+      <c r="F635" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="636" spans="1:6">
       <c r="A636" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B636">
         <v>46</v>
       </c>
-      <c r="C636" s="11" t="s">
+      <c r="C636" s="1" t="s">
         <v>65</v>
       </c>
       <c r="D636">
@@ -13990,19 +13867,19 @@
         <f>IF($D636="","",VLOOKUP($D636,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F636" s="11" t="s">
+      <c r="F636" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="637" spans="1:6">
       <c r="A637" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B637">
         <v>47</v>
       </c>
-      <c r="C637" s="11" t="s">
-        <v>139</v>
+      <c r="C637" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="D637">
         <v>3691165</v>
@@ -14011,18 +13888,18 @@
         <f>IF($D637="","",VLOOKUP($D637,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F637" s="11" t="s">
+      <c r="F637" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="638" spans="1:6">
       <c r="A638" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B638">
         <v>48</v>
       </c>
-      <c r="C638" s="11" t="s">
+      <c r="C638" s="1" t="s">
         <v>74</v>
       </c>
       <c r="D638">
@@ -14032,18 +13909,18 @@
         <f>IF($D638="","",VLOOKUP($D638,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F638" s="11" t="s">
+      <c r="F638" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="639" spans="1:6">
       <c r="A639" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B639">
         <v>49</v>
       </c>
-      <c r="C639" s="11" t="s">
+      <c r="C639" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D639">
@@ -14053,18 +13930,18 @@
         <f>IF($D639="","",VLOOKUP($D639,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F639" s="11" t="s">
+      <c r="F639" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="640" spans="1:6">
       <c r="A640" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B640">
         <v>50</v>
       </c>
-      <c r="C640" s="11" t="s">
+      <c r="C640" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D640">
@@ -14074,18 +13951,18 @@
         <f>IF($D640="","",VLOOKUP($D640,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F640" s="11" t="s">
+      <c r="F640" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="641" spans="1:6">
       <c r="A641" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B641">
         <v>51</v>
       </c>
-      <c r="C641" s="11" t="s">
+      <c r="C641" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D641">
@@ -14095,18 +13972,18 @@
         <f>IF($D641="","",VLOOKUP($D641,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F641" s="11" t="s">
+      <c r="F641" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="642" spans="1:6">
       <c r="A642" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B642">
         <v>52</v>
       </c>
-      <c r="C642" s="11" t="s">
+      <c r="C642" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D642">
@@ -14116,18 +13993,18 @@
         <f>IF($D642="","",VLOOKUP($D642,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F642" s="11" t="s">
+      <c r="F642" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="643" spans="1:6">
       <c r="A643" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B643">
         <v>53</v>
       </c>
-      <c r="C643" s="11" t="s">
+      <c r="C643" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D643">
@@ -14137,18 +14014,18 @@
         <f>IF($D643="","",VLOOKUP($D643,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F643" s="11" t="s">
+      <c r="F643" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="644" spans="1:6">
       <c r="A644" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B644">
         <v>54</v>
       </c>
-      <c r="C644" s="11" t="s">
+      <c r="C644" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D644">
@@ -14158,18 +14035,18 @@
         <f>IF($D644="","",VLOOKUP($D644,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-      <c r="F644" s="11" t="s">
+      <c r="F644" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="645" spans="1:6">
       <c r="A645" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B645">
         <v>55</v>
       </c>
-      <c r="C645" s="11" t="s">
+      <c r="C645" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D645">
@@ -14179,18 +14056,18 @@
         <f>IF($D645="","",VLOOKUP($D645,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>7단계</v>
       </c>
-      <c r="F645" s="11" t="s">
+      <c r="F645" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="646" spans="1:6">
       <c r="A646" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B646">
         <v>56</v>
       </c>
-      <c r="C646" s="11" t="s">
+      <c r="C646" s="1" t="s">
         <v>81</v>
       </c>
       <c r="D646">
@@ -14200,19 +14077,19 @@
         <f>IF($D646="","",VLOOKUP($D646,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>7단계</v>
       </c>
-      <c r="F646" s="11" t="s">
+      <c r="F646" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="647" spans="1:6">
       <c r="A647" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B647">
         <v>57</v>
       </c>
-      <c r="C647" s="11" t="s">
-        <v>140</v>
+      <c r="C647" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="D647">
         <v>2073540</v>
@@ -14221,18 +14098,18 @@
         <f>IF($D647="","",VLOOKUP($D647,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>6단계</v>
       </c>
-      <c r="F647" s="11" t="s">
+      <c r="F647" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="648" spans="1:6">
       <c r="A648" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B648">
         <v>58</v>
       </c>
-      <c r="C648" s="11" t="s">
+      <c r="C648" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D648">
@@ -14242,18 +14119,18 @@
         <f>IF($D648="","",VLOOKUP($D648,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>6단계</v>
       </c>
-      <c r="F648" s="11" t="s">
+      <c r="F648" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="649" spans="1:6">
       <c r="A649" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B649">
         <v>59</v>
       </c>
-      <c r="C649" s="11" t="s">
+      <c r="C649" s="1" t="s">
         <v>92</v>
       </c>
       <c r="D649">
@@ -14263,18 +14140,18 @@
         <f>IF($D649="","",VLOOKUP($D649,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>6단계</v>
       </c>
-      <c r="F649" s="11" t="s">
+      <c r="F649" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="650" spans="1:6">
       <c r="A650" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B650">
         <v>60</v>
       </c>
-      <c r="C650" s="11" t="s">
+      <c r="C650" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D650">
@@ -14284,18 +14161,18 @@
         <f>IF($D650="","",VLOOKUP($D650,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>6단계</v>
       </c>
-      <c r="F650" s="11" t="s">
+      <c r="F650" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="651" spans="1:6">
       <c r="A651" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B651">
         <v>61</v>
       </c>
-      <c r="C651" s="11" t="s">
+      <c r="C651" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D651">
@@ -14305,18 +14182,18 @@
         <f>IF($D651="","",VLOOKUP($D651,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>6단계</v>
       </c>
-      <c r="F651" s="11" t="s">
+      <c r="F651" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="652" spans="1:6">
       <c r="A652" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B652">
         <v>62</v>
       </c>
-      <c r="C652" s="11" t="s">
+      <c r="C652" s="1" t="s">
         <v>119</v>
       </c>
       <c r="D652">
@@ -14326,18 +14203,18 @@
         <f>IF($D652="","",VLOOKUP($D652,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>6단계</v>
       </c>
-      <c r="F652" s="11" t="s">
+      <c r="F652" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="653" spans="1:6">
       <c r="A653" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B653">
         <v>63</v>
       </c>
-      <c r="C653" s="11" t="s">
+      <c r="C653" s="1" t="s">
         <v>125</v>
       </c>
       <c r="D653">
@@ -14347,12 +14224,12 @@
         <f>IF($D653="","",VLOOKUP($D653,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>6단계</v>
       </c>
-      <c r="F653" s="11" t="s">
+      <c r="F653" s="1" t="s">
         <v>98</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -14365,7 +14242,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
@@ -14386,7 +14263,47 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D1D581-140A-4C7A-8DD4-E916C6A30ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A1E869B-3D96-41BE-8A8B-B51ACFFF7231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="기준표" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="144">
   <si>
     <t>하한점수</t>
   </si>
@@ -783,7 +783,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -836,14 +836,6 @@
       <charset val="129"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF999999"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="돋움"/>
       <family val="3"/>
@@ -885,7 +877,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -916,7 +908,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1295,7 +1286,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -14229,7 +14220,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -14263,7 +14254,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -14271,7 +14262,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -14287,23 +14278,15 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
+      <c r="A2" t="s">
         <v>110</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B2" t="s">
         <v>140</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03261387-8D67-41D9-BCE4-14E03106D9FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E41B5D5-CE4B-459A-B3E6-6F146DD5A11D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="140">
   <si>
     <t>하한점수</t>
   </si>
@@ -719,9 +719,6 @@
     <t>핑도노·훔치고·생각하는·편</t>
   </si>
   <si>
-    <t>해네도앤댈리는뒈</t>
-  </si>
-  <si>
     <t>뉴스나온그사람</t>
   </si>
   <si>
@@ -1563,7 +1560,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D17">
         <v>8351700</v>
@@ -2668,7 +2665,7 @@
         <v>21</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D82">
         <v>7931262</v>
@@ -3755,7 +3752,7 @@
         <v>20</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D146">
         <v>10606882</v>
@@ -4802,7 +4799,7 @@
         <v>12</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D205" s="6">
         <v>8226750</v>
@@ -6314,7 +6311,7 @@
         <v>16</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D277" s="6">
         <v>8594600</v>
@@ -7826,7 +7823,7 @@
         <v>21</v>
       </c>
       <c r="C349" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D349" s="2">
         <v>19328458</v>
@@ -9107,7 +9104,7 @@
         <v>15</v>
       </c>
       <c r="C410" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D410" s="2">
         <v>8350410</v>
@@ -10552,7 +10549,7 @@
         <v>16</v>
       </c>
       <c r="C479" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D479">
         <v>13933020</v>
@@ -11995,7 +11992,7 @@
         <v>22</v>
       </c>
       <c r="C548" s="1" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="D548">
         <v>8095292</v>
@@ -12058,7 +12055,7 @@
         <v>25</v>
       </c>
       <c r="C551" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D551">
         <v>7797750</v>
@@ -12121,7 +12118,7 @@
         <v>28</v>
       </c>
       <c r="C554" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D554">
         <v>7320600</v>
@@ -12268,7 +12265,7 @@
         <v>35</v>
       </c>
       <c r="C561" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D561">
         <v>6256712</v>
@@ -12871,7 +12868,7 @@
     </row>
     <row r="590" spans="1:6">
       <c r="A590" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B590" t="s">
         <v>93</v>
@@ -12889,7 +12886,7 @@
     </row>
     <row r="591" spans="1:6">
       <c r="A591" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B591">
         <v>1</v>
@@ -12910,7 +12907,7 @@
     </row>
     <row r="592" spans="1:6">
       <c r="A592" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B592">
         <v>2</v>
@@ -12931,7 +12928,7 @@
     </row>
     <row r="593" spans="1:6">
       <c r="A593" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B593">
         <v>3</v>
@@ -12952,7 +12949,7 @@
     </row>
     <row r="594" spans="1:6">
       <c r="A594" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B594">
         <v>4</v>
@@ -12973,7 +12970,7 @@
     </row>
     <row r="595" spans="1:6">
       <c r="A595" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B595">
         <v>5</v>
@@ -12994,7 +12991,7 @@
     </row>
     <row r="596" spans="1:6">
       <c r="A596" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B596">
         <v>6</v>
@@ -13015,7 +13012,7 @@
     </row>
     <row r="597" spans="1:6">
       <c r="A597" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B597">
         <v>7</v>
@@ -13036,13 +13033,13 @@
     </row>
     <row r="598" spans="1:6">
       <c r="A598" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B598">
         <v>8</v>
       </c>
       <c r="C598" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D598">
         <v>11921560</v>
@@ -13057,7 +13054,7 @@
     </row>
     <row r="599" spans="1:6">
       <c r="A599" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B599">
         <v>9</v>
@@ -13078,7 +13075,7 @@
     </row>
     <row r="600" spans="1:6">
       <c r="A600" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B600">
         <v>10</v>
@@ -13099,7 +13096,7 @@
     </row>
     <row r="601" spans="1:6">
       <c r="A601" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B601">
         <v>11</v>
@@ -13120,7 +13117,7 @@
     </row>
     <row r="602" spans="1:6">
       <c r="A602" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B602">
         <v>12</v>
@@ -13141,7 +13138,7 @@
     </row>
     <row r="603" spans="1:6">
       <c r="A603" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B603">
         <v>13</v>
@@ -13162,7 +13159,7 @@
     </row>
     <row r="604" spans="1:6">
       <c r="A604" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B604">
         <v>14</v>
@@ -13183,7 +13180,7 @@
     </row>
     <row r="605" spans="1:6">
       <c r="A605" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B605">
         <v>15</v>
@@ -13204,7 +13201,7 @@
     </row>
     <row r="606" spans="1:6">
       <c r="A606" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B606">
         <v>16</v>
@@ -13225,7 +13222,7 @@
     </row>
     <row r="607" spans="1:6">
       <c r="A607" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B607">
         <v>17</v>
@@ -13246,7 +13243,7 @@
     </row>
     <row r="608" spans="1:6">
       <c r="A608" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B608">
         <v>18</v>
@@ -13267,7 +13264,7 @@
     </row>
     <row r="609" spans="1:6">
       <c r="A609" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B609">
         <v>19</v>
@@ -13288,7 +13285,7 @@
     </row>
     <row r="610" spans="1:6">
       <c r="A610" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B610">
         <v>20</v>
@@ -13309,7 +13306,7 @@
     </row>
     <row r="611" spans="1:6">
       <c r="A611" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B611">
         <v>21</v>
@@ -13330,7 +13327,7 @@
     </row>
     <row r="612" spans="1:6">
       <c r="A612" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B612">
         <v>22</v>
@@ -13351,7 +13348,7 @@
     </row>
     <row r="613" spans="1:6">
       <c r="A613" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B613">
         <v>23</v>
@@ -13372,13 +13369,13 @@
     </row>
     <row r="614" spans="1:6">
       <c r="A614" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B614">
         <v>24</v>
       </c>
       <c r="C614" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D614">
         <v>7904200</v>
@@ -13393,7 +13390,7 @@
     </row>
     <row r="615" spans="1:6">
       <c r="A615" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B615">
         <v>25</v>
@@ -13414,13 +13411,13 @@
     </row>
     <row r="616" spans="1:6">
       <c r="A616" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B616">
         <v>26</v>
       </c>
       <c r="C616" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D616">
         <v>7670475</v>
@@ -13435,13 +13432,13 @@
     </row>
     <row r="617" spans="1:6">
       <c r="A617" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B617">
         <v>27</v>
       </c>
       <c r="C617" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D617">
         <v>7645700</v>
@@ -13456,7 +13453,7 @@
     </row>
     <row r="618" spans="1:6">
       <c r="A618" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B618">
         <v>28</v>
@@ -13477,7 +13474,7 @@
     </row>
     <row r="619" spans="1:6">
       <c r="A619" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B619">
         <v>29</v>
@@ -13498,7 +13495,7 @@
     </row>
     <row r="620" spans="1:6">
       <c r="A620" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B620">
         <v>30</v>
@@ -13519,7 +13516,7 @@
     </row>
     <row r="621" spans="1:6">
       <c r="A621" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B621">
         <v>31</v>
@@ -13540,7 +13537,7 @@
     </row>
     <row r="622" spans="1:6">
       <c r="A622" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B622">
         <v>32</v>
@@ -13561,13 +13558,13 @@
     </row>
     <row r="623" spans="1:6">
       <c r="A623" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B623">
         <v>33</v>
       </c>
       <c r="C623" s="1" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="D623">
         <v>6639073</v>
@@ -13582,7 +13579,7 @@
     </row>
     <row r="624" spans="1:6">
       <c r="A624" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B624">
         <v>34</v>
@@ -13603,7 +13600,7 @@
     </row>
     <row r="625" spans="1:6">
       <c r="A625" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B625">
         <v>35</v>
@@ -13624,7 +13621,7 @@
     </row>
     <row r="626" spans="1:6">
       <c r="A626" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B626">
         <v>36</v>
@@ -13645,7 +13642,7 @@
     </row>
     <row r="627" spans="1:6">
       <c r="A627" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B627">
         <v>37</v>
@@ -13666,7 +13663,7 @@
     </row>
     <row r="628" spans="1:6">
       <c r="A628" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B628">
         <v>38</v>
@@ -13687,7 +13684,7 @@
     </row>
     <row r="629" spans="1:6">
       <c r="A629" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B629">
         <v>39</v>
@@ -13708,7 +13705,7 @@
     </row>
     <row r="630" spans="1:6">
       <c r="A630" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B630">
         <v>40</v>
@@ -13729,13 +13726,13 @@
     </row>
     <row r="631" spans="1:6">
       <c r="A631" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B631">
         <v>41</v>
       </c>
       <c r="C631" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D631">
         <v>4703930</v>
@@ -13750,7 +13747,7 @@
     </row>
     <row r="632" spans="1:6">
       <c r="A632" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B632">
         <v>42</v>
@@ -13771,7 +13768,7 @@
     </row>
     <row r="633" spans="1:6">
       <c r="A633" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B633">
         <v>43</v>
@@ -13792,7 +13789,7 @@
     </row>
     <row r="634" spans="1:6">
       <c r="A634" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B634">
         <v>44</v>
@@ -13813,7 +13810,7 @@
     </row>
     <row r="635" spans="1:6">
       <c r="A635" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B635">
         <v>45</v>
@@ -13834,7 +13831,7 @@
     </row>
     <row r="636" spans="1:6">
       <c r="A636" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B636">
         <v>46</v>
@@ -13855,7 +13852,7 @@
     </row>
     <row r="637" spans="1:6">
       <c r="A637" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B637">
         <v>47</v>
@@ -13876,7 +13873,7 @@
     </row>
     <row r="638" spans="1:6">
       <c r="A638" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B638">
         <v>48</v>
@@ -13897,7 +13894,7 @@
     </row>
     <row r="639" spans="1:6">
       <c r="A639" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B639">
         <v>49</v>
@@ -13918,7 +13915,7 @@
     </row>
     <row r="640" spans="1:6">
       <c r="A640" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B640">
         <v>50</v>
@@ -13939,7 +13936,7 @@
     </row>
     <row r="641" spans="1:6">
       <c r="A641" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B641">
         <v>51</v>
@@ -13960,7 +13957,7 @@
     </row>
     <row r="642" spans="1:6">
       <c r="A642" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B642">
         <v>52</v>
@@ -13981,7 +13978,7 @@
     </row>
     <row r="643" spans="1:6">
       <c r="A643" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B643">
         <v>53</v>
@@ -14002,7 +13999,7 @@
     </row>
     <row r="644" spans="1:6">
       <c r="A644" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B644">
         <v>54</v>
@@ -14023,7 +14020,7 @@
     </row>
     <row r="645" spans="1:6">
       <c r="A645" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B645">
         <v>55</v>
@@ -14044,7 +14041,7 @@
     </row>
     <row r="646" spans="1:6">
       <c r="A646" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B646">
         <v>56</v>
@@ -14065,7 +14062,7 @@
     </row>
     <row r="647" spans="1:6">
       <c r="A647" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B647">
         <v>57</v>
@@ -14086,7 +14083,7 @@
     </row>
     <row r="648" spans="1:6">
       <c r="A648" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B648">
         <v>58</v>
@@ -14107,7 +14104,7 @@
     </row>
     <row r="649" spans="1:6">
       <c r="A649" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B649">
         <v>59</v>
@@ -14128,7 +14125,7 @@
     </row>
     <row r="650" spans="1:6">
       <c r="A650" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B650">
         <v>60</v>
@@ -14149,7 +14146,7 @@
     </row>
     <row r="651" spans="1:6">
       <c r="A651" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B651">
         <v>61</v>
@@ -14170,7 +14167,7 @@
     </row>
     <row r="652" spans="1:6">
       <c r="A652" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B652">
         <v>62</v>
@@ -14191,7 +14188,7 @@
     </row>
     <row r="653" spans="1:6">
       <c r="A653" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B653">
         <v>63</v>
@@ -14224,7 +14221,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
@@ -14262,10 +14259,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>139</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -14273,7 +14270,7 @@
         <v>108</v>
       </c>
       <c r="B2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -14281,7 +14278,7 @@
         <v>120</v>
       </c>
       <c r="B3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{343D3ADF-29AB-4C4A-8CBB-22C56493B4CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC3857D-9186-47C7-A6B7-82D70489607E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="기준표" sheetId="1" r:id="rId1"/>
@@ -853,9 +853,6 @@
     </r>
   </si>
   <si>
-    <t>해네도앤댈리는뒈</t>
-  </si>
-  <si>
     <t>나는매일건조된새우를잘씹어먹는다</t>
   </si>
   <si>
@@ -935,6 +932,10 @@
   </si>
   <si>
     <t>나는매일건조된새우를잘씹어먹는다</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>햬녜도얜덀리는뒈</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1039,7 +1040,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1071,9 +1072,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -13742,7 +13740,7 @@
         <v>33</v>
       </c>
       <c r="C623" s="1" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="D623">
         <v>6639073</v>
@@ -13910,7 +13908,7 @@
         <v>41</v>
       </c>
       <c r="C631" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D631">
         <v>4703930</v>
@@ -15044,7 +15042,7 @@
         <v>32</v>
       </c>
       <c r="C685" s="11" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="D685">
         <v>11246183</v>
@@ -15086,7 +15084,7 @@
         <v>34</v>
       </c>
       <c r="C687" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D687">
         <v>10428030</v>
@@ -15464,7 +15462,7 @@
         <v>52</v>
       </c>
       <c r="C705" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D705">
         <v>3713857</v>
@@ -15527,7 +15525,7 @@
         <v>55</v>
       </c>
       <c r="C708" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D708">
         <v>2952070</v>
@@ -15568,7 +15566,7 @@
       <c r="B710">
         <v>57</v>
       </c>
-      <c r="C710" s="13">
+      <c r="C710" s="8">
         <v>1090</v>
       </c>
       <c r="D710">
@@ -15680,7 +15678,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
@@ -15718,10 +15716,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>144</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -15745,7 +15743,7 @@
         <v>129</v>
       </c>
       <c r="B4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C328AAF8-E360-4FD6-9CC2-F2AC889895E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7B83C6-5851-4E70-AEBC-46A9B090D9C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="기준표" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2364" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2368" uniqueCount="140">
   <si>
     <t>📦 월별 보관 — 2026-06  (날짜별 길드전 랭킹 누적)</t>
   </si>
@@ -451,6 +451,13 @@
   <si>
     <t>현재닉네임</t>
   </si>
+  <si>
+    <t>노른</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>이중주차 사이드채결후 연락두절</t>
+  </si>
 </sst>
 </file>
 
@@ -548,7 +555,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -580,9 +587,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -16085,7 +16089,7 @@
       <c r="B758">
         <v>44</v>
       </c>
-      <c r="C758" s="13">
+      <c r="C758" s="8">
         <v>1090</v>
       </c>
       <c r="D758">
@@ -16541,7 +16545,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -16580,6 +16584,22 @@
         <v>118</v>
       </c>
     </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>139</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7B83C6-5851-4E70-AEBC-46A9B090D9C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B05E2D-8880-4EFE-A45C-21A09D4F1B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2368" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2368" uniqueCount="139">
   <si>
     <t>📦 월별 보관 — 2026-06  (날짜별 길드전 랭킹 누적)</t>
   </si>
@@ -401,9 +401,6 @@
     <t>노른</t>
   </si>
   <si>
-    <t>이중주차 사이드채운후 연락두절</t>
-  </si>
-  <si>
     <t>하한점수</t>
   </si>
   <si>
@@ -456,7 +453,8 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>이중주차 사이드채결후 연락두절</t>
+    <t>이중주차 사이드채운후 연락두절</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -856,13 +854,13 @@
   <sheetData>
     <row r="3" spans="2:4" ht="16.5" customHeight="1">
       <c r="B3" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="16.5" customHeight="1">
@@ -870,10 +868,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" t="s">
         <v>124</v>
-      </c>
-      <c r="D4" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="16.5" customHeight="1">
@@ -884,7 +882,7 @@
         <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="16.5" customHeight="1">
@@ -895,7 +893,7 @@
         <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="16.5" customHeight="1">
@@ -903,10 +901,10 @@
         <v>550001</v>
       </c>
       <c r="C7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D7" t="s">
         <v>128</v>
-      </c>
-      <c r="D7" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="16.5" customHeight="1">
@@ -917,7 +915,7 @@
         <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="16.5" customHeight="1">
@@ -928,7 +926,7 @@
         <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="16.5" customHeight="1">
@@ -939,7 +937,7 @@
         <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="16.5" customHeight="1">
@@ -950,7 +948,7 @@
         <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="16.5" customHeight="1">
@@ -961,7 +959,7 @@
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -15796,7 +15794,7 @@
         <v>30</v>
       </c>
       <c r="C744" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="D744">
         <v>7240847</v>
@@ -16516,7 +16514,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
@@ -16554,10 +16552,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>136</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -16589,7 +16587,7 @@
         <v>102</v>
       </c>
       <c r="B5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -16597,7 +16595,7 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC6B509E-02C1-4ADD-A4E6-5E5CA94752CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D165DEB-7F65-48EA-9973-73CC1ADED471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="기준표" sheetId="1" r:id="rId1"/>
@@ -773,9 +773,6 @@
     <t>2026-06-29</t>
   </si>
   <si>
-    <t>해녜도얜댈리는뒈</t>
-  </si>
-  <si>
     <t>📦 월별 보관 — 2026-07  (날짜별 길드전 랭킹 누적)</t>
   </si>
   <si>
@@ -786,6 +783,10 @@
   </si>
   <si>
     <t xml:space="preserve">[ 주택보증 ] 헌집줄게 새집줘봐 </t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>햬녜도얜덀리는뒈</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -17684,7 +17685,7 @@
         <v>41</v>
       </c>
       <c r="C818" s="1" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="D818">
         <v>2991801</v>
@@ -18167,7 +18168,7 @@
         <v>95</v>
       </c>
       <c r="C841" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E841" s="3" t="str">
         <f>IF($D841="","",VLOOKUP($D841,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -18920,7 +18921,7 @@
         <v>36</v>
       </c>
       <c r="C877" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D877">
         <v>3796510</v>
@@ -19430,7 +19431,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
@@ -19468,10 +19469,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="16.5" customHeight="1">
       <c r="A1" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>145</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="16.5" customHeight="1">

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A8BC74-A0CD-421E-A42F-E9F8FDD1FA53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1129934A-E960-4DB1-81D6-0A29E3DF6106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="기준표" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2680" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2740" uniqueCount="154">
   <si>
     <t>하한점수</t>
   </si>
@@ -18350,6 +18350,9 @@
         <f>IF($D842="","",VLOOKUP($D842,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
+      <c r="F842" s="1" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="843" spans="1:6">
       <c r="A843" t="s">
@@ -18368,6 +18371,9 @@
         <f>IF($D843="","",VLOOKUP($D843,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
+      <c r="F843" s="1" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="844" spans="1:6">
       <c r="A844" t="s">
@@ -18386,6 +18392,9 @@
         <f>IF($D844="","",VLOOKUP($D844,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
+      <c r="F844" s="1" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="845" spans="1:6">
       <c r="A845" t="s">
@@ -18404,6 +18413,9 @@
         <f>IF($D845="","",VLOOKUP($D845,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
+      <c r="F845" s="1" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="846" spans="1:6">
       <c r="A846" t="s">
@@ -18422,6 +18434,9 @@
         <f>IF($D846="","",VLOOKUP($D846,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
+      <c r="F846" s="1" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="847" spans="1:6">
       <c r="A847" t="s">
@@ -18440,6 +18455,9 @@
         <f>IF($D847="","",VLOOKUP($D847,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
+      <c r="F847" s="1" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="848" spans="1:6">
       <c r="A848" t="s">
@@ -18458,8 +18476,11 @@
         <f>IF($D848="","",VLOOKUP($D848,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="849" spans="1:5">
+      <c r="F848" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="849" spans="1:6">
       <c r="A849" t="s">
         <v>142</v>
       </c>
@@ -18476,8 +18497,11 @@
         <f>IF($D849="","",VLOOKUP($D849,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="850" spans="1:5">
+      <c r="F849" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="850" spans="1:6">
       <c r="A850" t="s">
         <v>142</v>
       </c>
@@ -18494,8 +18518,11 @@
         <f>IF($D850="","",VLOOKUP($D850,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="851" spans="1:5">
+      <c r="F850" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="851" spans="1:6">
       <c r="A851" t="s">
         <v>142</v>
       </c>
@@ -18512,8 +18539,11 @@
         <f>IF($D851="","",VLOOKUP($D851,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="852" spans="1:5">
+      <c r="F851" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="852" spans="1:6">
       <c r="A852" t="s">
         <v>142</v>
       </c>
@@ -18530,8 +18560,11 @@
         <f>IF($D852="","",VLOOKUP($D852,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="853" spans="1:5">
+      <c r="F852" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="853" spans="1:6">
       <c r="A853" t="s">
         <v>142</v>
       </c>
@@ -18548,8 +18581,11 @@
         <f>IF($D853="","",VLOOKUP($D853,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="854" spans="1:5">
+      <c r="F853" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="854" spans="1:6">
       <c r="A854" t="s">
         <v>142</v>
       </c>
@@ -18566,8 +18602,11 @@
         <f>IF($D854="","",VLOOKUP($D854,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="855" spans="1:5">
+      <c r="F854" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="855" spans="1:6">
       <c r="A855" t="s">
         <v>142</v>
       </c>
@@ -18584,8 +18623,11 @@
         <f>IF($D855="","",VLOOKUP($D855,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="856" spans="1:5">
+      <c r="F855" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="856" spans="1:6">
       <c r="A856" t="s">
         <v>142</v>
       </c>
@@ -18602,8 +18644,11 @@
         <f>IF($D856="","",VLOOKUP($D856,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="857" spans="1:5">
+      <c r="F856" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="857" spans="1:6">
       <c r="A857" t="s">
         <v>142</v>
       </c>
@@ -18620,8 +18665,11 @@
         <f>IF($D857="","",VLOOKUP($D857,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="858" spans="1:5">
+      <c r="F857" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="858" spans="1:6">
       <c r="A858" t="s">
         <v>142</v>
       </c>
@@ -18638,8 +18686,11 @@
         <f>IF($D858="","",VLOOKUP($D858,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="859" spans="1:5">
+      <c r="F858" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="859" spans="1:6">
       <c r="A859" t="s">
         <v>142</v>
       </c>
@@ -18656,8 +18707,11 @@
         <f>IF($D859="","",VLOOKUP($D859,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="860" spans="1:5">
+      <c r="F859" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="860" spans="1:6">
       <c r="A860" t="s">
         <v>142</v>
       </c>
@@ -18674,8 +18728,11 @@
         <f>IF($D860="","",VLOOKUP($D860,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="861" spans="1:5">
+      <c r="F860" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="861" spans="1:6">
       <c r="A861" t="s">
         <v>142</v>
       </c>
@@ -18692,8 +18749,11 @@
         <f>IF($D861="","",VLOOKUP($D861,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="862" spans="1:5">
+      <c r="F861" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="862" spans="1:6">
       <c r="A862" t="s">
         <v>142</v>
       </c>
@@ -18710,8 +18770,11 @@
         <f>IF($D862="","",VLOOKUP($D862,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="863" spans="1:5">
+      <c r="F862" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="863" spans="1:6">
       <c r="A863" t="s">
         <v>142</v>
       </c>
@@ -18728,8 +18791,11 @@
         <f>IF($D863="","",VLOOKUP($D863,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="864" spans="1:5">
+      <c r="F863" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="864" spans="1:6">
       <c r="A864" t="s">
         <v>142</v>
       </c>
@@ -18746,8 +18812,11 @@
         <f>IF($D864="","",VLOOKUP($D864,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="865" spans="1:5">
+      <c r="F864" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="865" spans="1:6">
       <c r="A865" t="s">
         <v>142</v>
       </c>
@@ -18764,8 +18833,11 @@
         <f>IF($D865="","",VLOOKUP($D865,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="866" spans="1:5">
+      <c r="F865" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="866" spans="1:6">
       <c r="A866" t="s">
         <v>142</v>
       </c>
@@ -18782,8 +18854,11 @@
         <f>IF($D866="","",VLOOKUP($D866,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="867" spans="1:5">
+      <c r="F866" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="867" spans="1:6">
       <c r="A867" t="s">
         <v>142</v>
       </c>
@@ -18800,8 +18875,11 @@
         <f>IF($D867="","",VLOOKUP($D867,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="868" spans="1:5">
+      <c r="F867" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="868" spans="1:6">
       <c r="A868" t="s">
         <v>142</v>
       </c>
@@ -18818,8 +18896,11 @@
         <f>IF($D868="","",VLOOKUP($D868,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="869" spans="1:5">
+      <c r="F868" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="869" spans="1:6">
       <c r="A869" t="s">
         <v>142</v>
       </c>
@@ -18836,8 +18917,11 @@
         <f>IF($D869="","",VLOOKUP($D869,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="870" spans="1:5">
+      <c r="F869" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="870" spans="1:6">
       <c r="A870" t="s">
         <v>142</v>
       </c>
@@ -18854,8 +18938,11 @@
         <f>IF($D870="","",VLOOKUP($D870,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="871" spans="1:5">
+      <c r="F870" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="871" spans="1:6">
       <c r="A871" t="s">
         <v>142</v>
       </c>
@@ -18872,8 +18959,11 @@
         <f>IF($D871="","",VLOOKUP($D871,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="872" spans="1:5">
+      <c r="F871" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="872" spans="1:6">
       <c r="A872" t="s">
         <v>142</v>
       </c>
@@ -18890,8 +18980,11 @@
         <f>IF($D872="","",VLOOKUP($D872,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="873" spans="1:5">
+      <c r="F872" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="873" spans="1:6">
       <c r="A873" t="s">
         <v>142</v>
       </c>
@@ -18908,8 +19001,11 @@
         <f>IF($D873="","",VLOOKUP($D873,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="874" spans="1:5">
+      <c r="F873" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="874" spans="1:6">
       <c r="A874" t="s">
         <v>142</v>
       </c>
@@ -18926,8 +19022,11 @@
         <f>IF($D874="","",VLOOKUP($D874,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="875" spans="1:5">
+      <c r="F874" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="875" spans="1:6">
       <c r="A875" t="s">
         <v>142</v>
       </c>
@@ -18944,8 +19043,11 @@
         <f>IF($D875="","",VLOOKUP($D875,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="876" spans="1:5">
+      <c r="F875" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="876" spans="1:6">
       <c r="A876" t="s">
         <v>142</v>
       </c>
@@ -18962,8 +19064,11 @@
         <f>IF($D876="","",VLOOKUP($D876,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="877" spans="1:5">
+      <c r="F876" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="877" spans="1:6">
       <c r="A877" t="s">
         <v>142</v>
       </c>
@@ -18980,8 +19085,11 @@
         <f>IF($D877="","",VLOOKUP($D877,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="878" spans="1:5">
+      <c r="F877" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="878" spans="1:6">
       <c r="A878" t="s">
         <v>142</v>
       </c>
@@ -18998,8 +19106,11 @@
         <f>IF($D878="","",VLOOKUP($D878,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="879" spans="1:5">
+      <c r="F878" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="879" spans="1:6">
       <c r="A879" t="s">
         <v>142</v>
       </c>
@@ -19016,8 +19127,11 @@
         <f>IF($D879="","",VLOOKUP($D879,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="880" spans="1:5">
+      <c r="F879" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="880" spans="1:6">
       <c r="A880" t="s">
         <v>142</v>
       </c>
@@ -19034,8 +19148,11 @@
         <f>IF($D880="","",VLOOKUP($D880,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="881" spans="1:5">
+      <c r="F880" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="881" spans="1:6">
       <c r="A881" t="s">
         <v>142</v>
       </c>
@@ -19052,8 +19169,11 @@
         <f>IF($D881="","",VLOOKUP($D881,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="882" spans="1:5">
+      <c r="F881" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="882" spans="1:6">
       <c r="A882" t="s">
         <v>142</v>
       </c>
@@ -19070,8 +19190,11 @@
         <f>IF($D882="","",VLOOKUP($D882,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>9단계</v>
       </c>
-    </row>
-    <row r="883" spans="1:5">
+      <c r="F882" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="883" spans="1:6">
       <c r="A883" t="s">
         <v>142</v>
       </c>
@@ -19088,8 +19211,11 @@
         <f>IF($D883="","",VLOOKUP($D883,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-    </row>
-    <row r="884" spans="1:5">
+      <c r="F883" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="884" spans="1:6">
       <c r="A884" t="s">
         <v>142</v>
       </c>
@@ -19106,8 +19232,11 @@
         <f>IF($D884="","",VLOOKUP($D884,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-    </row>
-    <row r="885" spans="1:5">
+      <c r="F884" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="885" spans="1:6">
       <c r="A885" t="s">
         <v>142</v>
       </c>
@@ -19124,8 +19253,11 @@
         <f>IF($D885="","",VLOOKUP($D885,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-    </row>
-    <row r="886" spans="1:5">
+      <c r="F885" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="886" spans="1:6">
       <c r="A886" t="s">
         <v>142</v>
       </c>
@@ -19142,8 +19274,11 @@
         <f>IF($D886="","",VLOOKUP($D886,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-    </row>
-    <row r="887" spans="1:5">
+      <c r="F886" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="887" spans="1:6">
       <c r="A887" t="s">
         <v>142</v>
       </c>
@@ -19160,8 +19295,11 @@
         <f>IF($D887="","",VLOOKUP($D887,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-    </row>
-    <row r="888" spans="1:5">
+      <c r="F887" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="888" spans="1:6">
       <c r="A888" t="s">
         <v>142</v>
       </c>
@@ -19178,8 +19316,11 @@
         <f>IF($D888="","",VLOOKUP($D888,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-    </row>
-    <row r="889" spans="1:5">
+      <c r="F888" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="889" spans="1:6">
       <c r="A889" t="s">
         <v>142</v>
       </c>
@@ -19196,8 +19337,11 @@
         <f>IF($D889="","",VLOOKUP($D889,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-    </row>
-    <row r="890" spans="1:5">
+      <c r="F889" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="890" spans="1:6">
       <c r="A890" t="s">
         <v>142</v>
       </c>
@@ -19214,8 +19358,11 @@
         <f>IF($D890="","",VLOOKUP($D890,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-    </row>
-    <row r="891" spans="1:5">
+      <c r="F890" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="891" spans="1:6">
       <c r="A891" t="s">
         <v>142</v>
       </c>
@@ -19232,8 +19379,11 @@
         <f>IF($D891="","",VLOOKUP($D891,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-    </row>
-    <row r="892" spans="1:5">
+      <c r="F891" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="892" spans="1:6">
       <c r="A892" t="s">
         <v>142</v>
       </c>
@@ -19250,8 +19400,11 @@
         <f>IF($D892="","",VLOOKUP($D892,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-    </row>
-    <row r="893" spans="1:5">
+      <c r="F892" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="893" spans="1:6">
       <c r="A893" t="s">
         <v>142</v>
       </c>
@@ -19268,8 +19421,11 @@
         <f>IF($D893="","",VLOOKUP($D893,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-    </row>
-    <row r="894" spans="1:5">
+      <c r="F893" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="894" spans="1:6">
       <c r="A894" t="s">
         <v>142</v>
       </c>
@@ -19286,8 +19442,11 @@
         <f>IF($D894="","",VLOOKUP($D894,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>8단계</v>
       </c>
-    </row>
-    <row r="895" spans="1:5">
+      <c r="F894" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="895" spans="1:6">
       <c r="A895" t="s">
         <v>142</v>
       </c>
@@ -19304,8 +19463,11 @@
         <f>IF($D895="","",VLOOKUP($D895,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>7단계</v>
       </c>
-    </row>
-    <row r="896" spans="1:5">
+      <c r="F895" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="896" spans="1:6">
       <c r="A896" t="s">
         <v>142</v>
       </c>
@@ -19322,8 +19484,11 @@
         <f>IF($D896="","",VLOOKUP($D896,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>6단계</v>
       </c>
-    </row>
-    <row r="897" spans="1:5">
+      <c r="F896" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="897" spans="1:6">
       <c r="A897" t="s">
         <v>142</v>
       </c>
@@ -19340,8 +19505,11 @@
         <f>IF($D897="","",VLOOKUP($D897,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>6단계</v>
       </c>
-    </row>
-    <row r="898" spans="1:5">
+      <c r="F897" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="898" spans="1:6">
       <c r="A898" t="s">
         <v>142</v>
       </c>
@@ -19358,8 +19526,11 @@
         <f>IF($D898="","",VLOOKUP($D898,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>6단계</v>
       </c>
-    </row>
-    <row r="899" spans="1:5">
+      <c r="F898" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="899" spans="1:6">
       <c r="A899" t="s">
         <v>142</v>
       </c>
@@ -19376,8 +19547,11 @@
         <f>IF($D899="","",VLOOKUP($D899,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>6단계</v>
       </c>
-    </row>
-    <row r="900" spans="1:5">
+      <c r="F899" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="900" spans="1:6">
       <c r="A900" t="s">
         <v>142</v>
       </c>
@@ -19394,8 +19568,11 @@
         <f>IF($D900="","",VLOOKUP($D900,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>6단계</v>
       </c>
-    </row>
-    <row r="901" spans="1:5">
+      <c r="F900" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="901" spans="1:6">
       <c r="A901" t="s">
         <v>142</v>
       </c>
@@ -19411,6 +19588,9 @@
       <c r="E901" t="str">
         <f>IF($D901="","",VLOOKUP($D901,기준표!$B$4:$C$12,2,TRUE()))</f>
         <v>6단계</v>
+      </c>
+      <c r="F901" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1129934A-E960-4DB1-81D6-0A29E3DF6106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F84DBCF-0BEE-4840-A157-88BE93E7DA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2740" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2740" uniqueCount="151">
   <si>
     <t>하한점수</t>
   </si>
@@ -773,15 +773,6 @@
     <t>2026-06-29</t>
   </si>
   <si>
-    <t>영화관에서결말스포한난</t>
-  </si>
-  <si>
-    <t>해녜도앤댈리는뒈</t>
-  </si>
-  <si>
-    <t>훔쳐뿃노</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -18175,7 +18166,7 @@
       <c r="B834">
         <v>57</v>
       </c>
-      <c r="C834">
+      <c r="C834" s="8">
         <v>1090</v>
       </c>
       <c r="D834">
@@ -18323,7 +18314,7 @@
         <v>95</v>
       </c>
       <c r="C841" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E841" s="3" t="str">
         <f>IF($D841="","",VLOOKUP($D841,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -18424,8 +18415,8 @@
       <c r="B846">
         <v>5</v>
       </c>
-      <c r="C846" s="11" t="s">
-        <v>143</v>
+      <c r="C846" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="D846">
         <v>15982694</v>
@@ -19096,8 +19087,8 @@
       <c r="B878">
         <v>37</v>
       </c>
-      <c r="C878" s="11" t="s">
-        <v>144</v>
+      <c r="C878" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="D878">
         <v>7305386</v>
@@ -19117,8 +19108,8 @@
       <c r="B879">
         <v>38</v>
       </c>
-      <c r="C879" s="11" t="s">
-        <v>145</v>
+      <c r="C879" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="D879">
         <v>7280144</v>
@@ -19181,7 +19172,7 @@
         <v>41</v>
       </c>
       <c r="C882" s="11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D882">
         <v>7218767</v>
@@ -19244,7 +19235,7 @@
         <v>44</v>
       </c>
       <c r="C885" s="11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D885">
         <v>5094316</v>
@@ -19328,7 +19319,7 @@
         <v>48</v>
       </c>
       <c r="C889" s="11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D889">
         <v>4176635</v>
@@ -19412,7 +19403,7 @@
         <v>52</v>
       </c>
       <c r="C893" s="11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D893">
         <v>3102924</v>
@@ -19607,7 +19598,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
@@ -19645,10 +19636,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="16.5" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="16.5" customHeight="1">

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F84DBCF-0BEE-4840-A157-88BE93E7DA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B0DB279-7DF8-42FB-8FD7-AFB1424C9612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="기준표" sheetId="1" r:id="rId1"/>
@@ -18,19 +18,8 @@
     <sheet name="2026-07" sheetId="3" r:id="rId3"/>
     <sheet name="별칭" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -39,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2740" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="152">
   <si>
     <t>하한점수</t>
   </si>
@@ -777,10 +766,20 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t>핑도노</t>
+      <t xml:space="preserve">주택보증 </t>
     </r>
     <r>
       <rPr>
@@ -790,7 +789,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t>·</t>
+      <t xml:space="preserve">] </t>
     </r>
     <r>
       <rPr>
@@ -799,127 +798,23 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t>훔치고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>생각하는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>편</t>
+      <t>헌집줄게 새집줘봐</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>티거</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>Ya</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>드랍더튀어</t>
-    </r>
+    <t>2026-06-30</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>독터키캔씨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>Turkey1881</t>
-    </r>
+    <t>뒤뚱뒤뚱펭귄</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>자르반</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>84</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>세</t>
-    </r>
+    <t>w0w</t>
+  </si>
+  <si>
+    <t>당근없는중간매운맛의묽지않은카레</t>
+  </si>
+  <si>
+    <t>세계최고미녀</t>
   </si>
   <si>
     <t>📦 월별 보관 — 2026-07  (날짜별 길드전 랭킹 누적)</t>
@@ -929,10 +824,6 @@
   </si>
   <si>
     <t>현재닉네임</t>
-  </si>
-  <si>
-    <t>[ 주택보증 ] 헌집줄게 새집줘봐</t>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1036,7 +927,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1066,7 +957,6 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1454,7 +1344,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F901"/>
+  <dimension ref="A1:F959"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="14.875" customWidth="1"/>
@@ -18314,7 +18204,7 @@
         <v>95</v>
       </c>
       <c r="C841" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E841" s="3" t="str">
         <f>IF($D841="","",VLOOKUP($D841,기준표!$B$4:$C$12,2,TRUE()))</f>
@@ -18352,7 +18242,7 @@
       <c r="B843">
         <v>2</v>
       </c>
-      <c r="C843" s="11" t="s">
+      <c r="C843" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D843">
@@ -18373,7 +18263,7 @@
       <c r="B844">
         <v>3</v>
       </c>
-      <c r="C844" s="11" t="s">
+      <c r="C844" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D844">
@@ -18394,7 +18284,7 @@
       <c r="B845">
         <v>4</v>
       </c>
-      <c r="C845" s="11" t="s">
+      <c r="C845" s="1" t="s">
         <v>105</v>
       </c>
       <c r="D845">
@@ -18436,7 +18326,7 @@
       <c r="B847">
         <v>6</v>
       </c>
-      <c r="C847" s="11" t="s">
+      <c r="C847" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D847">
@@ -18457,7 +18347,7 @@
       <c r="B848">
         <v>7</v>
       </c>
-      <c r="C848" s="11" t="s">
+      <c r="C848" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D848">
@@ -18478,7 +18368,7 @@
       <c r="B849">
         <v>8</v>
       </c>
-      <c r="C849" s="11" t="s">
+      <c r="C849" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D849">
@@ -18520,7 +18410,7 @@
       <c r="B851">
         <v>10</v>
       </c>
-      <c r="C851" s="11" t="s">
+      <c r="C851" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D851">
@@ -18541,7 +18431,7 @@
       <c r="B852">
         <v>11</v>
       </c>
-      <c r="C852" s="11" t="s">
+      <c r="C852" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D852">
@@ -18562,7 +18452,7 @@
       <c r="B853">
         <v>12</v>
       </c>
-      <c r="C853" s="11" t="s">
+      <c r="C853" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D853">
@@ -18583,7 +18473,7 @@
       <c r="B854">
         <v>13</v>
       </c>
-      <c r="C854" s="11" t="s">
+      <c r="C854" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D854">
@@ -18604,7 +18494,7 @@
       <c r="B855">
         <v>14</v>
       </c>
-      <c r="C855" s="11" t="s">
+      <c r="C855" s="1" t="s">
         <v>61</v>
       </c>
       <c r="D855">
@@ -18625,7 +18515,7 @@
       <c r="B856">
         <v>15</v>
       </c>
-      <c r="C856" s="11" t="s">
+      <c r="C856" s="1" t="s">
         <v>102</v>
       </c>
       <c r="D856">
@@ -18646,7 +18536,7 @@
       <c r="B857">
         <v>16</v>
       </c>
-      <c r="C857" s="11" t="s">
+      <c r="C857" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D857">
@@ -18667,7 +18557,7 @@
       <c r="B858">
         <v>17</v>
       </c>
-      <c r="C858" s="11" t="s">
+      <c r="C858" s="1" t="s">
         <v>109</v>
       </c>
       <c r="D858">
@@ -18688,7 +18578,7 @@
       <c r="B859">
         <v>18</v>
       </c>
-      <c r="C859" s="11" t="s">
+      <c r="C859" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D859">
@@ -18709,7 +18599,7 @@
       <c r="B860">
         <v>19</v>
       </c>
-      <c r="C860" s="11" t="s">
+      <c r="C860" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D860">
@@ -18730,7 +18620,7 @@
       <c r="B861">
         <v>20</v>
       </c>
-      <c r="C861" s="11" t="s">
+      <c r="C861" s="1" t="s">
         <v>134</v>
       </c>
       <c r="D861">
@@ -18751,7 +18641,7 @@
       <c r="B862">
         <v>21</v>
       </c>
-      <c r="C862" s="11" t="s">
+      <c r="C862" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D862">
@@ -18772,7 +18662,7 @@
       <c r="B863">
         <v>22</v>
       </c>
-      <c r="C863" s="11" t="s">
+      <c r="C863" s="1" t="s">
         <v>56</v>
       </c>
       <c r="D863">
@@ -18793,7 +18683,7 @@
       <c r="B864">
         <v>23</v>
       </c>
-      <c r="C864" s="11" t="s">
+      <c r="C864" s="1" t="s">
         <v>101</v>
       </c>
       <c r="D864">
@@ -18814,7 +18704,7 @@
       <c r="B865">
         <v>24</v>
       </c>
-      <c r="C865" s="11" t="s">
+      <c r="C865" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D865">
@@ -18835,7 +18725,7 @@
       <c r="B866">
         <v>25</v>
       </c>
-      <c r="C866" s="11" t="s">
+      <c r="C866" s="1" t="s">
         <v>73</v>
       </c>
       <c r="D866">
@@ -18856,7 +18746,7 @@
       <c r="B867">
         <v>26</v>
       </c>
-      <c r="C867" s="11" t="s">
+      <c r="C867" s="1" t="s">
         <v>65</v>
       </c>
       <c r="D867">
@@ -18877,7 +18767,7 @@
       <c r="B868">
         <v>27</v>
       </c>
-      <c r="C868" s="11" t="s">
+      <c r="C868" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D868">
@@ -18898,7 +18788,7 @@
       <c r="B869">
         <v>28</v>
       </c>
-      <c r="C869" s="11" t="s">
+      <c r="C869" s="1" t="s">
         <v>59</v>
       </c>
       <c r="D869">
@@ -18919,7 +18809,7 @@
       <c r="B870">
         <v>29</v>
       </c>
-      <c r="C870" s="11" t="s">
+      <c r="C870" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D870">
@@ -18940,7 +18830,7 @@
       <c r="B871">
         <v>30</v>
       </c>
-      <c r="C871" s="11" t="s">
+      <c r="C871" s="1" t="s">
         <v>108</v>
       </c>
       <c r="D871">
@@ -18961,7 +18851,7 @@
       <c r="B872">
         <v>31</v>
       </c>
-      <c r="C872" s="11" t="s">
+      <c r="C872" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D872">
@@ -18982,7 +18872,7 @@
       <c r="B873">
         <v>32</v>
       </c>
-      <c r="C873" s="11" t="s">
+      <c r="C873" s="1" t="s">
         <v>140</v>
       </c>
       <c r="D873">
@@ -19003,7 +18893,7 @@
       <c r="B874">
         <v>33</v>
       </c>
-      <c r="C874" s="11" t="s">
+      <c r="C874" s="1" t="s">
         <v>137</v>
       </c>
       <c r="D874">
@@ -19024,7 +18914,7 @@
       <c r="B875">
         <v>34</v>
       </c>
-      <c r="C875" s="11" t="s">
+      <c r="C875" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D875">
@@ -19045,7 +18935,7 @@
       <c r="B876">
         <v>35</v>
       </c>
-      <c r="C876" s="11" t="s">
+      <c r="C876" s="1" t="s">
         <v>135</v>
       </c>
       <c r="D876">
@@ -19066,7 +18956,7 @@
       <c r="B877">
         <v>36</v>
       </c>
-      <c r="C877" s="11" t="s">
+      <c r="C877" s="1" t="s">
         <v>139</v>
       </c>
       <c r="D877">
@@ -19129,7 +19019,7 @@
       <c r="B880">
         <v>39</v>
       </c>
-      <c r="C880" s="11" t="s">
+      <c r="C880" s="1" t="s">
         <v>60</v>
       </c>
       <c r="D880">
@@ -19150,7 +19040,7 @@
       <c r="B881">
         <v>40</v>
       </c>
-      <c r="C881" s="11" t="s">
+      <c r="C881" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D881">
@@ -19171,8 +19061,8 @@
       <c r="B882">
         <v>41</v>
       </c>
-      <c r="C882" s="11" t="s">
-        <v>143</v>
+      <c r="C882" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="D882">
         <v>7218767</v>
@@ -19192,7 +19082,7 @@
       <c r="B883">
         <v>42</v>
       </c>
-      <c r="C883" s="11" t="s">
+      <c r="C883" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D883">
@@ -19213,7 +19103,7 @@
       <c r="B884">
         <v>43</v>
       </c>
-      <c r="C884" s="11" t="s">
+      <c r="C884" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D884">
@@ -19234,8 +19124,8 @@
       <c r="B885">
         <v>44</v>
       </c>
-      <c r="C885" s="11" t="s">
-        <v>144</v>
+      <c r="C885" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="D885">
         <v>5094316</v>
@@ -19255,7 +19145,7 @@
       <c r="B886">
         <v>45</v>
       </c>
-      <c r="C886" s="11" t="s">
+      <c r="C886" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D886">
@@ -19276,7 +19166,7 @@
       <c r="B887">
         <v>46</v>
       </c>
-      <c r="C887" s="11" t="s">
+      <c r="C887" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D887">
@@ -19297,7 +19187,7 @@
       <c r="B888">
         <v>47</v>
       </c>
-      <c r="C888" s="11" t="s">
+      <c r="C888" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D888">
@@ -19318,8 +19208,8 @@
       <c r="B889">
         <v>48</v>
       </c>
-      <c r="C889" s="11" t="s">
-        <v>145</v>
+      <c r="C889" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="D889">
         <v>4176635</v>
@@ -19339,7 +19229,7 @@
       <c r="B890">
         <v>49</v>
       </c>
-      <c r="C890" s="11" t="s">
+      <c r="C890" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D890">
@@ -19381,7 +19271,7 @@
       <c r="B892">
         <v>51</v>
       </c>
-      <c r="C892" s="11" t="s">
+      <c r="C892" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D892">
@@ -19402,8 +19292,8 @@
       <c r="B893">
         <v>52</v>
       </c>
-      <c r="C893" s="11" t="s">
-        <v>146</v>
+      <c r="C893" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="D893">
         <v>3102924</v>
@@ -19423,7 +19313,7 @@
       <c r="B894">
         <v>53</v>
       </c>
-      <c r="C894" s="11" t="s">
+      <c r="C894" s="1" t="s">
         <v>125</v>
       </c>
       <c r="D894">
@@ -19444,7 +19334,7 @@
       <c r="B895">
         <v>54</v>
       </c>
-      <c r="C895" s="11" t="s">
+      <c r="C895" s="1" t="s">
         <v>119</v>
       </c>
       <c r="D895">
@@ -19465,7 +19355,7 @@
       <c r="B896">
         <v>55</v>
       </c>
-      <c r="C896" s="11" t="s">
+      <c r="C896" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D896">
@@ -19486,7 +19376,7 @@
       <c r="B897">
         <v>56</v>
       </c>
-      <c r="C897" s="11" t="s">
+      <c r="C897" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D897">
@@ -19507,7 +19397,7 @@
       <c r="B898">
         <v>57</v>
       </c>
-      <c r="C898" s="11" t="s">
+      <c r="C898" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D898">
@@ -19528,7 +19418,7 @@
       <c r="B899">
         <v>58</v>
       </c>
-      <c r="C899" s="11" t="s">
+      <c r="C899" s="1" t="s">
         <v>81</v>
       </c>
       <c r="D899">
@@ -19549,7 +19439,7 @@
       <c r="B900">
         <v>59</v>
       </c>
-      <c r="C900" s="11" t="s">
+      <c r="C900" s="1" t="s">
         <v>92</v>
       </c>
       <c r="D900">
@@ -19570,7 +19460,7 @@
       <c r="B901">
         <v>60</v>
       </c>
-      <c r="C901" s="11" t="s">
+      <c r="C901" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D901">
@@ -19581,6 +19471,1224 @@
         <v>6단계</v>
       </c>
       <c r="F901" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="902" spans="1:6">
+      <c r="A902" t="s">
+        <v>144</v>
+      </c>
+      <c r="B902">
+        <v>1</v>
+      </c>
+      <c r="C902" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D902">
+        <v>20860650</v>
+      </c>
+      <c r="E902" t="str">
+        <f>IF($D902="","",VLOOKUP($D902,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F902" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="903" spans="1:6">
+      <c r="A903" t="s">
+        <v>144</v>
+      </c>
+      <c r="B903">
+        <v>2</v>
+      </c>
+      <c r="C903" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D903">
+        <v>15967650</v>
+      </c>
+      <c r="E903" t="str">
+        <f>IF($D903="","",VLOOKUP($D903,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F903" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="904" spans="1:6">
+      <c r="A904" t="s">
+        <v>144</v>
+      </c>
+      <c r="B904">
+        <v>3</v>
+      </c>
+      <c r="C904" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D904">
+        <v>11715300</v>
+      </c>
+      <c r="E904" t="str">
+        <f>IF($D904="","",VLOOKUP($D904,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F904" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="905" spans="1:6">
+      <c r="A905" t="s">
+        <v>144</v>
+      </c>
+      <c r="B905">
+        <v>4</v>
+      </c>
+      <c r="C905" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D905">
+        <v>11280300</v>
+      </c>
+      <c r="E905" t="str">
+        <f>IF($D905="","",VLOOKUP($D905,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F905" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="906" spans="1:6">
+      <c r="A906" t="s">
+        <v>144</v>
+      </c>
+      <c r="B906">
+        <v>5</v>
+      </c>
+      <c r="C906" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D906">
+        <v>11203200</v>
+      </c>
+      <c r="E906" t="str">
+        <f>IF($D906="","",VLOOKUP($D906,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F906" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="907" spans="1:6">
+      <c r="A907" t="s">
+        <v>144</v>
+      </c>
+      <c r="B907">
+        <v>6</v>
+      </c>
+      <c r="C907" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D907">
+        <v>10767750</v>
+      </c>
+      <c r="E907" t="str">
+        <f>IF($D907="","",VLOOKUP($D907,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F907" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="908" spans="1:6">
+      <c r="A908" t="s">
+        <v>144</v>
+      </c>
+      <c r="B908">
+        <v>7</v>
+      </c>
+      <c r="C908" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D908">
+        <v>10474200</v>
+      </c>
+      <c r="E908" t="str">
+        <f>IF($D908="","",VLOOKUP($D908,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F908" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="909" spans="1:6">
+      <c r="A909" t="s">
+        <v>144</v>
+      </c>
+      <c r="B909">
+        <v>8</v>
+      </c>
+      <c r="C909" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D909">
+        <v>10381200</v>
+      </c>
+      <c r="E909" t="str">
+        <f>IF($D909="","",VLOOKUP($D909,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F909" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="910" spans="1:6">
+      <c r="A910" t="s">
+        <v>144</v>
+      </c>
+      <c r="B910">
+        <v>9</v>
+      </c>
+      <c r="C910" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D910">
+        <v>9676341</v>
+      </c>
+      <c r="E910" t="str">
+        <f>IF($D910="","",VLOOKUP($D910,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F910" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="911" spans="1:6">
+      <c r="A911" t="s">
+        <v>144</v>
+      </c>
+      <c r="B911">
+        <v>10</v>
+      </c>
+      <c r="C911" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D911">
+        <v>9216750</v>
+      </c>
+      <c r="E911" t="str">
+        <f>IF($D911="","",VLOOKUP($D911,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F911" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="912" spans="1:6">
+      <c r="A912" t="s">
+        <v>144</v>
+      </c>
+      <c r="B912">
+        <v>11</v>
+      </c>
+      <c r="C912" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D912">
+        <v>9100299</v>
+      </c>
+      <c r="E912" t="str">
+        <f>IF($D912="","",VLOOKUP($D912,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F912" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="913" spans="1:6">
+      <c r="A913" t="s">
+        <v>144</v>
+      </c>
+      <c r="B913">
+        <v>12</v>
+      </c>
+      <c r="C913" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D913">
+        <v>9049500</v>
+      </c>
+      <c r="E913" t="str">
+        <f>IF($D913="","",VLOOKUP($D913,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F913" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="914" spans="1:6">
+      <c r="A914" t="s">
+        <v>144</v>
+      </c>
+      <c r="B914">
+        <v>13</v>
+      </c>
+      <c r="C914" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D914">
+        <v>8786100</v>
+      </c>
+      <c r="E914" t="str">
+        <f>IF($D914="","",VLOOKUP($D914,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F914" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="915" spans="1:6">
+      <c r="A915" t="s">
+        <v>144</v>
+      </c>
+      <c r="B915">
+        <v>14</v>
+      </c>
+      <c r="C915" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D915">
+        <v>8670600</v>
+      </c>
+      <c r="E915" t="str">
+        <f>IF($D915="","",VLOOKUP($D915,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F915" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="916" spans="1:6">
+      <c r="A916" t="s">
+        <v>144</v>
+      </c>
+      <c r="B916">
+        <v>15</v>
+      </c>
+      <c r="C916" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D916">
+        <v>8469900</v>
+      </c>
+      <c r="E916" t="str">
+        <f>IF($D916="","",VLOOKUP($D916,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F916" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="917" spans="1:6">
+      <c r="A917" t="s">
+        <v>144</v>
+      </c>
+      <c r="B917">
+        <v>16</v>
+      </c>
+      <c r="C917" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D917">
+        <v>8378850</v>
+      </c>
+      <c r="E917" t="str">
+        <f>IF($D917="","",VLOOKUP($D917,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F917" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="918" spans="1:6">
+      <c r="A918" t="s">
+        <v>144</v>
+      </c>
+      <c r="B918">
+        <v>17</v>
+      </c>
+      <c r="C918" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D918">
+        <v>8234400</v>
+      </c>
+      <c r="E918" t="str">
+        <f>IF($D918="","",VLOOKUP($D918,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F918" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="919" spans="1:6">
+      <c r="A919" t="s">
+        <v>144</v>
+      </c>
+      <c r="B919">
+        <v>18</v>
+      </c>
+      <c r="C919" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D919">
+        <v>8140050</v>
+      </c>
+      <c r="E919" t="str">
+        <f>IF($D919="","",VLOOKUP($D919,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F919" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="920" spans="1:6">
+      <c r="A920" t="s">
+        <v>144</v>
+      </c>
+      <c r="B920">
+        <v>19</v>
+      </c>
+      <c r="C920" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D920">
+        <v>8115450</v>
+      </c>
+      <c r="E920" t="str">
+        <f>IF($D920="","",VLOOKUP($D920,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F920" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="921" spans="1:6">
+      <c r="A921" t="s">
+        <v>144</v>
+      </c>
+      <c r="B921">
+        <v>20</v>
+      </c>
+      <c r="C921" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D921">
+        <v>7808473</v>
+      </c>
+      <c r="E921" t="str">
+        <f>IF($D921="","",VLOOKUP($D921,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F921" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="922" spans="1:6">
+      <c r="A922" t="s">
+        <v>144</v>
+      </c>
+      <c r="B922">
+        <v>21</v>
+      </c>
+      <c r="C922" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D922">
+        <v>7774650</v>
+      </c>
+      <c r="E922" t="str">
+        <f>IF($D922="","",VLOOKUP($D922,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F922" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="923" spans="1:6">
+      <c r="A923" t="s">
+        <v>144</v>
+      </c>
+      <c r="B923">
+        <v>22</v>
+      </c>
+      <c r="C923" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D923">
+        <v>7616700</v>
+      </c>
+      <c r="E923" t="str">
+        <f>IF($D923="","",VLOOKUP($D923,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F923" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="924" spans="1:6">
+      <c r="A924" t="s">
+        <v>144</v>
+      </c>
+      <c r="B924">
+        <v>23</v>
+      </c>
+      <c r="C924" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D924">
+        <v>7563600</v>
+      </c>
+      <c r="E924" t="str">
+        <f>IF($D924="","",VLOOKUP($D924,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F924" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="925" spans="1:6">
+      <c r="A925" t="s">
+        <v>144</v>
+      </c>
+      <c r="B925">
+        <v>24</v>
+      </c>
+      <c r="C925" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D925">
+        <v>7395750</v>
+      </c>
+      <c r="E925" t="str">
+        <f>IF($D925="","",VLOOKUP($D925,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F925" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="926" spans="1:6">
+      <c r="A926" t="s">
+        <v>144</v>
+      </c>
+      <c r="B926">
+        <v>25</v>
+      </c>
+      <c r="C926" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D926">
+        <v>7309650</v>
+      </c>
+      <c r="E926" t="str">
+        <f>IF($D926="","",VLOOKUP($D926,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F926" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="927" spans="1:6">
+      <c r="A927" t="s">
+        <v>144</v>
+      </c>
+      <c r="B927">
+        <v>26</v>
+      </c>
+      <c r="C927" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D927">
+        <v>7230600</v>
+      </c>
+      <c r="E927" t="str">
+        <f>IF($D927="","",VLOOKUP($D927,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F927" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="928" spans="1:6">
+      <c r="A928" t="s">
+        <v>144</v>
+      </c>
+      <c r="B928">
+        <v>27</v>
+      </c>
+      <c r="C928" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D928">
+        <v>7219463</v>
+      </c>
+      <c r="E928" t="str">
+        <f>IF($D928="","",VLOOKUP($D928,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F928" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="929" spans="1:6">
+      <c r="A929" t="s">
+        <v>144</v>
+      </c>
+      <c r="B929">
+        <v>28</v>
+      </c>
+      <c r="C929" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D929">
+        <v>7193004</v>
+      </c>
+      <c r="E929" t="str">
+        <f>IF($D929="","",VLOOKUP($D929,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F929" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="930" spans="1:6">
+      <c r="A930" t="s">
+        <v>144</v>
+      </c>
+      <c r="B930">
+        <v>29</v>
+      </c>
+      <c r="C930" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D930">
+        <v>7190700</v>
+      </c>
+      <c r="E930" t="str">
+        <f>IF($D930="","",VLOOKUP($D930,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F930" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="931" spans="1:6">
+      <c r="A931" t="s">
+        <v>144</v>
+      </c>
+      <c r="B931">
+        <v>30</v>
+      </c>
+      <c r="C931" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D931">
+        <v>6560068</v>
+      </c>
+      <c r="E931" t="str">
+        <f>IF($D931="","",VLOOKUP($D931,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F931" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="932" spans="1:6">
+      <c r="A932" t="s">
+        <v>144</v>
+      </c>
+      <c r="B932">
+        <v>31</v>
+      </c>
+      <c r="C932" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D932">
+        <v>6211049</v>
+      </c>
+      <c r="E932" t="str">
+        <f>IF($D932="","",VLOOKUP($D932,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F932" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="933" spans="1:6">
+      <c r="A933" t="s">
+        <v>144</v>
+      </c>
+      <c r="B933">
+        <v>32</v>
+      </c>
+      <c r="C933" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D933">
+        <v>6106975</v>
+      </c>
+      <c r="E933" t="str">
+        <f>IF($D933="","",VLOOKUP($D933,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F933" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="934" spans="1:6">
+      <c r="A934" t="s">
+        <v>144</v>
+      </c>
+      <c r="B934">
+        <v>33</v>
+      </c>
+      <c r="C934" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D934">
+        <v>5936250</v>
+      </c>
+      <c r="E934" t="str">
+        <f>IF($D934="","",VLOOKUP($D934,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F934" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="935" spans="1:6">
+      <c r="A935" t="s">
+        <v>144</v>
+      </c>
+      <c r="B935">
+        <v>34</v>
+      </c>
+      <c r="C935" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D935">
+        <v>5899200</v>
+      </c>
+      <c r="E935" t="str">
+        <f>IF($D935="","",VLOOKUP($D935,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F935" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="936" spans="1:6">
+      <c r="A936" t="s">
+        <v>144</v>
+      </c>
+      <c r="B936">
+        <v>35</v>
+      </c>
+      <c r="C936" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D936">
+        <v>5559000</v>
+      </c>
+      <c r="E936" t="str">
+        <f>IF($D936="","",VLOOKUP($D936,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F936" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="937" spans="1:6">
+      <c r="A937" t="s">
+        <v>144</v>
+      </c>
+      <c r="B937">
+        <v>36</v>
+      </c>
+      <c r="C937" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D937">
+        <v>5398371</v>
+      </c>
+      <c r="E937" t="str">
+        <f>IF($D937="","",VLOOKUP($D937,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F937" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="938" spans="1:6">
+      <c r="A938" t="s">
+        <v>144</v>
+      </c>
+      <c r="B938">
+        <v>37</v>
+      </c>
+      <c r="C938" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D938">
+        <v>5366288</v>
+      </c>
+      <c r="E938" t="str">
+        <f>IF($D938="","",VLOOKUP($D938,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F938" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="939" spans="1:6">
+      <c r="A939" t="s">
+        <v>144</v>
+      </c>
+      <c r="B939">
+        <v>38</v>
+      </c>
+      <c r="C939" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D939">
+        <v>5065525</v>
+      </c>
+      <c r="E939" t="str">
+        <f>IF($D939="","",VLOOKUP($D939,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F939" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="940" spans="1:6">
+      <c r="A940" t="s">
+        <v>144</v>
+      </c>
+      <c r="B940">
+        <v>39</v>
+      </c>
+      <c r="C940" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D940">
+        <v>4766216</v>
+      </c>
+      <c r="E940" t="str">
+        <f>IF($D940="","",VLOOKUP($D940,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F940" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="941" spans="1:6">
+      <c r="A941" t="s">
+        <v>144</v>
+      </c>
+      <c r="B941">
+        <v>40</v>
+      </c>
+      <c r="C941" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D941">
+        <v>4168380</v>
+      </c>
+      <c r="E941" t="str">
+        <f>IF($D941="","",VLOOKUP($D941,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F941" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="942" spans="1:6">
+      <c r="A942" t="s">
+        <v>144</v>
+      </c>
+      <c r="B942">
+        <v>41</v>
+      </c>
+      <c r="C942" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D942">
+        <v>4123050</v>
+      </c>
+      <c r="E942" t="str">
+        <f>IF($D942="","",VLOOKUP($D942,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F942" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="943" spans="1:6">
+      <c r="A943" t="s">
+        <v>144</v>
+      </c>
+      <c r="B943">
+        <v>42</v>
+      </c>
+      <c r="C943" s="9">
+        <v>1090</v>
+      </c>
+      <c r="D943">
+        <v>4105175</v>
+      </c>
+      <c r="E943" t="str">
+        <f>IF($D943="","",VLOOKUP($D943,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F943" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="944" spans="1:6">
+      <c r="A944" t="s">
+        <v>144</v>
+      </c>
+      <c r="B944">
+        <v>43</v>
+      </c>
+      <c r="C944" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D944">
+        <v>3997964</v>
+      </c>
+      <c r="E944" t="str">
+        <f>IF($D944="","",VLOOKUP($D944,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F944" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="945" spans="1:6">
+      <c r="A945" t="s">
+        <v>144</v>
+      </c>
+      <c r="B945">
+        <v>44</v>
+      </c>
+      <c r="C945" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D945">
+        <v>3911929</v>
+      </c>
+      <c r="E945" t="str">
+        <f>IF($D945="","",VLOOKUP($D945,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F945" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="946" spans="1:6">
+      <c r="A946" t="s">
+        <v>144</v>
+      </c>
+      <c r="B946">
+        <v>45</v>
+      </c>
+      <c r="C946" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D946">
+        <v>3851857</v>
+      </c>
+      <c r="E946" t="str">
+        <f>IF($D946="","",VLOOKUP($D946,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F946" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="947" spans="1:6">
+      <c r="A947" t="s">
+        <v>144</v>
+      </c>
+      <c r="B947">
+        <v>46</v>
+      </c>
+      <c r="C947" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D947">
+        <v>3727480</v>
+      </c>
+      <c r="E947" t="str">
+        <f>IF($D947="","",VLOOKUP($D947,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F947" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="948" spans="1:6">
+      <c r="A948" t="s">
+        <v>144</v>
+      </c>
+      <c r="B948">
+        <v>47</v>
+      </c>
+      <c r="C948" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D948">
+        <v>3672225</v>
+      </c>
+      <c r="E948" t="str">
+        <f>IF($D948="","",VLOOKUP($D948,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F948" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="949" spans="1:6">
+      <c r="A949" t="s">
+        <v>144</v>
+      </c>
+      <c r="B949">
+        <v>48</v>
+      </c>
+      <c r="C949" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D949">
+        <v>3669000</v>
+      </c>
+      <c r="E949" t="str">
+        <f>IF($D949="","",VLOOKUP($D949,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F949" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="950" spans="1:6">
+      <c r="A950" t="s">
+        <v>144</v>
+      </c>
+      <c r="B950">
+        <v>49</v>
+      </c>
+      <c r="C950" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D950">
+        <v>3652491</v>
+      </c>
+      <c r="E950" t="str">
+        <f>IF($D950="","",VLOOKUP($D950,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F950" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="951" spans="1:6">
+      <c r="A951" t="s">
+        <v>144</v>
+      </c>
+      <c r="B951">
+        <v>50</v>
+      </c>
+      <c r="C951" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D951">
+        <v>3317400</v>
+      </c>
+      <c r="E951" t="str">
+        <f>IF($D951="","",VLOOKUP($D951,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F951" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="952" spans="1:6">
+      <c r="A952" t="s">
+        <v>144</v>
+      </c>
+      <c r="B952">
+        <v>51</v>
+      </c>
+      <c r="C952" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D952">
+        <v>3228634</v>
+      </c>
+      <c r="E952" t="str">
+        <f>IF($D952="","",VLOOKUP($D952,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F952" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="953" spans="1:6">
+      <c r="A953" t="s">
+        <v>144</v>
+      </c>
+      <c r="B953">
+        <v>52</v>
+      </c>
+      <c r="C953" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D953">
+        <v>2895075</v>
+      </c>
+      <c r="E953" t="str">
+        <f>IF($D953="","",VLOOKUP($D953,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F953" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="954" spans="1:6">
+      <c r="A954" t="s">
+        <v>144</v>
+      </c>
+      <c r="B954">
+        <v>53</v>
+      </c>
+      <c r="C954" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D954">
+        <v>2571475</v>
+      </c>
+      <c r="E954" t="str">
+        <f>IF($D954="","",VLOOKUP($D954,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>7단계</v>
+      </c>
+      <c r="F954" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="955" spans="1:6">
+      <c r="A955" t="s">
+        <v>144</v>
+      </c>
+      <c r="B955">
+        <v>54</v>
+      </c>
+      <c r="C955" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D955">
+        <v>1996671</v>
+      </c>
+      <c r="E955" t="str">
+        <f>IF($D955="","",VLOOKUP($D955,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+      <c r="F955" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="956" spans="1:6">
+      <c r="A956" t="s">
+        <v>144</v>
+      </c>
+      <c r="B956">
+        <v>55</v>
+      </c>
+      <c r="C956" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D956">
+        <v>1831127</v>
+      </c>
+      <c r="E956" t="str">
+        <f>IF($D956="","",VLOOKUP($D956,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+      <c r="F956" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="957" spans="1:6">
+      <c r="A957" t="s">
+        <v>144</v>
+      </c>
+      <c r="B957">
+        <v>56</v>
+      </c>
+      <c r="C957" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D957">
+        <v>1437690</v>
+      </c>
+      <c r="E957" t="str">
+        <f>IF($D957="","",VLOOKUP($D957,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+      <c r="F957" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="958" spans="1:6">
+      <c r="A958" t="s">
+        <v>144</v>
+      </c>
+      <c r="B958">
+        <v>57</v>
+      </c>
+      <c r="C958" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D958">
+        <v>1409994</v>
+      </c>
+      <c r="E958" t="str">
+        <f>IF($D958="","",VLOOKUP($D958,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+      <c r="F958" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="959" spans="1:6">
+      <c r="A959" t="s">
+        <v>144</v>
+      </c>
+      <c r="B959">
+        <v>58</v>
+      </c>
+      <c r="C959" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D959">
+        <v>1343344</v>
+      </c>
+      <c r="E959" t="str">
+        <f>IF($D959="","",VLOOKUP($D959,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+      <c r="F959" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -19598,7 +20706,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
@@ -19635,11 +20743,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A1" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>149</v>
+      <c r="A1" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="16.5" customHeight="1">

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B0DB279-7DF8-42FB-8FD7-AFB1424C9612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DBAC36B-8B82-4AED-99A6-0D9B0ED08A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10275" yWindow="3450" windowWidth="14385" windowHeight="15885" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="기준표" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,19 @@
     <sheet name="2026-07" sheetId="3" r:id="rId3"/>
     <sheet name="별칭" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -28,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2921" uniqueCount="155">
   <si>
     <t>하한점수</t>
   </si>
@@ -825,6 +836,16 @@
   <si>
     <t>현재닉네임</t>
   </si>
+  <si>
+    <t xml:space="preserve">자르반84세 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">-프리저- </t>
+  </si>
+  <si>
+    <t>독여울</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -833,7 +854,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -891,6 +912,14 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -927,7 +956,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -958,6 +987,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -20735,7 +20767,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -20790,6 +20822,38 @@
         <v>140</v>
       </c>
     </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>153</v>
+      </c>
+      <c r="B9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="B10" t="s">
+        <v>145</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/길드전_업로드_파일.xlsx
+++ b/길드전_업로드_파일.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MJ\Downloads\Rank_cap\길드전포인트\업로드용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DBAC36B-8B82-4AED-99A6-0D9B0ED08A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E73C159-72D2-4645-898F-6FEA98D16593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10275" yWindow="3450" windowWidth="14385" windowHeight="15885" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27990" yWindow="5895" windowWidth="28110" windowHeight="16440" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="기준표" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2921" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3206" uniqueCount="193">
   <si>
     <t>하한점수</t>
   </si>
@@ -831,20 +831,193 @@
     <t>📦 월별 보관 — 2026-07  (날짜별 길드전 랭킹 누적)</t>
   </si>
   <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>아쫌~</t>
+  </si>
+  <si>
+    <t>마호~</t>
+  </si>
+  <si>
+    <t>김팬더</t>
+  </si>
+  <si>
+    <t>먼지털이</t>
+  </si>
+  <si>
+    <t>썩은동아줄잡은할부지</t>
+  </si>
+  <si>
+    <t>타워보스라푼젤</t>
+  </si>
+  <si>
+    <t>아크로</t>
+  </si>
+  <si>
+    <t>풍기뮬란</t>
+  </si>
+  <si>
+    <t>꽁룡~</t>
+  </si>
+  <si>
+    <t>금쪽이랑</t>
+  </si>
+  <si>
+    <t>결제할때만신발끈묶음</t>
+  </si>
+  <si>
+    <t>1차선에서정속주행</t>
+  </si>
+  <si>
+    <t>핑도노•훔치고•생각하는•편</t>
+  </si>
+  <si>
+    <t>아기돼지삼합회</t>
+  </si>
+  <si>
+    <t>시수기릿</t>
+  </si>
+  <si>
+    <t>플란다스의개고생</t>
+  </si>
+  <si>
+    <t>피티체조 마지막 구호만 외친다</t>
+  </si>
+  <si>
+    <t>비타민C</t>
+  </si>
+  <si>
+    <t>왈왈야옹</t>
+  </si>
+  <si>
+    <t>소원먹튀지니</t>
+  </si>
+  <si>
+    <t>이상한나라의앨</t>
+  </si>
+  <si>
+    <t>삐삐망사스타킹</t>
+  </si>
+  <si>
+    <t>푸른등불</t>
+  </si>
+  <si>
+    <t>제이~</t>
+  </si>
+  <si>
+    <t>이뱅쓰</t>
+  </si>
+  <si>
+    <t>꼬사뿐다~</t>
+  </si>
+  <si>
+    <t>독사과판매원</t>
+  </si>
+  <si>
+    <t>은쪽이담</t>
+  </si>
+  <si>
+    <t>평안爱</t>
+  </si>
+  <si>
+    <t>김자르반102세</t>
+  </si>
+  <si>
+    <t>ZERO00</t>
+  </si>
+  <si>
+    <t>엄지살려</t>
+  </si>
+  <si>
+    <t>엘베닫힘연타범</t>
+  </si>
+  <si>
     <t>과거닉네임</t>
   </si>
   <si>
     <t>현재닉네임</t>
   </si>
   <si>
-    <t xml:space="preserve">자르반84세 </t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>자르반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>84</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">세 </t>
+    </r>
   </si>
   <si>
-    <t xml:space="preserve">-프리저- </t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>프리저</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">- </t>
+    </r>
   </si>
   <si>
-    <t>독여울</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <t>산도끼야일루와</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>독터키캔씨Turkey1881</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>빨강망사촤촤</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>햬녜도얜덀리는뒈</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>뺙센공주</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -907,16 +1080,15 @@
       <charset val="129"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -956,7 +1128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -987,7 +1159,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1368,7 +1541,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -20725,7 +20898,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -20733,15 +20906,22 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="50.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.25" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.5" customHeight="1">
+    <row r="1" spans="1:6" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="16.5" customHeight="1">
+    <row r="2" spans="1:6" ht="16.5" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -20758,8 +20938,2000 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3" spans="1:6" ht="16.5" customHeight="1">
+      <c r="A3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E3" s="3" t="str">
+        <f>IF($D3="","",VLOOKUP($D3,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v/>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D4">
+        <v>22891039</v>
+      </c>
+      <c r="E4" t="str">
+        <f>IF($D4="","",VLOOKUP($D4,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5">
+        <v>22863350</v>
+      </c>
+      <c r="E5" t="str">
+        <f>IF($D5="","",VLOOKUP($D5,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6">
+        <v>19747750</v>
+      </c>
+      <c r="E6" t="str">
+        <f>IF($D6="","",VLOOKUP($D6,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7">
+        <v>19108535</v>
+      </c>
+      <c r="E7" t="str">
+        <f>IF($D7="","",VLOOKUP($D7,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8">
+        <v>18925047</v>
+      </c>
+      <c r="E8" t="str">
+        <f>IF($D8="","",VLOOKUP($D8,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D9">
+        <v>18773600</v>
+      </c>
+      <c r="E9" t="str">
+        <f>IF($D9="","",VLOOKUP($D9,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>150</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D10">
+        <v>17819150</v>
+      </c>
+      <c r="E10" t="str">
+        <f>IF($D10="","",VLOOKUP($D10,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B11">
+        <v>8</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11">
+        <v>16620150</v>
+      </c>
+      <c r="E11" t="str">
+        <f>IF($D11="","",VLOOKUP($D11,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B12">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12">
+        <v>14316000</v>
+      </c>
+      <c r="E12" t="str">
+        <f>IF($D12="","",VLOOKUP($D12,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13">
+        <v>13163400</v>
+      </c>
+      <c r="E13" t="str">
+        <f>IF($D13="","",VLOOKUP($D13,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>150</v>
+      </c>
+      <c r="B14">
+        <v>11</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D14">
+        <v>12238181</v>
+      </c>
+      <c r="E14" t="str">
+        <f>IF($D14="","",VLOOKUP($D14,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B15">
+        <v>12</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D15">
+        <v>11945550</v>
+      </c>
+      <c r="E15" t="str">
+        <f>IF($D15="","",VLOOKUP($D15,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>150</v>
+      </c>
+      <c r="B16">
+        <v>13</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16">
+        <v>11889250</v>
+      </c>
+      <c r="E16" t="str">
+        <f>IF($D16="","",VLOOKUP($D16,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>150</v>
+      </c>
+      <c r="B17">
+        <v>14</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17">
+        <v>11631700</v>
+      </c>
+      <c r="E17" t="str">
+        <f>IF($D17="","",VLOOKUP($D17,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>150</v>
+      </c>
+      <c r="B18">
+        <v>15</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18">
+        <v>11509450</v>
+      </c>
+      <c r="E18" t="str">
+        <f>IF($D18="","",VLOOKUP($D18,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>150</v>
+      </c>
+      <c r="B19">
+        <v>16</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D19">
+        <v>11102200</v>
+      </c>
+      <c r="E19" t="str">
+        <f>IF($D19="","",VLOOKUP($D19,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>150</v>
+      </c>
+      <c r="B20">
+        <v>17</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20">
+        <v>11021150</v>
+      </c>
+      <c r="E20" t="str">
+        <f>IF($D20="","",VLOOKUP($D20,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>150</v>
+      </c>
+      <c r="B21">
+        <v>18</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D21">
+        <v>10978640</v>
+      </c>
+      <c r="E21" t="str">
+        <f>IF($D21="","",VLOOKUP($D21,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>150</v>
+      </c>
+      <c r="B22">
+        <v>19</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D22">
+        <v>10674948</v>
+      </c>
+      <c r="E22" t="str">
+        <f>IF($D22="","",VLOOKUP($D22,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>150</v>
+      </c>
+      <c r="B23">
+        <v>20</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23">
+        <v>10432400</v>
+      </c>
+      <c r="E23" t="str">
+        <f>IF($D23="","",VLOOKUP($D23,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>150</v>
+      </c>
+      <c r="B24">
+        <v>21</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24">
+        <v>9995000</v>
+      </c>
+      <c r="E24" t="str">
+        <f>IF($D24="","",VLOOKUP($D24,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>150</v>
+      </c>
+      <c r="B25">
+        <v>22</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D25">
+        <v>9681060</v>
+      </c>
+      <c r="E25" t="str">
+        <f>IF($D25="","",VLOOKUP($D25,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>150</v>
+      </c>
+      <c r="B26">
+        <v>23</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D26">
+        <v>9655450</v>
+      </c>
+      <c r="E26" t="str">
+        <f>IF($D26="","",VLOOKUP($D26,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
+        <v>150</v>
+      </c>
+      <c r="B27">
+        <v>24</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D27">
+        <v>9567703</v>
+      </c>
+      <c r="E27" t="str">
+        <f>IF($D27="","",VLOOKUP($D27,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>150</v>
+      </c>
+      <c r="B28">
+        <v>25</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28">
+        <v>9485550</v>
+      </c>
+      <c r="E28" t="str">
+        <f>IF($D28="","",VLOOKUP($D28,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
+        <v>150</v>
+      </c>
+      <c r="B29">
+        <v>26</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29">
+        <v>9244350</v>
+      </c>
+      <c r="E29" t="str">
+        <f>IF($D29="","",VLOOKUP($D29,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>150</v>
+      </c>
+      <c r="B30">
+        <v>27</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30">
+        <v>8959350</v>
+      </c>
+      <c r="E30" t="str">
+        <f>IF($D30="","",VLOOKUP($D30,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>150</v>
+      </c>
+      <c r="B31">
+        <v>28</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31">
+        <v>8783400</v>
+      </c>
+      <c r="E31" t="str">
+        <f>IF($D31="","",VLOOKUP($D31,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
+        <v>150</v>
+      </c>
+      <c r="B32">
+        <v>29</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D32">
+        <v>8568850</v>
+      </c>
+      <c r="E32" t="str">
+        <f>IF($D32="","",VLOOKUP($D32,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
+        <v>150</v>
+      </c>
+      <c r="B33">
+        <v>30</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33">
+        <v>8566850</v>
+      </c>
+      <c r="E33" t="str">
+        <f>IF($D33="","",VLOOKUP($D33,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" t="s">
+        <v>150</v>
+      </c>
+      <c r="B34">
+        <v>31</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D34">
+        <v>8554800</v>
+      </c>
+      <c r="E34" t="str">
+        <f>IF($D34="","",VLOOKUP($D34,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" t="s">
+        <v>150</v>
+      </c>
+      <c r="B35">
+        <v>32</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D35">
+        <v>8542383</v>
+      </c>
+      <c r="E35" t="str">
+        <f>IF($D35="","",VLOOKUP($D35,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" t="s">
+        <v>150</v>
+      </c>
+      <c r="B36">
+        <v>33</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D36">
+        <v>8485754</v>
+      </c>
+      <c r="E36" t="str">
+        <f>IF($D36="","",VLOOKUP($D36,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" t="s">
+        <v>150</v>
+      </c>
+      <c r="B37">
+        <v>34</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D37">
+        <v>8329562</v>
+      </c>
+      <c r="E37" t="str">
+        <f>IF($D37="","",VLOOKUP($D37,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" t="s">
+        <v>150</v>
+      </c>
+      <c r="B38">
+        <v>35</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D38">
+        <v>8324769</v>
+      </c>
+      <c r="E38" t="str">
+        <f>IF($D38="","",VLOOKUP($D38,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" t="s">
+        <v>150</v>
+      </c>
+      <c r="B39">
+        <v>36</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D39">
+        <v>8317500</v>
+      </c>
+      <c r="E39" t="str">
+        <f>IF($D39="","",VLOOKUP($D39,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" t="s">
+        <v>150</v>
+      </c>
+      <c r="B40">
+        <v>37</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D40">
+        <v>8224996</v>
+      </c>
+      <c r="E40" t="str">
+        <f>IF($D40="","",VLOOKUP($D40,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" t="s">
+        <v>150</v>
+      </c>
+      <c r="B41">
+        <v>38</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D41">
+        <v>8172500</v>
+      </c>
+      <c r="E41" t="str">
+        <f>IF($D41="","",VLOOKUP($D41,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" t="s">
+        <v>150</v>
+      </c>
+      <c r="B42">
+        <v>39</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D42">
+        <v>8158855</v>
+      </c>
+      <c r="E42" t="str">
+        <f>IF($D42="","",VLOOKUP($D42,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" t="s">
+        <v>150</v>
+      </c>
+      <c r="B43">
+        <v>40</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D43">
+        <v>8088046</v>
+      </c>
+      <c r="E43" t="str">
+        <f>IF($D43="","",VLOOKUP($D43,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" t="s">
+        <v>150</v>
+      </c>
+      <c r="B44">
+        <v>41</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D44">
+        <v>8021750</v>
+      </c>
+      <c r="E44" t="str">
+        <f>IF($D44="","",VLOOKUP($D44,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" t="s">
+        <v>150</v>
+      </c>
+      <c r="B45">
+        <v>42</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D45">
+        <v>8007197</v>
+      </c>
+      <c r="E45" t="str">
+        <f>IF($D45="","",VLOOKUP($D45,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" t="s">
+        <v>150</v>
+      </c>
+      <c r="B46">
+        <v>43</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D46">
+        <v>7815250</v>
+      </c>
+      <c r="E46" t="str">
+        <f>IF($D46="","",VLOOKUP($D46,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" t="s">
+        <v>150</v>
+      </c>
+      <c r="B47">
+        <v>44</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D47">
+        <v>7606740</v>
+      </c>
+      <c r="E47" t="str">
+        <f>IF($D47="","",VLOOKUP($D47,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" t="s">
+        <v>150</v>
+      </c>
+      <c r="B48">
+        <v>45</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D48">
+        <v>7586200</v>
+      </c>
+      <c r="E48" t="str">
+        <f>IF($D48="","",VLOOKUP($D48,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" t="s">
+        <v>150</v>
+      </c>
+      <c r="B49">
+        <v>46</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D49">
+        <v>7574428</v>
+      </c>
+      <c r="E49" t="str">
+        <f>IF($D49="","",VLOOKUP($D49,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" t="s">
+        <v>150</v>
+      </c>
+      <c r="B50">
+        <v>47</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D50">
+        <v>7561087</v>
+      </c>
+      <c r="E50" t="str">
+        <f>IF($D50="","",VLOOKUP($D50,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" t="s">
+        <v>150</v>
+      </c>
+      <c r="B51">
+        <v>48</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D51">
+        <v>7516880</v>
+      </c>
+      <c r="E51" t="str">
+        <f>IF($D51="","",VLOOKUP($D51,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" t="s">
+        <v>150</v>
+      </c>
+      <c r="B52">
+        <v>49</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D52">
+        <v>7486016</v>
+      </c>
+      <c r="E52" t="str">
+        <f>IF($D52="","",VLOOKUP($D52,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" t="s">
+        <v>150</v>
+      </c>
+      <c r="B53">
+        <v>50</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D53">
+        <v>7431007</v>
+      </c>
+      <c r="E53" t="str">
+        <f>IF($D53="","",VLOOKUP($D53,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" t="s">
+        <v>150</v>
+      </c>
+      <c r="B54">
+        <v>51</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D54">
+        <v>7363000</v>
+      </c>
+      <c r="E54" t="str">
+        <f>IF($D54="","",VLOOKUP($D54,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" t="s">
+        <v>150</v>
+      </c>
+      <c r="B55">
+        <v>52</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D55">
+        <v>7266393</v>
+      </c>
+      <c r="E55" t="str">
+        <f>IF($D55="","",VLOOKUP($D55,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>9단계</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" t="s">
+        <v>150</v>
+      </c>
+      <c r="B56">
+        <v>53</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D56">
+        <v>6830922</v>
+      </c>
+      <c r="E56" t="str">
+        <f>IF($D56="","",VLOOKUP($D56,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" t="s">
+        <v>150</v>
+      </c>
+      <c r="B57">
+        <v>54</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D57">
+        <v>6359150</v>
+      </c>
+      <c r="E57" t="str">
+        <f>IF($D57="","",VLOOKUP($D57,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" t="s">
+        <v>150</v>
+      </c>
+      <c r="B58">
+        <v>55</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D58">
+        <v>5969613</v>
+      </c>
+      <c r="E58" t="str">
+        <f>IF($D58="","",VLOOKUP($D58,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" t="s">
+        <v>150</v>
+      </c>
+      <c r="B59">
+        <v>56</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D59">
+        <v>5744139</v>
+      </c>
+      <c r="E59" t="str">
+        <f>IF($D59="","",VLOOKUP($D59,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" t="s">
+        <v>150</v>
+      </c>
+      <c r="B60">
+        <v>57</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D60">
+        <v>5738212</v>
+      </c>
+      <c r="E60" t="str">
+        <f>IF($D60="","",VLOOKUP($D60,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" t="s">
+        <v>150</v>
+      </c>
+      <c r="B61">
+        <v>58</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D61">
+        <v>5634760</v>
+      </c>
+      <c r="E61" t="str">
+        <f>IF($D61="","",VLOOKUP($D61,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" t="s">
+        <v>150</v>
+      </c>
+      <c r="B62">
+        <v>59</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D62">
+        <v>5611825</v>
+      </c>
+      <c r="E62" t="str">
+        <f>IF($D62="","",VLOOKUP($D62,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" t="s">
+        <v>150</v>
+      </c>
+      <c r="B63">
+        <v>60</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D63">
+        <v>5372222</v>
+      </c>
+      <c r="E63" t="str">
+        <f>IF($D63="","",VLOOKUP($D63,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" t="s">
+        <v>150</v>
+      </c>
+      <c r="B64">
+        <v>61</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D64">
+        <v>5239536</v>
+      </c>
+      <c r="E64" t="str">
+        <f>IF($D64="","",VLOOKUP($D64,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" t="s">
+        <v>150</v>
+      </c>
+      <c r="B65">
+        <v>62</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D65">
+        <v>5166652</v>
+      </c>
+      <c r="E65" t="str">
+        <f>IF($D65="","",VLOOKUP($D65,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" t="s">
+        <v>150</v>
+      </c>
+      <c r="B66">
+        <v>63</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D66">
+        <v>5071742</v>
+      </c>
+      <c r="E66" t="str">
+        <f>IF($D66="","",VLOOKUP($D66,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" t="s">
+        <v>150</v>
+      </c>
+      <c r="B67">
+        <v>64</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D67">
+        <v>4929807</v>
+      </c>
+      <c r="E67" t="str">
+        <f>IF($D67="","",VLOOKUP($D67,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" t="s">
+        <v>150</v>
+      </c>
+      <c r="B68">
+        <v>65</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D68">
+        <v>4787044</v>
+      </c>
+      <c r="E68" t="str">
+        <f>IF($D68="","",VLOOKUP($D68,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" t="s">
+        <v>150</v>
+      </c>
+      <c r="B69">
+        <v>66</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D69">
+        <v>4549943</v>
+      </c>
+      <c r="E69" t="str">
+        <f>IF($D69="","",VLOOKUP($D69,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" t="s">
+        <v>150</v>
+      </c>
+      <c r="B70">
+        <v>67</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D70">
+        <v>4340958</v>
+      </c>
+      <c r="E70" t="str">
+        <f>IF($D70="","",VLOOKUP($D70,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" t="s">
+        <v>150</v>
+      </c>
+      <c r="B71">
+        <v>68</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D71">
+        <v>4338989</v>
+      </c>
+      <c r="E71" t="str">
+        <f>IF($D71="","",VLOOKUP($D71,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" t="s">
+        <v>150</v>
+      </c>
+      <c r="B72">
+        <v>69</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D72">
+        <v>4167415</v>
+      </c>
+      <c r="E72" t="str">
+        <f>IF($D72="","",VLOOKUP($D72,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" t="s">
+        <v>150</v>
+      </c>
+      <c r="B73">
+        <v>70</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D73">
+        <v>4130350</v>
+      </c>
+      <c r="E73" t="str">
+        <f>IF($D73="","",VLOOKUP($D73,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" t="s">
+        <v>150</v>
+      </c>
+      <c r="B74">
+        <v>71</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D74">
+        <v>4044325</v>
+      </c>
+      <c r="E74" t="str">
+        <f>IF($D74="","",VLOOKUP($D74,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" t="s">
+        <v>150</v>
+      </c>
+      <c r="B75">
+        <v>72</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D75">
+        <v>3914300</v>
+      </c>
+      <c r="E75" t="str">
+        <f>IF($D75="","",VLOOKUP($D75,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" t="s">
+        <v>150</v>
+      </c>
+      <c r="B76">
+        <v>73</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D76">
+        <v>3847081</v>
+      </c>
+      <c r="E76" t="str">
+        <f>IF($D76="","",VLOOKUP($D76,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" t="s">
+        <v>150</v>
+      </c>
+      <c r="B77">
+        <v>74</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D77">
+        <v>3783400</v>
+      </c>
+      <c r="E77" t="str">
+        <f>IF($D77="","",VLOOKUP($D77,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" t="s">
+        <v>150</v>
+      </c>
+      <c r="B78">
+        <v>75</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D78">
+        <v>3752119</v>
+      </c>
+      <c r="E78" t="str">
+        <f>IF($D78="","",VLOOKUP($D78,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" t="s">
+        <v>150</v>
+      </c>
+      <c r="B79">
+        <v>76</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D79">
+        <v>3727093</v>
+      </c>
+      <c r="E79" t="str">
+        <f>IF($D79="","",VLOOKUP($D79,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" t="s">
+        <v>150</v>
+      </c>
+      <c r="B80">
+        <v>77</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D80">
+        <v>3631672</v>
+      </c>
+      <c r="E80" t="str">
+        <f>IF($D80="","",VLOOKUP($D80,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" t="s">
+        <v>150</v>
+      </c>
+      <c r="B81">
+        <v>78</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D81">
+        <v>3202030</v>
+      </c>
+      <c r="E81" t="str">
+        <f>IF($D81="","",VLOOKUP($D81,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" t="s">
+        <v>150</v>
+      </c>
+      <c r="B82">
+        <v>79</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D82">
+        <v>3172756</v>
+      </c>
+      <c r="E82" t="str">
+        <f>IF($D82="","",VLOOKUP($D82,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" t="s">
+        <v>150</v>
+      </c>
+      <c r="B83">
+        <v>80</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D83">
+        <v>3147980</v>
+      </c>
+      <c r="E83" t="str">
+        <f>IF($D83="","",VLOOKUP($D83,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" t="s">
+        <v>150</v>
+      </c>
+      <c r="B84">
+        <v>81</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D84">
+        <v>2860856</v>
+      </c>
+      <c r="E84" t="str">
+        <f>IF($D84="","",VLOOKUP($D84,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" t="s">
+        <v>150</v>
+      </c>
+      <c r="B85">
+        <v>82</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D85">
+        <v>2811350</v>
+      </c>
+      <c r="E85" t="str">
+        <f>IF($D85="","",VLOOKUP($D85,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" t="s">
+        <v>150</v>
+      </c>
+      <c r="B86">
+        <v>83</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D86">
+        <v>2805761</v>
+      </c>
+      <c r="E86" t="str">
+        <f>IF($D86="","",VLOOKUP($D86,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" t="s">
+        <v>150</v>
+      </c>
+      <c r="B87">
+        <v>84</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D87">
+        <v>2805195</v>
+      </c>
+      <c r="E87" t="str">
+        <f>IF($D87="","",VLOOKUP($D87,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" t="s">
+        <v>150</v>
+      </c>
+      <c r="B88">
+        <v>85</v>
+      </c>
+      <c r="C88" s="9">
+        <v>1090</v>
+      </c>
+      <c r="D88">
+        <v>2698750</v>
+      </c>
+      <c r="E88" t="str">
+        <f>IF($D88="","",VLOOKUP($D88,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>8단계</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" t="s">
+        <v>150</v>
+      </c>
+      <c r="B89">
+        <v>86</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="D89">
+        <v>2612085</v>
+      </c>
+      <c r="E89" t="str">
+        <f>IF($D89="","",VLOOKUP($D89,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>7단계</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" t="s">
+        <v>150</v>
+      </c>
+      <c r="B90">
+        <v>87</v>
+      </c>
+      <c r="C90" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="D90">
+        <v>2429508</v>
+      </c>
+      <c r="E90" t="str">
+        <f>IF($D90="","",VLOOKUP($D90,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>7단계</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" t="s">
+        <v>150</v>
+      </c>
+      <c r="B91">
+        <v>88</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D91">
+        <v>2288605</v>
+      </c>
+      <c r="E91" t="str">
+        <f>IF($D91="","",VLOOKUP($D91,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>7단계</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" t="s">
+        <v>150</v>
+      </c>
+      <c r="B92">
+        <v>89</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D92">
+        <v>2114073</v>
+      </c>
+      <c r="E92" t="str">
+        <f>IF($D92="","",VLOOKUP($D92,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" t="s">
+        <v>150</v>
+      </c>
+      <c r="B93">
+        <v>90</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D93">
+        <v>1672450</v>
+      </c>
+      <c r="E93" t="str">
+        <f>IF($D93="","",VLOOKUP($D93,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" t="s">
+        <v>150</v>
+      </c>
+      <c r="B94">
+        <v>91</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D94">
+        <v>1576826</v>
+      </c>
+      <c r="E94" t="str">
+        <f>IF($D94="","",VLOOKUP($D94,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" t="s">
+        <v>150</v>
+      </c>
+      <c r="B95">
+        <v>92</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D95">
+        <v>1551811</v>
+      </c>
+      <c r="E95" t="str">
+        <f>IF($D95="","",VLOOKUP($D95,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" t="s">
+        <v>150</v>
+      </c>
+      <c r="B96">
+        <v>93</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D96">
+        <v>1443505</v>
+      </c>
+      <c r="E96" t="str">
+        <f>IF($D96="","",VLOOKUP($D96,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" t="s">
+        <v>150</v>
+      </c>
+      <c r="B97">
+        <v>94</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D97">
+        <v>1382846</v>
+      </c>
+      <c r="E97" t="str">
+        <f>IF($D97="","",VLOOKUP($D97,기준표!$B$4:$C$12,2,TRUE()))</f>
+        <v>6단계</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -20776,10 +22948,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="16.5" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>151</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="16.5" customHeight="1">
@@ -20823,39 +22995,39 @@
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" t="s">
+      <c r="A7" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="12" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>152</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="A8" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="B9" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="A10" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="12" t="s">
         <v>145</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
